--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -716,9 +716,6 @@
     <t>ADM_LGN_FSD_042</t>
   </si>
   <si>
-    <t>FSD Source-Verified TCs</t>
-  </si>
-  <si>
     <t>[BUG-REF: BUG-AUTH-003] OTP is generated with insecure Math.random()</t>
   </si>
   <si>
@@ -765,6 +762,9 @@
   </si>
   <si>
     <t>ADM_LGN_FSD_045</t>
+  </si>
+  <si>
+    <t>FSD Source-Verified TCs</t>
   </si>
   <si>
     <t>Logout returns success but JWT remains valid until natural expiry</t>
@@ -4933,6 +4933,9 @@
     <t>ADM_ALLOC_FSD_038</t>
   </si>
   <si>
+    <t>Allocation Negative &amp; Edge Cases</t>
+  </si>
+  <si>
     <t>[FSD-CORRECTION] SM Admin cannot access admin allocation endpoints</t>
   </si>
   <si>
@@ -4949,9 +4952,6 @@
   </si>
   <si>
     <t>ADM_ALLOC_032</t>
-  </si>
-  <si>
-    <t>Allocation Negative &amp; Edge Cases</t>
   </si>
   <si>
     <t>Stopping a campaign with active payments mid-flow</t>
@@ -6175,6 +6175,9 @@
     <t>ADM_JBP_FSD_041</t>
   </si>
   <si>
+    <t>JBP Business Rules &amp; Edge Cases</t>
+  </si>
+  <si>
     <t>[BUG-REF: BUG-JBP-001] WhatsApp template `${+91}` emits "91" (template-string bug)</t>
   </si>
   <si>
@@ -6337,9 +6340,6 @@
   </si>
   <si>
     <t>ADM_JBP_037</t>
-  </si>
-  <si>
-    <t>JBP Business Rules &amp; Edge Cases</t>
   </si>
   <si>
     <t>Closed cycle cannot be reopened</t>
@@ -11524,7 +11524,7 @@
         <v>2428</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>109</v>
@@ -11556,7 +11556,7 @@
         <v>2432</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>219</v>
+        <v>2376</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>109</v>
@@ -11982,7 +11982,7 @@
         <v>2488</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>275</v>
@@ -12827,7 +12827,7 @@
         <v>2593</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>219</v>
+        <v>2495</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>109</v>
@@ -13367,7 +13367,7 @@
         <v>2668</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>219</v>
+        <v>2495</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>254</v>
@@ -15026,7 +15026,7 @@
         <v>2897</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>219</v>
+        <v>2684</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>109</v>
@@ -15058,7 +15058,7 @@
         <v>2902</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>219</v>
+        <v>2839</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>109</v>
@@ -15090,7 +15090,7 @@
         <v>2907</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>219</v>
+        <v>2747</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>109</v>
@@ -15122,7 +15122,7 @@
         <v>2912</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>219</v>
+        <v>2839</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>109</v>
@@ -15154,7 +15154,7 @@
         <v>2917</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>219</v>
+        <v>2684</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>109</v>
@@ -15353,7 +15353,7 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
@@ -17031,22 +17031,22 @@
         <v>218</v>
       </c>
       <c r="B39" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="C39" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="19" t="s">
+      <c r="E39" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="F39" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="G39" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>223</v>
       </c>
       <c r="H39" s="19" t="s">
         <v>42</v>
@@ -17060,25 +17060,25 @@
     </row>
     <row r="40" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="19" t="s">
+      <c r="E40" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="F40" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="G40" s="19" t="s">
         <v>227</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>228</v>
       </c>
       <c r="H40" s="19" t="s">
         <v>42</v>
@@ -17092,25 +17092,25 @@
     </row>
     <row r="41" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="16" t="s">
+      <c r="E41" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="F41" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="G41" s="16" t="s">
         <v>232</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>233</v>
       </c>
       <c r="H41" s="16" t="s">
         <v>42</v>
@@ -17124,10 +17124,10 @@
     </row>
     <row r="42" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B42" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>219</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>109</v>
@@ -17159,7 +17159,7 @@
         <v>239</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>109</v>
@@ -17205,7 +17205,7 @@
         <v>246</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>247</v>
@@ -17283,7 +17283,7 @@
         <v>258</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>254</v>
@@ -17727,7 +17727,7 @@
         <v>319</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>275</v>
@@ -20269,7 +20269,7 @@
         <v>681</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>219</v>
+        <v>514</v>
       </c>
       <c r="C80" s="14" t="s">
         <v>109</v>
@@ -20653,7 +20653,7 @@
         <v>741</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>219</v>
+        <v>514</v>
       </c>
       <c r="C92" s="17" t="s">
         <v>109</v>
@@ -20685,7 +20685,7 @@
         <v>746</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>219</v>
+        <v>514</v>
       </c>
       <c r="C93" s="17" t="s">
         <v>109</v>
@@ -20717,7 +20717,7 @@
         <v>751</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>219</v>
+        <v>652</v>
       </c>
       <c r="C94" s="20" t="s">
         <v>109</v>
@@ -20749,7 +20749,7 @@
         <v>756</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C95" s="17" t="s">
         <v>109</v>
@@ -20781,7 +20781,7 @@
         <v>761</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>219</v>
+        <v>514</v>
       </c>
       <c r="C96" s="17" t="s">
         <v>109</v>
@@ -20891,7 +20891,7 @@
         <v>774</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>219</v>
+        <v>464</v>
       </c>
       <c r="C100" s="20" t="s">
         <v>254</v>
@@ -22481,7 +22481,7 @@
         <v>994</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>219</v>
+        <v>808</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>989</v>
@@ -22527,7 +22527,7 @@
         <v>1000</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>219</v>
+        <v>808</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>1001</v>
@@ -22559,7 +22559,7 @@
         <v>1006</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>219</v>
+        <v>808</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>1001</v>
@@ -23963,7 +23963,7 @@
         <v>1192</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>219</v>
+        <v>1060</v>
       </c>
       <c r="C34" s="20" t="s">
         <v>109</v>
@@ -24311,7 +24311,7 @@
         <v>1240</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>219</v>
+        <v>1203</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>254</v>
@@ -24389,7 +24389,7 @@
         <v>1249</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>219</v>
+        <v>1060</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>1001</v>
@@ -25840,7 +25840,7 @@
         <v>1448</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>219</v>
+        <v>1303</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>109</v>
@@ -25872,7 +25872,7 @@
         <v>1453</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>219</v>
+        <v>1353</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>109</v>
@@ -26458,22 +26458,22 @@
         <v>1542</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>219</v>
+        <v>1543</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>1001</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>42</v>
@@ -26487,7 +26487,7 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
@@ -26501,10 +26501,10 @@
     </row>
     <row r="58" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>275</v>
@@ -26536,7 +26536,7 @@
         <v>1554</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="C59" s="20" t="s">
         <v>275</v>
@@ -26568,7 +26568,7 @@
         <v>1559</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>275</v>
@@ -26600,7 +26600,7 @@
         <v>1562</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>275</v>
@@ -28054,7 +28054,7 @@
         <v>1760</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>219</v>
+        <v>1570</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>109</v>
@@ -28086,7 +28086,7 @@
         <v>1765</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>219</v>
+        <v>1570</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>109</v>
@@ -28132,7 +28132,7 @@
         <v>1771</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>219</v>
+        <v>1697</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>254</v>
@@ -28178,7 +28178,7 @@
         <v>1777</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>219</v>
+        <v>1570</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>1778</v>
@@ -29438,22 +29438,22 @@
         <v>1945</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>219</v>
+        <v>1946</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H40" s="16" t="s">
         <v>42</v>
@@ -29467,25 +29467,25 @@
     </row>
     <row r="41" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>219</v>
+        <v>1809</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="H41" s="16" t="s">
         <v>42</v>
@@ -29499,25 +29499,25 @@
     </row>
     <row r="42" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>219</v>
+        <v>1914</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="H42" s="16" t="s">
         <v>42</v>
@@ -29531,25 +29531,25 @@
     </row>
     <row r="43" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>219</v>
+        <v>1914</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>109</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>42</v>
@@ -29563,25 +29563,25 @@
     </row>
     <row r="44" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>219</v>
+        <v>1809</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>42</v>
@@ -29595,25 +29595,25 @@
     </row>
     <row r="45" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>219</v>
+        <v>1809</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>109</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H45" s="19" t="s">
         <v>42</v>
@@ -29627,25 +29627,25 @@
     </row>
     <row r="46" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>219</v>
+        <v>1914</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H46" s="16" t="s">
         <v>42</v>
@@ -29659,25 +29659,25 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>219</v>
+        <v>1809</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H47" s="16" t="s">
         <v>42</v>
@@ -29691,25 +29691,25 @@
     </row>
     <row r="48" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>219</v>
+        <v>1865</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>109</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H48" s="19" t="s">
         <v>42</v>
@@ -29737,25 +29737,25 @@
     </row>
     <row r="50" ht="44" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>219</v>
+        <v>1946</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>254</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>42</v>
@@ -29769,7 +29769,7 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -29783,10 +29783,10 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>265</v>
@@ -29818,7 +29818,7 @@
         <v>2002</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>265</v>
@@ -29850,7 +29850,7 @@
         <v>2007</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>265</v>
@@ -29882,7 +29882,7 @@
         <v>2012</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>265</v>
@@ -29914,7 +29914,7 @@
         <v>2017</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>265</v>
@@ -29946,7 +29946,7 @@
         <v>2021</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C57" s="20" t="s">
         <v>265</v>
@@ -29978,7 +29978,7 @@
         <v>2026</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C58" s="20" t="s">
         <v>265</v>
@@ -30056,7 +30056,7 @@
         <v>2036</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>275</v>
@@ -30088,7 +30088,7 @@
         <v>2041</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>219</v>
+        <v>1946</v>
       </c>
       <c r="C62" s="20" t="s">
         <v>275</v>
@@ -31317,7 +31317,7 @@
         <v>2204</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>219</v>
+        <v>2076</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>109</v>
@@ -31349,7 +31349,7 @@
         <v>2209</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>219</v>
+        <v>2048</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>109</v>
@@ -31456,7 +31456,7 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -14,15 +14,14 @@
     <sheet sheetId="8" name="JBP" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Offers" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Channel Partners" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Admin CMS" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Config" state="visible" r:id="rId15"/>
+    <sheet sheetId="12" name="Config" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9602" uniqueCount="3037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8965" uniqueCount="2850">
   <si>
     <t>ADMIN PORTAL — MASTER TEST CASE DOCUMENT</t>
   </si>
@@ -7991,579 +7990,10 @@
     <t>No such UI or API exists. Verified by enumerating admin-cp routes (`routes/admin.routes.js:187-200`): only list/get/mark-master/map/bulk-map. Any BRD claim of CP CRUD from admin is INVALID.</t>
   </si>
   <si>
-    <t>ADMIN PORTAL — Admin CMS Test Cases</t>
+    <t>ADMIN PORTAL — Config Test Cases</t>
   </si>
   <si>
     <t>━━━━━━━━━━  UI TESTS  (12)  ━━━━━━━━━━</t>
-  </si>
-  <si>
-    <t>ADM_CMS_001</t>
-  </si>
-  <si>
-    <t>Portal Shell &amp; Sidebar Navigation</t>
-  </si>
-  <si>
-    <t>Admin portal shell loads after successful login</t>
-  </si>
-  <si>
-    <t>Admin completed OTP login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete login flow
-2. Observe portal layout</t>
-  </si>
-  <si>
-    <t>Left sidebar navigation, top header, and main content area render; default landing is Customers page</t>
-  </si>
-  <si>
-    <t>ADM_CMS_002</t>
-  </si>
-  <si>
-    <t>Left sidebar shows all 10 module links plus Logout</t>
-  </si>
-  <si>
-    <t>1. Inspect left sidebar</t>
-  </si>
-  <si>
-    <t>Sidebar shows: Customers, Config, Allocation, Offers, Towers, JBP Mgmt, Channel Partners, Sales Managers, Transactions, CMS (external), Logout</t>
-  </si>
-  <si>
-    <t>ADM_CMS_003</t>
-  </si>
-  <si>
-    <t>Sidebar persistent across all admin pages</t>
-  </si>
-  <si>
-    <t>1. Navigate to Towers, then Allocation, then Offers</t>
-  </si>
-  <si>
-    <t>Sidebar remains visible and consistent on every page</t>
-  </si>
-  <si>
-    <t>ADM_CMS_013</t>
-  </si>
-  <si>
-    <t>Current page is highlighted in sidebar</t>
-  </si>
-  <si>
-    <t>Admin on a module page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to Towers
-2. Inspect sidebar</t>
-  </si>
-  <si>
-    <t>Towers sidebar item visually highlighted (different color/background)</t>
-  </si>
-  <si>
-    <t>ADM_CMS_014</t>
-  </si>
-  <si>
-    <t>Sidebar item order matches BRD specification</t>
-  </si>
-  <si>
-    <t>1. Read sidebar items top-to-bottom</t>
-  </si>
-  <si>
-    <t>Order: Customers, Config, Allocation, Offers, Towers, JBP Mgmt, Channel Partners, Sales Managers, Transactions, CMS, Logout</t>
-  </si>
-  <si>
-    <t>ADM_CMS_015</t>
-  </si>
-  <si>
-    <t>External CMS Link</t>
-  </si>
-  <si>
-    <t>Sidebar shows separate CMS link</t>
-  </si>
-  <si>
-    <t>1. Locate "CMS" item in sidebar (separate from Config)</t>
-  </si>
-  <si>
-    <t>"CMS" link is visible and distinct from "Config"</t>
-  </si>
-  <si>
-    <t>ADM_CMS_017</t>
-  </si>
-  <si>
-    <t>External CMS opens in new tab/window</t>
-  </si>
-  <si>
-    <t>1. Click CMS link</t>
-  </si>
-  <si>
-    <t>External CMS opens in new tab; admin portal session remains in original tab</t>
-  </si>
-  <si>
-    <t>ADM_CMS_019</t>
-  </si>
-  <si>
-    <t>Logout &amp; Session</t>
-  </si>
-  <si>
-    <t>Logout button visible at bottom of sidebar</t>
-  </si>
-  <si>
-    <t>1. Inspect bottom of sidebar</t>
-  </si>
-  <si>
-    <t>Logout button visible</t>
-  </si>
-  <si>
-    <t>ADM_CMS_029</t>
-  </si>
-  <si>
-    <t>Page Rendering &amp; Responsiveness</t>
-  </si>
-  <si>
-    <t>Sidebar always visible (no full-screen mode)</t>
-  </si>
-  <si>
-    <t>Admin on any module</t>
-  </si>
-  <si>
-    <t>1. Look for any toggle to hide/collapse sidebar</t>
-  </si>
-  <si>
-    <t>Sidebar always visible per BRD; no full-screen mode toggle</t>
-  </si>
-  <si>
-    <t>ADM_CMS_033</t>
-  </si>
-  <si>
-    <t>Page renders correctly at 1920x1080 desktop resolution</t>
-  </si>
-  <si>
-    <t>Browser at 1920x1080</t>
-  </si>
-  <si>
-    <t>1. Load any admin page</t>
-  </si>
-  <si>
-    <t>All elements visible without scrolling for primary content</t>
-  </si>
-  <si>
-    <t>ADM_CMS_034</t>
-  </si>
-  <si>
-    <t>Page renders at 1366x768 laptop resolution</t>
-  </si>
-  <si>
-    <t>Browser at 1366x768</t>
-  </si>
-  <si>
-    <t>1. Load each module</t>
-  </si>
-  <si>
-    <t>All elements visible; sidebar and content area readable</t>
-  </si>
-  <si>
-    <t>ADM_CMS_039</t>
-  </si>
-  <si>
-    <t>External CMS link has target="_blank" / rel="noopener"</t>
-  </si>
-  <si>
-    <t>1. Inspect HTML of the CMS sidebar item via DevTools</t>
-  </si>
-  <si>
-    <t>Anchor has `target="_blank"` and ideally `rel="noopener noreferrer"` so external CMS opens in a new tab without leaking session</t>
-  </si>
-  <si>
-    <t>ADM_CMS_004</t>
-  </si>
-  <si>
-    <t>Click Customers in sidebar navigates to /admin/customers</t>
-  </si>
-  <si>
-    <t>Admin on any admin page</t>
-  </si>
-  <si>
-    <t>1. Click "Customers" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/customers; Customers page loads</t>
-  </si>
-  <si>
-    <t>ADM_CMS_005</t>
-  </si>
-  <si>
-    <t>Click Config navigates to /admin/cms</t>
-  </si>
-  <si>
-    <t>1. Click "Config" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/cms; Configurations page loads</t>
-  </si>
-  <si>
-    <t>ADM_CMS_006</t>
-  </si>
-  <si>
-    <t>Click Allocation navigates to /admin/allocation</t>
-  </si>
-  <si>
-    <t>1. Click "Allocation" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/allocation</t>
-  </si>
-  <si>
-    <t>ADM_CMS_007</t>
-  </si>
-  <si>
-    <t>Click Offers navigates to /admin/offers</t>
-  </si>
-  <si>
-    <t>1. Click "Offers" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/offers</t>
-  </si>
-  <si>
-    <t>ADM_CMS_008</t>
-  </si>
-  <si>
-    <t>Click Towers navigates to /admin/towers</t>
-  </si>
-  <si>
-    <t>1. Click "Towers" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/towers</t>
-  </si>
-  <si>
-    <t>ADM_CMS_009</t>
-  </si>
-  <si>
-    <t>Click JBP Mgmt navigates to /admin/jbp-management</t>
-  </si>
-  <si>
-    <t>1. Click "JBP Mgmt" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/jbp-management</t>
-  </si>
-  <si>
-    <t>ADM_CMS_010</t>
-  </si>
-  <si>
-    <t>Click Channel Partners navigates to /admin/channel-partners</t>
-  </si>
-  <si>
-    <t>1. Click "Channel Partners" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/channel-partners</t>
-  </si>
-  <si>
-    <t>ADM_CMS_011</t>
-  </si>
-  <si>
-    <t>Click Sales Managers navigates to /admin/sales-managers</t>
-  </si>
-  <si>
-    <t>1. Click "Sales Managers" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/sales-managers</t>
-  </si>
-  <si>
-    <t>ADM_CMS_012</t>
-  </si>
-  <si>
-    <t>Click Transactions navigates to /admin/payment-transactions</t>
-  </si>
-  <si>
-    <t>1. Click "Transactions" in sidebar</t>
-  </si>
-  <si>
-    <t>URL becomes /admin/payment-transactions</t>
-  </si>
-  <si>
-    <t>ADM_CMS_020</t>
-  </si>
-  <si>
-    <t>Click Logout ends session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Logout in sidebar
-2. Observe redirect</t>
-  </si>
-  <si>
-    <t>Session ended; redirected to /admin login page</t>
-  </si>
-  <si>
-    <t>ADM_CMS_023</t>
-  </si>
-  <si>
-    <t>Logout clears browser session storage</t>
-  </si>
-  <si>
-    <t>Just logged out</t>
-  </si>
-  <si>
-    <t>1. Open DevTools → Application → Local/Session Storage</t>
-  </si>
-  <si>
-    <t>Admin session keys cleared from browser storage</t>
-  </si>
-  <si>
-    <t>ADM_CMS_030</t>
-  </si>
-  <si>
-    <t>Browser back button navigates module history</t>
-  </si>
-  <si>
-    <t>Navigated Customers → Towers → Offers</t>
-  </si>
-  <si>
-    <t>1. Click browser Back button</t>
-  </si>
-  <si>
-    <t>Returns to Towers page; sidebar reflects active page</t>
-  </si>
-  <si>
-    <t>ADM_CMS_031</t>
-  </si>
-  <si>
-    <t>Direct URL navigation works for all modules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type /admin/offers directly in URL bar
-2. Press Enter</t>
-  </si>
-  <si>
-    <t>Offers page loads directly without navigating via sidebar</t>
-  </si>
-  <si>
-    <t>ADM_CMS_035</t>
-  </si>
-  <si>
-    <t>F5 refresh maintains session and page</t>
-  </si>
-  <si>
-    <t>Admin on /admin/towers</t>
-  </si>
-  <si>
-    <t>1. Press F5</t>
-  </si>
-  <si>
-    <t>Towers page reloads; user stays logged in</t>
-  </si>
-  <si>
-    <t>ADM_CMS_040</t>
-  </si>
-  <si>
-    <t>CMS link does not break admin session in original tab</t>
-  </si>
-  <si>
-    <t>Admin logged in on /admin/customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click CMS link (opens new tab)
-2. Return to original tab
-3. Refresh /admin/customers</t>
-  </si>
-  <si>
-    <t>Original tab still shows logged-in admin with Customers page; session unaffected by external CMS open</t>
-  </si>
-  <si>
-    <t>ADM_CMS_018</t>
-  </si>
-  <si>
-    <t>External CMS is documented as out-of-scope</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>1. Review BRD for CMS link</t>
-  </si>
-  <si>
-    <t>BRD confirms external CMS is separate system, excluded from admin portal scope and testing</t>
-  </si>
-  <si>
-    <t>ADM_CMS_024</t>
-  </si>
-  <si>
-    <t>Access Control &amp; Roles</t>
-  </si>
-  <si>
-    <t>Admin (roleId=1) can access all modules</t>
-  </si>
-  <si>
-    <t>Logged in as Admin role</t>
-  </si>
-  <si>
-    <t>1. Click each sidebar item in turn</t>
-  </si>
-  <si>
-    <t>All 9 portal pages load without access denied errors</t>
-  </si>
-  <si>
-    <t>ADM_CMS_025</t>
-  </si>
-  <si>
-    <t>Sales Manager Admin (roleId=4) accesses all modules</t>
-  </si>
-  <si>
-    <t>Logged in as SM Admin</t>
-  </si>
-  <si>
-    <t>1. Navigate through all sidebar items</t>
-  </si>
-  <si>
-    <t>All modules accessible (with possible config restrictions per BRD)</t>
-  </si>
-  <si>
-    <t>━━━━━━━━━━  INTEGRATION TESTS  (4)  ━━━━━━━━━━</t>
-  </si>
-  <si>
-    <t>ADM_CMS_016</t>
-  </si>
-  <si>
-    <t>Clicking external CMS opens different domain</t>
-  </si>
-  <si>
-    <t>1. Click "CMS" in sidebar</t>
-  </si>
-  <si>
-    <t>Opens external content management system at a different domain (Strapi); not part of admin portal</t>
-  </si>
-  <si>
-    <t>ADM_CMS_038</t>
-  </si>
-  <si>
-    <t>External CMS link href points to non-XR domain</t>
-  </si>
-  <si>
-    <t>1. Right-click "CMS" item in sidebar → Copy Link Address</t>
-  </si>
-  <si>
-    <t>URL points to a different domain than `uat-web.xrportal.in/admin` (Strapi-hosted CMS); confirms it is external</t>
-  </si>
-  <si>
-    <t>ADM_CMS_041</t>
-  </si>
-  <si>
-    <t>CMS link is separate from /admin/cms Config route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "Config" → confirm URL = /admin/cms
-2. Click "CMS" → confirm URL is external Strapi domain</t>
-  </si>
-  <si>
-    <t>Two distinct sidebar items with different destinations: Config = internal /admin/cms config-console; CMS = external Strapi</t>
-  </si>
-  <si>
-    <t>ADM_CMS_FSD_037</t>
-  </si>
-  <si>
-    <t>[FSD-CORRECTION] Strapi-sourced content is NOT testable from XR admin portal</t>
-  </si>
-  <si>
-    <t>Buyer home page has Strapi-driven banner/content visible</t>
-  </si>
-  <si>
-    <t>1. As admin, try to find any way to modify the buyer home page banner content from within /admin</t>
-  </si>
-  <si>
-    <t>Not possible. All such content edits happen in Strapi admin (out of scope). Any test asserting admin-side content editability is INVALID.</t>
-  </si>
-  <si>
-    <t>ADM_CMS_021</t>
-  </si>
-  <si>
-    <t>After logout, JWT token is invalidated</t>
-  </si>
-  <si>
-    <t>1. Try to use old token to access protected API endpoint</t>
-  </si>
-  <si>
-    <t>API rejects request with 401 Unauthorized; token no longer valid</t>
-  </si>
-  <si>
-    <t>━━━━━━━━━━  NEGATIVE TESTS  (6)  ━━━━━━━━━━</t>
-  </si>
-  <si>
-    <t>ADM_CMS_022</t>
-  </si>
-  <si>
-    <t>After logout, accessing protected route redirects to login</t>
-  </si>
-  <si>
-    <t>1. Try to navigate to /admin/customers via URL</t>
-  </si>
-  <si>
-    <t>ADM_CMS_026</t>
-  </si>
-  <si>
-    <t>Buyer role cannot access admin portal</t>
-  </si>
-  <si>
-    <t>Buyer session token (non-admin)</t>
-  </si>
-  <si>
-    <t>1. Try to access /admin with buyer credentials</t>
-  </si>
-  <si>
-    <t>Access denied; redirected away from admin portal</t>
-  </si>
-  <si>
-    <t>ADM_CMS_027</t>
-  </si>
-  <si>
-    <t>CP role cannot access admin portal</t>
-  </si>
-  <si>
-    <t>CP session token</t>
-  </si>
-  <si>
-    <t>1. Try to access /admin</t>
-  </si>
-  <si>
-    <t>Access denied or redirected to CP portal</t>
-  </si>
-  <si>
-    <t>ADM_CMS_028</t>
-  </si>
-  <si>
-    <t>Standard SM (non-admin) cannot access admin portal</t>
-  </si>
-  <si>
-    <t>Standard SM (not SM Admin) session</t>
-  </si>
-  <si>
-    <t>Access denied; redirected to SM portal</t>
-  </si>
-  <si>
-    <t>ADM_CMS_032</t>
-  </si>
-  <si>
-    <t>Invalid /admin/xyz URL shows 404 or redirects</t>
-  </si>
-  <si>
-    <t>1. Navigate to /admin/nonexistent-module</t>
-  </si>
-  <si>
-    <t>404 page or redirect to /admin/customers</t>
-  </si>
-  <si>
-    <t>ADM_CMS_FSD_036</t>
-  </si>
-  <si>
-    <t>[FSD-CORRECTION] No banner/gallery/testimonial CRUD exists in XR admin portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Look for any UI in /admin to create or edit a banner, image gallery, testimonial, FAQ, or homepage content
-2. Inspect all sidebar items</t>
-  </si>
-  <si>
-    <t>No such UI exists. The "CMS" entry in the sidebar opens config/bulk-upload screens (Customer Actions, Bulk Cancel, Bulk Refund). All visual content shown on the buyer portal home page comes from Strapi (external CMS) — not editable from XR admin. Document as platform constraint.</t>
-  </si>
-  <si>
-    <t>ADMIN PORTAL — Config Test Cases</t>
   </si>
   <si>
     <t>ADM_CFG_001</t>
@@ -13034,2154 +12464,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="38" customWidth="1"/>
-    <col min="14" max="14" width="32" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>2525</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>2526</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>2527</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>2529</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>2530</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>2531</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>2532</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>2533</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>2534</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>2535</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>2536</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>2537</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>2538</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>2539</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>2540</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>2541</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>2542</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>2543</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>2544</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>2545</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O7" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>2546</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>2547</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>2548</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>2549</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>2550</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>2552</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>2553</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>2554</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>2555</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>2556</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>2557</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>2558</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O10" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>2559</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>2561</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>2562</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>2563</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>2564</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>2566</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>2567</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>2568</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>2569</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>2570</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>2571</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>2572</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>2573</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>2574</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>2575</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>2576</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>2577</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>2578</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>2579</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L14" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O14" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>2580</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>2581</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>2582</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>2583</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O15" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-    </row>
-    <row r="17" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>2584</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>2585</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>2586</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>2587</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>2588</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>2589</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>2590</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>2591</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>2592</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>2593</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>2594</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>2595</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>2596</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>2597</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>2598</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>2599</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>2600</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>2601</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>2602</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>2603</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>2604</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O21" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>2605</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>2606</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>2607</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>2608</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O22" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>2609</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>2610</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>2611</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>2612</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O23" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>2613</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>2614</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>2615</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>2616</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M24" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>2617</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>2618</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>2619</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>2620</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M25" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O25" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>2621</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>2622</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>2623</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>2624</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O26" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>2625</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>2626</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>2627</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>2628</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>2629</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J27" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M27" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O27" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>2630</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>2631</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>2632</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>2633</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>2634</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M28" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N28" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>2635</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>2636</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>2637</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>2638</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M29" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O29" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>2639</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>2640</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>2641</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>2642</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>2643</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K30" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M30" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O30" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>2644</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>2645</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>2646</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>2647</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>2648</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J31" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O31" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-    </row>
-    <row r="33" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>2649</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>2650</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>2651</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>2652</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>2653</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L33" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M33" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N33" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>2656</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>2657</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>2658</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>2659</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K34" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L34" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O34" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>2660</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>2661</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>2662</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>2663</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>2664</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I35" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M35" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O35" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>2665</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-    </row>
-    <row r="37" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>2666</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>2667</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>2668</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>2669</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L37" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O37" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>2670</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>2671</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>2672</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>2673</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I38" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K38" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L38" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M38" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N38" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O38" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>2674</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>2675</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>2676</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>2677</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I39" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J39" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K39" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M39" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N39" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O39" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>2678</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>2679</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>2680</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>2681</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>2682</v>
-      </c>
-      <c r="H40" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L40" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M40" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N40" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O40" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-    </row>
-    <row r="42" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>2683</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>702</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>2684</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>2627</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>2685</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>2686</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L42" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M42" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N42" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O42" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
-        <v>2687</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-    </row>
-    <row r="44" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>2688</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>2689</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>2627</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>2690</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K44" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L44" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M44" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O44" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>2691</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>2692</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>2693</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>2694</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>2695</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L45" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M45" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N45" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O45" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>2696</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>2697</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>2698</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>2699</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>2700</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L46" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M46" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N46" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O46" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
-        <v>2701</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>2703</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>2699</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>2704</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I47" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L47" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M47" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N47" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O47" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>2705</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>2706</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>2707</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>2708</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I48" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J48" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K48" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L48" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M48" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N48" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="O48" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>2709</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2710</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>2711</v>
-      </c>
-      <c r="G49" s="17" t="s">
-        <v>2712</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J49" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K49" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="L49" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="O49" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:O2"/>
-  <mergeCells count="7">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A16:O16"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A43:O43"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -15209,7 +12491,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2713</v>
+        <v>2525</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15294,25 +12576,25 @@
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>2714</v>
+        <v>2527</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>2716</v>
+        <v>2529</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>171</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>2717</v>
+        <v>2530</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>2718</v>
+        <v>2531</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>54</v>
@@ -15341,25 +12623,25 @@
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>2719</v>
+        <v>2532</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>2720</v>
+        <v>2533</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>2721</v>
+        <v>2534</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>2722</v>
+        <v>2535</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>2723</v>
+        <v>2536</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -15388,25 +12670,25 @@
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>2724</v>
+        <v>2537</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>2725</v>
+        <v>2538</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>2721</v>
+        <v>2534</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>2726</v>
+        <v>2539</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>2727</v>
+        <v>2540</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>54</v>
@@ -15435,25 +12717,25 @@
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>2728</v>
+        <v>2541</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>2729</v>
+        <v>2542</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>2730</v>
+        <v>2543</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>2731</v>
+        <v>2544</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>2732</v>
+        <v>2545</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -15482,25 +12764,25 @@
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>2733</v>
+        <v>2546</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>2734</v>
+        <v>2547</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2735</v>
+        <v>2548</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>2736</v>
+        <v>2549</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>2737</v>
+        <v>2550</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>54</v>
@@ -15529,25 +12811,25 @@
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>2738</v>
+        <v>2551</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>2739</v>
+        <v>2552</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>2740</v>
+        <v>2553</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>2721</v>
+        <v>2534</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>2741</v>
+        <v>2554</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>2742</v>
+        <v>2555</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -15576,25 +12858,25 @@
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>2743</v>
+        <v>2556</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>2745</v>
+        <v>2558</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>2746</v>
+        <v>2559</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>2747</v>
+        <v>2560</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>2748</v>
+        <v>2561</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -15623,25 +12905,25 @@
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>2749</v>
+        <v>2562</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>2751</v>
+        <v>2564</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>2752</v>
+        <v>2565</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>2753</v>
+        <v>2566</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>2754</v>
+        <v>2567</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>54</v>
@@ -15670,25 +12952,25 @@
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>2755</v>
+        <v>2568</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>76</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>2756</v>
+        <v>2569</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>2730</v>
+        <v>2543</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>2757</v>
+        <v>2570</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>2758</v>
+        <v>2571</v>
       </c>
       <c r="H12" s="20" t="s">
         <v>54</v>
@@ -15717,25 +12999,25 @@
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>2759</v>
+        <v>2572</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>2760</v>
+        <v>2573</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>2761</v>
+        <v>2574</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>2762</v>
+        <v>2575</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>2763</v>
+        <v>2576</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>2764</v>
+        <v>2577</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>54</v>
@@ -15764,25 +13046,25 @@
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>2765</v>
+        <v>2578</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>2766</v>
+        <v>2579</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>2767</v>
+        <v>2580</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>2721</v>
+        <v>2534</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>2768</v>
+        <v>2581</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>2769</v>
+        <v>2582</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>54</v>
@@ -15811,25 +13093,25 @@
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>2770</v>
+        <v>2583</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>2766</v>
+        <v>2579</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>2771</v>
+        <v>2584</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>2721</v>
+        <v>2534</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>2772</v>
+        <v>2585</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>2773</v>
+        <v>2586</v>
       </c>
       <c r="H15" s="20" t="s">
         <v>54</v>
@@ -15858,7 +13140,7 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>2774</v>
+        <v>2587</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -15877,25 +13159,25 @@
     </row>
     <row r="17" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>2775</v>
+        <v>2588</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>2776</v>
+        <v>2589</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>2777</v>
+        <v>2590</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>2778</v>
+        <v>2591</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>2779</v>
+        <v>2592</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>54</v>
@@ -15924,25 +13206,25 @@
     </row>
     <row r="18" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>2780</v>
+        <v>2593</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>2781</v>
+        <v>2594</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>2782</v>
+        <v>2595</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>2783</v>
+        <v>2596</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>2784</v>
+        <v>2597</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>54</v>
@@ -15971,25 +13253,25 @@
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>2785</v>
+        <v>2598</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>2786</v>
+        <v>2599</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>2735</v>
+        <v>2548</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>2787</v>
+        <v>2600</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>2788</v>
+        <v>2601</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>54</v>
@@ -16018,25 +13300,25 @@
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>2789</v>
+        <v>2602</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>2739</v>
+        <v>2552</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>2790</v>
+        <v>2603</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>2791</v>
+        <v>2604</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>2792</v>
+        <v>2605</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>2793</v>
+        <v>2606</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>54</v>
@@ -16065,25 +13347,25 @@
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>2794</v>
+        <v>2607</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>2739</v>
+        <v>2552</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>2795</v>
+        <v>2608</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>2796</v>
+        <v>2609</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>2797</v>
+        <v>2610</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>2798</v>
+        <v>2611</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>54</v>
@@ -16112,25 +13394,25 @@
     </row>
     <row r="22" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>2799</v>
+        <v>2612</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>2739</v>
+        <v>2552</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>2800</v>
+        <v>2613</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>2801</v>
+        <v>2614</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>2803</v>
+        <v>2616</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>54</v>
@@ -16159,25 +13441,25 @@
     </row>
     <row r="23" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>2804</v>
+        <v>2617</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>2806</v>
+        <v>2619</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>2807</v>
+        <v>2620</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>2808</v>
+        <v>2621</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>2809</v>
+        <v>2622</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>54</v>
@@ -16206,25 +13488,25 @@
     </row>
     <row r="24" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>2810</v>
+        <v>2623</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>2811</v>
+        <v>2624</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>2812</v>
+        <v>2625</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>2813</v>
+        <v>2626</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>54</v>
@@ -16253,25 +13535,25 @@
     </row>
     <row r="25" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>2814</v>
+        <v>2627</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>2815</v>
+        <v>2628</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>2816</v>
+        <v>2629</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2817</v>
+        <v>2630</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>54</v>
@@ -16300,25 +13582,25 @@
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>2818</v>
+        <v>2631</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>2819</v>
+        <v>2632</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>2820</v>
+        <v>2633</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>2821</v>
+        <v>2634</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>2822</v>
+        <v>2635</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>2823</v>
+        <v>2636</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>54</v>
@@ -16347,25 +13629,25 @@
     </row>
     <row r="27" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>2824</v>
+        <v>2637</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>2819</v>
+        <v>2632</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>2825</v>
+        <v>2638</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>2826</v>
+        <v>2639</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>1032</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>2827</v>
+        <v>2640</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>54</v>
@@ -16394,25 +13676,25 @@
     </row>
     <row r="28" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>2828</v>
+        <v>2641</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>2819</v>
+        <v>2632</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>2829</v>
+        <v>2642</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>2830</v>
+        <v>2643</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>2831</v>
+        <v>2644</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>2832</v>
+        <v>2645</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>54</v>
@@ -16441,25 +13723,25 @@
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>2833</v>
+        <v>2646</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>2835</v>
+        <v>2648</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>2836</v>
+        <v>2649</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>2837</v>
+        <v>2650</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>2838</v>
+        <v>2651</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>54</v>
@@ -16488,25 +13770,25 @@
     </row>
     <row r="30" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>2839</v>
+        <v>2652</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>2840</v>
+        <v>2653</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>2841</v>
+        <v>2654</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>1032</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>2842</v>
+        <v>2655</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>54</v>
@@ -16535,25 +13817,25 @@
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>2843</v>
+        <v>2656</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C31" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>2845</v>
+        <v>2658</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>2846</v>
+        <v>2659</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>2837</v>
+        <v>2650</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>2847</v>
+        <v>2660</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>54</v>
@@ -16582,25 +13864,25 @@
     </row>
     <row r="32" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>2848</v>
+        <v>2661</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>2849</v>
+        <v>2662</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>2850</v>
+        <v>2663</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>2851</v>
+        <v>2664</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>2852</v>
+        <v>2665</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>54</v>
@@ -16629,25 +13911,25 @@
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>2853</v>
+        <v>2666</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>2854</v>
+        <v>2667</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>926</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>2855</v>
+        <v>2668</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>2856</v>
+        <v>2669</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>54</v>
@@ -16676,10 +13958,10 @@
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>2857</v>
+        <v>2670</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>121</v>
@@ -16688,13 +13970,13 @@
         <v>930</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>2858</v>
+        <v>2671</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>2859</v>
+        <v>2672</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>54</v>
@@ -16723,25 +14005,25 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>2860</v>
+        <v>2673</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>2861</v>
+        <v>2674</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>2862</v>
+        <v>2675</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>2863</v>
+        <v>2676</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>54</v>
@@ -16770,25 +14052,25 @@
     </row>
     <row r="36" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>2864</v>
+        <v>2677</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>121</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>2865</v>
+        <v>2678</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>2866</v>
+        <v>2679</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>2867</v>
+        <v>2680</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>2868</v>
+        <v>2681</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>54</v>
@@ -16817,25 +14099,25 @@
     </row>
     <row r="37" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>2869</v>
+        <v>2682</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>2760</v>
+        <v>2573</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>2870</v>
+        <v>2683</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>2762</v>
+        <v>2575</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>2871</v>
+        <v>2684</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>2872</v>
+        <v>2685</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>54</v>
@@ -16864,25 +14146,25 @@
     </row>
     <row r="38" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>2873</v>
+        <v>2686</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>2874</v>
+        <v>2687</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>2875</v>
+        <v>2688</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>2876</v>
+        <v>2689</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>2877</v>
+        <v>2690</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>54</v>
@@ -16911,25 +14193,25 @@
     </row>
     <row r="39" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>2878</v>
+        <v>2691</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>2879</v>
+        <v>2692</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>2880</v>
+        <v>2693</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>2881</v>
+        <v>2694</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>2882</v>
+        <v>2695</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>54</v>
@@ -16977,25 +14259,25 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>2883</v>
+        <v>2696</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>2739</v>
+        <v>2552</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>195</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>2884</v>
+        <v>2697</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>2885</v>
+        <v>2698</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>2886</v>
+        <v>2699</v>
       </c>
       <c r="H41" s="20" t="s">
         <v>54</v>
@@ -17024,25 +14306,25 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>2887</v>
+        <v>2700</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>195</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>2888</v>
+        <v>2701</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>2889</v>
+        <v>2702</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>2890</v>
+        <v>2703</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>54</v>
@@ -17071,25 +14353,25 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>2891</v>
+        <v>2704</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>2760</v>
+        <v>2573</v>
       </c>
       <c r="C43" s="21" t="s">
         <v>195</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>2892</v>
+        <v>2705</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>2762</v>
+        <v>2575</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>2893</v>
+        <v>2706</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>2894</v>
+        <v>2707</v>
       </c>
       <c r="H43" s="20" t="s">
         <v>54</v>
@@ -17118,25 +14400,25 @@
     </row>
     <row r="44" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>2895</v>
+        <v>2708</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>195</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>2896</v>
+        <v>2709</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>2897</v>
+        <v>2710</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>2898</v>
+        <v>2711</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>2899</v>
+        <v>2712</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>54</v>
@@ -17165,25 +14447,25 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>2900</v>
+        <v>2713</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>195</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>2901</v>
+        <v>2714</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>2902</v>
+        <v>2715</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>2903</v>
+        <v>2716</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>54</v>
@@ -17212,7 +14494,7 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>2904</v>
+        <v>2717</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -17231,25 +14513,25 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>2905</v>
+        <v>2718</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>2906</v>
+        <v>2719</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>2907</v>
+        <v>2720</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>2908</v>
+        <v>2721</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>54</v>
@@ -17278,25 +14560,25 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>2909</v>
+        <v>2722</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>2819</v>
+        <v>2632</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>2910</v>
+        <v>2723</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>2911</v>
+        <v>2724</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>2912</v>
+        <v>2725</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>54</v>
@@ -17325,25 +14607,25 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>2913</v>
+        <v>2726</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>2914</v>
+        <v>2727</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>2915</v>
+        <v>2728</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>2916</v>
+        <v>2729</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>2917</v>
+        <v>2730</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>54</v>
@@ -17372,25 +14654,25 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>2918</v>
+        <v>2731</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C50" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>2919</v>
+        <v>2732</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>732</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>2920</v>
+        <v>2733</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>2921</v>
+        <v>2734</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>54</v>
@@ -17419,25 +14701,25 @@
     </row>
     <row r="51" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>2922</v>
+        <v>2735</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>226</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>2923</v>
+        <v>2736</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>2924</v>
+        <v>2737</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>2925</v>
+        <v>2738</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>2926</v>
+        <v>2739</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>54</v>
@@ -17466,25 +14748,25 @@
     </row>
     <row r="52" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>2927</v>
+        <v>2740</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>2928</v>
+        <v>2741</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>2929</v>
+        <v>2742</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>2930</v>
+        <v>2743</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>2931</v>
+        <v>2744</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>54</v>
@@ -17513,25 +14795,25 @@
     </row>
     <row r="53" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>2932</v>
+        <v>2745</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>2760</v>
+        <v>2573</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>2933</v>
+        <v>2746</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>2934</v>
+        <v>2747</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>2935</v>
+        <v>2748</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>2936</v>
+        <v>2749</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>54</v>
@@ -17560,25 +14842,25 @@
     </row>
     <row r="54" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>2937</v>
+        <v>2750</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>226</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>2938</v>
+        <v>2751</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>2939</v>
+        <v>2752</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>2940</v>
+        <v>2753</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>2941</v>
+        <v>2754</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>54</v>
@@ -17607,25 +14889,25 @@
     </row>
     <row r="55" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>2942</v>
+        <v>2755</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>226</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>2943</v>
+        <v>2756</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>2944</v>
+        <v>2757</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>2945</v>
+        <v>2758</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>2946</v>
+        <v>2759</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>54</v>
@@ -17654,25 +14936,25 @@
     </row>
     <row r="56" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>2947</v>
+        <v>2760</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>2948</v>
+        <v>2761</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>2949</v>
+        <v>2762</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>2898</v>
+        <v>2711</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>2950</v>
+        <v>2763</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>54</v>
@@ -17701,25 +14983,25 @@
     </row>
     <row r="57" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>2951</v>
+        <v>2764</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>2952</v>
+        <v>2765</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>2953</v>
+        <v>2766</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>2954</v>
+        <v>2767</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>2955</v>
+        <v>2768</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>54</v>
@@ -17748,25 +15030,25 @@
     </row>
     <row r="58" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>2956</v>
+        <v>2769</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>226</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>2957</v>
+        <v>2770</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>2958</v>
+        <v>2771</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>2959</v>
+        <v>2772</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>2960</v>
+        <v>2773</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>54</v>
@@ -17795,25 +15077,25 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>2961</v>
+        <v>2774</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C59" s="21" t="s">
         <v>226</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>2962</v>
+        <v>2775</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>2963</v>
+        <v>2776</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>2964</v>
+        <v>2777</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>2965</v>
+        <v>2778</v>
       </c>
       <c r="H59" s="20" t="s">
         <v>54</v>
@@ -17861,25 +15143,25 @@
     </row>
     <row r="61" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>2966</v>
+        <v>2779</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>2819</v>
+        <v>2632</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>243</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2967</v>
+        <v>2780</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>2968</v>
+        <v>2781</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>2969</v>
+        <v>2782</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>2970</v>
+        <v>2783</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>54</v>
@@ -17927,25 +15209,25 @@
     </row>
     <row r="63" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>2971</v>
+        <v>2784</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>2766</v>
+        <v>2579</v>
       </c>
       <c r="C63" s="18" t="s">
         <v>702</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>2972</v>
+        <v>2785</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>2973</v>
+        <v>2786</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>2974</v>
+        <v>2787</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>2975</v>
+        <v>2788</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>54</v>
@@ -17974,25 +15256,25 @@
     </row>
     <row r="64" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>2976</v>
+        <v>2789</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>702</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>2977</v>
+        <v>2790</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>2978</v>
+        <v>2791</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>2979</v>
+        <v>2792</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>2980</v>
+        <v>2793</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>54</v>
@@ -18021,25 +15303,25 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
-        <v>2981</v>
+        <v>2794</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C65" s="21" t="s">
         <v>702</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>2982</v>
+        <v>2795</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>2983</v>
+        <v>2796</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>2984</v>
+        <v>2797</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>2985</v>
+        <v>2798</v>
       </c>
       <c r="H65" s="20" t="s">
         <v>54</v>
@@ -18087,25 +15369,25 @@
     </row>
     <row r="67" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>2986</v>
+        <v>2799</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C67" s="18" t="s">
         <v>255</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>2987</v>
+        <v>2800</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>2988</v>
+        <v>2801</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>2989</v>
+        <v>2802</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>2990</v>
+        <v>2803</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>54</v>
@@ -18134,25 +15416,25 @@
     </row>
     <row r="68" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>2991</v>
+        <v>2804</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>2750</v>
+        <v>2563</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>255</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>2992</v>
+        <v>2805</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>2993</v>
+        <v>2806</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>2994</v>
+        <v>2807</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>2995</v>
+        <v>2808</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>54</v>
@@ -18200,25 +15482,25 @@
     </row>
     <row r="70" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
-        <v>2996</v>
+        <v>2809</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>2715</v>
+        <v>2528</v>
       </c>
       <c r="C70" s="21" t="s">
         <v>737</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>2997</v>
+        <v>2810</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>2735</v>
+        <v>2548</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>2998</v>
+        <v>2811</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>2999</v>
+        <v>2812</v>
       </c>
       <c r="H70" s="20" t="s">
         <v>54</v>
@@ -18247,25 +15529,25 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
-        <v>3000</v>
+        <v>2813</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>2805</v>
+        <v>2618</v>
       </c>
       <c r="C71" s="21" t="s">
         <v>737</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>3001</v>
+        <v>2814</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>3002</v>
+        <v>2815</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>3003</v>
+        <v>2816</v>
       </c>
       <c r="H71" s="20" t="s">
         <v>54</v>
@@ -18294,25 +15576,25 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
-        <v>3004</v>
+        <v>2817</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>2766</v>
+        <v>2579</v>
       </c>
       <c r="C72" s="21" t="s">
         <v>737</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>3005</v>
+        <v>2818</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>3006</v>
+        <v>2819</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>3007</v>
+        <v>2820</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>3008</v>
+        <v>2821</v>
       </c>
       <c r="H72" s="20" t="s">
         <v>54</v>
@@ -18341,25 +15623,25 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
-        <v>3009</v>
+        <v>2822</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C73" s="21" t="s">
         <v>737</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>3010</v>
+        <v>2823</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>3011</v>
+        <v>2824</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>3012</v>
+        <v>2825</v>
       </c>
       <c r="H73" s="20" t="s">
         <v>54</v>
@@ -18388,7 +15670,7 @@
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>3013</v>
+        <v>2826</v>
       </c>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
@@ -18407,25 +15689,25 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>3014</v>
+        <v>2827</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>2739</v>
+        <v>2552</v>
       </c>
       <c r="C75" s="18" t="s">
         <v>267</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>3015</v>
+        <v>2828</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>3016</v>
+        <v>2829</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>3017</v>
+        <v>2830</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>3018</v>
+        <v>2831</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>54</v>
@@ -18454,25 +15736,25 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>3019</v>
+        <v>2832</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>2744</v>
+        <v>2557</v>
       </c>
       <c r="C76" s="18" t="s">
         <v>267</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>3020</v>
+        <v>2833</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>3021</v>
+        <v>2834</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>3022</v>
+        <v>2835</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>3023</v>
+        <v>2836</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>54</v>
@@ -18501,25 +15783,25 @@
     </row>
     <row r="77" ht="60" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>3024</v>
+        <v>2837</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C77" s="18" t="s">
         <v>267</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>3025</v>
+        <v>2838</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>3026</v>
+        <v>2839</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>3027</v>
+        <v>2840</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>3028</v>
+        <v>2841</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>54</v>
@@ -18548,22 +15830,22 @@
     </row>
     <row r="78" ht="44" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>3029</v>
+        <v>2842</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>2834</v>
+        <v>2647</v>
       </c>
       <c r="C78" s="18" t="s">
         <v>267</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>3030</v>
+        <v>2843</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>3031</v>
+        <v>2844</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>3032</v>
+        <v>2845</v>
       </c>
       <c r="G78" s="17" t="s">
         <v>971</v>
@@ -18595,25 +15877,25 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
-        <v>3033</v>
+        <v>2846</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>2844</v>
+        <v>2657</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>267</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>3034</v>
+        <v>2847</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>3035</v>
+        <v>2848</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>2802</v>
+        <v>2615</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>3036</v>
+        <v>2849</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>54</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5753">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18527,6 +18527,15 @@
   </si>
   <si>
     <t>Not Automated</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:32 IST — pass in 5.1s</t>
+  </si>
+  <si>
+    <t>PASS — matched expected</t>
   </si>
 </sst>
 </file>
@@ -35225,19 +35234,19 @@
         <v>2649</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>5751</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G2" t="s">
         <v>24</v>
@@ -52517,7 +52526,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5758">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18536,6 +18536,21 @@
   </si>
   <si>
     <t>PASS — matched expected</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:33 IST — pass in 3.2s</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:33 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>Not executed</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:33 IST — pass in 4.3s</t>
   </si>
 </sst>
 </file>
@@ -35280,19 +35295,19 @@
         <v>2661</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G4" t="s">
         <v>24</v>
@@ -35326,19 +35341,19 @@
         <v>2673</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>5755</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>5756</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -35349,19 +35364,19 @@
         <v>2680</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>5755</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>5756</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -35372,19 +35387,19 @@
         <v>2686</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>5755</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>5756</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -35395,19 +35410,19 @@
         <v>2693</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>5755</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>5756</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -35418,19 +35433,19 @@
         <v>2699</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>5757</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -35487,19 +35502,19 @@
         <v>2718</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>5755</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>5756</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5760">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18532,10 +18532,16 @@
     <t>Pass</t>
   </si>
   <si>
+    <t>2026-06-15 13:52 IST — pass in 18.2s</t>
+  </si>
+  <si>
+    <t>PASS — matched expected</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:52 IST — pass in 34.8s</t>
+  </si>
+  <si>
     <t>2026-06-15 00:32 IST — pass in 5.1s</t>
-  </si>
-  <si>
-    <t>PASS — matched expected</t>
   </si>
   <si>
     <t>2026-06-15 00:33 IST — pass in 3.2s</t>
@@ -32446,19 +32452,19 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>5751</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G2" t="s">
         <v>24</v>
@@ -32469,19 +32475,19 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>5751</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G3" t="s">
         <v>24</v>
@@ -32492,19 +32498,19 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>5751</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G4" t="s">
         <v>24</v>
@@ -32607,19 +32613,19 @@
         <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>5751</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -32630,19 +32636,19 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -32676,19 +32682,19 @@
         <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G12" t="s">
         <v>24</v>
@@ -32699,19 +32705,19 @@
         <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -32722,19 +32728,19 @@
         <v>123</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G14" t="s">
         <v>24</v>
@@ -32745,19 +32751,19 @@
         <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G15" t="s">
         <v>24</v>
@@ -32837,19 +32843,19 @@
         <v>147</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>5751</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
@@ -35258,7 +35264,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5751</v>
+        <v>5754</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35304,7 +35310,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35341,19 +35347,19 @@
         <v>2673</v>
       </c>
       <c r="B6" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D6" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="E6" t="s">
-        <v>5755</v>
+        <v>5757</v>
       </c>
       <c r="F6" t="s">
-        <v>5756</v>
+        <v>5758</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -35364,19 +35370,19 @@
         <v>2680</v>
       </c>
       <c r="B7" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D7" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="E7" t="s">
-        <v>5755</v>
+        <v>5757</v>
       </c>
       <c r="F7" t="s">
-        <v>5756</v>
+        <v>5758</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -35387,19 +35393,19 @@
         <v>2686</v>
       </c>
       <c r="B8" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D8" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="E8" t="s">
-        <v>5755</v>
+        <v>5757</v>
       </c>
       <c r="F8" t="s">
-        <v>5756</v>
+        <v>5758</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -35410,19 +35416,19 @@
         <v>2693</v>
       </c>
       <c r="B9" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D9" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="E9" t="s">
-        <v>5755</v>
+        <v>5757</v>
       </c>
       <c r="F9" t="s">
-        <v>5756</v>
+        <v>5758</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -35442,7 +35448,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5757</v>
+        <v>5759</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35502,19 +35508,19 @@
         <v>2718</v>
       </c>
       <c r="B13" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D13" t="s">
-        <v>5754</v>
+        <v>5756</v>
       </c>
       <c r="E13" t="s">
-        <v>5755</v>
+        <v>5757</v>
       </c>
       <c r="F13" t="s">
-        <v>5756</v>
+        <v>5758</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5766">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18538,7 +18538,25 @@
     <t>PASS — matched expected</t>
   </si>
   <si>
+    <t>2026-06-15 13:55 IST — pass in 18.2s</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:55 IST — pass in 19.3s</t>
+  </si>
+  <si>
     <t>2026-06-15 13:52 IST — pass in 34.8s</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:55 IST — pass in 17.2s</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:55 IST — pass in 18.4s</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:55 IST — pass in 18.5s</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:55 IST — pass in 18.3s</t>
   </si>
   <si>
     <t>2026-06-15 00:32 IST — pass in 5.1s</t>
@@ -32521,19 +32539,19 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>5753</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -32544,19 +32562,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -32567,19 +32585,19 @@
         <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -32645,7 +32663,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -32691,7 +32709,7 @@
         <v>5750</v>
       </c>
       <c r="E12" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F12" t="s">
         <v>5752</v>
@@ -32714,7 +32732,7 @@
         <v>5750</v>
       </c>
       <c r="E13" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F13" t="s">
         <v>5752</v>
@@ -32737,7 +32755,7 @@
         <v>5750</v>
       </c>
       <c r="E14" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F14" t="s">
         <v>5752</v>
@@ -32760,7 +32778,7 @@
         <v>5750</v>
       </c>
       <c r="E15" t="s">
-        <v>5753</v>
+        <v>5755</v>
       </c>
       <c r="F15" t="s">
         <v>5752</v>
@@ -32774,19 +32792,19 @@
         <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>5754</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G16" t="s">
         <v>24</v>
@@ -32797,19 +32815,19 @@
         <v>137</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>5756</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G17" t="s">
         <v>24</v>
@@ -33326,19 +33344,19 @@
         <v>264</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>5757</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -33349,19 +33367,19 @@
         <v>270</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>5758</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
@@ -33993,19 +34011,19 @@
         <v>417</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -34959,19 +34977,19 @@
         <v>657</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C111" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D111" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="F111" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G111" t="s">
         <v>24</v>
@@ -35264,7 +35282,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5754</v>
+        <v>5760</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35310,7 +35328,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5755</v>
+        <v>5761</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35347,19 +35365,19 @@
         <v>2673</v>
       </c>
       <c r="B6" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D6" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="E6" t="s">
-        <v>5757</v>
+        <v>5763</v>
       </c>
       <c r="F6" t="s">
-        <v>5758</v>
+        <v>5764</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -35370,19 +35388,19 @@
         <v>2680</v>
       </c>
       <c r="B7" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D7" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="E7" t="s">
-        <v>5757</v>
+        <v>5763</v>
       </c>
       <c r="F7" t="s">
-        <v>5758</v>
+        <v>5764</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -35393,19 +35411,19 @@
         <v>2686</v>
       </c>
       <c r="B8" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D8" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="E8" t="s">
-        <v>5757</v>
+        <v>5763</v>
       </c>
       <c r="F8" t="s">
-        <v>5758</v>
+        <v>5764</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -35416,19 +35434,19 @@
         <v>2693</v>
       </c>
       <c r="B9" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D9" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="E9" t="s">
-        <v>5757</v>
+        <v>5763</v>
       </c>
       <c r="F9" t="s">
-        <v>5758</v>
+        <v>5764</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -35448,7 +35466,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5759</v>
+        <v>5765</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35508,19 +35526,19 @@
         <v>2718</v>
       </c>
       <c r="B13" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D13" t="s">
-        <v>5756</v>
+        <v>5762</v>
       </c>
       <c r="E13" t="s">
-        <v>5757</v>
+        <v>5763</v>
       </c>
       <c r="F13" t="s">
-        <v>5758</v>
+        <v>5764</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5774">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18544,12 +18544,42 @@
     <t>2026-06-15 13:55 IST — pass in 19.3s</t>
   </si>
   <si>
+    <t>2026-06-15 15:39 IST — pass in 21.4s</t>
+  </si>
+  <si>
     <t>2026-06-15 13:52 IST — pass in 34.8s</t>
   </si>
   <si>
+    <t>2026-06-15 15:39 IST — pass in 24.2s</t>
+  </si>
+  <si>
     <t>2026-06-15 13:55 IST — pass in 17.2s</t>
   </si>
   <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:39 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>Not executed</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:39 IST — skip in phone-only search</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:39 IST — pass in 23.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:39 IST — pass in 22.2s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:39 IST — pass in 22.5s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:39 IST — pass in 21.7s</t>
+  </si>
+  <si>
     <t>2026-06-15 13:55 IST — pass in 18.4s</t>
   </si>
   <si>
@@ -18565,13 +18595,7 @@
     <t>2026-06-15 00:33 IST — pass in 3.2s</t>
   </si>
   <si>
-    <t>Skip</t>
-  </si>
-  <si>
     <t>2026-06-15 00:33 IST — skip in n/a</t>
-  </si>
-  <si>
-    <t>Not executed</t>
   </si>
   <si>
     <t>2026-06-15 00:33 IST — pass in 4.3s</t>
@@ -32608,19 +32632,19 @@
         <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>5755</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -32663,7 +32687,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -32677,19 +32701,19 @@
         <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>5757</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>
@@ -32709,7 +32733,7 @@
         <v>5750</v>
       </c>
       <c r="E12" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="F12" t="s">
         <v>5752</v>
@@ -32732,7 +32756,7 @@
         <v>5750</v>
       </c>
       <c r="E13" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="F13" t="s">
         <v>5752</v>
@@ -32755,7 +32779,7 @@
         <v>5750</v>
       </c>
       <c r="E14" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="F14" t="s">
         <v>5752</v>
@@ -32778,7 +32802,7 @@
         <v>5750</v>
       </c>
       <c r="E15" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="F15" t="s">
         <v>5752</v>
@@ -32824,7 +32848,7 @@
         <v>5750</v>
       </c>
       <c r="E17" t="s">
-        <v>5756</v>
+        <v>5758</v>
       </c>
       <c r="F17" t="s">
         <v>5752</v>
@@ -32999,19 +33023,19 @@
         <v>181</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>5761</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -33022,19 +33046,19 @@
         <v>186</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>5761</v>
       </c>
       <c r="G26" t="s">
         <v>24</v>
@@ -33045,19 +33069,19 @@
         <v>193</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>5763</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G27" t="s">
         <v>24</v>
@@ -33068,19 +33092,19 @@
         <v>198</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>5763</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G28" t="s">
         <v>24</v>
@@ -33091,19 +33115,19 @@
         <v>203</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>5764</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G29" t="s">
         <v>24</v>
@@ -33114,19 +33138,19 @@
         <v>208</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>5765</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
@@ -33137,19 +33161,19 @@
         <v>213</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>5766</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G31" t="s">
         <v>24</v>
@@ -33353,7 +33377,7 @@
         <v>5750</v>
       </c>
       <c r="E40" t="s">
-        <v>5757</v>
+        <v>5767</v>
       </c>
       <c r="F40" t="s">
         <v>5752</v>
@@ -33376,7 +33400,7 @@
         <v>5750</v>
       </c>
       <c r="E41" t="s">
-        <v>5758</v>
+        <v>5768</v>
       </c>
       <c r="F41" t="s">
         <v>5752</v>
@@ -34020,7 +34044,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5759</v>
+        <v>5769</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -34986,7 +35010,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5759</v>
+        <v>5769</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35282,7 +35306,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5760</v>
+        <v>5770</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35328,7 +35352,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5761</v>
+        <v>5771</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35365,19 +35389,19 @@
         <v>2673</v>
       </c>
       <c r="B6" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D6" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="E6" t="s">
-        <v>5763</v>
+        <v>5772</v>
       </c>
       <c r="F6" t="s">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -35388,19 +35412,19 @@
         <v>2680</v>
       </c>
       <c r="B7" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D7" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="E7" t="s">
-        <v>5763</v>
+        <v>5772</v>
       </c>
       <c r="F7" t="s">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -35411,19 +35435,19 @@
         <v>2686</v>
       </c>
       <c r="B8" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D8" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="E8" t="s">
-        <v>5763</v>
+        <v>5772</v>
       </c>
       <c r="F8" t="s">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -35434,19 +35458,19 @@
         <v>2693</v>
       </c>
       <c r="B9" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D9" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="E9" t="s">
-        <v>5763</v>
+        <v>5772</v>
       </c>
       <c r="F9" t="s">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -35466,7 +35490,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5765</v>
+        <v>5773</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35526,19 +35550,19 @@
         <v>2718</v>
       </c>
       <c r="B13" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D13" t="s">
-        <v>5762</v>
+        <v>5759</v>
       </c>
       <c r="E13" t="s">
-        <v>5763</v>
+        <v>5772</v>
       </c>
       <c r="F13" t="s">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5777">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18578,6 +18578,15 @@
   </si>
   <si>
     <t>2026-06-15 15:39 IST — pass in 21.7s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:42 IST — pass in 21.6s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:42 IST — pass in 21.2s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:42 IST — pass in 22.3s</t>
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.4s</t>
@@ -33276,19 +33285,19 @@
         <v>242</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>5767</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G36" t="s">
         <v>24</v>
@@ -33299,19 +33308,19 @@
         <v>247</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>5768</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G37" t="s">
         <v>24</v>
@@ -33322,19 +33331,19 @@
         <v>252</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>5769</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G38" t="s">
         <v>24</v>
@@ -33377,7 +33386,7 @@
         <v>5750</v>
       </c>
       <c r="E40" t="s">
-        <v>5767</v>
+        <v>5770</v>
       </c>
       <c r="F40" t="s">
         <v>5752</v>
@@ -33400,7 +33409,7 @@
         <v>5750</v>
       </c>
       <c r="E41" t="s">
-        <v>5768</v>
+        <v>5771</v>
       </c>
       <c r="F41" t="s">
         <v>5752</v>
@@ -34044,7 +34053,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5769</v>
+        <v>5772</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -35010,7 +35019,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5769</v>
+        <v>5772</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35306,7 +35315,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5770</v>
+        <v>5773</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35352,7 +35361,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5771</v>
+        <v>5774</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35398,7 +35407,7 @@
         <v>5759</v>
       </c>
       <c r="E6" t="s">
-        <v>5772</v>
+        <v>5775</v>
       </c>
       <c r="F6" t="s">
         <v>5761</v>
@@ -35421,7 +35430,7 @@
         <v>5759</v>
       </c>
       <c r="E7" t="s">
-        <v>5772</v>
+        <v>5775</v>
       </c>
       <c r="F7" t="s">
         <v>5761</v>
@@ -35444,7 +35453,7 @@
         <v>5759</v>
       </c>
       <c r="E8" t="s">
-        <v>5772</v>
+        <v>5775</v>
       </c>
       <c r="F8" t="s">
         <v>5761</v>
@@ -35467,7 +35476,7 @@
         <v>5759</v>
       </c>
       <c r="E9" t="s">
-        <v>5772</v>
+        <v>5775</v>
       </c>
       <c r="F9" t="s">
         <v>5761</v>
@@ -35490,7 +35499,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5773</v>
+        <v>5776</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35559,7 +35568,7 @@
         <v>5759</v>
       </c>
       <c r="E13" t="s">
-        <v>5772</v>
+        <v>5775</v>
       </c>
       <c r="F13" t="s">
         <v>5761</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5780">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18556,6 +18556,9 @@
     <t>2026-06-15 13:55 IST — pass in 17.2s</t>
   </si>
   <si>
+    <t>2026-06-15 15:45 IST — pass in 26.7s</t>
+  </si>
+  <si>
     <t>Skip</t>
   </si>
   <si>
@@ -18596,6 +18599,12 @@
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:45 IST — pass in 26.9s</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:45 IST — pass in 24.5s</t>
   </si>
   <si>
     <t>2026-06-15 00:32 IST — pass in 5.1s</t>
@@ -32871,19 +32880,19 @@
         <v>141</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>5759</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G18" t="s">
         <v>24</v>
@@ -33032,19 +33041,19 @@
         <v>181</v>
       </c>
       <c r="B25" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D25" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E25" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="F25" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -33055,19 +33064,19 @@
         <v>186</v>
       </c>
       <c r="B26" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D26" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E26" t="s">
+        <v>5763</v>
+      </c>
+      <c r="F26" t="s">
         <v>5762</v>
-      </c>
-      <c r="F26" t="s">
-        <v>5761</v>
       </c>
       <c r="G26" t="s">
         <v>24</v>
@@ -33087,7 +33096,7 @@
         <v>5750</v>
       </c>
       <c r="E27" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="F27" t="s">
         <v>5752</v>
@@ -33110,7 +33119,7 @@
         <v>5750</v>
       </c>
       <c r="E28" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="F28" t="s">
         <v>5752</v>
@@ -33133,7 +33142,7 @@
         <v>5750</v>
       </c>
       <c r="E29" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F29" t="s">
         <v>5752</v>
@@ -33156,7 +33165,7 @@
         <v>5750</v>
       </c>
       <c r="E30" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="F30" t="s">
         <v>5752</v>
@@ -33179,7 +33188,7 @@
         <v>5750</v>
       </c>
       <c r="E31" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="F31" t="s">
         <v>5752</v>
@@ -33294,7 +33303,7 @@
         <v>5750</v>
       </c>
       <c r="E36" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="F36" t="s">
         <v>5752</v>
@@ -33317,7 +33326,7 @@
         <v>5750</v>
       </c>
       <c r="E37" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
       <c r="F37" t="s">
         <v>5752</v>
@@ -33340,7 +33349,7 @@
         <v>5750</v>
       </c>
       <c r="E38" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="F38" t="s">
         <v>5752</v>
@@ -33386,7 +33395,7 @@
         <v>5750</v>
       </c>
       <c r="E40" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
       <c r="F40" t="s">
         <v>5752</v>
@@ -33409,7 +33418,7 @@
         <v>5750</v>
       </c>
       <c r="E41" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
       <c r="F41" t="s">
         <v>5752</v>
@@ -34053,7 +34062,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -35019,7 +35028,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35033,19 +35042,19 @@
         <v>662</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>24</v>
+        <v>5774</v>
       </c>
       <c r="F112" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G112" t="s">
         <v>24</v>
@@ -35056,19 +35065,19 @@
         <v>668</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D113" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>24</v>
+        <v>5775</v>
       </c>
       <c r="F113" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G113" t="s">
         <v>24</v>
@@ -35315,7 +35324,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5773</v>
+        <v>5776</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35361,7 +35370,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5774</v>
+        <v>5777</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35398,19 +35407,19 @@
         <v>2673</v>
       </c>
       <c r="B6" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D6" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F6" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -35421,19 +35430,19 @@
         <v>2680</v>
       </c>
       <c r="B7" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D7" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F7" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -35444,19 +35453,19 @@
         <v>2686</v>
       </c>
       <c r="B8" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D8" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F8" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -35467,19 +35476,19 @@
         <v>2693</v>
       </c>
       <c r="B9" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D9" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F9" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -35499,7 +35508,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5776</v>
+        <v>5779</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35559,19 +35568,19 @@
         <v>2718</v>
       </c>
       <c r="B13" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D13" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F13" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5784">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18596,6 +18596,18 @@
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.5s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:06 IST — pass in 23.5s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:06 IST — pass in 23.8s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:06 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:06 IST — pass in 25.5s</t>
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.3s</t>
@@ -33570,19 +33582,19 @@
         <v>306</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>5773</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -33639,19 +33651,19 @@
         <v>322</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E51" t="s">
-        <v>24</v>
+        <v>5774</v>
       </c>
       <c r="F51" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G51" t="s">
         <v>24</v>
@@ -33823,19 +33835,19 @@
         <v>367</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E59" t="s">
-        <v>24</v>
+        <v>5775</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G59" t="s">
         <v>24</v>
@@ -33846,19 +33858,19 @@
         <v>372</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E60" t="s">
-        <v>24</v>
+        <v>5776</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G60" t="s">
         <v>24</v>
@@ -33869,19 +33881,19 @@
         <v>376</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>5774</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -33915,19 +33927,19 @@
         <v>387</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>5775</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -34062,7 +34074,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5773</v>
+        <v>5777</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -35028,7 +35040,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5773</v>
+        <v>5777</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35051,7 +35063,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5774</v>
+        <v>5778</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35074,7 +35086,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5775</v>
+        <v>5779</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35324,7 +35336,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5776</v>
+        <v>5780</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35370,7 +35382,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5777</v>
+        <v>5781</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35416,7 +35428,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5778</v>
+        <v>5782</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35439,7 +35451,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5778</v>
+        <v>5782</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35462,7 +35474,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5778</v>
+        <v>5782</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35485,7 +35497,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5778</v>
+        <v>5782</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35508,7 +35520,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5779</v>
+        <v>5783</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35577,7 +35589,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5778</v>
+        <v>5782</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5788">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18601,13 +18601,25 @@
     <t>2026-06-15 16:06 IST — pass in 23.5s</t>
   </si>
   <si>
+    <t>2026-06-15 16:16 IST — pass in 23.9s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:16 IST — pass in 19.8s</t>
+  </si>
+  <si>
     <t>2026-06-15 16:06 IST — pass in 23.8s</t>
   </si>
   <si>
+    <t>2026-06-15 16:16 IST — pass in 20.8s</t>
+  </si>
+  <si>
     <t>2026-06-15 16:06 IST — skip in n/a</t>
   </si>
   <si>
     <t>2026-06-15 16:06 IST — pass in 25.5s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:16 IST — pass in 19.6s</t>
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.3s</t>
@@ -33605,19 +33617,19 @@
         <v>312</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E49" t="s">
-        <v>24</v>
+        <v>5774</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -33628,19 +33640,19 @@
         <v>317</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>5775</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G50" t="s">
         <v>24</v>
@@ -33660,7 +33672,7 @@
         <v>5750</v>
       </c>
       <c r="E51" t="s">
-        <v>5774</v>
+        <v>5776</v>
       </c>
       <c r="F51" t="s">
         <v>5752</v>
@@ -33789,19 +33801,19 @@
         <v>355</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>5777</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -33844,7 +33856,7 @@
         <v>5760</v>
       </c>
       <c r="E59" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F59" t="s">
         <v>5762</v>
@@ -33867,7 +33879,7 @@
         <v>5750</v>
       </c>
       <c r="E60" t="s">
-        <v>5776</v>
+        <v>5779</v>
       </c>
       <c r="F60" t="s">
         <v>5752</v>
@@ -33890,7 +33902,7 @@
         <v>5750</v>
       </c>
       <c r="E61" t="s">
-        <v>5774</v>
+        <v>5776</v>
       </c>
       <c r="F61" t="s">
         <v>5752</v>
@@ -33936,7 +33948,7 @@
         <v>5760</v>
       </c>
       <c r="E63" t="s">
-        <v>5775</v>
+        <v>5778</v>
       </c>
       <c r="F63" t="s">
         <v>5762</v>
@@ -34042,19 +34054,19 @@
         <v>411</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E68" t="s">
-        <v>24</v>
+        <v>5780</v>
       </c>
       <c r="F68" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G68" t="s">
         <v>24</v>
@@ -34074,7 +34086,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5777</v>
+        <v>5781</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -35040,7 +35052,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5777</v>
+        <v>5781</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35063,7 +35075,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5778</v>
+        <v>5782</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35086,7 +35098,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5779</v>
+        <v>5783</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35336,7 +35348,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5780</v>
+        <v>5784</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35382,7 +35394,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5781</v>
+        <v>5785</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35428,7 +35440,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5782</v>
+        <v>5786</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35451,7 +35463,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5782</v>
+        <v>5786</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35474,7 +35486,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5782</v>
+        <v>5786</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35497,7 +35509,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5782</v>
+        <v>5786</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35520,7 +35532,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5783</v>
+        <v>5787</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35589,7 +35601,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5782</v>
+        <v>5786</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5792">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18598,6 +18598,9 @@
     <t>2026-06-15 13:55 IST — pass in 18.5s</t>
   </si>
   <si>
+    <t>2026-06-15 16:20 IST — pass in 24.4s</t>
+  </si>
+  <si>
     <t>2026-06-15 16:06 IST — pass in 23.5s</t>
   </si>
   <si>
@@ -18623,6 +18626,15 @@
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:20 IST — pass in 25.2s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:20 IST — pass in 25.0s</t>
+  </si>
+  <si>
+    <t>2026-06-15 16:20 IST — pass in 24.9s</t>
   </si>
   <si>
     <t>2026-06-15 15:45 IST — pass in 26.9s</t>
@@ -33479,19 +33491,19 @@
         <v>279</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>5773</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G43" t="s">
         <v>24</v>
@@ -33603,7 +33615,7 @@
         <v>5750</v>
       </c>
       <c r="E48" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="F48" t="s">
         <v>5752</v>
@@ -33626,7 +33638,7 @@
         <v>5750</v>
       </c>
       <c r="E49" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F49" t="s">
         <v>5752</v>
@@ -33649,7 +33661,7 @@
         <v>5750</v>
       </c>
       <c r="E50" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="F50" t="s">
         <v>5752</v>
@@ -33672,7 +33684,7 @@
         <v>5750</v>
       </c>
       <c r="E51" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="F51" t="s">
         <v>5752</v>
@@ -33810,7 +33822,7 @@
         <v>5750</v>
       </c>
       <c r="E57" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F57" t="s">
         <v>5752</v>
@@ -33856,7 +33868,7 @@
         <v>5760</v>
       </c>
       <c r="E59" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="F59" t="s">
         <v>5762</v>
@@ -33879,7 +33891,7 @@
         <v>5750</v>
       </c>
       <c r="E60" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="F60" t="s">
         <v>5752</v>
@@ -33902,7 +33914,7 @@
         <v>5750</v>
       </c>
       <c r="E61" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="F61" t="s">
         <v>5752</v>
@@ -33948,7 +33960,7 @@
         <v>5760</v>
       </c>
       <c r="E63" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="F63" t="s">
         <v>5762</v>
@@ -34063,7 +34075,7 @@
         <v>5750</v>
       </c>
       <c r="E68" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="F68" t="s">
         <v>5752</v>
@@ -34086,7 +34098,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -34514,19 +34526,19 @@
         <v>528</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C88" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E88" t="s">
-        <v>24</v>
+        <v>5783</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G88" t="s">
         <v>24</v>
@@ -34537,19 +34549,19 @@
         <v>533</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C89" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D89" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E89" t="s">
-        <v>24</v>
+        <v>5784</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G89" t="s">
         <v>24</v>
@@ -34560,19 +34572,19 @@
         <v>538</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C90" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D90" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E90" t="s">
-        <v>24</v>
+        <v>5785</v>
       </c>
       <c r="F90" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G90" t="s">
         <v>24</v>
@@ -34583,19 +34595,19 @@
         <v>543</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C91" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D91" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E91" t="s">
-        <v>24</v>
+        <v>5785</v>
       </c>
       <c r="F91" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G91" t="s">
         <v>24</v>
@@ -35052,7 +35064,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35075,7 +35087,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5782</v>
+        <v>5786</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35098,7 +35110,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5783</v>
+        <v>5787</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35348,7 +35360,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5784</v>
+        <v>5788</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35394,7 +35406,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5785</v>
+        <v>5789</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35440,7 +35452,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5786</v>
+        <v>5790</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35463,7 +35475,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5786</v>
+        <v>5790</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35486,7 +35498,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5786</v>
+        <v>5790</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35509,7 +35521,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5786</v>
+        <v>5790</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35532,7 +35544,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5787</v>
+        <v>5791</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35601,7 +35613,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5786</v>
+        <v>5790</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5794">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18601,6 +18601,9 @@
     <t>2026-06-15 16:20 IST — pass in 24.4s</t>
   </si>
   <si>
+    <t>2026-06-15 17:18 IST — pass in 25.7s</t>
+  </si>
+  <si>
     <t>2026-06-15 16:06 IST — pass in 23.5s</t>
   </si>
   <si>
@@ -18635,6 +18638,9 @@
   </si>
   <si>
     <t>2026-06-15 16:20 IST — pass in 24.9s</t>
+  </si>
+  <si>
+    <t>2026-06-15 17:18 IST — skip in n/a</t>
   </si>
   <si>
     <t>2026-06-15 15:45 IST — pass in 26.9s</t>
@@ -33514,19 +33520,19 @@
         <v>283</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>5774</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G44" t="s">
         <v>24</v>
@@ -33615,7 +33621,7 @@
         <v>5750</v>
       </c>
       <c r="E48" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F48" t="s">
         <v>5752</v>
@@ -33638,7 +33644,7 @@
         <v>5750</v>
       </c>
       <c r="E49" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="F49" t="s">
         <v>5752</v>
@@ -33661,7 +33667,7 @@
         <v>5750</v>
       </c>
       <c r="E50" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="F50" t="s">
         <v>5752</v>
@@ -33684,7 +33690,7 @@
         <v>5750</v>
       </c>
       <c r="E51" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F51" t="s">
         <v>5752</v>
@@ -33822,7 +33828,7 @@
         <v>5750</v>
       </c>
       <c r="E57" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="F57" t="s">
         <v>5752</v>
@@ -33868,7 +33874,7 @@
         <v>5760</v>
       </c>
       <c r="E59" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="F59" t="s">
         <v>5762</v>
@@ -33891,7 +33897,7 @@
         <v>5750</v>
       </c>
       <c r="E60" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="F60" t="s">
         <v>5752</v>
@@ -33914,7 +33920,7 @@
         <v>5750</v>
       </c>
       <c r="E61" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F61" t="s">
         <v>5752</v>
@@ -33960,7 +33966,7 @@
         <v>5760</v>
       </c>
       <c r="E63" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="F63" t="s">
         <v>5762</v>
@@ -34075,7 +34081,7 @@
         <v>5750</v>
       </c>
       <c r="E68" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="F68" t="s">
         <v>5752</v>
@@ -34098,7 +34104,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -34535,7 +34541,7 @@
         <v>5750</v>
       </c>
       <c r="E88" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="F88" t="s">
         <v>5752</v>
@@ -34558,7 +34564,7 @@
         <v>5750</v>
       </c>
       <c r="E89" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
       <c r="F89" t="s">
         <v>5752</v>
@@ -34581,7 +34587,7 @@
         <v>5750</v>
       </c>
       <c r="E90" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="F90" t="s">
         <v>5752</v>
@@ -34604,7 +34610,7 @@
         <v>5750</v>
       </c>
       <c r="E91" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="F91" t="s">
         <v>5752</v>
@@ -34779,19 +34785,19 @@
         <v>587</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C99" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E99" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F99" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G99" t="s">
         <v>24</v>
@@ -34802,19 +34808,19 @@
         <v>594</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D100" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E100" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F100" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
@@ -34871,19 +34877,19 @@
         <v>611</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D103" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E103" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F103" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G103" t="s">
         <v>24</v>
@@ -34940,19 +34946,19 @@
         <v>629</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E106" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F106" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G106" t="s">
         <v>24</v>
@@ -34963,19 +34969,19 @@
         <v>635</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E107" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F107" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G107" t="s">
         <v>24</v>
@@ -35064,7 +35070,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35087,7 +35093,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5786</v>
+        <v>5788</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35110,7 +35116,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35360,7 +35366,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5788</v>
+        <v>5790</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35406,7 +35412,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35452,7 +35458,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35475,7 +35481,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35498,7 +35504,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35521,7 +35527,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35544,7 +35550,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5791</v>
+        <v>5793</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35613,7 +35619,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5796">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18602,6 +18602,12 @@
   </si>
   <si>
     <t>2026-06-15 17:18 IST — pass in 25.7s</t>
+  </si>
+  <si>
+    <t>2026-06-15 17:23 IST — pass in 25.7s</t>
+  </si>
+  <si>
+    <t>2026-06-15 17:23 IST — skip in n/a</t>
   </si>
   <si>
     <t>2026-06-15 16:06 IST — pass in 23.5s</t>
@@ -33543,19 +33549,19 @@
         <v>288</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>5775</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G45" t="s">
         <v>24</v>
@@ -33566,19 +33572,19 @@
         <v>294</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E46" t="s">
-        <v>24</v>
+        <v>5776</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
@@ -33621,7 +33627,7 @@
         <v>5750</v>
       </c>
       <c r="E48" t="s">
-        <v>5775</v>
+        <v>5777</v>
       </c>
       <c r="F48" t="s">
         <v>5752</v>
@@ -33644,7 +33650,7 @@
         <v>5750</v>
       </c>
       <c r="E49" t="s">
-        <v>5776</v>
+        <v>5778</v>
       </c>
       <c r="F49" t="s">
         <v>5752</v>
@@ -33667,7 +33673,7 @@
         <v>5750</v>
       </c>
       <c r="E50" t="s">
-        <v>5777</v>
+        <v>5779</v>
       </c>
       <c r="F50" t="s">
         <v>5752</v>
@@ -33690,7 +33696,7 @@
         <v>5750</v>
       </c>
       <c r="E51" t="s">
-        <v>5778</v>
+        <v>5780</v>
       </c>
       <c r="F51" t="s">
         <v>5752</v>
@@ -33828,7 +33834,7 @@
         <v>5750</v>
       </c>
       <c r="E57" t="s">
-        <v>5779</v>
+        <v>5781</v>
       </c>
       <c r="F57" t="s">
         <v>5752</v>
@@ -33874,7 +33880,7 @@
         <v>5760</v>
       </c>
       <c r="E59" t="s">
-        <v>5780</v>
+        <v>5782</v>
       </c>
       <c r="F59" t="s">
         <v>5762</v>
@@ -33897,7 +33903,7 @@
         <v>5750</v>
       </c>
       <c r="E60" t="s">
-        <v>5781</v>
+        <v>5783</v>
       </c>
       <c r="F60" t="s">
         <v>5752</v>
@@ -33920,7 +33926,7 @@
         <v>5750</v>
       </c>
       <c r="E61" t="s">
-        <v>5778</v>
+        <v>5780</v>
       </c>
       <c r="F61" t="s">
         <v>5752</v>
@@ -33966,7 +33972,7 @@
         <v>5760</v>
       </c>
       <c r="E63" t="s">
-        <v>5780</v>
+        <v>5782</v>
       </c>
       <c r="F63" t="s">
         <v>5762</v>
@@ -34081,7 +34087,7 @@
         <v>5750</v>
       </c>
       <c r="E68" t="s">
-        <v>5782</v>
+        <v>5784</v>
       </c>
       <c r="F68" t="s">
         <v>5752</v>
@@ -34104,7 +34110,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5783</v>
+        <v>5785</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -34541,7 +34547,7 @@
         <v>5750</v>
       </c>
       <c r="E88" t="s">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="F88" t="s">
         <v>5752</v>
@@ -34564,7 +34570,7 @@
         <v>5750</v>
       </c>
       <c r="E89" t="s">
-        <v>5785</v>
+        <v>5787</v>
       </c>
       <c r="F89" t="s">
         <v>5752</v>
@@ -34587,7 +34593,7 @@
         <v>5750</v>
       </c>
       <c r="E90" t="s">
-        <v>5786</v>
+        <v>5788</v>
       </c>
       <c r="F90" t="s">
         <v>5752</v>
@@ -34610,7 +34616,7 @@
         <v>5750</v>
       </c>
       <c r="E91" t="s">
-        <v>5786</v>
+        <v>5788</v>
       </c>
       <c r="F91" t="s">
         <v>5752</v>
@@ -34794,7 +34800,7 @@
         <v>5760</v>
       </c>
       <c r="E99" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F99" t="s">
         <v>5762</v>
@@ -34817,7 +34823,7 @@
         <v>5760</v>
       </c>
       <c r="E100" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F100" t="s">
         <v>5762</v>
@@ -34886,7 +34892,7 @@
         <v>5760</v>
       </c>
       <c r="E103" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F103" t="s">
         <v>5762</v>
@@ -34955,7 +34961,7 @@
         <v>5760</v>
       </c>
       <c r="E106" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F106" t="s">
         <v>5762</v>
@@ -34978,7 +34984,7 @@
         <v>5760</v>
       </c>
       <c r="E107" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F107" t="s">
         <v>5762</v>
@@ -35070,7 +35076,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5783</v>
+        <v>5785</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35093,7 +35099,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5788</v>
+        <v>5790</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35116,7 +35122,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35366,7 +35372,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35412,7 +35418,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5791</v>
+        <v>5793</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35458,7 +35464,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5792</v>
+        <v>5794</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35481,7 +35487,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5792</v>
+        <v>5794</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35504,7 +35510,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5792</v>
+        <v>5794</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35527,7 +35533,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5792</v>
+        <v>5794</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35550,7 +35556,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5793</v>
+        <v>5795</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35619,7 +35625,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5792</v>
+        <v>5794</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5798">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18598,6 +18598,9 @@
     <t>2026-06-15 13:55 IST — pass in 18.5s</t>
   </si>
   <si>
+    <t>2026-06-15 17:24 IST — pass in 22.7s</t>
+  </si>
+  <si>
     <t>2026-06-15 16:20 IST — pass in 24.4s</t>
   </si>
   <si>
@@ -18635,6 +18638,9 @@
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 17:24 IST — skip in n/a</t>
   </si>
   <si>
     <t>2026-06-15 16:20 IST — pass in 25.2s</t>
@@ -33480,19 +33486,19 @@
         <v>275</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>5773</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G42" t="s">
         <v>24</v>
@@ -33512,7 +33518,7 @@
         <v>5750</v>
       </c>
       <c r="E43" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="F43" t="s">
         <v>5752</v>
@@ -33535,7 +33541,7 @@
         <v>5750</v>
       </c>
       <c r="E44" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F44" t="s">
         <v>5752</v>
@@ -33558,7 +33564,7 @@
         <v>5750</v>
       </c>
       <c r="E45" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="F45" t="s">
         <v>5752</v>
@@ -33581,7 +33587,7 @@
         <v>5760</v>
       </c>
       <c r="E46" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="F46" t="s">
         <v>5762</v>
@@ -33627,7 +33633,7 @@
         <v>5750</v>
       </c>
       <c r="E48" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="F48" t="s">
         <v>5752</v>
@@ -33650,7 +33656,7 @@
         <v>5750</v>
       </c>
       <c r="E49" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="F49" t="s">
         <v>5752</v>
@@ -33673,7 +33679,7 @@
         <v>5750</v>
       </c>
       <c r="E50" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="F50" t="s">
         <v>5752</v>
@@ -33696,7 +33702,7 @@
         <v>5750</v>
       </c>
       <c r="E51" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="F51" t="s">
         <v>5752</v>
@@ -33834,7 +33840,7 @@
         <v>5750</v>
       </c>
       <c r="E57" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="F57" t="s">
         <v>5752</v>
@@ -33880,7 +33886,7 @@
         <v>5760</v>
       </c>
       <c r="E59" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F59" t="s">
         <v>5762</v>
@@ -33903,7 +33909,7 @@
         <v>5750</v>
       </c>
       <c r="E60" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="F60" t="s">
         <v>5752</v>
@@ -33926,7 +33932,7 @@
         <v>5750</v>
       </c>
       <c r="E61" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="F61" t="s">
         <v>5752</v>
@@ -33972,7 +33978,7 @@
         <v>5760</v>
       </c>
       <c r="E63" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F63" t="s">
         <v>5762</v>
@@ -34087,7 +34093,7 @@
         <v>5750</v>
       </c>
       <c r="E68" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
       <c r="F68" t="s">
         <v>5752</v>
@@ -34110,7 +34116,7 @@
         <v>5750</v>
       </c>
       <c r="E69" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="F69" t="s">
         <v>5752</v>
@@ -34331,19 +34337,19 @@
         <v>479</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E79" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G79" t="s">
         <v>24</v>
@@ -34354,19 +34360,19 @@
         <v>485</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C80" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D80" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E80" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F80" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G80" t="s">
         <v>24</v>
@@ -34377,19 +34383,19 @@
         <v>490</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C81" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D81" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E81" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F81" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G81" t="s">
         <v>24</v>
@@ -34400,19 +34406,19 @@
         <v>495</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C82" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E82" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F82" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G82" t="s">
         <v>24</v>
@@ -34423,19 +34429,19 @@
         <v>500</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C83" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D83" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E83" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G83" t="s">
         <v>24</v>
@@ -34469,19 +34475,19 @@
         <v>511</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C85" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D85" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E85" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F85" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G85" t="s">
         <v>24</v>
@@ -34492,19 +34498,19 @@
         <v>516</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C86" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D86" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E86" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F86" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G86" t="s">
         <v>24</v>
@@ -34515,19 +34521,19 @@
         <v>521</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C87" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D87" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>
@@ -34547,7 +34553,7 @@
         <v>5750</v>
       </c>
       <c r="E88" t="s">
-        <v>5786</v>
+        <v>5788</v>
       </c>
       <c r="F88" t="s">
         <v>5752</v>
@@ -34570,7 +34576,7 @@
         <v>5750</v>
       </c>
       <c r="E89" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="F89" t="s">
         <v>5752</v>
@@ -34593,7 +34599,7 @@
         <v>5750</v>
       </c>
       <c r="E90" t="s">
-        <v>5788</v>
+        <v>5790</v>
       </c>
       <c r="F90" t="s">
         <v>5752</v>
@@ -34616,7 +34622,7 @@
         <v>5750</v>
       </c>
       <c r="E91" t="s">
-        <v>5788</v>
+        <v>5790</v>
       </c>
       <c r="F91" t="s">
         <v>5752</v>
@@ -34800,7 +34806,7 @@
         <v>5760</v>
       </c>
       <c r="E99" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F99" t="s">
         <v>5762</v>
@@ -34823,7 +34829,7 @@
         <v>5760</v>
       </c>
       <c r="E100" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F100" t="s">
         <v>5762</v>
@@ -34892,7 +34898,7 @@
         <v>5760</v>
       </c>
       <c r="E103" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F103" t="s">
         <v>5762</v>
@@ -34961,7 +34967,7 @@
         <v>5760</v>
       </c>
       <c r="E106" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F106" t="s">
         <v>5762</v>
@@ -34984,7 +34990,7 @@
         <v>5760</v>
       </c>
       <c r="E107" t="s">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="F107" t="s">
         <v>5762</v>
@@ -35076,7 +35082,7 @@
         <v>5750</v>
       </c>
       <c r="E111" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="F111" t="s">
         <v>5752</v>
@@ -35099,7 +35105,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5790</v>
+        <v>5792</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35122,7 +35128,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5791</v>
+        <v>5793</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35372,7 +35378,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5792</v>
+        <v>5794</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35418,7 +35424,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5793</v>
+        <v>5795</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35464,7 +35470,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5794</v>
+        <v>5796</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35487,7 +35493,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5794</v>
+        <v>5796</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35510,7 +35516,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5794</v>
+        <v>5796</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35533,7 +35539,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5794</v>
+        <v>5796</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35556,7 +35562,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5795</v>
+        <v>5797</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35625,7 +35631,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5794</v>
+        <v>5796</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5799">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18638,6 +18638,9 @@
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 18.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 17:25 IST — pass in 21.7s</t>
   </si>
   <si>
     <t>2026-06-15 17:24 IST — skip in n/a</t>
@@ -34153,19 +34156,19 @@
         <v>428</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F71" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G71" t="s">
         <v>24</v>
@@ -34346,7 +34349,7 @@
         <v>5760</v>
       </c>
       <c r="E79" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F79" t="s">
         <v>5762</v>
@@ -34369,7 +34372,7 @@
         <v>5760</v>
       </c>
       <c r="E80" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F80" t="s">
         <v>5762</v>
@@ -34392,7 +34395,7 @@
         <v>5760</v>
       </c>
       <c r="E81" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F81" t="s">
         <v>5762</v>
@@ -34415,7 +34418,7 @@
         <v>5760</v>
       </c>
       <c r="E82" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F82" t="s">
         <v>5762</v>
@@ -34438,7 +34441,7 @@
         <v>5760</v>
       </c>
       <c r="E83" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F83" t="s">
         <v>5762</v>
@@ -34484,7 +34487,7 @@
         <v>5760</v>
       </c>
       <c r="E85" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F85" t="s">
         <v>5762</v>
@@ -34507,7 +34510,7 @@
         <v>5760</v>
       </c>
       <c r="E86" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F86" t="s">
         <v>5762</v>
@@ -34530,7 +34533,7 @@
         <v>5760</v>
       </c>
       <c r="E87" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="F87" t="s">
         <v>5762</v>
@@ -34553,7 +34556,7 @@
         <v>5750</v>
       </c>
       <c r="E88" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="F88" t="s">
         <v>5752</v>
@@ -34576,7 +34579,7 @@
         <v>5750</v>
       </c>
       <c r="E89" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
       <c r="F89" t="s">
         <v>5752</v>
@@ -34599,7 +34602,7 @@
         <v>5750</v>
       </c>
       <c r="E90" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
       <c r="F90" t="s">
         <v>5752</v>
@@ -34622,7 +34625,7 @@
         <v>5750</v>
       </c>
       <c r="E91" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
       <c r="F91" t="s">
         <v>5752</v>
@@ -34806,7 +34809,7 @@
         <v>5760</v>
       </c>
       <c r="E99" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="F99" t="s">
         <v>5762</v>
@@ -34829,7 +34832,7 @@
         <v>5760</v>
       </c>
       <c r="E100" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="F100" t="s">
         <v>5762</v>
@@ -34898,7 +34901,7 @@
         <v>5760</v>
       </c>
       <c r="E103" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="F103" t="s">
         <v>5762</v>
@@ -34967,7 +34970,7 @@
         <v>5760</v>
       </c>
       <c r="E106" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="F106" t="s">
         <v>5762</v>
@@ -34990,7 +34993,7 @@
         <v>5760</v>
       </c>
       <c r="E107" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="F107" t="s">
         <v>5762</v>
@@ -35105,7 +35108,7 @@
         <v>5750</v>
       </c>
       <c r="E112" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
       <c r="F112" t="s">
         <v>5752</v>
@@ -35128,7 +35131,7 @@
         <v>5750</v>
       </c>
       <c r="E113" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F113" t="s">
         <v>5752</v>
@@ -35378,7 +35381,7 @@
         <v>5750</v>
       </c>
       <c r="E2" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
       <c r="F2" t="s">
         <v>5752</v>
@@ -35424,7 +35427,7 @@
         <v>5750</v>
       </c>
       <c r="E4" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
       <c r="F4" t="s">
         <v>5752</v>
@@ -35470,7 +35473,7 @@
         <v>5760</v>
       </c>
       <c r="E6" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="F6" t="s">
         <v>5762</v>
@@ -35493,7 +35496,7 @@
         <v>5760</v>
       </c>
       <c r="E7" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="F7" t="s">
         <v>5762</v>
@@ -35516,7 +35519,7 @@
         <v>5760</v>
       </c>
       <c r="E8" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="F8" t="s">
         <v>5762</v>
@@ -35539,7 +35542,7 @@
         <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="F9" t="s">
         <v>5762</v>
@@ -35562,7 +35565,7 @@
         <v>5750</v>
       </c>
       <c r="E10" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
       <c r="F10" t="s">
         <v>5752</v>
@@ -35631,7 +35634,7 @@
         <v>5760</v>
       </c>
       <c r="E13" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="F13" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5800">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18674,6 +18674,9 @@
   </si>
   <si>
     <t>2026-06-15 00:33 IST — pass in 4.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:27 IST — pass in 7.1s</t>
   </si>
 </sst>
 </file>
@@ -35993,19 +35996,19 @@
         <v>2814</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>5799</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G29" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5805">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18676,7 +18676,22 @@
     <t>2026-06-15 00:33 IST — pass in 4.3s</t>
   </si>
   <si>
+    <t>2026-06-15 18:34 IST — pass in 6.6s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:34 IST — pass in 8.8s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:34 IST — pass in 7.5s</t>
+  </si>
+  <si>
     <t>2026-06-15 18:27 IST — pass in 7.1s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:34 IST — pass in 8.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:34 IST — pass in 8.4s</t>
   </si>
 </sst>
 </file>
@@ -35766,19 +35781,19 @@
         <v>2755</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>5799</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
@@ -35835,19 +35850,19 @@
         <v>2772</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>5800</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G22" t="s">
         <v>24</v>
@@ -35973,19 +35988,19 @@
         <v>2807</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>5801</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G28" t="s">
         <v>24</v>
@@ -36005,7 +36020,7 @@
         <v>5750</v>
       </c>
       <c r="E29" t="s">
-        <v>5799</v>
+        <v>5802</v>
       </c>
       <c r="F29" t="s">
         <v>5752</v>
@@ -36019,19 +36034,19 @@
         <v>2821</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>5803</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
@@ -36065,19 +36080,19 @@
         <v>2834</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>5804</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G32" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5810">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18692,6 +18692,21 @@
   </si>
   <si>
     <t>2026-06-15 18:34 IST — pass in 8.4s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:36 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:36 IST — skip in Close dismisses without action</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:36 IST — skip in not Cancel</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:36 IST — skip in not Stop</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:36 IST — pass in 7.4s</t>
   </si>
 </sst>
 </file>
@@ -36448,19 +36463,19 @@
         <v>2940</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>5805</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -36471,19 +36486,19 @@
         <v>2947</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E49" t="s">
-        <v>24</v>
+        <v>5806</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -36655,19 +36670,19 @@
         <v>3001</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>5805</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -36747,19 +36762,19 @@
         <v>3030</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>5807</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -36770,19 +36785,19 @@
         <v>3037</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>5808</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -36793,19 +36808,19 @@
         <v>3044</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>5809</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -36816,19 +36831,19 @@
         <v>3052</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>5805</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -36931,19 +36946,19 @@
         <v>3087</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>5805</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5814">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18692,6 +18692,18 @@
   </si>
   <si>
     <t>2026-06-15 18:34 IST — pass in 8.4s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:42 IST — pass in 8.4s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:42 IST — pass in 7.8s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:42 IST — pass in 5.5s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:42 IST — pass in 7.0s</t>
   </si>
   <si>
     <t>2026-06-15 18:36 IST — skip in n/a</t>
@@ -36141,19 +36153,19 @@
         <v>2847</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>5805</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G34" t="s">
         <v>24</v>
@@ -36164,19 +36176,19 @@
         <v>2853</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
+        <v>5806</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G35" t="s">
         <v>24</v>
@@ -36210,19 +36222,19 @@
         <v>2865</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>5805</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G37" t="s">
         <v>24</v>
@@ -36279,19 +36291,19 @@
         <v>2884</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>5807</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -36302,19 +36314,19 @@
         <v>2890</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>5808</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
@@ -36472,7 +36484,7 @@
         <v>5760</v>
       </c>
       <c r="E48" t="s">
-        <v>5805</v>
+        <v>5809</v>
       </c>
       <c r="F48" t="s">
         <v>5762</v>
@@ -36495,7 +36507,7 @@
         <v>5760</v>
       </c>
       <c r="E49" t="s">
-        <v>5806</v>
+        <v>5810</v>
       </c>
       <c r="F49" t="s">
         <v>5762</v>
@@ -36679,7 +36691,7 @@
         <v>5760</v>
       </c>
       <c r="E57" t="s">
-        <v>5805</v>
+        <v>5809</v>
       </c>
       <c r="F57" t="s">
         <v>5762</v>
@@ -36771,7 +36783,7 @@
         <v>5760</v>
       </c>
       <c r="E61" t="s">
-        <v>5807</v>
+        <v>5811</v>
       </c>
       <c r="F61" t="s">
         <v>5762</v>
@@ -36794,7 +36806,7 @@
         <v>5760</v>
       </c>
       <c r="E62" t="s">
-        <v>5808</v>
+        <v>5812</v>
       </c>
       <c r="F62" t="s">
         <v>5762</v>
@@ -36817,7 +36829,7 @@
         <v>5750</v>
       </c>
       <c r="E63" t="s">
-        <v>5809</v>
+        <v>5813</v>
       </c>
       <c r="F63" t="s">
         <v>5752</v>
@@ -36840,7 +36852,7 @@
         <v>5760</v>
       </c>
       <c r="E64" t="s">
-        <v>5805</v>
+        <v>5809</v>
       </c>
       <c r="F64" t="s">
         <v>5762</v>
@@ -36955,7 +36967,7 @@
         <v>5760</v>
       </c>
       <c r="E69" t="s">
-        <v>5805</v>
+        <v>5809</v>
       </c>
       <c r="F69" t="s">
         <v>5762</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16942" uniqueCount="5817">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18719,6 +18719,15 @@
   </si>
   <si>
     <t>2026-06-15 18:36 IST — pass in 7.4s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:43 IST — pass in 6.3s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:43 IST — pass in 5.1s</t>
+  </si>
+  <si>
+    <t>2026-06-15 18:43 IST — skip in n/a</t>
   </si>
 </sst>
 </file>
@@ -36981,19 +36990,19 @@
         <v>3094</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E70" t="s">
-        <v>24</v>
+        <v>5814</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G70" t="s">
         <v>24</v>
@@ -37349,19 +37358,19 @@
         <v>3205</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="C86" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D86" t="s">
-        <v>24</v>
+        <v>5750</v>
       </c>
       <c r="E86" t="s">
-        <v>24</v>
+        <v>5815</v>
       </c>
       <c r="F86" t="s">
-        <v>24</v>
+        <v>5752</v>
       </c>
       <c r="G86" t="s">
         <v>24</v>
@@ -37372,19 +37381,19 @@
         <v>3211</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="C87" s="16" t="s">
         <v>5748</v>
       </c>
       <c r="D87" t="s">
-        <v>24</v>
+        <v>5760</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>5816</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>5762</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18532,7 +18532,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-06-15 13:52 IST — pass in 18.2s</t>
+    <t>2026-06-20 09:49 IST — pass in 17.2s</t>
   </si>
   <si>
     <t>PASS — matched expected</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18538,7 +18538,7 @@
     <t>PASS — matched expected</t>
   </si>
   <si>
-    <t>2026-06-15 13:55 IST — pass in 18.2s</t>
+    <t>2026-06-20 09:59 IST — pass in 17.2s</t>
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 19.3s</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18541,7 +18541,7 @@
     <t>2026-06-20 09:59 IST — pass in 17.2s</t>
   </si>
   <si>
-    <t>2026-06-15 13:55 IST — pass in 19.3s</t>
+    <t>2026-06-20 10:02 IST — pass in 18.1s</t>
   </si>
   <si>
     <t>2026-06-15 15:39 IST — pass in 21.4s</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18544,7 +18544,7 @@
     <t>2026-06-20 10:02 IST — pass in 18.1s</t>
   </si>
   <si>
-    <t>2026-06-15 15:39 IST — pass in 21.4s</t>
+    <t>2026-06-20 10:05 IST — pass in 17.8s</t>
   </si>
   <si>
     <t>2026-06-15 13:52 IST — pass in 34.8s</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18547,7 +18547,7 @@
     <t>2026-06-20 10:05 IST — pass in 17.8s</t>
   </si>
   <si>
-    <t>2026-06-15 13:52 IST — pass in 34.8s</t>
+    <t>2026-06-20 10:07 IST — pass in 33.4s</t>
   </si>
   <si>
     <t>2026-06-15 15:39 IST — pass in 24.2s</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18550,7 +18550,7 @@
     <t>2026-06-20 10:07 IST — pass in 33.4s</t>
   </si>
   <si>
-    <t>2026-06-15 15:39 IST — pass in 24.2s</t>
+    <t>2026-06-20 10:10 IST — pass in 17.1s</t>
   </si>
   <si>
     <t>2026-06-15 13:55 IST — pass in 17.2s</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18553,10 +18553,10 @@
     <t>2026-06-20 10:10 IST — pass in 17.1s</t>
   </si>
   <si>
-    <t>2026-06-15 13:55 IST — pass in 17.2s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:45 IST — pass in 26.7s</t>
+    <t>2026-06-20 10:15 IST — pass in 17.1s</t>
+  </si>
+  <si>
+    <t>2026-06-20 10:15 IST — pass in 17.6s</t>
   </si>
   <si>
     <t>Skip</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17020" uniqueCount="5849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17245" uniqueCount="5906">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18547,7 +18547,7 @@
     <t>Not Automated</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 17.9s</t>
+    <t>2026-06-20 15:52 IST — pass in 17.7s</t>
   </si>
   <si>
     <t>ADM_CUST_001.png</t>
@@ -18559,13 +18559,13 @@
     <t>ADM_CUST_003.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:49 IST — pass in 17.8s</t>
+    <t>2026-06-20 15:52 IST — pass in 17.5s</t>
   </si>
   <si>
     <t>ADM_CUST_004.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 19.6s</t>
+    <t>2026-06-20 15:52 IST — pass in 18.4s</t>
   </si>
   <si>
     <t>ADM_CUST_005.png</t>
@@ -18574,7 +18574,7 @@
     <t>ADM_CUST_040.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 19.4s</t>
+    <t>2026-06-20 15:52 IST — pass in 18.0s</t>
   </si>
   <si>
     <t>TC_CUST_NEG_011.png</t>
@@ -18583,13 +18583,13 @@
     <t>ADM_CUST_006.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 34.6s</t>
+    <t>2026-06-20 15:52 IST — pass in 33.4s</t>
   </si>
   <si>
     <t>ADM_CUST_007.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 17.5s</t>
+    <t>2026-06-20 15:52 IST — pass in 17.8s</t>
   </si>
   <si>
     <t>ADM_CUST_008.png</t>
@@ -18610,13 +18610,13 @@
     <t>ADM_CUST_038.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 17.8s</t>
+    <t>2026-06-20 15:52 IST — pass in 17.4s</t>
   </si>
   <si>
     <t>ADM_CUST_025.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 19.3s</t>
+    <t>2026-06-20 15:52 IST — pass in 17.9s</t>
   </si>
   <si>
     <t>TC_CUST_NEG_049.png</t>
@@ -18625,151 +18625,322 @@
     <t>TC_CUST_UI_041.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — skip in 18.2s</t>
+    <t>2026-06-20 15:52 IST — skip in n/a</t>
   </si>
   <si>
     <t>TC_CUST_FUNC_128.png</t>
   </si>
   <si>
-    <t>2026-06-20 11:38 IST — pass in 17.3s</t>
-  </si>
-  <si>
     <t>TC_CUST_FUNC_122.png</t>
   </si>
   <si>
     <t>TC_CUST_FUNC_123.png</t>
   </si>
   <si>
-    <t>2026-06-15 15:39 IST — skip in n/a</t>
+    <t>ADM_CUST_013.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 17.3s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_014.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_037.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — skip in phone-only search</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_010.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_015.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_016.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 18.6s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_017.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 18.7s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_019.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 18.5s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_018.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_124.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_125.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 17.6s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_126.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_021.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_022.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_023.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_024.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 29.1s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_130.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_020.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:54 IST — pass in 17.8s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_030.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_050.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 22.0s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_060.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 22.1s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_080.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:54 IST — skip in 17.8s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_031.png</t>
+  </si>
+  <si>
+    <t>Deferred</t>
+  </si>
+  <si>
+    <t>Manual — destructive</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>[DESTRUCT] not run as live e2e</t>
+  </si>
+  <si>
+    <t>Home Loan approval applies to all sub-units — requires SUBMIT on live data + user OK</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 21.9s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_026.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_042.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_043.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 19.0s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_044.png</t>
+  </si>
+  <si>
+    <t>API spec (not e2e)</t>
+  </si>
+  <si>
+    <t>[API] not run as live e2e</t>
+  </si>
+  <si>
+    <t>Verified at API layer (tests/api) — not an e2e/browser test</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_091.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — skip in prevents double submit</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 22.3s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_046.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 21.8s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_027.png</t>
+  </si>
+  <si>
+    <t>Verify cancellation cannot be undone — requires an actual cancel on live data + user OK</t>
+  </si>
+  <si>
+    <t>ADM_CUST_104.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_033.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_121.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_092.png</t>
+  </si>
+  <si>
+    <t>Offline unit assignment happy-path BOOKS a unit — requires SUBMIT on live data + user OK</t>
+  </si>
+  <si>
+    <t>Assign Unit validation — Assign Unit modal access needs a Waitlisted fixture; submit-path destructive</t>
+  </si>
+  <si>
+    <t>Unit availability re-checked at submit — requires SUBMIT + concurrent fixture, user OK</t>
+  </si>
+  <si>
+    <t>Reject 2nd unit when already booked — requires a fixture with an active booking + user OK</t>
+  </si>
+  <si>
+    <t>Blocked — Milestones POM</t>
+  </si>
+  <si>
+    <t>[POM] not run as live e2e</t>
+  </si>
+  <si>
+    <t>Payment-proof upload validation — needs Milestones page POM (separate page), not yet built</t>
+  </si>
+  <si>
+    <t>Integration (provider stub)</t>
+  </si>
+  <si>
+    <t>[INT] not run as live e2e</t>
+  </si>
+  <si>
+    <t>WhatsApp + SMS dispatch — needs provider stub, out of e2e scope</t>
+  </si>
+  <si>
+    <t>WhatsApp dispatch — needs provider stub, out of e2e scope</t>
+  </si>
+  <si>
+    <t>Offline Payment form (Principal/GST/Milestone summary) — needs Milestones POM, not yet built</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_061.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_062.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_063.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_064.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_065.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 22.2s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_066.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 18.2s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_070.png</t>
+  </si>
+  <si>
+    <t>Parking update sends no buyer message — requires parking SUBMIT on live data + user OK</t>
+  </si>
+  <si>
+    <t>Backend validation gap (parking enabled=true,count=0) — API-layer test, not e2e</t>
+  </si>
+  <si>
+    <t>ADM_CUST_034.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_035.png</t>
+  </si>
+  <si>
+    <t>ADM_CUST_036.png</t>
+  </si>
+  <si>
+    <t>Covered by alias</t>
+  </si>
+  <si>
+    <t>Pass (via alias)</t>
+  </si>
+  <si>
+    <t>[ALIAS] not run as live e2e</t>
+  </si>
+  <si>
+    <t>Covered by TC_CUST_FUNC_008b (download with active filter)</t>
+  </si>
+  <si>
+    <t>DB spec (not e2e)</t>
+  </si>
+  <si>
+    <t>[DB] not run as live e2e</t>
+  </si>
+  <si>
+    <t>Hardcoded gateway/value check — DB-layer test (db/queries), not e2e</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 2.4s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_123.png</t>
+  </si>
+  <si>
+    <t>JWT-after-logout (server logout no-op) — API-layer test, not e2e</t>
+  </si>
+  <si>
+    <t>projectId cross-project leak check — API-layer test, not e2e</t>
+  </si>
+  <si>
+    <t>2026-06-20 15:52 IST — pass in 24.7s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_124.png</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:32 IST — pass in 5.1s</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:33 IST — pass in 3.2s</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:33 IST — skip in n/a</t>
   </si>
   <si>
     <t>Not executed</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:39 IST — skip in phone-only search</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:39 IST — pass in 23.3s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:39 IST — pass in 22.2s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:39 IST — pass in 22.5s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:39 IST — pass in 21.7s</t>
-  </si>
-  <si>
-    <t>TC_CUST_FUNC_124.png</t>
-  </si>
-  <si>
-    <t>TC_CUST_FUNC_125.png</t>
-  </si>
-  <si>
-    <t>TC_CUST_FUNC_126.png</t>
-  </si>
-  <si>
-    <t>2026-06-20 11:38 IST — pass in 18.4s</t>
-  </si>
-  <si>
-    <t>ADM_CUST_021.png</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:42 IST — pass in 21.6s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:42 IST — pass in 21.2s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:42 IST — pass in 22.3s</t>
-  </si>
-  <si>
-    <t>2026-06-20 11:38 IST — pass in 18.0s</t>
-  </si>
-  <si>
-    <t>TC_CUST_FUNC_130.png</t>
-  </si>
-  <si>
-    <t>2026-06-15 13:55 IST — pass in 18.4s</t>
-  </si>
-  <si>
-    <t>2026-06-15 13:55 IST — pass in 18.5s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:24 IST — pass in 22.7s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:20 IST — pass in 24.4s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:18 IST — pass in 25.7s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:23 IST — pass in 25.7s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:23 IST — skip in n/a</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:06 IST — pass in 23.5s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:16 IST — pass in 23.9s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:16 IST — pass in 19.8s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:06 IST — pass in 23.8s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:16 IST — pass in 20.8s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:06 IST — skip in n/a</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:06 IST — pass in 25.5s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:16 IST — pass in 19.6s</t>
-  </si>
-  <si>
-    <t>2026-06-15 13:55 IST — pass in 18.3s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:25 IST — pass in 21.7s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:24 IST — skip in n/a</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:20 IST — pass in 25.2s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:20 IST — pass in 25.0s</t>
-  </si>
-  <si>
-    <t>2026-06-15 16:20 IST — pass in 24.9s</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:18 IST — skip in n/a</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:45 IST — pass in 26.9s</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:45 IST — pass in 24.5s</t>
-  </si>
-  <si>
-    <t>2026-06-15 00:32 IST — pass in 5.1s</t>
-  </si>
-  <si>
-    <t>2026-06-15 00:33 IST — pass in 3.2s</t>
-  </si>
-  <si>
-    <t>2026-06-15 00:33 IST — skip in n/a</t>
   </si>
   <si>
     <t>2026-06-15 00:33 IST — pass in 4.3s</t>
@@ -19434,7 +19605,6 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>46</v>
@@ -20311,9 +20481,15 @@
       <c r="I35" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="J35" s="12"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
+      <c r="J35" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="36" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
@@ -20339,9 +20515,15 @@
       <c r="I36" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
+      <c r="J36" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="37" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
@@ -20367,9 +20549,15 @@
       <c r="I37" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="J37" s="12"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
+      <c r="J37" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="38" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
@@ -20395,9 +20583,15 @@
       <c r="I38" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="J38" s="12"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
+      <c r="J38" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -20443,9 +20637,15 @@
       <c r="I40" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="J40" s="12"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
+      <c r="J40" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
@@ -20471,9 +20671,15 @@
       <c r="I41" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="J41" s="12"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
+      <c r="J41" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="42" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
@@ -20499,9 +20705,15 @@
       <c r="I42" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="J42" s="12"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
+      <c r="J42" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="43" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20527,9 +20739,15 @@
       <c r="I43" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="J43" s="12"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
+      <c r="J43" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="44" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
@@ -20555,9 +20773,15 @@
       <c r="I44" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="J44" s="12"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
+      <c r="J44" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="45" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
@@ -20739,9 +20963,15 @@
       <c r="I50" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
+      <c r="J50" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="51" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
@@ -20767,9 +20997,15 @@
       <c r="I51" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="J51" s="12"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
+      <c r="J51" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="52" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
@@ -20795,9 +21031,15 @@
       <c r="I52" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="J52" s="12"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
+      <c r="J52" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="53" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
@@ -20877,9 +21119,15 @@
       <c r="I55" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="J55" s="12"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
+      <c r="J55" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L55" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
@@ -20925,9 +21173,15 @@
       <c r="I57" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="J57" s="12"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
+      <c r="J57" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="58" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
@@ -20953,9 +21207,15 @@
       <c r="I58" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="J58" s="12"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
+      <c r="J58" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L58" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="59" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
@@ -20981,9 +21241,15 @@
       <c r="I59" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="J59" s="12"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
+      <c r="J59" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="60" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
@@ -21009,9 +21275,15 @@
       <c r="I60" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="J60" s="12"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
+      <c r="J60" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K60" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L60" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
@@ -21057,9 +21329,15 @@
       <c r="I62" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="J62" s="12"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13"/>
+      <c r="J62" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L62" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="63" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
@@ -21085,9 +21363,15 @@
       <c r="I63" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="J63" s="12"/>
-      <c r="K63" s="13"/>
-      <c r="L63" s="13"/>
+      <c r="J63" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L63" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="64" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
@@ -21161,9 +21445,15 @@
       <c r="I66" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="J66" s="12"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
+      <c r="J66" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K66" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L66" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="67" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
@@ -21189,9 +21479,15 @@
       <c r="I67" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="J67" s="12"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="13"/>
+      <c r="J67" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K67" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L67" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="68" ht="89.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
@@ -21217,9 +21513,15 @@
       <c r="I68" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="J68" s="12"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
+      <c r="J68" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K68" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L68" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="69" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
@@ -21245,9 +21547,15 @@
       <c r="I69" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="J69" s="12"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
+      <c r="J69" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L69" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="70" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
@@ -21273,9 +21581,15 @@
       <c r="I70" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="J70" s="12"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
+      <c r="J70" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K70" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L70" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="71" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
@@ -21301,9 +21615,15 @@
       <c r="I71" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="J71" s="12"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
+      <c r="J71" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K71" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L71" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="72" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
@@ -21329,9 +21649,15 @@
       <c r="I72" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="J72" s="12"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
+      <c r="J72" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L72" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="73" ht="89.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
@@ -21357,9 +21683,15 @@
       <c r="I73" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="J73" s="12"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
+      <c r="J73" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L73" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="74" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
@@ -21413,9 +21745,15 @@
       <c r="I75" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="J75" s="12"/>
-      <c r="K75" s="13"/>
-      <c r="L75" s="13"/>
+      <c r="J75" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L75" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
@@ -21461,9 +21799,15 @@
       <c r="I77" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="J77" s="12"/>
-      <c r="K77" s="13"/>
-      <c r="L77" s="13"/>
+      <c r="J77" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K77" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L77" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="78" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
@@ -21489,9 +21833,15 @@
       <c r="I78" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="J78" s="12"/>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13"/>
+      <c r="J78" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L78" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="79" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
@@ -21517,9 +21867,15 @@
       <c r="I79" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="J79" s="12"/>
-      <c r="K79" s="13"/>
-      <c r="L79" s="13"/>
+      <c r="J79" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K79" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L79" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="80" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
@@ -21545,9 +21901,15 @@
       <c r="I80" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="J80" s="12"/>
-      <c r="K80" s="13"/>
-      <c r="L80" s="13"/>
+      <c r="J80" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K80" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L80" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="81" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21573,9 +21935,15 @@
       <c r="I81" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="J81" s="12"/>
-      <c r="K81" s="13"/>
-      <c r="L81" s="13"/>
+      <c r="J81" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K81" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L81" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="82" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
@@ -21601,9 +21969,15 @@
       <c r="I82" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="J82" s="12"/>
-      <c r="K82" s="13"/>
-      <c r="L82" s="13"/>
+      <c r="J82" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K82" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L82" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="83" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
@@ -21629,9 +22003,15 @@
       <c r="I83" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="J83" s="12"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
+      <c r="J83" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L83" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="84" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
@@ -21657,9 +22037,15 @@
       <c r="I84" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="J84" s="12"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="13"/>
+      <c r="J84" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L84" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="85" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
@@ -21685,9 +22071,15 @@
       <c r="I85" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="J85" s="12"/>
-      <c r="K85" s="13"/>
-      <c r="L85" s="13"/>
+      <c r="J85" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K85" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L85" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="86" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
@@ -21741,9 +22133,15 @@
       <c r="I87" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="J87" s="12"/>
-      <c r="K87" s="13"/>
-      <c r="L87" s="13"/>
+      <c r="J87" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L87" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
@@ -21789,9 +22187,15 @@
       <c r="I89" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="J89" s="12"/>
-      <c r="K89" s="13"/>
-      <c r="L89" s="13"/>
+      <c r="J89" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L89" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="90" ht="89.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
@@ -21817,9 +22221,15 @@
       <c r="I90" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="J90" s="12"/>
-      <c r="K90" s="13"/>
-      <c r="L90" s="13"/>
+      <c r="J90" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L90" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="91" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
@@ -21845,9 +22255,15 @@
       <c r="I91" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="J91" s="12"/>
-      <c r="K91" s="13"/>
-      <c r="L91" s="13"/>
+      <c r="J91" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K91" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L91" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
@@ -22109,9 +22525,15 @@
       <c r="I101" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="J101" s="12"/>
-      <c r="K101" s="13"/>
-      <c r="L101" s="13"/>
+      <c r="J101" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K101" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="102" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
@@ -22137,9 +22559,15 @@
       <c r="I102" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="J102" s="12"/>
-      <c r="K102" s="13"/>
-      <c r="L102" s="13"/>
+      <c r="J102" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K102" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L102" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="103" ht="102" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
@@ -22165,9 +22593,15 @@
       <c r="I103" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="J103" s="12"/>
-      <c r="K103" s="13"/>
-      <c r="L103" s="13"/>
+      <c r="J103" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K103" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L103" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="104" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
@@ -22193,9 +22627,15 @@
       <c r="I104" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="J104" s="12"/>
-      <c r="K104" s="13"/>
-      <c r="L104" s="13"/>
+      <c r="J104" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K104" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L104" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="105" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
@@ -22221,9 +22661,15 @@
       <c r="I105" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="J105" s="12"/>
-      <c r="K105" s="13"/>
-      <c r="L105" s="13"/>
+      <c r="J105" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L105" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="106" ht="102" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
@@ -22277,9 +22723,15 @@
       <c r="I107" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="J107" s="12"/>
-      <c r="K107" s="13"/>
-      <c r="L107" s="13"/>
+      <c r="J107" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K107" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L107" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="108" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
@@ -22305,9 +22757,15 @@
       <c r="I108" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="J108" s="12"/>
-      <c r="K108" s="13"/>
-      <c r="L108" s="13"/>
+      <c r="J108" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K108" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L108" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="109" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
@@ -22333,9 +22791,15 @@
       <c r="I109" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="J109" s="12"/>
-      <c r="K109" s="13"/>
-      <c r="L109" s="13"/>
+      <c r="J109" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K109" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L109" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
@@ -22381,9 +22845,15 @@
       <c r="I111" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="J111" s="12"/>
-      <c r="K111" s="13"/>
-      <c r="L111" s="13"/>
+      <c r="J111" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K111" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L111" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="112" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
@@ -22409,9 +22879,15 @@
       <c r="I112" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="J112" s="12"/>
-      <c r="K112" s="13"/>
-      <c r="L112" s="13"/>
+      <c r="J112" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K112" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L112" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="113" ht="89.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
@@ -22437,9 +22913,15 @@
       <c r="I113" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="J113" s="12"/>
-      <c r="K113" s="13"/>
-      <c r="L113" s="13"/>
+      <c r="J113" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K113" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L113" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="114" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
@@ -22465,9 +22947,15 @@
       <c r="I114" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="J114" s="12"/>
-      <c r="K114" s="13"/>
-      <c r="L114" s="13"/>
+      <c r="J114" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K114" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L114" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="115" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
@@ -22493,9 +22981,15 @@
       <c r="I115" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="J115" s="12"/>
-      <c r="K115" s="13"/>
-      <c r="L115" s="13"/>
+      <c r="J115" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K115" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L115" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="116" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
@@ -22521,9 +23015,15 @@
       <c r="I116" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="J116" s="12"/>
-      <c r="K116" s="13"/>
-      <c r="L116" s="13"/>
+      <c r="J116" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K116" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L116" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="117" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
@@ -22549,9 +23049,15 @@
       <c r="I117" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="J117" s="12"/>
-      <c r="K117" s="13"/>
-      <c r="L117" s="13"/>
+      <c r="J117" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K117" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L117" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="118" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
@@ -22577,9 +23083,15 @@
       <c r="I118" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="J118" s="12"/>
-      <c r="K118" s="13"/>
-      <c r="L118" s="13"/>
+      <c r="J118" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K118" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L118" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="119" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
@@ -22605,9 +23117,15 @@
       <c r="I119" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="J119" s="12"/>
-      <c r="K119" s="13"/>
-      <c r="L119" s="13"/>
+      <c r="J119" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K119" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L119" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="120" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
@@ -22633,9 +23151,15 @@
       <c r="I120" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="J120" s="12"/>
-      <c r="K120" s="13"/>
-      <c r="L120" s="13"/>
+      <c r="J120" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K120" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L120" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="121" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
@@ -22661,9 +23185,15 @@
       <c r="I121" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="J121" s="12"/>
-      <c r="K121" s="13"/>
-      <c r="L121" s="13"/>
+      <c r="J121" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K121" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L121" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
@@ -22709,9 +23239,15 @@
       <c r="I123" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="J123" s="12"/>
-      <c r="K123" s="13"/>
-      <c r="L123" s="13"/>
+      <c r="J123" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K123" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L123" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="124" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
@@ -22737,9 +23273,15 @@
       <c r="I124" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="J124" s="12"/>
-      <c r="K124" s="13"/>
-      <c r="L124" s="13"/>
+      <c r="J124" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K124" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L124" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="125" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
@@ -22765,9 +23307,15 @@
       <c r="I125" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="J125" s="12"/>
-      <c r="K125" s="13"/>
-      <c r="L125" s="13"/>
+      <c r="J125" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K125" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L125" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="126" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
@@ -22793,9 +23341,15 @@
       <c r="I126" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="J126" s="12"/>
-      <c r="K126" s="13"/>
-      <c r="L126" s="13"/>
+      <c r="J126" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K126" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L126" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="127" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
@@ -22821,9 +23375,15 @@
       <c r="I127" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="J127" s="12"/>
-      <c r="K127" s="13"/>
-      <c r="L127" s="13"/>
+      <c r="J127" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K127" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L127" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="128" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
@@ -22849,9 +23409,15 @@
       <c r="I128" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="J128" s="12"/>
-      <c r="K128" s="13"/>
-      <c r="L128" s="13"/>
+      <c r="J128" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K128" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L128" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="129" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
@@ -22877,9 +23443,15 @@
       <c r="I129" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="J129" s="12"/>
-      <c r="K129" s="13"/>
-      <c r="L129" s="13"/>
+      <c r="J129" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K129" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L129" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="130" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
@@ -22905,9 +23477,15 @@
       <c r="I130" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="J130" s="12"/>
-      <c r="K130" s="13"/>
-      <c r="L130" s="13"/>
+      <c r="J130" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K130" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L130" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="131" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
@@ -22933,9 +23511,15 @@
       <c r="I131" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="J131" s="12"/>
-      <c r="K131" s="13"/>
-      <c r="L131" s="13"/>
+      <c r="J131" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K131" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L131" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="132" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
@@ -22961,9 +23545,15 @@
       <c r="I132" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="J132" s="12"/>
-      <c r="K132" s="13"/>
-      <c r="L132" s="13"/>
+      <c r="J132" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K132" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L132" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="133" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
@@ -23065,9 +23655,15 @@
       <c r="I136" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="J136" s="12"/>
-      <c r="K136" s="13"/>
-      <c r="L136" s="13"/>
+      <c r="J136" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K136" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L136" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="137" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
@@ -23093,9 +23689,15 @@
       <c r="I137" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="J137" s="12"/>
-      <c r="K137" s="13"/>
-      <c r="L137" s="13"/>
+      <c r="J137" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K137" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L137" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="138" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
@@ -23121,9 +23723,15 @@
       <c r="I138" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="J138" s="12"/>
-      <c r="K138" s="13"/>
-      <c r="L138" s="13"/>
+      <c r="J138" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K138" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L138" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="139" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
@@ -23281,9 +23889,15 @@
       <c r="I144" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="J144" s="12"/>
-      <c r="K144" s="13"/>
-      <c r="L144" s="13"/>
+      <c r="J144" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K144" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L144" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="145" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
@@ -23385,9 +23999,15 @@
       <c r="I148" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="J148" s="12"/>
-      <c r="K148" s="13"/>
-      <c r="L148" s="13"/>
+      <c r="J148" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K148" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L148" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -33358,13 +33978,13 @@
         <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>5783</v>
+        <v>5776</v>
       </c>
       <c r="F21" t="s">
         <v>66</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>5784</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -33381,13 +34001,13 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5776</v>
+        <v>5759</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>5785</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -33395,22 +34015,22 @@
         <v>174</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>5785</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -33418,22 +34038,22 @@
         <v>181</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>5786</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>5787</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -33450,13 +34070,13 @@
         <v>161</v>
       </c>
       <c r="E25" t="s">
-        <v>5786</v>
+        <v>5781</v>
       </c>
       <c r="F25" t="s">
-        <v>5787</v>
-      </c>
-      <c r="G25" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>5788</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -33473,13 +34093,13 @@
         <v>161</v>
       </c>
       <c r="E26" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="F26" t="s">
-        <v>5787</v>
-      </c>
-      <c r="G26" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>5790</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -33496,13 +34116,13 @@
         <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>5789</v>
+        <v>5778</v>
       </c>
       <c r="F27" t="s">
         <v>66</v>
       </c>
-      <c r="G27" t="s">
-        <v>24</v>
+      <c r="G27" s="20" t="s">
+        <v>5791</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -33519,13 +34139,13 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5789</v>
+        <v>5778</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
       </c>
-      <c r="G28" t="s">
-        <v>24</v>
+      <c r="G28" s="20" t="s">
+        <v>5792</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -33542,13 +34162,13 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5790</v>
+        <v>5793</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
       </c>
-      <c r="G29" t="s">
-        <v>24</v>
+      <c r="G29" s="20" t="s">
+        <v>5794</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -33565,13 +34185,13 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5791</v>
+        <v>5795</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
       </c>
-      <c r="G30" t="s">
-        <v>24</v>
+      <c r="G30" s="20" t="s">
+        <v>5796</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -33588,13 +34208,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>5792</v>
+        <v>5797</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
-      <c r="G31" t="s">
-        <v>24</v>
+      <c r="G31" s="20" t="s">
+        <v>5798</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -33611,13 +34231,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5755</v>
+        <v>5759</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>5793</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -33634,13 +34254,13 @@
         <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>5776</v>
+        <v>5759</v>
       </c>
       <c r="F33" t="s">
         <v>66</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>5794</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -33657,13 +34277,13 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5776</v>
+        <v>5801</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>5795</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -33680,13 +34300,13 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5796</v>
+        <v>5759</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>5797</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -33703,13 +34323,13 @@
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>5798</v>
+        <v>5801</v>
       </c>
       <c r="F36" t="s">
         <v>66</v>
       </c>
-      <c r="G36" t="s">
-        <v>24</v>
+      <c r="G36" s="20" t="s">
+        <v>5804</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -33726,13 +34346,13 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5799</v>
+        <v>5786</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
       </c>
-      <c r="G37" t="s">
-        <v>24</v>
+      <c r="G37" s="20" t="s">
+        <v>5805</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -33749,13 +34369,13 @@
         <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="F38" t="s">
         <v>66</v>
       </c>
-      <c r="G38" t="s">
-        <v>24</v>
+      <c r="G38" s="20" t="s">
+        <v>5806</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -33772,13 +34392,13 @@
         <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>5801</v>
+        <v>5807</v>
       </c>
       <c r="F39" t="s">
         <v>66</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>5802</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -33795,13 +34415,13 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5803</v>
+        <v>5801</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
       </c>
-      <c r="G40" t="s">
-        <v>24</v>
+      <c r="G40" s="20" t="s">
+        <v>5809</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -33818,13 +34438,13 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5804</v>
+        <v>5810</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
       </c>
-      <c r="G41" t="s">
-        <v>24</v>
+      <c r="G41" s="20" t="s">
+        <v>5811</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -33841,13 +34461,13 @@
         <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>5805</v>
+        <v>5764</v>
       </c>
       <c r="F42" t="s">
         <v>66</v>
       </c>
-      <c r="G42" t="s">
-        <v>24</v>
+      <c r="G42" s="20" t="s">
+        <v>5812</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -33864,13 +34484,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>5806</v>
+        <v>5813</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
-      <c r="G43" t="s">
-        <v>24</v>
+      <c r="G43" s="20" t="s">
+        <v>5814</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -33887,13 +34507,13 @@
         <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>5807</v>
+        <v>5815</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
-      <c r="G44" t="s">
-        <v>24</v>
+      <c r="G44" s="20" t="s">
+        <v>5816</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -33901,22 +34521,22 @@
         <v>293</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D45" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="E45" t="s">
-        <v>5808</v>
+        <v>5817</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>5818</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -33933,10 +34553,10 @@
         <v>161</v>
       </c>
       <c r="E46" t="s">
-        <v>5809</v>
+        <v>5781</v>
       </c>
       <c r="F46" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
@@ -33947,19 +34567,19 @@
         <v>304</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>5823</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
@@ -33979,13 +34599,13 @@
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>5810</v>
+        <v>5824</v>
       </c>
       <c r="F48" t="s">
         <v>66</v>
       </c>
-      <c r="G48" t="s">
-        <v>24</v>
+      <c r="G48" s="20" t="s">
+        <v>5825</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -34002,13 +34622,13 @@
         <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>5811</v>
+        <v>5813</v>
       </c>
       <c r="F49" t="s">
         <v>66</v>
       </c>
-      <c r="G49" t="s">
-        <v>24</v>
+      <c r="G49" s="20" t="s">
+        <v>5826</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -34025,13 +34645,13 @@
         <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>5812</v>
+        <v>5764</v>
       </c>
       <c r="F50" t="s">
         <v>66</v>
       </c>
-      <c r="G50" t="s">
-        <v>24</v>
+      <c r="G50" s="20" t="s">
+        <v>5827</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -34048,13 +34668,13 @@
         <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>5813</v>
+        <v>5828</v>
       </c>
       <c r="F51" t="s">
         <v>66</v>
       </c>
-      <c r="G51" t="s">
-        <v>24</v>
+      <c r="G51" s="20" t="s">
+        <v>5829</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -34062,19 +34682,19 @@
         <v>333</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
@@ -34085,19 +34705,19 @@
         <v>338</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F53" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G53" t="s">
         <v>24</v>
@@ -34108,19 +34728,19 @@
         <v>343</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C54" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F54" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G54" t="s">
         <v>24</v>
@@ -34131,19 +34751,19 @@
         <v>349</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G55" t="s">
         <v>24</v>
@@ -34154,19 +34774,19 @@
         <v>355</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>5753</v>
+        <v>5830</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E56" t="s">
-        <v>24</v>
+        <v>5831</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>5832</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -34186,13 +34806,13 @@
         <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>5814</v>
+        <v>5778</v>
       </c>
       <c r="F57" t="s">
         <v>66</v>
       </c>
-      <c r="G57" t="s">
-        <v>24</v>
+      <c r="G57" s="20" t="s">
+        <v>5833</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -34200,19 +34820,19 @@
         <v>366</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>5834</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -34232,10 +34852,10 @@
         <v>161</v>
       </c>
       <c r="E59" t="s">
-        <v>5815</v>
+        <v>5781</v>
       </c>
       <c r="F59" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G59" t="s">
         <v>24</v>
@@ -34255,13 +34875,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5816</v>
+        <v>5835</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
-      <c r="G60" t="s">
-        <v>24</v>
+      <c r="G60" s="20" t="s">
+        <v>5836</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -34278,13 +34898,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5813</v>
+        <v>5837</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
-      <c r="G61" t="s">
-        <v>24</v>
+      <c r="G61" s="20" t="s">
+        <v>5838</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -34292,19 +34912,19 @@
         <v>386</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -34324,10 +34944,10 @@
         <v>161</v>
       </c>
       <c r="E63" t="s">
-        <v>5815</v>
+        <v>5781</v>
       </c>
       <c r="F63" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -34338,19 +34958,19 @@
         <v>396</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -34361,19 +34981,19 @@
         <v>402</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F65" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>24</v>
@@ -34384,19 +35004,19 @@
         <v>407</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E66" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F66" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
         <v>24</v>
@@ -34407,19 +35027,19 @@
         <v>411</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E67" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>5839</v>
       </c>
       <c r="G67" t="s">
         <v>24</v>
@@ -34439,13 +35059,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>5817</v>
+        <v>5778</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
-      <c r="G68" t="s">
-        <v>24</v>
+      <c r="G68" s="20" t="s">
+        <v>5840</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -34462,13 +35082,13 @@
         <v>67</v>
       </c>
       <c r="E69" t="s">
-        <v>5818</v>
+        <v>5776</v>
       </c>
       <c r="F69" t="s">
         <v>66</v>
       </c>
-      <c r="G69" t="s">
-        <v>24</v>
+      <c r="G69" s="20" t="s">
+        <v>5841</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -34476,22 +35096,22 @@
         <v>427</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E70" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>5842</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -34508,13 +35128,13 @@
         <v>67</v>
       </c>
       <c r="E71" t="s">
-        <v>5819</v>
+        <v>5795</v>
       </c>
       <c r="F71" t="s">
         <v>66</v>
       </c>
-      <c r="G71" t="s">
-        <v>24</v>
+      <c r="G71" s="20" t="s">
+        <v>5843</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -34522,19 +35142,19 @@
         <v>440</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E72" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
+        <v>5844</v>
       </c>
       <c r="G72" t="s">
         <v>24</v>
@@ -34545,19 +35165,19 @@
         <v>447</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E73" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F73" t="s">
-        <v>24</v>
+        <v>5845</v>
       </c>
       <c r="G73" t="s">
         <v>24</v>
@@ -34568,19 +35188,19 @@
         <v>453</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E74" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>5846</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -34591,19 +35211,19 @@
         <v>459</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F75" t="s">
-        <v>24</v>
+        <v>5847</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>
@@ -34614,19 +35234,19 @@
         <v>465</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>5754</v>
+        <v>5848</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>5849</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
+        <v>5850</v>
       </c>
       <c r="G76" t="s">
         <v>24</v>
@@ -34637,19 +35257,19 @@
         <v>471</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5753</v>
+        <v>5851</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E77" t="s">
-        <v>24</v>
+        <v>5852</v>
       </c>
       <c r="F77" t="s">
-        <v>24</v>
+        <v>5853</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -34660,19 +35280,19 @@
         <v>477</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5753</v>
+        <v>5851</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E78" t="s">
-        <v>24</v>
+        <v>5852</v>
       </c>
       <c r="F78" t="s">
-        <v>24</v>
+        <v>5854</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -34692,10 +35312,10 @@
         <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F79" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G79" t="s">
         <v>24</v>
@@ -34715,10 +35335,10 @@
         <v>161</v>
       </c>
       <c r="E80" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F80" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G80" t="s">
         <v>24</v>
@@ -34738,10 +35358,10 @@
         <v>161</v>
       </c>
       <c r="E81" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F81" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G81" t="s">
         <v>24</v>
@@ -34761,10 +35381,10 @@
         <v>161</v>
       </c>
       <c r="E82" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F82" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G82" t="s">
         <v>24</v>
@@ -34784,10 +35404,10 @@
         <v>161</v>
       </c>
       <c r="E83" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F83" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G83" t="s">
         <v>24</v>
@@ -34798,19 +35418,19 @@
         <v>510</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>5754</v>
+        <v>5848</v>
       </c>
       <c r="D84" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E84" t="s">
-        <v>24</v>
+        <v>5849</v>
       </c>
       <c r="F84" t="s">
-        <v>24</v>
+        <v>5855</v>
       </c>
       <c r="G84" t="s">
         <v>24</v>
@@ -34830,10 +35450,10 @@
         <v>161</v>
       </c>
       <c r="E85" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F85" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G85" t="s">
         <v>24</v>
@@ -34853,10 +35473,10 @@
         <v>161</v>
       </c>
       <c r="E86" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F86" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G86" t="s">
         <v>24</v>
@@ -34876,10 +35496,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5820</v>
+        <v>5781</v>
       </c>
       <c r="F87" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>
@@ -34899,13 +35519,13 @@
         <v>67</v>
       </c>
       <c r="E88" t="s">
-        <v>5821</v>
+        <v>5815</v>
       </c>
       <c r="F88" t="s">
         <v>66</v>
       </c>
-      <c r="G88" t="s">
-        <v>24</v>
+      <c r="G88" s="20" t="s">
+        <v>5856</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -34922,13 +35542,13 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>5822</v>
+        <v>5835</v>
       </c>
       <c r="F89" t="s">
         <v>66</v>
       </c>
-      <c r="G89" t="s">
-        <v>24</v>
+      <c r="G89" s="20" t="s">
+        <v>5857</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -34945,13 +35565,13 @@
         <v>67</v>
       </c>
       <c r="E90" t="s">
-        <v>5823</v>
+        <v>5815</v>
       </c>
       <c r="F90" t="s">
         <v>66</v>
       </c>
-      <c r="G90" t="s">
-        <v>24</v>
+      <c r="G90" s="20" t="s">
+        <v>5858</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -34968,13 +35588,13 @@
         <v>67</v>
       </c>
       <c r="E91" t="s">
-        <v>5823</v>
+        <v>5815</v>
       </c>
       <c r="F91" t="s">
         <v>66</v>
       </c>
-      <c r="G91" t="s">
-        <v>24</v>
+      <c r="G91" s="20" t="s">
+        <v>5859</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -34982,19 +35602,19 @@
         <v>554</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C92" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E92" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F92" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G92" t="s">
         <v>24</v>
@@ -35005,22 +35625,22 @@
         <v>559</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C93" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D93" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>24</v>
+        <v>5815</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
-      </c>
-      <c r="G93" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>5860</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35028,22 +35648,22 @@
         <v>564</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C94" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>24</v>
+        <v>5861</v>
       </c>
       <c r="F94" t="s">
-        <v>24</v>
-      </c>
-      <c r="G94" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G94" s="20" t="s">
+        <v>5862</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35051,19 +35671,19 @@
         <v>570</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C95" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D95" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E95" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F95" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G95" t="s">
         <v>24</v>
@@ -35074,19 +35694,19 @@
         <v>575</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C96" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E96" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F96" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G96" t="s">
         <v>24</v>
@@ -35097,19 +35717,19 @@
         <v>581</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C97" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D97" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E97" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F97" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G97" t="s">
         <v>24</v>
@@ -35120,22 +35740,22 @@
         <v>586</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D98" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>24</v>
+        <v>5863</v>
       </c>
       <c r="F98" t="s">
-        <v>24</v>
-      </c>
-      <c r="G98" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>5864</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -35152,10 +35772,10 @@
         <v>161</v>
       </c>
       <c r="E99" t="s">
-        <v>5824</v>
+        <v>5781</v>
       </c>
       <c r="F99" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G99" t="s">
         <v>24</v>
@@ -35175,10 +35795,10 @@
         <v>161</v>
       </c>
       <c r="E100" t="s">
-        <v>5824</v>
+        <v>5781</v>
       </c>
       <c r="F100" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
@@ -35189,19 +35809,19 @@
         <v>604</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C101" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D101" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F101" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G101" t="s">
         <v>24</v>
@@ -35212,19 +35832,19 @@
         <v>610</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C102" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E102" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F102" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G102" t="s">
         <v>24</v>
@@ -35244,10 +35864,10 @@
         <v>161</v>
       </c>
       <c r="E103" t="s">
-        <v>5824</v>
+        <v>5781</v>
       </c>
       <c r="F103" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G103" t="s">
         <v>24</v>
@@ -35258,19 +35878,19 @@
         <v>622</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C104" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D104" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E104" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F104" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G104" t="s">
         <v>24</v>
@@ -35281,19 +35901,19 @@
         <v>628</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C105" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E105" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F105" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G105" t="s">
         <v>24</v>
@@ -35313,10 +35933,10 @@
         <v>161</v>
       </c>
       <c r="E106" t="s">
-        <v>5824</v>
+        <v>5781</v>
       </c>
       <c r="F106" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G106" t="s">
         <v>24</v>
@@ -35336,10 +35956,10 @@
         <v>161</v>
       </c>
       <c r="E107" t="s">
-        <v>5824</v>
+        <v>5781</v>
       </c>
       <c r="F107" t="s">
-        <v>5787</v>
+        <v>160</v>
       </c>
       <c r="G107" t="s">
         <v>24</v>
@@ -35350,19 +35970,19 @@
         <v>646</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D108" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E108" t="s">
-        <v>24</v>
+        <v>5781</v>
       </c>
       <c r="F108" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G108" t="s">
         <v>24</v>
@@ -35373,19 +35993,19 @@
         <v>650</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>5754</v>
+        <v>5820</v>
       </c>
       <c r="D109" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E109" t="s">
-        <v>24</v>
+        <v>5822</v>
       </c>
       <c r="F109" t="s">
-        <v>24</v>
+        <v>5865</v>
       </c>
       <c r="G109" t="s">
         <v>24</v>
@@ -35396,19 +36016,19 @@
         <v>655</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>5754</v>
+        <v>5830</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E110" t="s">
-        <v>24</v>
+        <v>5831</v>
       </c>
       <c r="F110" t="s">
-        <v>24</v>
+        <v>5866</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -35428,13 +36048,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>5818</v>
+        <v>5776</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
-      <c r="G111" t="s">
-        <v>24</v>
+      <c r="G111" s="20" t="s">
+        <v>5867</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -35451,13 +36071,13 @@
         <v>67</v>
       </c>
       <c r="E112" t="s">
-        <v>5825</v>
+        <v>5797</v>
       </c>
       <c r="F112" t="s">
         <v>66</v>
       </c>
-      <c r="G112" t="s">
-        <v>24</v>
+      <c r="G112" s="20" t="s">
+        <v>5868</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -35474,13 +36094,13 @@
         <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>5826</v>
+        <v>5795</v>
       </c>
       <c r="F113" t="s">
         <v>66</v>
       </c>
-      <c r="G113" t="s">
-        <v>24</v>
+      <c r="G113" s="20" t="s">
+        <v>5869</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -35488,19 +36108,19 @@
         <v>679</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5753</v>
+        <v>5870</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>5871</v>
       </c>
       <c r="E114" t="s">
-        <v>24</v>
+        <v>5872</v>
       </c>
       <c r="F114" t="s">
-        <v>24</v>
+        <v>5873</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -35511,19 +36131,19 @@
         <v>684</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>5753</v>
+        <v>5830</v>
       </c>
       <c r="D115" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E115" t="s">
-        <v>24</v>
+        <v>5831</v>
       </c>
       <c r="F115" t="s">
-        <v>24</v>
+        <v>5832</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -35534,19 +36154,19 @@
         <v>691</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>5753</v>
+        <v>5830</v>
       </c>
       <c r="D116" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E116" t="s">
-        <v>24</v>
+        <v>5831</v>
       </c>
       <c r="F116" t="s">
-        <v>24</v>
+        <v>5832</v>
       </c>
       <c r="G116" t="s">
         <v>24</v>
@@ -35557,19 +36177,19 @@
         <v>698</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5753</v>
+        <v>5874</v>
       </c>
       <c r="D117" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E117" t="s">
-        <v>24</v>
+        <v>5875</v>
       </c>
       <c r="F117" t="s">
-        <v>24</v>
+        <v>5876</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -35580,22 +36200,22 @@
         <v>703</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
       <c r="D118" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>24</v>
+        <v>5877</v>
       </c>
       <c r="F118" t="s">
-        <v>24</v>
-      </c>
-      <c r="G118" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G118" s="20" t="s">
+        <v>5878</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -35603,19 +36223,19 @@
         <v>709</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>5754</v>
+        <v>5830</v>
       </c>
       <c r="D119" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E119" t="s">
-        <v>24</v>
+        <v>5831</v>
       </c>
       <c r="F119" t="s">
-        <v>24</v>
+        <v>5879</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -35626,19 +36246,19 @@
         <v>715</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>5819</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>5754</v>
+        <v>5830</v>
       </c>
       <c r="D120" t="s">
-        <v>24</v>
+        <v>5821</v>
       </c>
       <c r="E120" t="s">
-        <v>24</v>
+        <v>5831</v>
       </c>
       <c r="F120" t="s">
-        <v>24</v>
+        <v>5880</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -35649,22 +36269,22 @@
         <v>722</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
       <c r="D121" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>24</v>
+        <v>5881</v>
       </c>
       <c r="F121" t="s">
-        <v>24</v>
-      </c>
-      <c r="G121" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G121" s="20" t="s">
+        <v>5882</v>
       </c>
     </row>
   </sheetData>
@@ -35690,11 +36310,52 @@
     <hyperlink ref="G20" r:id="rId19"/>
     <hyperlink ref="G21" r:id="rId20"/>
     <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G32" r:id="rId22"/>
-    <hyperlink ref="G33" r:id="rId23"/>
-    <hyperlink ref="G34" r:id="rId24"/>
-    <hyperlink ref="G35" r:id="rId25"/>
-    <hyperlink ref="G39" r:id="rId26"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
+    <hyperlink ref="G26" r:id="rId25"/>
+    <hyperlink ref="G27" r:id="rId26"/>
+    <hyperlink ref="G28" r:id="rId27"/>
+    <hyperlink ref="G29" r:id="rId28"/>
+    <hyperlink ref="G30" r:id="rId29"/>
+    <hyperlink ref="G31" r:id="rId30"/>
+    <hyperlink ref="G32" r:id="rId31"/>
+    <hyperlink ref="G33" r:id="rId32"/>
+    <hyperlink ref="G34" r:id="rId33"/>
+    <hyperlink ref="G35" r:id="rId34"/>
+    <hyperlink ref="G36" r:id="rId35"/>
+    <hyperlink ref="G37" r:id="rId36"/>
+    <hyperlink ref="G38" r:id="rId37"/>
+    <hyperlink ref="G39" r:id="rId38"/>
+    <hyperlink ref="G40" r:id="rId39"/>
+    <hyperlink ref="G41" r:id="rId40"/>
+    <hyperlink ref="G42" r:id="rId41"/>
+    <hyperlink ref="G43" r:id="rId42"/>
+    <hyperlink ref="G44" r:id="rId43"/>
+    <hyperlink ref="G45" r:id="rId44"/>
+    <hyperlink ref="G48" r:id="rId45"/>
+    <hyperlink ref="G49" r:id="rId46"/>
+    <hyperlink ref="G50" r:id="rId47"/>
+    <hyperlink ref="G51" r:id="rId48"/>
+    <hyperlink ref="G57" r:id="rId49"/>
+    <hyperlink ref="G60" r:id="rId50"/>
+    <hyperlink ref="G61" r:id="rId51"/>
+    <hyperlink ref="G68" r:id="rId52"/>
+    <hyperlink ref="G69" r:id="rId53"/>
+    <hyperlink ref="G70" r:id="rId54"/>
+    <hyperlink ref="G71" r:id="rId55"/>
+    <hyperlink ref="G88" r:id="rId56"/>
+    <hyperlink ref="G89" r:id="rId57"/>
+    <hyperlink ref="G90" r:id="rId58"/>
+    <hyperlink ref="G91" r:id="rId59"/>
+    <hyperlink ref="G93" r:id="rId60"/>
+    <hyperlink ref="G94" r:id="rId61"/>
+    <hyperlink ref="G98" r:id="rId62"/>
+    <hyperlink ref="G111" r:id="rId63"/>
+    <hyperlink ref="G112" r:id="rId64"/>
+    <hyperlink ref="G113" r:id="rId65"/>
+    <hyperlink ref="G118" r:id="rId66"/>
+    <hyperlink ref="G121" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -35752,7 +36413,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5827</v>
+        <v>5883</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -35798,7 +36459,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5828</v>
+        <v>5884</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -35844,10 +36505,10 @@
         <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>5829</v>
+        <v>5885</v>
       </c>
       <c r="F6" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -35867,10 +36528,10 @@
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>5829</v>
+        <v>5885</v>
       </c>
       <c r="F7" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -35890,10 +36551,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5829</v>
+        <v>5885</v>
       </c>
       <c r="F8" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -35913,10 +36574,10 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>5829</v>
+        <v>5885</v>
       </c>
       <c r="F9" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -35936,7 +36597,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5830</v>
+        <v>5887</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36005,10 +36666,10 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>5829</v>
+        <v>5885</v>
       </c>
       <c r="F13" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -36143,7 +36804,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5831</v>
+        <v>5888</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -36212,7 +36873,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5832</v>
+        <v>5889</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -36350,7 +37011,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5833</v>
+        <v>5890</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -36373,7 +37034,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5834</v>
+        <v>5891</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -36396,7 +37057,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5835</v>
+        <v>5892</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -36442,7 +37103,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5836</v>
+        <v>5893</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -36488,7 +37149,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5837</v>
+        <v>5894</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -36511,7 +37172,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5838</v>
+        <v>5895</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -36557,7 +37218,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5837</v>
+        <v>5894</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -36626,7 +37287,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5839</v>
+        <v>5896</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -36649,7 +37310,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5840</v>
+        <v>5897</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -36810,10 +37471,10 @@
         <v>161</v>
       </c>
       <c r="E48" t="s">
-        <v>5841</v>
+        <v>5898</v>
       </c>
       <c r="F48" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -36833,10 +37494,10 @@
         <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>5842</v>
+        <v>5899</v>
       </c>
       <c r="F49" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37017,10 +37678,10 @@
         <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>5841</v>
+        <v>5898</v>
       </c>
       <c r="F57" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37109,10 +37770,10 @@
         <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>5843</v>
+        <v>5900</v>
       </c>
       <c r="F61" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37132,10 +37793,10 @@
         <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>5844</v>
+        <v>5901</v>
       </c>
       <c r="F62" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -37155,7 +37816,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5845</v>
+        <v>5902</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -37178,10 +37839,10 @@
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>5841</v>
+        <v>5898</v>
       </c>
       <c r="F64" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -37293,10 +37954,10 @@
         <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>5841</v>
+        <v>5898</v>
       </c>
       <c r="F69" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -37316,7 +37977,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5846</v>
+        <v>5903</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -37684,7 +38345,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5847</v>
+        <v>5904</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -37707,10 +38368,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5848</v>
+        <v>5905</v>
       </c>
       <c r="F87" t="s">
-        <v>5787</v>
+        <v>5886</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17245" uniqueCount="5906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17251" uniqueCount="5917">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18826,13 +18826,10 @@
     <t>Reject 2nd unit when already booked — requires a fixture with an active booking + user OK</t>
   </si>
   <si>
-    <t>Blocked — Milestones POM</t>
-  </si>
-  <si>
-    <t>[POM] not run as live e2e</t>
-  </si>
-  <si>
-    <t>Payment-proof upload validation — needs Milestones page POM (separate page), not yet built</t>
+    <t>2026-06-20 18:19 IST — pass in 33.3s</t>
+  </si>
+  <si>
+    <t>TC_CUST_VAL_120.png</t>
   </si>
   <si>
     <t>Integration (provider stub)</t>
@@ -18847,7 +18844,43 @@
     <t>WhatsApp dispatch — needs provider stub, out of e2e scope</t>
   </si>
   <si>
-    <t>Offline Payment form (Principal/GST/Milestone summary) — needs Milestones POM, not yet built</t>
+    <t>2026-06-20 18:19 IST — pass in 17.6s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_051.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 18:19 IST — pass in 17.7s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_052.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 18:19 IST — pass in 17.5s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_053.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_054.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_055.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 18:19 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_127.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_056.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 18:19 IST — pass in 17.4s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_057.png</t>
   </si>
   <si>
     <t>TC_CUST_FUNC_061.png</t>
@@ -19605,6 +19638,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>46</v>
@@ -22421,9 +22455,15 @@
       <c r="I97" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="J97" s="12"/>
-      <c r="K97" s="13"/>
-      <c r="L97" s="13"/>
+      <c r="J97" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K97" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L97" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="98" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
@@ -22526,10 +22566,10 @@
         <v>489</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K101" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L101" s="13" t="s">
         <v>68</v>
@@ -22560,10 +22600,10 @@
         <v>494</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K102" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L102" s="13" t="s">
         <v>68</v>
@@ -22594,10 +22634,10 @@
         <v>499</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L103" s="13" t="s">
         <v>68</v>
@@ -22628,10 +22668,10 @@
         <v>504</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L104" s="13" t="s">
         <v>68</v>
@@ -22662,10 +22702,10 @@
         <v>509</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L105" s="13" t="s">
         <v>68</v>
@@ -22695,9 +22735,15 @@
       <c r="I106" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="J106" s="12"/>
-      <c r="K106" s="13"/>
-      <c r="L106" s="13"/>
+      <c r="J106" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K106" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L106" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="107" ht="38.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
@@ -22724,10 +22770,10 @@
         <v>520</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L107" s="13" t="s">
         <v>68</v>
@@ -22758,10 +22804,10 @@
         <v>525</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L108" s="13" t="s">
         <v>68</v>
@@ -35234,22 +35280,22 @@
         <v>465</v>
       </c>
       <c r="B76" t="s">
-        <v>5819</v>
+        <v>67</v>
       </c>
       <c r="C76" s="19" t="s">
+        <v>5753</v>
+      </c>
+      <c r="D76" t="s">
+        <v>67</v>
+      </c>
+      <c r="E76" t="s">
         <v>5848</v>
       </c>
-      <c r="D76" t="s">
-        <v>5821</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
+        <v>66</v>
+      </c>
+      <c r="G76" s="20" t="s">
         <v>5849</v>
-      </c>
-      <c r="F76" t="s">
-        <v>5850</v>
-      </c>
-      <c r="G76" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35260,16 +35306,16 @@
         <v>5819</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5851</v>
+        <v>5850</v>
       </c>
       <c r="D77" t="s">
         <v>5821</v>
       </c>
       <c r="E77" t="s">
+        <v>5851</v>
+      </c>
+      <c r="F77" t="s">
         <v>5852</v>
-      </c>
-      <c r="F77" t="s">
-        <v>5853</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35283,16 +35329,16 @@
         <v>5819</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5851</v>
+        <v>5850</v>
       </c>
       <c r="D78" t="s">
         <v>5821</v>
       </c>
       <c r="E78" t="s">
-        <v>5852</v>
+        <v>5851</v>
       </c>
       <c r="F78" t="s">
-        <v>5854</v>
+        <v>5853</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35303,22 +35349,22 @@
         <v>484</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D79" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5781</v>
+        <v>5854</v>
       </c>
       <c r="F79" t="s">
-        <v>160</v>
-      </c>
-      <c r="G79" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>5855</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35326,22 +35372,22 @@
         <v>490</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C80" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D80" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5781</v>
+        <v>5856</v>
       </c>
       <c r="F80" t="s">
-        <v>160</v>
-      </c>
-      <c r="G80" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G80" s="20" t="s">
+        <v>5857</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35349,22 +35395,22 @@
         <v>495</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D81" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5781</v>
+        <v>5858</v>
       </c>
       <c r="F81" t="s">
-        <v>160</v>
-      </c>
-      <c r="G81" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>5859</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35372,22 +35418,22 @@
         <v>500</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C82" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D82" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5781</v>
+        <v>5858</v>
       </c>
       <c r="F82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G82" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G82" s="20" t="s">
+        <v>5860</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35395,22 +35441,22 @@
         <v>505</v>
       </c>
       <c r="B83" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D83" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5781</v>
+        <v>5848</v>
       </c>
       <c r="F83" t="s">
-        <v>160</v>
-      </c>
-      <c r="G83" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>5861</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35418,22 +35464,22 @@
         <v>510</v>
       </c>
       <c r="B84" t="s">
-        <v>5819</v>
+        <v>161</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>5848</v>
+        <v>5753</v>
       </c>
       <c r="D84" t="s">
-        <v>5821</v>
+        <v>161</v>
       </c>
       <c r="E84" t="s">
-        <v>5849</v>
+        <v>5862</v>
       </c>
       <c r="F84" t="s">
-        <v>5855</v>
-      </c>
-      <c r="G84" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>5863</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35441,22 +35487,22 @@
         <v>516</v>
       </c>
       <c r="B85" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C85" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D85" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5781</v>
+        <v>5854</v>
       </c>
       <c r="F85" t="s">
-        <v>160</v>
-      </c>
-      <c r="G85" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>5864</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35464,22 +35510,22 @@
         <v>521</v>
       </c>
       <c r="B86" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C86" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D86" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5781</v>
+        <v>5865</v>
       </c>
       <c r="F86" t="s">
-        <v>160</v>
-      </c>
-      <c r="G86" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>5866</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35525,7 +35571,7 @@
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5856</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35548,7 +35594,7 @@
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5857</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35571,7 +35617,7 @@
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5858</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35594,7 +35640,7 @@
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5859</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35640,7 +35686,7 @@
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5860</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35657,13 +35703,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5861</v>
+        <v>5872</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5862</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35749,13 +35795,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5863</v>
+        <v>5874</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5864</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -36005,7 +36051,7 @@
         <v>5822</v>
       </c>
       <c r="F109" t="s">
-        <v>5865</v>
+        <v>5876</v>
       </c>
       <c r="G109" t="s">
         <v>24</v>
@@ -36028,7 +36074,7 @@
         <v>5831</v>
       </c>
       <c r="F110" t="s">
-        <v>5866</v>
+        <v>5877</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36054,7 +36100,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5867</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36077,7 +36123,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5868</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36100,7 +36146,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5869</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36111,16 +36157,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5870</v>
+        <v>5881</v>
       </c>
       <c r="D114" t="s">
-        <v>5871</v>
+        <v>5882</v>
       </c>
       <c r="E114" t="s">
-        <v>5872</v>
+        <v>5883</v>
       </c>
       <c r="F114" t="s">
-        <v>5873</v>
+        <v>5884</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36180,16 +36226,16 @@
         <v>5819</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5874</v>
+        <v>5885</v>
       </c>
       <c r="D117" t="s">
         <v>5821</v>
       </c>
       <c r="E117" t="s">
-        <v>5875</v>
+        <v>5886</v>
       </c>
       <c r="F117" t="s">
-        <v>5876</v>
+        <v>5887</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36209,13 +36255,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5877</v>
+        <v>5888</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5878</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36235,7 +36281,7 @@
         <v>5831</v>
       </c>
       <c r="F119" t="s">
-        <v>5879</v>
+        <v>5890</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36258,7 +36304,7 @@
         <v>5831</v>
       </c>
       <c r="F120" t="s">
-        <v>5880</v>
+        <v>5891</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36278,13 +36324,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5881</v>
+        <v>5892</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5882</v>
+        <v>5893</v>
       </c>
     </row>
   </sheetData>
@@ -36344,18 +36390,27 @@
     <hyperlink ref="G69" r:id="rId53"/>
     <hyperlink ref="G70" r:id="rId54"/>
     <hyperlink ref="G71" r:id="rId55"/>
-    <hyperlink ref="G88" r:id="rId56"/>
-    <hyperlink ref="G89" r:id="rId57"/>
-    <hyperlink ref="G90" r:id="rId58"/>
-    <hyperlink ref="G91" r:id="rId59"/>
-    <hyperlink ref="G93" r:id="rId60"/>
-    <hyperlink ref="G94" r:id="rId61"/>
-    <hyperlink ref="G98" r:id="rId62"/>
-    <hyperlink ref="G111" r:id="rId63"/>
-    <hyperlink ref="G112" r:id="rId64"/>
-    <hyperlink ref="G113" r:id="rId65"/>
-    <hyperlink ref="G118" r:id="rId66"/>
-    <hyperlink ref="G121" r:id="rId67"/>
+    <hyperlink ref="G76" r:id="rId56"/>
+    <hyperlink ref="G79" r:id="rId57"/>
+    <hyperlink ref="G80" r:id="rId58"/>
+    <hyperlink ref="G81" r:id="rId59"/>
+    <hyperlink ref="G82" r:id="rId60"/>
+    <hyperlink ref="G83" r:id="rId61"/>
+    <hyperlink ref="G84" r:id="rId62"/>
+    <hyperlink ref="G85" r:id="rId63"/>
+    <hyperlink ref="G86" r:id="rId64"/>
+    <hyperlink ref="G88" r:id="rId65"/>
+    <hyperlink ref="G89" r:id="rId66"/>
+    <hyperlink ref="G90" r:id="rId67"/>
+    <hyperlink ref="G91" r:id="rId68"/>
+    <hyperlink ref="G93" r:id="rId69"/>
+    <hyperlink ref="G94" r:id="rId70"/>
+    <hyperlink ref="G98" r:id="rId71"/>
+    <hyperlink ref="G111" r:id="rId72"/>
+    <hyperlink ref="G112" r:id="rId73"/>
+    <hyperlink ref="G113" r:id="rId74"/>
+    <hyperlink ref="G118" r:id="rId75"/>
+    <hyperlink ref="G121" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36413,7 +36468,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5883</v>
+        <v>5894</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36459,7 +36514,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5884</v>
+        <v>5895</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36505,10 +36560,10 @@
         <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>5885</v>
+        <v>5896</v>
       </c>
       <c r="F6" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36528,10 +36583,10 @@
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>5885</v>
+        <v>5896</v>
       </c>
       <c r="F7" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36551,10 +36606,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5885</v>
+        <v>5896</v>
       </c>
       <c r="F8" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36574,10 +36629,10 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>5885</v>
+        <v>5896</v>
       </c>
       <c r="F9" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36597,7 +36652,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5887</v>
+        <v>5898</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36666,10 +36721,10 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>5885</v>
+        <v>5896</v>
       </c>
       <c r="F13" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -36804,7 +36859,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5888</v>
+        <v>5899</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -36873,7 +36928,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5889</v>
+        <v>5900</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37011,7 +37066,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5890</v>
+        <v>5901</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37034,7 +37089,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5891</v>
+        <v>5902</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37057,7 +37112,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5892</v>
+        <v>5903</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37103,7 +37158,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5893</v>
+        <v>5904</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37149,7 +37204,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5894</v>
+        <v>5905</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37172,7 +37227,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5895</v>
+        <v>5906</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37218,7 +37273,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5894</v>
+        <v>5905</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37287,7 +37342,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5896</v>
+        <v>5907</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37310,7 +37365,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5897</v>
+        <v>5908</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37471,10 +37526,10 @@
         <v>161</v>
       </c>
       <c r="E48" t="s">
-        <v>5898</v>
+        <v>5909</v>
       </c>
       <c r="F48" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37494,10 +37549,10 @@
         <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>5899</v>
+        <v>5910</v>
       </c>
       <c r="F49" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37678,10 +37733,10 @@
         <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>5898</v>
+        <v>5909</v>
       </c>
       <c r="F57" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37770,10 +37825,10 @@
         <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>5900</v>
+        <v>5911</v>
       </c>
       <c r="F61" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37793,10 +37848,10 @@
         <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>5901</v>
+        <v>5912</v>
       </c>
       <c r="F62" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -37816,7 +37871,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5902</v>
+        <v>5913</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -37839,10 +37894,10 @@
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>5898</v>
+        <v>5909</v>
       </c>
       <c r="F64" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -37954,10 +38009,10 @@
         <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>5898</v>
+        <v>5909</v>
       </c>
       <c r="F69" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -37977,7 +38032,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5903</v>
+        <v>5914</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38345,7 +38400,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5904</v>
+        <v>5915</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38368,10 +38423,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5905</v>
+        <v>5916</v>
       </c>
       <c r="F87" t="s">
-        <v>5886</v>
+        <v>5897</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17251" uniqueCount="5917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17251" uniqueCount="5919">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18797,6 +18797,12 @@
   </si>
   <si>
     <t>ADM_CUST_027.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 19:55 IST — pass in 18.1s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_047.png</t>
   </si>
   <si>
     <t>Verify cancellation cannot be undone — requires an actual cancel on live data + user OK</t>
@@ -21970,10 +21976,10 @@
         <v>391</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L81" s="13" t="s">
         <v>68</v>
@@ -34958,22 +34964,22 @@
         <v>386</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D62" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>5781</v>
+        <v>5839</v>
       </c>
       <c r="F62" t="s">
-        <v>160</v>
-      </c>
-      <c r="G62" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>5840</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -35085,7 +35091,7 @@
         <v>5822</v>
       </c>
       <c r="F67" t="s">
-        <v>5839</v>
+        <v>5841</v>
       </c>
       <c r="G67" t="s">
         <v>24</v>
@@ -35111,7 +35117,7 @@
         <v>66</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>5840</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -35134,7 +35140,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>5841</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -35157,7 +35163,7 @@
         <v>160</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>5842</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -35180,7 +35186,7 @@
         <v>66</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>5843</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -35200,7 +35206,7 @@
         <v>5822</v>
       </c>
       <c r="F72" t="s">
-        <v>5844</v>
+        <v>5846</v>
       </c>
       <c r="G72" t="s">
         <v>24</v>
@@ -35223,7 +35229,7 @@
         <v>5822</v>
       </c>
       <c r="F73" t="s">
-        <v>5845</v>
+        <v>5847</v>
       </c>
       <c r="G73" t="s">
         <v>24</v>
@@ -35246,7 +35252,7 @@
         <v>5822</v>
       </c>
       <c r="F74" t="s">
-        <v>5846</v>
+        <v>5848</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35269,7 +35275,7 @@
         <v>5822</v>
       </c>
       <c r="F75" t="s">
-        <v>5847</v>
+        <v>5849</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>
@@ -35289,13 +35295,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5848</v>
+        <v>5850</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>5849</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35306,16 +35312,16 @@
         <v>5819</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5850</v>
+        <v>5852</v>
       </c>
       <c r="D77" t="s">
         <v>5821</v>
       </c>
       <c r="E77" t="s">
-        <v>5851</v>
+        <v>5853</v>
       </c>
       <c r="F77" t="s">
-        <v>5852</v>
+        <v>5854</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35329,16 +35335,16 @@
         <v>5819</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5850</v>
+        <v>5852</v>
       </c>
       <c r="D78" t="s">
         <v>5821</v>
       </c>
       <c r="E78" t="s">
-        <v>5851</v>
+        <v>5853</v>
       </c>
       <c r="F78" t="s">
-        <v>5853</v>
+        <v>5855</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35358,13 +35364,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5854</v>
+        <v>5856</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>5855</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35381,13 +35387,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5856</v>
+        <v>5858</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>5857</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35404,13 +35410,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5858</v>
+        <v>5860</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>5859</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35427,13 +35433,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5858</v>
+        <v>5860</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>5860</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35450,13 +35456,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5848</v>
+        <v>5850</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>5861</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35473,13 +35479,13 @@
         <v>161</v>
       </c>
       <c r="E84" t="s">
-        <v>5862</v>
+        <v>5864</v>
       </c>
       <c r="F84" t="s">
         <v>160</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>5863</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35496,13 +35502,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5854</v>
+        <v>5856</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>5864</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35519,13 +35525,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5865</v>
+        <v>5867</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>5866</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35571,7 +35577,7 @@
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5867</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35594,7 +35600,7 @@
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5868</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35617,7 +35623,7 @@
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5869</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35640,7 +35646,7 @@
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5870</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35686,7 +35692,7 @@
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5871</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35703,13 +35709,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5872</v>
+        <v>5874</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5873</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35795,13 +35801,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5874</v>
+        <v>5876</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5875</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -36051,7 +36057,7 @@
         <v>5822</v>
       </c>
       <c r="F109" t="s">
-        <v>5876</v>
+        <v>5878</v>
       </c>
       <c r="G109" t="s">
         <v>24</v>
@@ -36074,7 +36080,7 @@
         <v>5831</v>
       </c>
       <c r="F110" t="s">
-        <v>5877</v>
+        <v>5879</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36100,7 +36106,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5878</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36123,7 +36129,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5879</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36146,7 +36152,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5880</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36157,16 +36163,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5881</v>
+        <v>5883</v>
       </c>
       <c r="D114" t="s">
-        <v>5882</v>
+        <v>5884</v>
       </c>
       <c r="E114" t="s">
-        <v>5883</v>
+        <v>5885</v>
       </c>
       <c r="F114" t="s">
-        <v>5884</v>
+        <v>5886</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36226,16 +36232,16 @@
         <v>5819</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5885</v>
+        <v>5887</v>
       </c>
       <c r="D117" t="s">
         <v>5821</v>
       </c>
       <c r="E117" t="s">
-        <v>5886</v>
+        <v>5888</v>
       </c>
       <c r="F117" t="s">
-        <v>5887</v>
+        <v>5889</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36255,13 +36261,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5888</v>
+        <v>5890</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5889</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36281,7 +36287,7 @@
         <v>5831</v>
       </c>
       <c r="F119" t="s">
-        <v>5890</v>
+        <v>5892</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36304,7 +36310,7 @@
         <v>5831</v>
       </c>
       <c r="F120" t="s">
-        <v>5891</v>
+        <v>5893</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36324,13 +36330,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5892</v>
+        <v>5894</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5893</v>
+        <v>5895</v>
       </c>
     </row>
   </sheetData>
@@ -36386,31 +36392,32 @@
     <hyperlink ref="G57" r:id="rId49"/>
     <hyperlink ref="G60" r:id="rId50"/>
     <hyperlink ref="G61" r:id="rId51"/>
-    <hyperlink ref="G68" r:id="rId52"/>
-    <hyperlink ref="G69" r:id="rId53"/>
-    <hyperlink ref="G70" r:id="rId54"/>
-    <hyperlink ref="G71" r:id="rId55"/>
-    <hyperlink ref="G76" r:id="rId56"/>
-    <hyperlink ref="G79" r:id="rId57"/>
-    <hyperlink ref="G80" r:id="rId58"/>
-    <hyperlink ref="G81" r:id="rId59"/>
-    <hyperlink ref="G82" r:id="rId60"/>
-    <hyperlink ref="G83" r:id="rId61"/>
-    <hyperlink ref="G84" r:id="rId62"/>
-    <hyperlink ref="G85" r:id="rId63"/>
-    <hyperlink ref="G86" r:id="rId64"/>
-    <hyperlink ref="G88" r:id="rId65"/>
-    <hyperlink ref="G89" r:id="rId66"/>
-    <hyperlink ref="G90" r:id="rId67"/>
-    <hyperlink ref="G91" r:id="rId68"/>
-    <hyperlink ref="G93" r:id="rId69"/>
-    <hyperlink ref="G94" r:id="rId70"/>
-    <hyperlink ref="G98" r:id="rId71"/>
-    <hyperlink ref="G111" r:id="rId72"/>
-    <hyperlink ref="G112" r:id="rId73"/>
-    <hyperlink ref="G113" r:id="rId74"/>
-    <hyperlink ref="G118" r:id="rId75"/>
-    <hyperlink ref="G121" r:id="rId76"/>
+    <hyperlink ref="G62" r:id="rId52"/>
+    <hyperlink ref="G68" r:id="rId53"/>
+    <hyperlink ref="G69" r:id="rId54"/>
+    <hyperlink ref="G70" r:id="rId55"/>
+    <hyperlink ref="G71" r:id="rId56"/>
+    <hyperlink ref="G76" r:id="rId57"/>
+    <hyperlink ref="G79" r:id="rId58"/>
+    <hyperlink ref="G80" r:id="rId59"/>
+    <hyperlink ref="G81" r:id="rId60"/>
+    <hyperlink ref="G82" r:id="rId61"/>
+    <hyperlink ref="G83" r:id="rId62"/>
+    <hyperlink ref="G84" r:id="rId63"/>
+    <hyperlink ref="G85" r:id="rId64"/>
+    <hyperlink ref="G86" r:id="rId65"/>
+    <hyperlink ref="G88" r:id="rId66"/>
+    <hyperlink ref="G89" r:id="rId67"/>
+    <hyperlink ref="G90" r:id="rId68"/>
+    <hyperlink ref="G91" r:id="rId69"/>
+    <hyperlink ref="G93" r:id="rId70"/>
+    <hyperlink ref="G94" r:id="rId71"/>
+    <hyperlink ref="G98" r:id="rId72"/>
+    <hyperlink ref="G111" r:id="rId73"/>
+    <hyperlink ref="G112" r:id="rId74"/>
+    <hyperlink ref="G113" r:id="rId75"/>
+    <hyperlink ref="G118" r:id="rId76"/>
+    <hyperlink ref="G121" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36468,7 +36475,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5894</v>
+        <v>5896</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36514,7 +36521,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5895</v>
+        <v>5897</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36560,10 +36567,10 @@
         <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F6" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36583,10 +36590,10 @@
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F7" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36606,10 +36613,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F8" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36629,10 +36636,10 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F9" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36652,7 +36659,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36721,10 +36728,10 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F13" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -36859,7 +36866,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -36928,7 +36935,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5900</v>
+        <v>5902</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37066,7 +37073,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5901</v>
+        <v>5903</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37089,7 +37096,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5902</v>
+        <v>5904</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37112,7 +37119,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5903</v>
+        <v>5905</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37158,7 +37165,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5904</v>
+        <v>5906</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37204,7 +37211,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5905</v>
+        <v>5907</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37227,7 +37234,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37273,7 +37280,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5905</v>
+        <v>5907</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37342,7 +37349,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5907</v>
+        <v>5909</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37365,7 +37372,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37526,10 +37533,10 @@
         <v>161</v>
       </c>
       <c r="E48" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="F48" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37549,10 +37556,10 @@
         <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>5910</v>
+        <v>5912</v>
       </c>
       <c r="F49" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37733,10 +37740,10 @@
         <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="F57" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37825,10 +37832,10 @@
         <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="F61" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37848,10 +37855,10 @@
         <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>5912</v>
+        <v>5914</v>
       </c>
       <c r="F62" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -37871,7 +37878,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5913</v>
+        <v>5915</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -37894,10 +37901,10 @@
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="F64" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38009,10 +38016,10 @@
         <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="F69" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38032,7 +38039,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5914</v>
+        <v>5916</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38400,7 +38407,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38423,10 +38430,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5916</v>
+        <v>5918</v>
       </c>
       <c r="F87" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17251" uniqueCount="5919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17251" uniqueCount="5921">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18770,6 +18770,12 @@
   </si>
   <si>
     <t>TC_CUST_FUNC_044.png</t>
+  </si>
+  <si>
+    <t>2026-06-20 22:13 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>ADM_CUST_099.png</t>
   </si>
   <si>
     <t>API spec (not e2e)</t>
@@ -34789,13 +34795,13 @@
         <v>161</v>
       </c>
       <c r="E54" t="s">
-        <v>5781</v>
+        <v>5830</v>
       </c>
       <c r="F54" t="s">
         <v>160</v>
       </c>
-      <c r="G54" t="s">
-        <v>24</v>
+      <c r="G54" s="20" t="s">
+        <v>5831</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -34829,16 +34835,16 @@
         <v>5819</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>5830</v>
+        <v>5832</v>
       </c>
       <c r="D56" t="s">
         <v>5821</v>
       </c>
       <c r="E56" t="s">
-        <v>5831</v>
+        <v>5833</v>
       </c>
       <c r="F56" t="s">
-        <v>5832</v>
+        <v>5834</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -34864,7 +34870,7 @@
         <v>66</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>5833</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -34881,7 +34887,7 @@
         <v>161</v>
       </c>
       <c r="E58" t="s">
-        <v>5834</v>
+        <v>5836</v>
       </c>
       <c r="F58" t="s">
         <v>160</v>
@@ -34927,13 +34933,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5835</v>
+        <v>5837</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>5836</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -34950,13 +34956,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5837</v>
+        <v>5839</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>5838</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -34973,13 +34979,13 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>5839</v>
+        <v>5841</v>
       </c>
       <c r="F62" t="s">
         <v>66</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>5840</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -35091,7 +35097,7 @@
         <v>5822</v>
       </c>
       <c r="F67" t="s">
-        <v>5841</v>
+        <v>5843</v>
       </c>
       <c r="G67" t="s">
         <v>24</v>
@@ -35117,7 +35123,7 @@
         <v>66</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>5842</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -35140,7 +35146,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>5843</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -35163,7 +35169,7 @@
         <v>160</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>5844</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -35186,7 +35192,7 @@
         <v>66</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>5845</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -35206,7 +35212,7 @@
         <v>5822</v>
       </c>
       <c r="F72" t="s">
-        <v>5846</v>
+        <v>5848</v>
       </c>
       <c r="G72" t="s">
         <v>24</v>
@@ -35229,7 +35235,7 @@
         <v>5822</v>
       </c>
       <c r="F73" t="s">
-        <v>5847</v>
+        <v>5849</v>
       </c>
       <c r="G73" t="s">
         <v>24</v>
@@ -35252,7 +35258,7 @@
         <v>5822</v>
       </c>
       <c r="F74" t="s">
-        <v>5848</v>
+        <v>5850</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35275,7 +35281,7 @@
         <v>5822</v>
       </c>
       <c r="F75" t="s">
-        <v>5849</v>
+        <v>5851</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>
@@ -35295,13 +35301,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5850</v>
+        <v>5852</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>5851</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35312,16 +35318,16 @@
         <v>5819</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5852</v>
+        <v>5854</v>
       </c>
       <c r="D77" t="s">
         <v>5821</v>
       </c>
       <c r="E77" t="s">
-        <v>5853</v>
+        <v>5855</v>
       </c>
       <c r="F77" t="s">
-        <v>5854</v>
+        <v>5856</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35335,16 +35341,16 @@
         <v>5819</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5852</v>
+        <v>5854</v>
       </c>
       <c r="D78" t="s">
         <v>5821</v>
       </c>
       <c r="E78" t="s">
-        <v>5853</v>
+        <v>5855</v>
       </c>
       <c r="F78" t="s">
-        <v>5855</v>
+        <v>5857</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35364,13 +35370,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5856</v>
+        <v>5858</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>5857</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35387,13 +35393,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5858</v>
+        <v>5860</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>5859</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35410,13 +35416,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5860</v>
+        <v>5862</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>5861</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35433,13 +35439,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5860</v>
+        <v>5862</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>5862</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35456,13 +35462,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5850</v>
+        <v>5852</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>5863</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35479,13 +35485,13 @@
         <v>161</v>
       </c>
       <c r="E84" t="s">
-        <v>5864</v>
+        <v>5866</v>
       </c>
       <c r="F84" t="s">
         <v>160</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>5865</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35502,13 +35508,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5856</v>
+        <v>5858</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>5866</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35525,13 +35531,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5867</v>
+        <v>5869</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>5868</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35577,7 +35583,7 @@
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5869</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35594,13 +35600,13 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>5835</v>
+        <v>5837</v>
       </c>
       <c r="F89" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5870</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35623,7 +35629,7 @@
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5871</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35646,7 +35652,7 @@
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5872</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35692,7 +35698,7 @@
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5873</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35709,13 +35715,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5874</v>
+        <v>5876</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5875</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35801,13 +35807,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5876</v>
+        <v>5878</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5877</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -36057,7 +36063,7 @@
         <v>5822</v>
       </c>
       <c r="F109" t="s">
-        <v>5878</v>
+        <v>5880</v>
       </c>
       <c r="G109" t="s">
         <v>24</v>
@@ -36071,16 +36077,16 @@
         <v>5819</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>5830</v>
+        <v>5832</v>
       </c>
       <c r="D110" t="s">
         <v>5821</v>
       </c>
       <c r="E110" t="s">
-        <v>5831</v>
+        <v>5833</v>
       </c>
       <c r="F110" t="s">
-        <v>5879</v>
+        <v>5881</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36106,7 +36112,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5880</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36129,7 +36135,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5881</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36152,7 +36158,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5882</v>
+        <v>5884</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36163,16 +36169,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5883</v>
+        <v>5885</v>
       </c>
       <c r="D114" t="s">
-        <v>5884</v>
+        <v>5886</v>
       </c>
       <c r="E114" t="s">
-        <v>5885</v>
+        <v>5887</v>
       </c>
       <c r="F114" t="s">
-        <v>5886</v>
+        <v>5888</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36186,16 +36192,16 @@
         <v>5819</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>5830</v>
+        <v>5832</v>
       </c>
       <c r="D115" t="s">
         <v>5821</v>
       </c>
       <c r="E115" t="s">
-        <v>5831</v>
+        <v>5833</v>
       </c>
       <c r="F115" t="s">
-        <v>5832</v>
+        <v>5834</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -36209,16 +36215,16 @@
         <v>5819</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>5830</v>
+        <v>5832</v>
       </c>
       <c r="D116" t="s">
         <v>5821</v>
       </c>
       <c r="E116" t="s">
-        <v>5831</v>
+        <v>5833</v>
       </c>
       <c r="F116" t="s">
-        <v>5832</v>
+        <v>5834</v>
       </c>
       <c r="G116" t="s">
         <v>24</v>
@@ -36232,16 +36238,16 @@
         <v>5819</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5887</v>
+        <v>5889</v>
       </c>
       <c r="D117" t="s">
         <v>5821</v>
       </c>
       <c r="E117" t="s">
-        <v>5888</v>
+        <v>5890</v>
       </c>
       <c r="F117" t="s">
-        <v>5889</v>
+        <v>5891</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36261,13 +36267,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5890</v>
+        <v>5892</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5891</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36278,16 +36284,16 @@
         <v>5819</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>5830</v>
+        <v>5832</v>
       </c>
       <c r="D119" t="s">
         <v>5821</v>
       </c>
       <c r="E119" t="s">
-        <v>5831</v>
+        <v>5833</v>
       </c>
       <c r="F119" t="s">
-        <v>5892</v>
+        <v>5894</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36301,16 +36307,16 @@
         <v>5819</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>5830</v>
+        <v>5832</v>
       </c>
       <c r="D120" t="s">
         <v>5821</v>
       </c>
       <c r="E120" t="s">
-        <v>5831</v>
+        <v>5833</v>
       </c>
       <c r="F120" t="s">
-        <v>5893</v>
+        <v>5895</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36330,13 +36336,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5894</v>
+        <v>5896</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5895</v>
+        <v>5897</v>
       </c>
     </row>
   </sheetData>
@@ -36389,35 +36395,36 @@
     <hyperlink ref="G49" r:id="rId46"/>
     <hyperlink ref="G50" r:id="rId47"/>
     <hyperlink ref="G51" r:id="rId48"/>
-    <hyperlink ref="G57" r:id="rId49"/>
-    <hyperlink ref="G60" r:id="rId50"/>
-    <hyperlink ref="G61" r:id="rId51"/>
-    <hyperlink ref="G62" r:id="rId52"/>
-    <hyperlink ref="G68" r:id="rId53"/>
-    <hyperlink ref="G69" r:id="rId54"/>
-    <hyperlink ref="G70" r:id="rId55"/>
-    <hyperlink ref="G71" r:id="rId56"/>
-    <hyperlink ref="G76" r:id="rId57"/>
-    <hyperlink ref="G79" r:id="rId58"/>
-    <hyperlink ref="G80" r:id="rId59"/>
-    <hyperlink ref="G81" r:id="rId60"/>
-    <hyperlink ref="G82" r:id="rId61"/>
-    <hyperlink ref="G83" r:id="rId62"/>
-    <hyperlink ref="G84" r:id="rId63"/>
-    <hyperlink ref="G85" r:id="rId64"/>
-    <hyperlink ref="G86" r:id="rId65"/>
-    <hyperlink ref="G88" r:id="rId66"/>
-    <hyperlink ref="G89" r:id="rId67"/>
-    <hyperlink ref="G90" r:id="rId68"/>
-    <hyperlink ref="G91" r:id="rId69"/>
-    <hyperlink ref="G93" r:id="rId70"/>
-    <hyperlink ref="G94" r:id="rId71"/>
-    <hyperlink ref="G98" r:id="rId72"/>
-    <hyperlink ref="G111" r:id="rId73"/>
-    <hyperlink ref="G112" r:id="rId74"/>
-    <hyperlink ref="G113" r:id="rId75"/>
-    <hyperlink ref="G118" r:id="rId76"/>
-    <hyperlink ref="G121" r:id="rId77"/>
+    <hyperlink ref="G54" r:id="rId49"/>
+    <hyperlink ref="G57" r:id="rId50"/>
+    <hyperlink ref="G60" r:id="rId51"/>
+    <hyperlink ref="G61" r:id="rId52"/>
+    <hyperlink ref="G62" r:id="rId53"/>
+    <hyperlink ref="G68" r:id="rId54"/>
+    <hyperlink ref="G69" r:id="rId55"/>
+    <hyperlink ref="G70" r:id="rId56"/>
+    <hyperlink ref="G71" r:id="rId57"/>
+    <hyperlink ref="G76" r:id="rId58"/>
+    <hyperlink ref="G79" r:id="rId59"/>
+    <hyperlink ref="G80" r:id="rId60"/>
+    <hyperlink ref="G81" r:id="rId61"/>
+    <hyperlink ref="G82" r:id="rId62"/>
+    <hyperlink ref="G83" r:id="rId63"/>
+    <hyperlink ref="G84" r:id="rId64"/>
+    <hyperlink ref="G85" r:id="rId65"/>
+    <hyperlink ref="G86" r:id="rId66"/>
+    <hyperlink ref="G88" r:id="rId67"/>
+    <hyperlink ref="G89" r:id="rId68"/>
+    <hyperlink ref="G90" r:id="rId69"/>
+    <hyperlink ref="G91" r:id="rId70"/>
+    <hyperlink ref="G93" r:id="rId71"/>
+    <hyperlink ref="G94" r:id="rId72"/>
+    <hyperlink ref="G98" r:id="rId73"/>
+    <hyperlink ref="G111" r:id="rId74"/>
+    <hyperlink ref="G112" r:id="rId75"/>
+    <hyperlink ref="G113" r:id="rId76"/>
+    <hyperlink ref="G118" r:id="rId77"/>
+    <hyperlink ref="G121" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36475,7 +36482,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36521,7 +36528,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36567,10 +36574,10 @@
         <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F6" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36590,10 +36597,10 @@
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F7" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36613,10 +36620,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F8" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36636,10 +36643,10 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F9" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36659,7 +36666,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5900</v>
+        <v>5902</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36728,10 +36735,10 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F13" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -36866,7 +36873,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5901</v>
+        <v>5903</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -36935,7 +36942,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5902</v>
+        <v>5904</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37073,7 +37080,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5903</v>
+        <v>5905</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37096,7 +37103,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5904</v>
+        <v>5906</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37119,7 +37126,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5905</v>
+        <v>5907</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37165,7 +37172,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37211,7 +37218,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5907</v>
+        <v>5909</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37234,7 +37241,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37280,7 +37287,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5907</v>
+        <v>5909</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37349,7 +37356,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37372,7 +37379,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5910</v>
+        <v>5912</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37533,10 +37540,10 @@
         <v>161</v>
       </c>
       <c r="E48" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="F48" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37556,10 +37563,10 @@
         <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>5912</v>
+        <v>5914</v>
       </c>
       <c r="F49" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37740,10 +37747,10 @@
         <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="F57" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37832,10 +37839,10 @@
         <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>5913</v>
+        <v>5915</v>
       </c>
       <c r="F61" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37855,10 +37862,10 @@
         <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>5914</v>
+        <v>5916</v>
       </c>
       <c r="F62" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -37878,7 +37885,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -37901,10 +37908,10 @@
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="F64" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38016,10 +38023,10 @@
         <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="F69" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38039,7 +38046,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5916</v>
+        <v>5918</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38407,7 +38414,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5917</v>
+        <v>5919</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38430,10 +38437,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5918</v>
+        <v>5920</v>
       </c>
       <c r="F87" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18772,7 +18772,7 @@
     <t>TC_CUST_FUNC_044.png</t>
   </si>
   <si>
-    <t>2026-06-20 22:13 IST — skip in n/a</t>
+    <t>2026-06-20 22:31 IST — pass in 17.4s</t>
   </si>
   <si>
     <t>ADM_CUST_099.png</t>
@@ -21696,10 +21696,10 @@
         <v>348</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L72" s="13" t="s">
         <v>68</v>
@@ -34786,19 +34786,19 @@
         <v>343</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C54" s="18" t="s">
         <v>5753</v>
       </c>
       <c r="D54" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E54" t="s">
         <v>5830</v>
       </c>
       <c r="F54" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="G54" s="20" t="s">
         <v>5831</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5948">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18950,6 +18950,57 @@
   </si>
   <si>
     <t>TC_CUST_NEG_070.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:09 IST — pass in 17.2s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_081.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:21 IST — pass in 17.2s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_082.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:21 IST — pass in 17.0s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_086.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:09 IST — pass in 16.7s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_087.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:09 IST — pass in 16.9s</t>
+  </si>
+  <si>
+    <t>TC_CUST_VAL_084.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_VAL_085.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:21 IST — pass in 21.3s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_088.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:09 IST — pass in 21.2s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_089.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:09 IST — pass in 16.6s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_090.png</t>
   </si>
   <si>
     <t>TC_CUST_NEG_093.png</t>
@@ -23334,10 +23385,10 @@
         <v>604</v>
       </c>
       <c r="J123" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L123" s="13" t="s">
         <v>68</v>
@@ -23368,10 +23419,10 @@
         <v>609</v>
       </c>
       <c r="J124" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L124" s="13" t="s">
         <v>68</v>
@@ -23436,10 +23487,10 @@
         <v>621</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L126" s="13" t="s">
         <v>68</v>
@@ -23470,10 +23521,10 @@
         <v>627</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L127" s="13" t="s">
         <v>68</v>
@@ -23504,10 +23555,10 @@
         <v>633</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K128" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L128" s="13" t="s">
         <v>68</v>
@@ -23538,10 +23589,10 @@
         <v>639</v>
       </c>
       <c r="J129" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L129" s="13" t="s">
         <v>68</v>
@@ -23572,10 +23623,10 @@
         <v>645</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K130" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L130" s="13" t="s">
         <v>68</v>
@@ -23606,10 +23657,10 @@
         <v>651</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L131" s="13" t="s">
         <v>68</v>
@@ -23640,10 +23691,10 @@
         <v>596</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K132" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L132" s="13" t="s">
         <v>68</v>
@@ -35863,22 +35914,22 @@
         <v>598</v>
       </c>
       <c r="B99" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C99" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D99" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5788</v>
+        <v>5890</v>
       </c>
       <c r="F99" t="s">
-        <v>160</v>
-      </c>
-      <c r="G99" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G99" s="20" t="s">
+        <v>5891</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -35886,22 +35937,22 @@
         <v>605</v>
       </c>
       <c r="B100" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C100" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D100" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5788</v>
+        <v>5892</v>
       </c>
       <c r="F100" t="s">
-        <v>160</v>
-      </c>
-      <c r="G100" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G100" s="20" t="s">
+        <v>5893</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -35932,22 +35983,22 @@
         <v>616</v>
       </c>
       <c r="B102" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C102" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D102" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5788</v>
+        <v>5894</v>
       </c>
       <c r="F102" t="s">
-        <v>160</v>
-      </c>
-      <c r="G102" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>5895</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -35955,22 +36006,22 @@
         <v>622</v>
       </c>
       <c r="B103" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C103" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D103" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5788</v>
+        <v>5896</v>
       </c>
       <c r="F103" t="s">
-        <v>160</v>
-      </c>
-      <c r="G103" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G103" s="20" t="s">
+        <v>5897</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -35978,22 +36029,22 @@
         <v>628</v>
       </c>
       <c r="B104" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C104" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D104" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5788</v>
+        <v>5898</v>
       </c>
       <c r="F104" t="s">
-        <v>160</v>
-      </c>
-      <c r="G104" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G104" s="20" t="s">
+        <v>5899</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36001,22 +36052,22 @@
         <v>634</v>
       </c>
       <c r="B105" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C105" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D105" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5788</v>
+        <v>5896</v>
       </c>
       <c r="F105" t="s">
-        <v>160</v>
-      </c>
-      <c r="G105" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>5900</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36024,22 +36075,22 @@
         <v>640</v>
       </c>
       <c r="B106" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C106" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D106" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5788</v>
+        <v>5901</v>
       </c>
       <c r="F106" t="s">
-        <v>160</v>
-      </c>
-      <c r="G106" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G106" s="20" t="s">
+        <v>5902</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36047,22 +36098,22 @@
         <v>646</v>
       </c>
       <c r="B107" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C107" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D107" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5788</v>
+        <v>5903</v>
       </c>
       <c r="F107" t="s">
-        <v>160</v>
-      </c>
-      <c r="G107" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G107" s="20" t="s">
+        <v>5904</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36070,22 +36121,22 @@
         <v>652</v>
       </c>
       <c r="B108" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D108" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5788</v>
+        <v>5905</v>
       </c>
       <c r="F108" t="s">
-        <v>160</v>
-      </c>
-      <c r="G108" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G108" s="20" t="s">
+        <v>5906</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36108,7 +36159,7 @@
         <v>661</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5890</v>
+        <v>5907</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36128,7 +36179,7 @@
         <v>5842</v>
       </c>
       <c r="F110" t="s">
-        <v>5891</v>
+        <v>5908</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36154,7 +36205,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5892</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36177,7 +36228,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5893</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36200,7 +36251,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5894</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36211,16 +36262,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5895</v>
+        <v>5912</v>
       </c>
       <c r="D114" t="s">
-        <v>5896</v>
+        <v>5913</v>
       </c>
       <c r="E114" t="s">
-        <v>5897</v>
+        <v>5914</v>
       </c>
       <c r="F114" t="s">
-        <v>5898</v>
+        <v>5915</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36280,16 +36331,16 @@
         <v>5828</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5899</v>
+        <v>5916</v>
       </c>
       <c r="D117" t="s">
         <v>5830</v>
       </c>
       <c r="E117" t="s">
-        <v>5900</v>
+        <v>5917</v>
       </c>
       <c r="F117" t="s">
-        <v>5901</v>
+        <v>5918</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36309,13 +36360,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5902</v>
+        <v>5919</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5903</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36335,7 +36386,7 @@
         <v>5842</v>
       </c>
       <c r="F119" t="s">
-        <v>5904</v>
+        <v>5921</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36358,7 +36409,7 @@
         <v>5842</v>
       </c>
       <c r="F120" t="s">
-        <v>5905</v>
+        <v>5922</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36378,13 +36429,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5906</v>
+        <v>5923</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5907</v>
+        <v>5924</v>
       </c>
     </row>
   </sheetData>
@@ -36465,12 +36516,21 @@
     <hyperlink ref="G93" r:id="rId74"/>
     <hyperlink ref="G94" r:id="rId75"/>
     <hyperlink ref="G98" r:id="rId76"/>
-    <hyperlink ref="G109" r:id="rId77"/>
-    <hyperlink ref="G111" r:id="rId78"/>
-    <hyperlink ref="G112" r:id="rId79"/>
-    <hyperlink ref="G113" r:id="rId80"/>
-    <hyperlink ref="G118" r:id="rId81"/>
-    <hyperlink ref="G121" r:id="rId82"/>
+    <hyperlink ref="G99" r:id="rId77"/>
+    <hyperlink ref="G100" r:id="rId78"/>
+    <hyperlink ref="G102" r:id="rId79"/>
+    <hyperlink ref="G103" r:id="rId80"/>
+    <hyperlink ref="G104" r:id="rId81"/>
+    <hyperlink ref="G105" r:id="rId82"/>
+    <hyperlink ref="G106" r:id="rId83"/>
+    <hyperlink ref="G107" r:id="rId84"/>
+    <hyperlink ref="G108" r:id="rId85"/>
+    <hyperlink ref="G109" r:id="rId86"/>
+    <hyperlink ref="G111" r:id="rId87"/>
+    <hyperlink ref="G112" r:id="rId88"/>
+    <hyperlink ref="G113" r:id="rId89"/>
+    <hyperlink ref="G118" r:id="rId90"/>
+    <hyperlink ref="G121" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36528,7 +36588,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5908</v>
+        <v>5925</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36574,7 +36634,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5909</v>
+        <v>5926</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36620,10 +36680,10 @@
         <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>5910</v>
+        <v>5927</v>
       </c>
       <c r="F6" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36643,10 +36703,10 @@
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>5910</v>
+        <v>5927</v>
       </c>
       <c r="F7" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36666,10 +36726,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5910</v>
+        <v>5927</v>
       </c>
       <c r="F8" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36689,10 +36749,10 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>5910</v>
+        <v>5927</v>
       </c>
       <c r="F9" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36712,7 +36772,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5912</v>
+        <v>5929</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36781,10 +36841,10 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>5910</v>
+        <v>5927</v>
       </c>
       <c r="F13" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -36919,7 +36979,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5913</v>
+        <v>5930</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -36988,7 +37048,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5914</v>
+        <v>5931</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37126,7 +37186,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5915</v>
+        <v>5932</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37149,7 +37209,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5916</v>
+        <v>5933</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37172,7 +37232,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5917</v>
+        <v>5934</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37218,7 +37278,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5918</v>
+        <v>5935</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37264,7 +37324,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5919</v>
+        <v>5936</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37287,7 +37347,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5920</v>
+        <v>5937</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37333,7 +37393,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5919</v>
+        <v>5936</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37402,7 +37462,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5921</v>
+        <v>5938</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37425,7 +37485,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5922</v>
+        <v>5939</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37586,10 +37646,10 @@
         <v>161</v>
       </c>
       <c r="E48" t="s">
-        <v>5923</v>
+        <v>5940</v>
       </c>
       <c r="F48" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37609,10 +37669,10 @@
         <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>5924</v>
+        <v>5941</v>
       </c>
       <c r="F49" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37793,10 +37853,10 @@
         <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>5923</v>
+        <v>5940</v>
       </c>
       <c r="F57" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37885,10 +37945,10 @@
         <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>5925</v>
+        <v>5942</v>
       </c>
       <c r="F61" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37908,10 +37968,10 @@
         <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>5926</v>
+        <v>5943</v>
       </c>
       <c r="F62" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -37931,7 +37991,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5927</v>
+        <v>5944</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -37954,10 +38014,10 @@
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>5923</v>
+        <v>5940</v>
       </c>
       <c r="F64" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38069,10 +38129,10 @@
         <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>5923</v>
+        <v>5940</v>
       </c>
       <c r="F69" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38092,7 +38152,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5928</v>
+        <v>5945</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38460,7 +38520,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5929</v>
+        <v>5946</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38483,10 +38543,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5930</v>
+        <v>5947</v>
       </c>
       <c r="F87" t="s">
-        <v>5911</v>
+        <v>5928</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5958">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18754,7 +18754,7 @@
     <t>TC_CUST_FUNC_080.png</t>
   </si>
   <si>
-    <t>2026-06-20 15:54 IST — skip in 17.8s</t>
+    <t>2026-06-21 13:36 IST — skip in n/a</t>
   </si>
   <si>
     <t>ADM_CUST_031.png</t>
@@ -18799,6 +18799,18 @@
     <t>TC_CUST_FUNC_044.png</t>
   </si>
   <si>
+    <t>2026-06-21 13:32 IST — pass in 21.0s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_101.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:32 IST — pass in 16.8s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_098.png</t>
+  </si>
+  <si>
     <t>2026-06-21 — Pass (verified)</t>
   </si>
   <si>
@@ -18835,6 +18847,18 @@
     <t>TC_CUST_FUNC_047.png</t>
   </si>
   <si>
+    <t>2026-06-21 13:32 IST — pass in 18.6s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_028.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:32 IST — pass in 20.0s</t>
+  </si>
+  <si>
+    <t>ADM_CUST_029.png</t>
+  </si>
+  <si>
     <t>ADM_CUST_104.png</t>
   </si>
   <si>
@@ -18944,6 +18968,12 @@
   </si>
   <si>
     <t>TC_CUST_NEG_066.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:36 IST — pass in 21.4s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_067.png</t>
   </si>
   <si>
     <t>2026-06-20 15:52 IST — pass in 18.2s</t>
@@ -21709,10 +21739,10 @@
         <v>338</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L70" s="13" t="s">
         <v>68</v>
@@ -21743,10 +21773,10 @@
         <v>343</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L71" s="13" t="s">
         <v>68</v>
@@ -22097,10 +22127,10 @@
         <v>398</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L82" s="13" t="s">
         <v>68</v>
@@ -22199,10 +22229,10 @@
         <v>413</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L85" s="13" t="s">
         <v>68</v>
@@ -23229,10 +23259,10 @@
         <v>580</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L118" s="13" t="s">
         <v>68</v>
@@ -34833,22 +34863,22 @@
         <v>334</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D52" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>5788</v>
+        <v>5839</v>
       </c>
       <c r="F52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G52" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>5840</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -34856,22 +34886,22 @@
         <v>339</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>5788</v>
+        <v>5841</v>
       </c>
       <c r="F53" t="s">
-        <v>160</v>
-      </c>
-      <c r="G53" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>5842</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -34888,13 +34918,13 @@
         <v>67</v>
       </c>
       <c r="E54" t="s">
-        <v>5839</v>
+        <v>5843</v>
       </c>
       <c r="F54" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>5840</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -34928,16 +34958,16 @@
         <v>5828</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="D56" t="s">
         <v>5830</v>
       </c>
       <c r="E56" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="F56" t="s">
-        <v>5843</v>
+        <v>5847</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -34963,7 +34993,7 @@
         <v>66</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>5844</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -34980,7 +35010,7 @@
         <v>161</v>
       </c>
       <c r="E58" t="s">
-        <v>5845</v>
+        <v>5849</v>
       </c>
       <c r="F58" t="s">
         <v>160</v>
@@ -35026,13 +35056,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5846</v>
+        <v>5850</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>5847</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -35049,13 +35079,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5848</v>
+        <v>5852</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>5849</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -35072,13 +35102,13 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>5839</v>
+        <v>5843</v>
       </c>
       <c r="F62" t="s">
         <v>394</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>5850</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -35086,22 +35116,22 @@
         <v>395</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C63" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D63" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5788</v>
+        <v>5855</v>
       </c>
       <c r="F63" t="s">
-        <v>160</v>
-      </c>
-      <c r="G63" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>5856</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -35155,22 +35185,22 @@
         <v>410</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>5788</v>
+        <v>5857</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
-      </c>
-      <c r="G66" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>5858</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -35187,7 +35217,7 @@
         <v>67</v>
       </c>
       <c r="E67" t="s">
-        <v>5839</v>
+        <v>5843</v>
       </c>
       <c r="F67" t="s">
         <v>419</v>
@@ -35216,7 +35246,7 @@
         <v>66</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>5851</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -35239,7 +35269,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>5852</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -35262,7 +35292,7 @@
         <v>160</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>5853</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -35285,7 +35315,7 @@
         <v>66</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>5854</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -35305,7 +35335,7 @@
         <v>5831</v>
       </c>
       <c r="F72" t="s">
-        <v>5855</v>
+        <v>5863</v>
       </c>
       <c r="G72" t="s">
         <v>24</v>
@@ -35328,7 +35358,7 @@
         <v>5831</v>
       </c>
       <c r="F73" t="s">
-        <v>5856</v>
+        <v>5864</v>
       </c>
       <c r="G73" t="s">
         <v>24</v>
@@ -35351,7 +35381,7 @@
         <v>5831</v>
       </c>
       <c r="F74" t="s">
-        <v>5857</v>
+        <v>5865</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35374,7 +35404,7 @@
         <v>5831</v>
       </c>
       <c r="F75" t="s">
-        <v>5858</v>
+        <v>5866</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>
@@ -35394,13 +35424,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5859</v>
+        <v>5867</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>5860</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35411,16 +35441,16 @@
         <v>5828</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5861</v>
+        <v>5869</v>
       </c>
       <c r="D77" t="s">
         <v>5830</v>
       </c>
       <c r="E77" t="s">
-        <v>5862</v>
+        <v>5870</v>
       </c>
       <c r="F77" t="s">
-        <v>5863</v>
+        <v>5871</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35434,16 +35464,16 @@
         <v>5828</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5861</v>
+        <v>5869</v>
       </c>
       <c r="D78" t="s">
         <v>5830</v>
       </c>
       <c r="E78" t="s">
-        <v>5862</v>
+        <v>5870</v>
       </c>
       <c r="F78" t="s">
-        <v>5864</v>
+        <v>5872</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35463,13 +35493,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5865</v>
+        <v>5873</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>5866</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35486,13 +35516,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5867</v>
+        <v>5875</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>5868</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35509,13 +35539,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5869</v>
+        <v>5877</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>5870</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35532,13 +35562,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5869</v>
+        <v>5877</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>5871</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35555,13 +35585,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5859</v>
+        <v>5867</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>5872</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35578,13 +35608,13 @@
         <v>161</v>
       </c>
       <c r="E84" t="s">
-        <v>5873</v>
+        <v>5881</v>
       </c>
       <c r="F84" t="s">
         <v>160</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>5874</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35601,13 +35631,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5865</v>
+        <v>5873</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>5875</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35624,13 +35654,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5876</v>
+        <v>5884</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>5877</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35647,13 +35677,13 @@
         <v>67</v>
       </c>
       <c r="E87" t="s">
-        <v>5878</v>
+        <v>5886</v>
       </c>
       <c r="F87" t="s">
         <v>536</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>5879</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -35676,7 +35706,7 @@
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5880</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35693,13 +35723,13 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>5846</v>
+        <v>5850</v>
       </c>
       <c r="F89" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5881</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35722,7 +35752,7 @@
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5882</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35745,7 +35775,7 @@
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5883</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35768,7 +35798,7 @@
         <v>564</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>5884</v>
+        <v>5892</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -35791,7 +35821,7 @@
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5885</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35808,13 +35838,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5886</v>
+        <v>5894</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5887</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35822,22 +35852,22 @@
         <v>576</v>
       </c>
       <c r="B95" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C95" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D95" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>5788</v>
+        <v>5896</v>
       </c>
       <c r="F95" t="s">
-        <v>160</v>
-      </c>
-      <c r="G95" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G95" s="20" t="s">
+        <v>5897</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -35900,13 +35930,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5888</v>
+        <v>5898</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5889</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -35923,13 +35953,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5890</v>
+        <v>5900</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>5891</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -35946,13 +35976,13 @@
         <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5892</v>
+        <v>5902</v>
       </c>
       <c r="F100" t="s">
         <v>66</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>5893</v>
+        <v>5903</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -35992,13 +36022,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5894</v>
+        <v>5904</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>5895</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36015,13 +36045,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5896</v>
+        <v>5906</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>5897</v>
+        <v>5907</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36038,13 +36068,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5898</v>
+        <v>5908</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>5899</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36061,13 +36091,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5896</v>
+        <v>5906</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>5900</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36084,13 +36114,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5901</v>
+        <v>5911</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>5902</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36107,13 +36137,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5903</v>
+        <v>5913</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>5904</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36130,13 +36160,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5905</v>
+        <v>5915</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>5906</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36159,7 +36189,7 @@
         <v>661</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5907</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36170,16 +36200,16 @@
         <v>5828</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="D110" t="s">
         <v>5830</v>
       </c>
       <c r="E110" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="F110" t="s">
-        <v>5908</v>
+        <v>5918</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36205,7 +36235,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5909</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36228,7 +36258,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5910</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36251,7 +36281,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5911</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36262,16 +36292,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5912</v>
+        <v>5922</v>
       </c>
       <c r="D114" t="s">
-        <v>5913</v>
+        <v>5923</v>
       </c>
       <c r="E114" t="s">
-        <v>5914</v>
+        <v>5924</v>
       </c>
       <c r="F114" t="s">
-        <v>5915</v>
+        <v>5925</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36285,16 +36315,16 @@
         <v>5828</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="D115" t="s">
         <v>5830</v>
       </c>
       <c r="E115" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="F115" t="s">
-        <v>5843</v>
+        <v>5847</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -36308,16 +36338,16 @@
         <v>5828</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="D116" t="s">
         <v>5830</v>
       </c>
       <c r="E116" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="F116" t="s">
-        <v>5843</v>
+        <v>5847</v>
       </c>
       <c r="G116" t="s">
         <v>24</v>
@@ -36331,16 +36361,16 @@
         <v>5828</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5916</v>
+        <v>5926</v>
       </c>
       <c r="D117" t="s">
         <v>5830</v>
       </c>
       <c r="E117" t="s">
-        <v>5917</v>
+        <v>5927</v>
       </c>
       <c r="F117" t="s">
-        <v>5918</v>
+        <v>5928</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36360,13 +36390,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5919</v>
+        <v>5929</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5920</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36377,16 +36407,16 @@
         <v>5828</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="D119" t="s">
         <v>5830</v>
       </c>
       <c r="E119" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="F119" t="s">
-        <v>5921</v>
+        <v>5931</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36400,16 +36430,16 @@
         <v>5828</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="D120" t="s">
         <v>5830</v>
       </c>
       <c r="E120" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="F120" t="s">
-        <v>5922</v>
+        <v>5932</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36429,13 +36459,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5923</v>
+        <v>5933</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5924</v>
+        <v>5934</v>
       </c>
     </row>
   </sheetData>
@@ -36489,48 +36519,53 @@
     <hyperlink ref="G49" r:id="rId47"/>
     <hyperlink ref="G50" r:id="rId48"/>
     <hyperlink ref="G51" r:id="rId49"/>
-    <hyperlink ref="G54" r:id="rId50"/>
-    <hyperlink ref="G57" r:id="rId51"/>
-    <hyperlink ref="G60" r:id="rId52"/>
-    <hyperlink ref="G61" r:id="rId53"/>
-    <hyperlink ref="G62" r:id="rId54"/>
-    <hyperlink ref="G68" r:id="rId55"/>
-    <hyperlink ref="G69" r:id="rId56"/>
-    <hyperlink ref="G70" r:id="rId57"/>
-    <hyperlink ref="G71" r:id="rId58"/>
-    <hyperlink ref="G76" r:id="rId59"/>
-    <hyperlink ref="G79" r:id="rId60"/>
-    <hyperlink ref="G80" r:id="rId61"/>
-    <hyperlink ref="G81" r:id="rId62"/>
-    <hyperlink ref="G82" r:id="rId63"/>
-    <hyperlink ref="G83" r:id="rId64"/>
-    <hyperlink ref="G84" r:id="rId65"/>
-    <hyperlink ref="G85" r:id="rId66"/>
-    <hyperlink ref="G86" r:id="rId67"/>
-    <hyperlink ref="G87" r:id="rId68"/>
-    <hyperlink ref="G88" r:id="rId69"/>
-    <hyperlink ref="G89" r:id="rId70"/>
-    <hyperlink ref="G90" r:id="rId71"/>
-    <hyperlink ref="G91" r:id="rId72"/>
-    <hyperlink ref="G92" r:id="rId73"/>
-    <hyperlink ref="G93" r:id="rId74"/>
-    <hyperlink ref="G94" r:id="rId75"/>
-    <hyperlink ref="G98" r:id="rId76"/>
-    <hyperlink ref="G99" r:id="rId77"/>
-    <hyperlink ref="G100" r:id="rId78"/>
-    <hyperlink ref="G102" r:id="rId79"/>
-    <hyperlink ref="G103" r:id="rId80"/>
-    <hyperlink ref="G104" r:id="rId81"/>
-    <hyperlink ref="G105" r:id="rId82"/>
-    <hyperlink ref="G106" r:id="rId83"/>
-    <hyperlink ref="G107" r:id="rId84"/>
-    <hyperlink ref="G108" r:id="rId85"/>
-    <hyperlink ref="G109" r:id="rId86"/>
-    <hyperlink ref="G111" r:id="rId87"/>
-    <hyperlink ref="G112" r:id="rId88"/>
-    <hyperlink ref="G113" r:id="rId89"/>
-    <hyperlink ref="G118" r:id="rId90"/>
-    <hyperlink ref="G121" r:id="rId91"/>
+    <hyperlink ref="G52" r:id="rId50"/>
+    <hyperlink ref="G53" r:id="rId51"/>
+    <hyperlink ref="G54" r:id="rId52"/>
+    <hyperlink ref="G57" r:id="rId53"/>
+    <hyperlink ref="G60" r:id="rId54"/>
+    <hyperlink ref="G61" r:id="rId55"/>
+    <hyperlink ref="G62" r:id="rId56"/>
+    <hyperlink ref="G63" r:id="rId57"/>
+    <hyperlink ref="G66" r:id="rId58"/>
+    <hyperlink ref="G68" r:id="rId59"/>
+    <hyperlink ref="G69" r:id="rId60"/>
+    <hyperlink ref="G70" r:id="rId61"/>
+    <hyperlink ref="G71" r:id="rId62"/>
+    <hyperlink ref="G76" r:id="rId63"/>
+    <hyperlink ref="G79" r:id="rId64"/>
+    <hyperlink ref="G80" r:id="rId65"/>
+    <hyperlink ref="G81" r:id="rId66"/>
+    <hyperlink ref="G82" r:id="rId67"/>
+    <hyperlink ref="G83" r:id="rId68"/>
+    <hyperlink ref="G84" r:id="rId69"/>
+    <hyperlink ref="G85" r:id="rId70"/>
+    <hyperlink ref="G86" r:id="rId71"/>
+    <hyperlink ref="G87" r:id="rId72"/>
+    <hyperlink ref="G88" r:id="rId73"/>
+    <hyperlink ref="G89" r:id="rId74"/>
+    <hyperlink ref="G90" r:id="rId75"/>
+    <hyperlink ref="G91" r:id="rId76"/>
+    <hyperlink ref="G92" r:id="rId77"/>
+    <hyperlink ref="G93" r:id="rId78"/>
+    <hyperlink ref="G94" r:id="rId79"/>
+    <hyperlink ref="G95" r:id="rId80"/>
+    <hyperlink ref="G98" r:id="rId81"/>
+    <hyperlink ref="G99" r:id="rId82"/>
+    <hyperlink ref="G100" r:id="rId83"/>
+    <hyperlink ref="G102" r:id="rId84"/>
+    <hyperlink ref="G103" r:id="rId85"/>
+    <hyperlink ref="G104" r:id="rId86"/>
+    <hyperlink ref="G105" r:id="rId87"/>
+    <hyperlink ref="G106" r:id="rId88"/>
+    <hyperlink ref="G107" r:id="rId89"/>
+    <hyperlink ref="G108" r:id="rId90"/>
+    <hyperlink ref="G109" r:id="rId91"/>
+    <hyperlink ref="G111" r:id="rId92"/>
+    <hyperlink ref="G112" r:id="rId93"/>
+    <hyperlink ref="G113" r:id="rId94"/>
+    <hyperlink ref="G118" r:id="rId95"/>
+    <hyperlink ref="G121" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36588,7 +36623,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5925</v>
+        <v>5935</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36634,7 +36669,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5926</v>
+        <v>5936</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36680,10 +36715,10 @@
         <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>5927</v>
+        <v>5937</v>
       </c>
       <c r="F6" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36703,10 +36738,10 @@
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>5927</v>
+        <v>5937</v>
       </c>
       <c r="F7" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36726,10 +36761,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5927</v>
+        <v>5937</v>
       </c>
       <c r="F8" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36749,10 +36784,10 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>5927</v>
+        <v>5937</v>
       </c>
       <c r="F9" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36772,7 +36807,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5929</v>
+        <v>5939</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36841,10 +36876,10 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>5927</v>
+        <v>5937</v>
       </c>
       <c r="F13" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -36979,7 +37014,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5930</v>
+        <v>5940</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37048,7 +37083,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5931</v>
+        <v>5941</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37186,7 +37221,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5932</v>
+        <v>5942</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37209,7 +37244,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5933</v>
+        <v>5943</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37232,7 +37267,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5934</v>
+        <v>5944</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37278,7 +37313,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5935</v>
+        <v>5945</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37324,7 +37359,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5936</v>
+        <v>5946</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37347,7 +37382,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5937</v>
+        <v>5947</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37393,7 +37428,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5936</v>
+        <v>5946</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37462,7 +37497,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5938</v>
+        <v>5948</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37485,7 +37520,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5939</v>
+        <v>5949</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37646,10 +37681,10 @@
         <v>161</v>
       </c>
       <c r="E48" t="s">
-        <v>5940</v>
+        <v>5950</v>
       </c>
       <c r="F48" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37669,10 +37704,10 @@
         <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>5941</v>
+        <v>5951</v>
       </c>
       <c r="F49" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37853,10 +37888,10 @@
         <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>5940</v>
+        <v>5950</v>
       </c>
       <c r="F57" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37945,10 +37980,10 @@
         <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>5942</v>
+        <v>5952</v>
       </c>
       <c r="F61" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37968,10 +38003,10 @@
         <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>5943</v>
+        <v>5953</v>
       </c>
       <c r="F62" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -37991,7 +38026,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5944</v>
+        <v>5954</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38014,10 +38049,10 @@
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>5940</v>
+        <v>5950</v>
       </c>
       <c r="F64" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38129,10 +38164,10 @@
         <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>5940</v>
+        <v>5950</v>
       </c>
       <c r="F69" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38152,7 +38187,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5945</v>
+        <v>5955</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38520,7 +38555,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5946</v>
+        <v>5956</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38543,10 +38578,10 @@
         <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>5947</v>
+        <v>5957</v>
       </c>
       <c r="F87" t="s">
-        <v>5928</v>
+        <v>5938</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5960">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -530,12 +530,6 @@
     <t>A unit-details PDF downloads/opens for that registration.</t>
   </si>
   <si>
-    <t>SKIPPED — not executed (ENV-guarded or fixme)</t>
-  </si>
-  <si>
-    <t>Skip</t>
-  </si>
-  <si>
     <t>Sorting &amp; Column Filters</t>
   </si>
   <si>
@@ -597,6 +591,12 @@
   </si>
   <si>
     <t>The table updates to show only rows whose Phone column matches the number typed. (Search is on phone number only - it does not match on customer name, registration number, or unit number.)</t>
+  </si>
+  <si>
+    <t>SKIPPED — not executed (ENV-guarded or fixme)</t>
+  </si>
+  <si>
+    <t>Skip</t>
   </si>
   <si>
     <t>ADM_CUST_014</t>
@@ -18646,18 +18646,21 @@
     <t>TC_CUST_UI_041.png</t>
   </si>
   <si>
+    <t>2026-06-21 13:42 IST — pass in 16.0s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_128.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_122.png</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_123.png</t>
+  </si>
+  <si>
     <t>2026-06-20 15:52 IST — skip in n/a</t>
   </si>
   <si>
-    <t>TC_CUST_FUNC_128.png</t>
-  </si>
-  <si>
-    <t>TC_CUST_FUNC_122.png</t>
-  </si>
-  <si>
-    <t>TC_CUST_FUNC_123.png</t>
-  </si>
-  <si>
     <t>ADM_CUST_013.png</t>
   </si>
   <si>
@@ -18667,12 +18670,12 @@
     <t>ADM_CUST_014.png</t>
   </si>
   <si>
+    <t>2026-06-21 13:42 IST — pass in 16.2s</t>
+  </si>
+  <si>
     <t>ADM_CUST_037.png</t>
   </si>
   <si>
-    <t>2026-06-20 15:52 IST — skip in phone-only search</t>
-  </si>
-  <si>
     <t>TC_CUST_NEG_010.png</t>
   </si>
   <si>
@@ -18863,6 +18866,9 @@
   </si>
   <si>
     <t>ADM_CUST_033.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:42 IST — pass in 17.4s</t>
   </si>
   <si>
     <t>TC_CUST_FUNC_121.png</t>
@@ -20497,10 +20503,10 @@
         <v>159</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>68</v>
@@ -20508,7 +20514,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -20524,31 +20530,31 @@
     </row>
     <row r="32" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="E32" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="G32" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>167</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>75</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J32" s="12" t="s">
         <v>66</v>
@@ -20562,27 +20568,27 @@
     </row>
     <row r="33" ht="63.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>75</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>66</v>
@@ -20596,7 +20602,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -20612,37 +20618,37 @@
     </row>
     <row r="35" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="E35" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="G35" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="H35" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="I35" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="J35" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="K35" s="13" t="s">
         <v>180</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>161</v>
       </c>
       <c r="L35" s="13" t="s">
         <v>68</v>
@@ -20654,7 +20660,7 @@
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12" t="s">
@@ -20688,7 +20694,7 @@
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12" t="s">
@@ -20707,10 +20713,10 @@
         <v>190</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L37" s="13" t="s">
         <v>68</v>
@@ -20722,7 +20728,7 @@
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12" t="s">
@@ -20741,10 +20747,10 @@
         <v>196</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L38" s="13" t="s">
         <v>68</v>
@@ -21487,10 +21493,10 @@
         <v>298</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L62" s="13" t="s">
         <v>68</v>
@@ -21841,10 +21847,10 @@
         <v>356</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L73" s="13" t="s">
         <v>68</v>
@@ -21957,10 +21963,10 @@
         <v>373</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L77" s="13" t="s">
         <v>68</v>
@@ -21991,10 +21997,10 @@
         <v>378</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L78" s="13" t="s">
         <v>68</v>
@@ -22161,10 +22167,10 @@
         <v>404</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L83" s="13" t="s">
         <v>68</v>
@@ -22195,10 +22201,10 @@
         <v>409</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L84" s="13" t="s">
         <v>68</v>
@@ -22385,10 +22391,10 @@
         <v>436</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="L90" s="13" t="s">
         <v>68</v>
@@ -22865,10 +22871,10 @@
         <v>519</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L106" s="13" t="s">
         <v>68</v>
@@ -23293,10 +23299,10 @@
         <v>586</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L119" s="13" t="s">
         <v>68</v>
@@ -23327,10 +23333,10 @@
         <v>591</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L120" s="13" t="s">
         <v>68</v>
@@ -23483,10 +23489,10 @@
         <v>615</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="L125" s="13" t="s">
         <v>68</v>
@@ -24781,7 +24787,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -24803,7 +24809,7 @@
         <v>20</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>4630</v>
@@ -24841,7 +24847,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>4637</v>
@@ -24879,7 +24885,7 @@
         <v>20</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>4643</v>
@@ -24917,7 +24923,7 @@
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>4650</v>
@@ -34127,19 +34133,19 @@
         <v>154</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>5760</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
         <v>5788</v>
       </c>
       <c r="F20" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>5789</v>
@@ -34147,7 +34153,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B21" t="s">
         <v>67</v>
@@ -34170,7 +34176,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B22" t="s">
         <v>67</v>
@@ -34193,25 +34199,25 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F23" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -34228,13 +34234,13 @@
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -34242,22 +34248,22 @@
         <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>5788</v>
+        <v>5796</v>
       </c>
       <c r="F25" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>5795</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -34265,22 +34271,22 @@
         <v>191</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D26" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>5796</v>
+        <v>5788</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -34303,7 +34309,7 @@
         <v>66</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -34326,7 +34332,7 @@
         <v>66</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -34343,13 +34349,13 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -34366,13 +34372,13 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -34389,13 +34395,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -34418,7 +34424,7 @@
         <v>66</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -34441,7 +34447,7 @@
         <v>66</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -34458,13 +34464,13 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -34487,7 +34493,7 @@
         <v>66</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -34504,13 +34510,13 @@
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="F36" t="s">
         <v>66</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -34527,13 +34533,13 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -34550,13 +34556,13 @@
         <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="F38" t="s">
         <v>66</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -34573,13 +34579,13 @@
         <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="F39" t="s">
         <v>66</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -34596,13 +34602,13 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -34619,13 +34625,13 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -34648,7 +34654,7 @@
         <v>66</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -34665,13 +34671,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -34688,13 +34694,13 @@
         <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -34702,22 +34708,22 @@
         <v>293</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
       <c r="F45" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -34734,13 +34740,13 @@
         <v>67</v>
       </c>
       <c r="E46" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="F46" t="s">
         <v>304</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -34748,19 +34754,19 @@
         <v>305</v>
       </c>
       <c r="B47" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="D47" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E47" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="F47" t="s">
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
@@ -34780,13 +34786,13 @@
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>5833</v>
+        <v>5834</v>
       </c>
       <c r="F48" t="s">
         <v>66</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>5834</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -34803,13 +34809,13 @@
         <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
       <c r="F49" t="s">
         <v>66</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>5835</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -34832,7 +34838,7 @@
         <v>66</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -34849,13 +34855,13 @@
         <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
       <c r="F51" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -34872,13 +34878,13 @@
         <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>5839</v>
+        <v>5840</v>
       </c>
       <c r="F52" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>5840</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -34895,13 +34901,13 @@
         <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>5841</v>
+        <v>5842</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>5842</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -34918,13 +34924,13 @@
         <v>67</v>
       </c>
       <c r="E54" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
       <c r="F54" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>5844</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -34932,19 +34938,19 @@
         <v>351</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E55" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F55" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G55" t="s">
         <v>24</v>
@@ -34955,19 +34961,19 @@
         <v>357</v>
       </c>
       <c r="B56" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D56" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E56" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="F56" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -34993,7 +34999,7 @@
         <v>66</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>5848</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -35001,19 +35007,19 @@
         <v>368</v>
       </c>
       <c r="B58" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E58" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
       <c r="F58" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -35024,19 +35030,19 @@
         <v>374</v>
       </c>
       <c r="B59" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C59" s="19" t="s">
         <v>5760</v>
       </c>
       <c r="D59" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E59" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F59" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G59" t="s">
         <v>24</v>
@@ -35056,13 +35062,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>5851</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -35079,13 +35085,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5852</v>
+        <v>5853</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>5853</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -35102,13 +35108,13 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
       <c r="F62" t="s">
         <v>394</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -35125,13 +35131,13 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -35139,19 +35145,19 @@
         <v>399</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C64" s="19" t="s">
         <v>5760</v>
       </c>
       <c r="D64" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -35162,19 +35168,19 @@
         <v>405</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C65" s="19" t="s">
         <v>5760</v>
       </c>
       <c r="D65" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E65" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G65" t="s">
         <v>24</v>
@@ -35194,13 +35200,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>5857</v>
+        <v>5858</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>5858</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -35217,7 +35223,7 @@
         <v>67</v>
       </c>
       <c r="E67" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
       <c r="F67" t="s">
         <v>419</v>
@@ -35246,7 +35252,7 @@
         <v>66</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>5859</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -35269,7 +35275,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -35277,22 +35283,22 @@
         <v>431</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="C70" s="19" t="s">
         <v>5760</v>
       </c>
       <c r="D70" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5788</v>
+        <v>5862</v>
       </c>
       <c r="F70" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>5861</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -35309,13 +35315,13 @@
         <v>67</v>
       </c>
       <c r="E71" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="F71" t="s">
         <v>66</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>5862</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -35323,19 +35329,19 @@
         <v>444</v>
       </c>
       <c r="B72" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="D72" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E72" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="F72" t="s">
-        <v>5863</v>
+        <v>5865</v>
       </c>
       <c r="G72" t="s">
         <v>24</v>
@@ -35346,19 +35352,19 @@
         <v>451</v>
       </c>
       <c r="B73" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="D73" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E73" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="F73" t="s">
-        <v>5864</v>
+        <v>5866</v>
       </c>
       <c r="G73" t="s">
         <v>24</v>
@@ -35369,19 +35375,19 @@
         <v>457</v>
       </c>
       <c r="B74" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="D74" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E74" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="F74" t="s">
-        <v>5865</v>
+        <v>5867</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35392,19 +35398,19 @@
         <v>463</v>
       </c>
       <c r="B75" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="D75" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E75" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="F75" t="s">
-        <v>5866</v>
+        <v>5868</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>
@@ -35424,13 +35430,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5867</v>
+        <v>5869</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>5868</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35438,19 +35444,19 @@
         <v>475</v>
       </c>
       <c r="B77" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5869</v>
+        <v>5871</v>
       </c>
       <c r="D77" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E77" t="s">
-        <v>5870</v>
+        <v>5872</v>
       </c>
       <c r="F77" t="s">
-        <v>5871</v>
+        <v>5873</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35461,19 +35467,19 @@
         <v>481</v>
       </c>
       <c r="B78" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5869</v>
+        <v>5871</v>
       </c>
       <c r="D78" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E78" t="s">
-        <v>5870</v>
+        <v>5872</v>
       </c>
       <c r="F78" t="s">
-        <v>5872</v>
+        <v>5874</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35493,13 +35499,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5873</v>
+        <v>5875</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>5874</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35516,13 +35522,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5875</v>
+        <v>5877</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>5876</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35539,13 +35545,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5877</v>
+        <v>5879</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>5878</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35562,13 +35568,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5877</v>
+        <v>5879</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>5879</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35585,13 +35591,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5867</v>
+        <v>5869</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>5880</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35599,22 +35605,22 @@
         <v>514</v>
       </c>
       <c r="B84" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>5760</v>
       </c>
       <c r="D84" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>5881</v>
+        <v>5883</v>
       </c>
       <c r="F84" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>5882</v>
+        <v>5884</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35631,13 +35637,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5873</v>
+        <v>5875</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>5883</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35654,13 +35660,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5884</v>
+        <v>5886</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>5885</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35677,13 +35683,13 @@
         <v>67</v>
       </c>
       <c r="E87" t="s">
-        <v>5886</v>
+        <v>5888</v>
       </c>
       <c r="F87" t="s">
         <v>536</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>5887</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -35700,13 +35706,13 @@
         <v>67</v>
       </c>
       <c r="E88" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="F88" t="s">
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5888</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35723,13 +35729,13 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="F89" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5889</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35746,13 +35752,13 @@
         <v>67</v>
       </c>
       <c r="E90" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="F90" t="s">
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5890</v>
+        <v>5892</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35769,13 +35775,13 @@
         <v>67</v>
       </c>
       <c r="E91" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="F91" t="s">
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5891</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35792,13 +35798,13 @@
         <v>67</v>
       </c>
       <c r="E92" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="F92" t="s">
         <v>564</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>5892</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -35815,13 +35821,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5893</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35838,13 +35844,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5894</v>
+        <v>5896</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5895</v>
+        <v>5897</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35861,13 +35867,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -35875,19 +35881,19 @@
         <v>581</v>
       </c>
       <c r="B96" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C96" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D96" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E96" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F96" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G96" t="s">
         <v>24</v>
@@ -35898,19 +35904,19 @@
         <v>587</v>
       </c>
       <c r="B97" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C97" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D97" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E97" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F97" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G97" t="s">
         <v>24</v>
@@ -35930,13 +35936,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -35953,13 +35959,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5900</v>
+        <v>5902</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>5901</v>
+        <v>5903</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -35976,13 +35982,13 @@
         <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5902</v>
+        <v>5904</v>
       </c>
       <c r="F100" t="s">
         <v>66</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>5903</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -35990,19 +35996,19 @@
         <v>610</v>
       </c>
       <c r="B101" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C101" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D101" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E101" t="s">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="F101" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G101" t="s">
         <v>24</v>
@@ -36022,13 +36028,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5904</v>
+        <v>5906</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>5905</v>
+        <v>5907</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36045,13 +36051,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>5907</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36068,13 +36074,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36091,13 +36097,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>5910</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36114,13 +36120,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>5912</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36137,13 +36143,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5913</v>
+        <v>5915</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>5914</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36160,13 +36166,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>5916</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36183,13 +36189,13 @@
         <v>67</v>
       </c>
       <c r="E109" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="F109" t="s">
         <v>661</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5917</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36197,19 +36203,19 @@
         <v>662</v>
       </c>
       <c r="B110" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D110" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E110" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="F110" t="s">
-        <v>5918</v>
+        <v>5920</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36235,7 +36241,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5919</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36252,13 +36258,13 @@
         <v>67</v>
       </c>
       <c r="E112" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F112" t="s">
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5920</v>
+        <v>5922</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36275,13 +36281,13 @@
         <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="F113" t="s">
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5921</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36292,16 +36298,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5922</v>
+        <v>5924</v>
       </c>
       <c r="D114" t="s">
-        <v>5923</v>
+        <v>5925</v>
       </c>
       <c r="E114" t="s">
-        <v>5924</v>
+        <v>5926</v>
       </c>
       <c r="F114" t="s">
-        <v>5925</v>
+        <v>5927</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36312,19 +36318,19 @@
         <v>691</v>
       </c>
       <c r="B115" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D115" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E115" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="F115" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -36335,19 +36341,19 @@
         <v>698</v>
       </c>
       <c r="B116" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D116" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E116" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="F116" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="G116" t="s">
         <v>24</v>
@@ -36358,19 +36364,19 @@
         <v>705</v>
       </c>
       <c r="B117" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5926</v>
+        <v>5928</v>
       </c>
       <c r="D117" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E117" t="s">
-        <v>5927</v>
+        <v>5929</v>
       </c>
       <c r="F117" t="s">
-        <v>5928</v>
+        <v>5930</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36390,13 +36396,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5929</v>
+        <v>5931</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5930</v>
+        <v>5932</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36404,19 +36410,19 @@
         <v>716</v>
       </c>
       <c r="B119" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D119" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E119" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="F119" t="s">
-        <v>5931</v>
+        <v>5933</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36427,19 +36433,19 @@
         <v>722</v>
       </c>
       <c r="B120" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D120" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="E120" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="F120" t="s">
-        <v>5932</v>
+        <v>5934</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36459,13 +36465,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5933</v>
+        <v>5935</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5934</v>
+        <v>5936</v>
       </c>
     </row>
   </sheetData>
@@ -36623,7 +36629,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5935</v>
+        <v>5937</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36669,7 +36675,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5936</v>
+        <v>5938</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36706,19 +36712,19 @@
         <v>2685</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F6" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36729,19 +36735,19 @@
         <v>2692</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F7" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36752,19 +36758,19 @@
         <v>2698</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F8" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36775,19 +36781,19 @@
         <v>2705</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F9" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36807,7 +36813,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36867,19 +36873,19 @@
         <v>2730</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F13" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37014,7 +37020,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37083,7 +37089,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37221,7 +37227,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37244,7 +37250,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37267,7 +37273,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37313,7 +37319,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5945</v>
+        <v>5947</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37359,7 +37365,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5946</v>
+        <v>5948</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37382,7 +37388,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5947</v>
+        <v>5949</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37428,7 +37434,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5946</v>
+        <v>5948</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37497,7 +37503,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5948</v>
+        <v>5950</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37520,7 +37526,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5949</v>
+        <v>5951</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37672,19 +37678,19 @@
         <v>2952</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D48" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F48" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37695,19 +37701,19 @@
         <v>2959</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D49" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>5951</v>
+        <v>5953</v>
       </c>
       <c r="F49" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37879,19 +37885,19 @@
         <v>3013</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F57" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37971,19 +37977,19 @@
         <v>3042</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D61" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F61" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -37994,19 +38000,19 @@
         <v>3049</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D62" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>5953</v>
+        <v>5955</v>
       </c>
       <c r="F62" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38026,7 +38032,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38040,19 +38046,19 @@
         <v>3064</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D64" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F64" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38155,19 +38161,19 @@
         <v>3099</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C69" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D69" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F69" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38187,7 +38193,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5955</v>
+        <v>5957</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38555,7 +38561,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38569,19 +38575,19 @@
         <v>3223</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C87" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D87" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F87" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17257" uniqueCount="5960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17269" uniqueCount="5962">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19066,6 +19066,12 @@
     <t>Covered by TC_CUST_FUNC_008b (download with active filter)</t>
   </si>
   <si>
+    <t>2026-06-21 13:47 IST — pass in 82ms</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:47 IST — pass in 224ms</t>
+  </si>
+  <si>
     <t>DB spec (not e2e)</t>
   </si>
   <si>
@@ -19081,10 +19087,10 @@
     <t>TC_CUST_NEG_123.png</t>
   </si>
   <si>
-    <t>JWT-after-logout (server logout no-op) — API-layer test, not e2e</t>
-  </si>
-  <si>
-    <t>projectId cross-project leak check — API-layer test, not e2e</t>
+    <t>2026-06-21 13:48 IST — pass in 360ms</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:48 IST — pass in 248ms</t>
   </si>
   <si>
     <t>2026-06-20 15:52 IST — pass in 24.7s</t>
@@ -23972,9 +23978,15 @@
       <c r="I140" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="J140" s="12"/>
-      <c r="K140" s="13"/>
-      <c r="L140" s="13"/>
+      <c r="J140" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K140" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L140" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
@@ -24020,9 +24032,15 @@
       <c r="I142" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="J142" s="12"/>
-      <c r="K142" s="13"/>
-      <c r="L142" s="13"/>
+      <c r="J142" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K142" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L142" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="143" ht="102" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
@@ -24110,9 +24128,15 @@
       <c r="I145" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="J145" s="12"/>
-      <c r="K145" s="13"/>
-      <c r="L145" s="13"/>
+      <c r="J145" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K145" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L145" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="146" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
@@ -24138,9 +24162,15 @@
       <c r="I146" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="J146" s="12"/>
-      <c r="K146" s="13"/>
-      <c r="L146" s="13"/>
+      <c r="J146" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K146" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L146" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
@@ -36318,19 +36348,19 @@
         <v>691</v>
       </c>
       <c r="B115" t="s">
-        <v>5829</v>
+        <v>67</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>5846</v>
+        <v>5760</v>
       </c>
       <c r="D115" t="s">
-        <v>5831</v>
+        <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>5847</v>
+        <v>5928</v>
       </c>
       <c r="F115" t="s">
-        <v>5848</v>
+        <v>66</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -36341,19 +36371,19 @@
         <v>698</v>
       </c>
       <c r="B116" t="s">
-        <v>5829</v>
+        <v>67</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>5846</v>
+        <v>5760</v>
       </c>
       <c r="D116" t="s">
-        <v>5831</v>
+        <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>5847</v>
+        <v>5929</v>
       </c>
       <c r="F116" t="s">
-        <v>5848</v>
+        <v>66</v>
       </c>
       <c r="G116" t="s">
         <v>24</v>
@@ -36367,16 +36397,16 @@
         <v>5829</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5928</v>
+        <v>5930</v>
       </c>
       <c r="D117" t="s">
         <v>5831</v>
       </c>
       <c r="E117" t="s">
-        <v>5929</v>
+        <v>5931</v>
       </c>
       <c r="F117" t="s">
-        <v>5930</v>
+        <v>5932</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36396,13 +36426,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5931</v>
+        <v>5933</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5932</v>
+        <v>5934</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36410,19 +36440,19 @@
         <v>716</v>
       </c>
       <c r="B119" t="s">
-        <v>5829</v>
+        <v>67</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>5846</v>
+        <v>5760</v>
       </c>
       <c r="D119" t="s">
-        <v>5831</v>
+        <v>67</v>
       </c>
       <c r="E119" t="s">
-        <v>5847</v>
+        <v>5935</v>
       </c>
       <c r="F119" t="s">
-        <v>5933</v>
+        <v>66</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
@@ -36433,19 +36463,19 @@
         <v>722</v>
       </c>
       <c r="B120" t="s">
-        <v>5829</v>
+        <v>67</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>5846</v>
+        <v>5760</v>
       </c>
       <c r="D120" t="s">
-        <v>5831</v>
+        <v>67</v>
       </c>
       <c r="E120" t="s">
-        <v>5847</v>
+        <v>5936</v>
       </c>
       <c r="F120" t="s">
-        <v>5934</v>
+        <v>66</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -36465,13 +36495,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5935</v>
+        <v>5937</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5936</v>
+        <v>5938</v>
       </c>
     </row>
   </sheetData>
@@ -36629,7 +36659,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36675,7 +36705,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36721,10 +36751,10 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F6" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36744,10 +36774,10 @@
         <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F7" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36767,10 +36797,10 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F8" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36790,10 +36820,10 @@
         <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F9" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36813,7 +36843,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36882,10 +36912,10 @@
         <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F13" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37020,7 +37050,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37089,7 +37119,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37227,7 +37257,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37250,7 +37280,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5945</v>
+        <v>5947</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37273,7 +37303,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5946</v>
+        <v>5948</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37319,7 +37349,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5947</v>
+        <v>5949</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37365,7 +37395,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5948</v>
+        <v>5950</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37388,7 +37418,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5949</v>
+        <v>5951</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37434,7 +37464,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5948</v>
+        <v>5950</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37503,7 +37533,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37526,7 +37556,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5951</v>
+        <v>5953</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37687,10 +37717,10 @@
         <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F48" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37710,10 +37740,10 @@
         <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>5953</v>
+        <v>5955</v>
       </c>
       <c r="F49" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37894,10 +37924,10 @@
         <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F57" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -37986,10 +38016,10 @@
         <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F61" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -38009,10 +38039,10 @@
         <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>5955</v>
+        <v>5957</v>
       </c>
       <c r="F62" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38032,7 +38062,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38055,10 +38085,10 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F64" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38170,10 +38200,10 @@
         <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F69" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38193,7 +38223,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38561,7 +38591,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5958</v>
+        <v>5960</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38584,10 +38614,10 @@
         <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>5959</v>
+        <v>5961</v>
       </c>
       <c r="F87" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17269" uniqueCount="5962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17269" uniqueCount="5964">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18998,6 +18998,12 @@
   </si>
   <si>
     <t>TC_CUST_FUNC_082.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:52 IST — pass in 24.1s</t>
+  </si>
+  <si>
+    <t>TC_CUST_FUNC_083.png</t>
   </si>
   <si>
     <t>2026-06-21 13:21 IST — pass in 17.0s</t>
@@ -23495,10 +23501,10 @@
         <v>615</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L125" s="13" t="s">
         <v>68</v>
@@ -36026,22 +36032,22 @@
         <v>610</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C101" s="18" t="s">
         <v>5760</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>5792</v>
+        <v>5906</v>
       </c>
       <c r="F101" t="s">
-        <v>179</v>
-      </c>
-      <c r="G101" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G101" s="20" t="s">
+        <v>5907</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -36058,13 +36064,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>5907</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36081,13 +36087,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36104,13 +36110,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5910</v>
+        <v>5912</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36127,13 +36133,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>5912</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36150,13 +36156,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5913</v>
+        <v>5915</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>5914</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36173,13 +36179,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>5916</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36196,13 +36202,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5917</v>
+        <v>5919</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>5918</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36225,7 +36231,7 @@
         <v>661</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5919</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36245,7 +36251,7 @@
         <v>5847</v>
       </c>
       <c r="F110" t="s">
-        <v>5920</v>
+        <v>5922</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36271,7 +36277,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5921</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36294,7 +36300,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5922</v>
+        <v>5924</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36317,7 +36323,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5923</v>
+        <v>5925</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36328,16 +36334,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5924</v>
+        <v>5926</v>
       </c>
       <c r="D114" t="s">
-        <v>5925</v>
+        <v>5927</v>
       </c>
       <c r="E114" t="s">
-        <v>5926</v>
+        <v>5928</v>
       </c>
       <c r="F114" t="s">
-        <v>5927</v>
+        <v>5929</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36357,7 +36363,7 @@
         <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>5928</v>
+        <v>5930</v>
       </c>
       <c r="F115" t="s">
         <v>66</v>
@@ -36380,7 +36386,7 @@
         <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>5929</v>
+        <v>5931</v>
       </c>
       <c r="F116" t="s">
         <v>66</v>
@@ -36397,16 +36403,16 @@
         <v>5829</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5930</v>
+        <v>5932</v>
       </c>
       <c r="D117" t="s">
         <v>5831</v>
       </c>
       <c r="E117" t="s">
-        <v>5931</v>
+        <v>5933</v>
       </c>
       <c r="F117" t="s">
-        <v>5932</v>
+        <v>5934</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36426,13 +36432,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5933</v>
+        <v>5935</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5934</v>
+        <v>5936</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36449,7 +36455,7 @@
         <v>67</v>
       </c>
       <c r="E119" t="s">
-        <v>5935</v>
+        <v>5937</v>
       </c>
       <c r="F119" t="s">
         <v>66</v>
@@ -36472,7 +36478,7 @@
         <v>67</v>
       </c>
       <c r="E120" t="s">
-        <v>5936</v>
+        <v>5938</v>
       </c>
       <c r="F120" t="s">
         <v>66</v>
@@ -36495,13 +36501,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
     </row>
   </sheetData>
@@ -36589,19 +36595,20 @@
     <hyperlink ref="G98" r:id="rId81"/>
     <hyperlink ref="G99" r:id="rId82"/>
     <hyperlink ref="G100" r:id="rId83"/>
-    <hyperlink ref="G102" r:id="rId84"/>
-    <hyperlink ref="G103" r:id="rId85"/>
-    <hyperlink ref="G104" r:id="rId86"/>
-    <hyperlink ref="G105" r:id="rId87"/>
-    <hyperlink ref="G106" r:id="rId88"/>
-    <hyperlink ref="G107" r:id="rId89"/>
-    <hyperlink ref="G108" r:id="rId90"/>
-    <hyperlink ref="G109" r:id="rId91"/>
-    <hyperlink ref="G111" r:id="rId92"/>
-    <hyperlink ref="G112" r:id="rId93"/>
-    <hyperlink ref="G113" r:id="rId94"/>
-    <hyperlink ref="G118" r:id="rId95"/>
-    <hyperlink ref="G121" r:id="rId96"/>
+    <hyperlink ref="G101" r:id="rId84"/>
+    <hyperlink ref="G102" r:id="rId85"/>
+    <hyperlink ref="G103" r:id="rId86"/>
+    <hyperlink ref="G104" r:id="rId87"/>
+    <hyperlink ref="G105" r:id="rId88"/>
+    <hyperlink ref="G106" r:id="rId89"/>
+    <hyperlink ref="G107" r:id="rId90"/>
+    <hyperlink ref="G108" r:id="rId91"/>
+    <hyperlink ref="G109" r:id="rId92"/>
+    <hyperlink ref="G111" r:id="rId93"/>
+    <hyperlink ref="G112" r:id="rId94"/>
+    <hyperlink ref="G113" r:id="rId95"/>
+    <hyperlink ref="G118" r:id="rId96"/>
+    <hyperlink ref="G121" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36659,7 +36666,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36705,7 +36712,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36751,10 +36758,10 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F6" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36774,10 +36781,10 @@
         <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F7" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36797,10 +36804,10 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F8" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36820,10 +36827,10 @@
         <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F9" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36843,7 +36850,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36912,10 +36919,10 @@
         <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F13" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37050,7 +37057,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37119,7 +37126,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5945</v>
+        <v>5947</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37257,7 +37264,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5946</v>
+        <v>5948</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37280,7 +37287,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5947</v>
+        <v>5949</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37303,7 +37310,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5948</v>
+        <v>5950</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37349,7 +37356,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5949</v>
+        <v>5951</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37395,7 +37402,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37418,7 +37425,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5951</v>
+        <v>5953</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37464,7 +37471,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37533,7 +37540,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37556,7 +37563,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5953</v>
+        <v>5955</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37717,10 +37724,10 @@
         <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F48" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37740,10 +37747,10 @@
         <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>5955</v>
+        <v>5957</v>
       </c>
       <c r="F49" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37924,10 +37931,10 @@
         <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F57" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -38016,10 +38023,10 @@
         <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F61" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -38039,10 +38046,10 @@
         <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F62" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38062,7 +38069,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5958</v>
+        <v>5960</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38085,10 +38092,10 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F64" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38200,10 +38207,10 @@
         <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F69" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38223,7 +38230,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5959</v>
+        <v>5961</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38591,7 +38598,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5960</v>
+        <v>5962</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38614,10 +38621,10 @@
         <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>5961</v>
+        <v>5963</v>
       </c>
       <c r="F87" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17269" uniqueCount="5964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17275" uniqueCount="5966">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18880,13 +18880,19 @@
     <t>Offline unit assignment happy-path BOOKS a unit — requires SUBMIT on live data + user OK</t>
   </si>
   <si>
-    <t>Assign Unit validation — Assign Unit modal access needs a Waitlisted fixture; submit-path destructive</t>
+    <t>2026-06-21 14:07 IST — pass in 16.9s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_120.png</t>
   </si>
   <si>
     <t>Unit availability re-checked at submit — requires SUBMIT + concurrent fixture, user OK</t>
   </si>
   <si>
-    <t>Reject 2nd unit when already booked — requires a fixture with an active booking + user OK</t>
+    <t>2026-06-21 14:07 IST — pass in 16.1s</t>
+  </si>
+  <si>
+    <t>TC_CUST_NEG_122.png</t>
   </si>
   <si>
     <t>2026-06-20 18:19 IST — pass in 33.3s</t>
@@ -22518,9 +22524,15 @@
       <c r="I94" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="J94" s="12"/>
-      <c r="K94" s="13"/>
-      <c r="L94" s="13"/>
+      <c r="J94" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K94" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L94" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="95" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
@@ -22574,9 +22586,15 @@
       <c r="I96" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="J96" s="12"/>
-      <c r="K96" s="13"/>
-      <c r="L96" s="13"/>
+      <c r="J96" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K96" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L96" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="97" ht="76.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
@@ -35388,22 +35406,22 @@
         <v>451</v>
       </c>
       <c r="B73" t="s">
-        <v>5829</v>
+        <v>67</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>5830</v>
+        <v>5760</v>
       </c>
       <c r="D73" t="s">
-        <v>5831</v>
+        <v>67</v>
       </c>
       <c r="E73" t="s">
-        <v>5832</v>
+        <v>5866</v>
       </c>
       <c r="F73" t="s">
-        <v>5866</v>
-      </c>
-      <c r="G73" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>5867</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -35423,7 +35441,7 @@
         <v>5832</v>
       </c>
       <c r="F74" t="s">
-        <v>5867</v>
+        <v>5868</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35434,22 +35452,22 @@
         <v>463</v>
       </c>
       <c r="B75" t="s">
-        <v>5829</v>
+        <v>67</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>5830</v>
+        <v>5760</v>
       </c>
       <c r="D75" t="s">
-        <v>5831</v>
+        <v>67</v>
       </c>
       <c r="E75" t="s">
-        <v>5832</v>
+        <v>5869</v>
       </c>
       <c r="F75" t="s">
-        <v>5868</v>
-      </c>
-      <c r="G75" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>5870</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -35466,13 +35484,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5869</v>
+        <v>5871</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>5870</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35483,16 +35501,16 @@
         <v>5829</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5871</v>
+        <v>5873</v>
       </c>
       <c r="D77" t="s">
         <v>5831</v>
       </c>
       <c r="E77" t="s">
-        <v>5872</v>
+        <v>5874</v>
       </c>
       <c r="F77" t="s">
-        <v>5873</v>
+        <v>5875</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35506,16 +35524,16 @@
         <v>5829</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5871</v>
+        <v>5873</v>
       </c>
       <c r="D78" t="s">
         <v>5831</v>
       </c>
       <c r="E78" t="s">
-        <v>5872</v>
+        <v>5874</v>
       </c>
       <c r="F78" t="s">
-        <v>5874</v>
+        <v>5876</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35535,13 +35553,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5875</v>
+        <v>5877</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>5876</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35558,13 +35576,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5877</v>
+        <v>5879</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>5878</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35581,13 +35599,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5879</v>
+        <v>5881</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>5880</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35604,13 +35622,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5879</v>
+        <v>5881</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>5881</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35627,13 +35645,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5869</v>
+        <v>5871</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>5882</v>
+        <v>5884</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35650,13 +35668,13 @@
         <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>5883</v>
+        <v>5885</v>
       </c>
       <c r="F84" t="s">
         <v>179</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>5884</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35673,13 +35691,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5875</v>
+        <v>5877</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>5885</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35696,13 +35714,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5886</v>
+        <v>5888</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>5887</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35719,13 +35737,13 @@
         <v>67</v>
       </c>
       <c r="E87" t="s">
-        <v>5888</v>
+        <v>5890</v>
       </c>
       <c r="F87" t="s">
         <v>536</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>5889</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -35748,7 +35766,7 @@
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5890</v>
+        <v>5892</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35771,7 +35789,7 @@
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5891</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35794,7 +35812,7 @@
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5892</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35817,7 +35835,7 @@
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5893</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35840,7 +35858,7 @@
         <v>564</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>5894</v>
+        <v>5896</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -35863,7 +35881,7 @@
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5895</v>
+        <v>5897</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35880,13 +35898,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5897</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35903,13 +35921,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>5899</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -35972,13 +35990,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5900</v>
+        <v>5902</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5901</v>
+        <v>5903</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -35995,13 +36013,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5902</v>
+        <v>5904</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>5903</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -36018,13 +36036,13 @@
         <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5904</v>
+        <v>5906</v>
       </c>
       <c r="F100" t="s">
         <v>66</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>5905</v>
+        <v>5907</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -36041,13 +36059,13 @@
         <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="F101" t="s">
         <v>66</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>5907</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -36064,13 +36082,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>5909</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36087,13 +36105,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5910</v>
+        <v>5912</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>5911</v>
+        <v>5913</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36110,13 +36128,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5912</v>
+        <v>5914</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>5913</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36133,13 +36151,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5910</v>
+        <v>5912</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>5914</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36156,13 +36174,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5915</v>
+        <v>5917</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>5916</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36179,13 +36197,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5917</v>
+        <v>5919</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>5918</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36202,13 +36220,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5919</v>
+        <v>5921</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>5920</v>
+        <v>5922</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36231,7 +36249,7 @@
         <v>661</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5921</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36251,7 +36269,7 @@
         <v>5847</v>
       </c>
       <c r="F110" t="s">
-        <v>5922</v>
+        <v>5924</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36277,7 +36295,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5923</v>
+        <v>5925</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36300,7 +36318,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5924</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36323,7 +36341,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5925</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36334,16 +36352,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5926</v>
+        <v>5928</v>
       </c>
       <c r="D114" t="s">
-        <v>5927</v>
+        <v>5929</v>
       </c>
       <c r="E114" t="s">
-        <v>5928</v>
+        <v>5930</v>
       </c>
       <c r="F114" t="s">
-        <v>5929</v>
+        <v>5931</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36363,7 +36381,7 @@
         <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>5930</v>
+        <v>5932</v>
       </c>
       <c r="F115" t="s">
         <v>66</v>
@@ -36386,7 +36404,7 @@
         <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>5931</v>
+        <v>5933</v>
       </c>
       <c r="F116" t="s">
         <v>66</v>
@@ -36403,16 +36421,16 @@
         <v>5829</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5932</v>
+        <v>5934</v>
       </c>
       <c r="D117" t="s">
         <v>5831</v>
       </c>
       <c r="E117" t="s">
-        <v>5933</v>
+        <v>5935</v>
       </c>
       <c r="F117" t="s">
-        <v>5934</v>
+        <v>5936</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36432,13 +36450,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5935</v>
+        <v>5937</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5936</v>
+        <v>5938</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36455,7 +36473,7 @@
         <v>67</v>
       </c>
       <c r="E119" t="s">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F119" t="s">
         <v>66</v>
@@ -36478,7 +36496,7 @@
         <v>67</v>
       </c>
       <c r="E120" t="s">
-        <v>5938</v>
+        <v>5940</v>
       </c>
       <c r="F120" t="s">
         <v>66</v>
@@ -36501,13 +36519,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5940</v>
+        <v>5942</v>
       </c>
     </row>
   </sheetData>
@@ -36574,41 +36592,43 @@
     <hyperlink ref="G69" r:id="rId60"/>
     <hyperlink ref="G70" r:id="rId61"/>
     <hyperlink ref="G71" r:id="rId62"/>
-    <hyperlink ref="G76" r:id="rId63"/>
-    <hyperlink ref="G79" r:id="rId64"/>
-    <hyperlink ref="G80" r:id="rId65"/>
-    <hyperlink ref="G81" r:id="rId66"/>
-    <hyperlink ref="G82" r:id="rId67"/>
-    <hyperlink ref="G83" r:id="rId68"/>
-    <hyperlink ref="G84" r:id="rId69"/>
-    <hyperlink ref="G85" r:id="rId70"/>
-    <hyperlink ref="G86" r:id="rId71"/>
-    <hyperlink ref="G87" r:id="rId72"/>
-    <hyperlink ref="G88" r:id="rId73"/>
-    <hyperlink ref="G89" r:id="rId74"/>
-    <hyperlink ref="G90" r:id="rId75"/>
-    <hyperlink ref="G91" r:id="rId76"/>
-    <hyperlink ref="G92" r:id="rId77"/>
-    <hyperlink ref="G93" r:id="rId78"/>
-    <hyperlink ref="G94" r:id="rId79"/>
-    <hyperlink ref="G95" r:id="rId80"/>
-    <hyperlink ref="G98" r:id="rId81"/>
-    <hyperlink ref="G99" r:id="rId82"/>
-    <hyperlink ref="G100" r:id="rId83"/>
-    <hyperlink ref="G101" r:id="rId84"/>
-    <hyperlink ref="G102" r:id="rId85"/>
-    <hyperlink ref="G103" r:id="rId86"/>
-    <hyperlink ref="G104" r:id="rId87"/>
-    <hyperlink ref="G105" r:id="rId88"/>
-    <hyperlink ref="G106" r:id="rId89"/>
-    <hyperlink ref="G107" r:id="rId90"/>
-    <hyperlink ref="G108" r:id="rId91"/>
-    <hyperlink ref="G109" r:id="rId92"/>
-    <hyperlink ref="G111" r:id="rId93"/>
-    <hyperlink ref="G112" r:id="rId94"/>
-    <hyperlink ref="G113" r:id="rId95"/>
-    <hyperlink ref="G118" r:id="rId96"/>
-    <hyperlink ref="G121" r:id="rId97"/>
+    <hyperlink ref="G73" r:id="rId63"/>
+    <hyperlink ref="G75" r:id="rId64"/>
+    <hyperlink ref="G76" r:id="rId65"/>
+    <hyperlink ref="G79" r:id="rId66"/>
+    <hyperlink ref="G80" r:id="rId67"/>
+    <hyperlink ref="G81" r:id="rId68"/>
+    <hyperlink ref="G82" r:id="rId69"/>
+    <hyperlink ref="G83" r:id="rId70"/>
+    <hyperlink ref="G84" r:id="rId71"/>
+    <hyperlink ref="G85" r:id="rId72"/>
+    <hyperlink ref="G86" r:id="rId73"/>
+    <hyperlink ref="G87" r:id="rId74"/>
+    <hyperlink ref="G88" r:id="rId75"/>
+    <hyperlink ref="G89" r:id="rId76"/>
+    <hyperlink ref="G90" r:id="rId77"/>
+    <hyperlink ref="G91" r:id="rId78"/>
+    <hyperlink ref="G92" r:id="rId79"/>
+    <hyperlink ref="G93" r:id="rId80"/>
+    <hyperlink ref="G94" r:id="rId81"/>
+    <hyperlink ref="G95" r:id="rId82"/>
+    <hyperlink ref="G98" r:id="rId83"/>
+    <hyperlink ref="G99" r:id="rId84"/>
+    <hyperlink ref="G100" r:id="rId85"/>
+    <hyperlink ref="G101" r:id="rId86"/>
+    <hyperlink ref="G102" r:id="rId87"/>
+    <hyperlink ref="G103" r:id="rId88"/>
+    <hyperlink ref="G104" r:id="rId89"/>
+    <hyperlink ref="G105" r:id="rId90"/>
+    <hyperlink ref="G106" r:id="rId91"/>
+    <hyperlink ref="G107" r:id="rId92"/>
+    <hyperlink ref="G108" r:id="rId93"/>
+    <hyperlink ref="G109" r:id="rId94"/>
+    <hyperlink ref="G111" r:id="rId95"/>
+    <hyperlink ref="G112" r:id="rId96"/>
+    <hyperlink ref="G113" r:id="rId97"/>
+    <hyperlink ref="G118" r:id="rId98"/>
+    <hyperlink ref="G121" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -36666,7 +36686,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5941</v>
+        <v>5943</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36712,7 +36732,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5942</v>
+        <v>5944</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36758,10 +36778,10 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F6" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36781,10 +36801,10 @@
         <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F7" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36804,10 +36824,10 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F8" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36827,10 +36847,10 @@
         <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F9" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36850,7 +36870,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5945</v>
+        <v>5947</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36919,10 +36939,10 @@
         <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="F13" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37057,7 +37077,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5946</v>
+        <v>5948</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37126,7 +37146,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5947</v>
+        <v>5949</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37264,7 +37284,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5948</v>
+        <v>5950</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37287,7 +37307,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5949</v>
+        <v>5951</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37310,7 +37330,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5950</v>
+        <v>5952</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37356,7 +37376,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5951</v>
+        <v>5953</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37402,7 +37422,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37425,7 +37445,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5953</v>
+        <v>5955</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37471,7 +37491,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5952</v>
+        <v>5954</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37540,7 +37560,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5954</v>
+        <v>5956</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37563,7 +37583,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5955</v>
+        <v>5957</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37724,10 +37744,10 @@
         <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F48" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37747,10 +37767,10 @@
         <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F49" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37931,10 +37951,10 @@
         <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F57" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -38023,10 +38043,10 @@
         <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>5958</v>
+        <v>5960</v>
       </c>
       <c r="F61" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -38046,10 +38066,10 @@
         <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>5959</v>
+        <v>5961</v>
       </c>
       <c r="F62" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38069,7 +38089,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5960</v>
+        <v>5962</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38092,10 +38112,10 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F64" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38207,10 +38227,10 @@
         <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>5956</v>
+        <v>5958</v>
       </c>
       <c r="F69" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38230,7 +38250,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5961</v>
+        <v>5963</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38598,7 +38618,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5962</v>
+        <v>5964</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38621,10 +38641,10 @@
         <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>5963</v>
+        <v>5965</v>
       </c>
       <c r="F87" t="s">
-        <v>5944</v>
+        <v>5946</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17278" uniqueCount="5968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17281" uniqueCount="5967">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18994,6 +18994,9 @@
     <t>TC_CUST_NEG_067.png</t>
   </si>
   <si>
+    <t>2026-06-21 14:41 IST — pass in 76ms</t>
+  </si>
+  <si>
     <t>2026-06-20 15:52 IST — pass in 18.2s</t>
   </si>
   <si>
@@ -19090,13 +19093,7 @@
     <t>2026-06-21 13:47 IST — pass in 224ms</t>
   </si>
   <si>
-    <t>DB spec (not e2e)</t>
-  </si>
-  <si>
-    <t>[DB] not run as live e2e</t>
-  </si>
-  <si>
-    <t>Hardcoded gateway/value check — DB-layer test (db/queries), not e2e</t>
+    <t>2026-06-21 14:41 IST — pass in 184ms</t>
   </si>
   <si>
     <t>2026-06-20 15:52 IST — pass in 2.4s</t>
@@ -23341,10 +23338,10 @@
         <v>587</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L119" s="13" t="s">
         <v>68</v>
@@ -24102,9 +24099,15 @@
       <c r="I143" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="J143" s="12"/>
-      <c r="K143" s="13"/>
-      <c r="L143" s="13"/>
+      <c r="J143" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K143" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L143" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="144" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
@@ -35947,19 +35950,19 @@
         <v>582</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C96" s="18" t="s">
         <v>5761</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E96" t="s">
-        <v>5793</v>
+        <v>5904</v>
       </c>
       <c r="F96" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="G96" t="s">
         <v>24</v>
@@ -36002,13 +36005,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5905</v>
+        <v>5906</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -36025,13 +36028,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>5907</v>
+        <v>5908</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -36048,13 +36051,13 @@
         <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="F100" t="s">
         <v>66</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>5909</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -36071,13 +36074,13 @@
         <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="F101" t="s">
         <v>66</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>5911</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -36094,13 +36097,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36117,13 +36120,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>5915</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36140,13 +36143,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36163,13 +36166,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36186,13 +36189,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>5920</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36209,13 +36212,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>5922</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36232,13 +36235,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>5924</v>
+        <v>5925</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36261,7 +36264,7 @@
         <v>662</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5925</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36281,7 +36284,7 @@
         <v>5848</v>
       </c>
       <c r="F110" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36307,7 +36310,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36330,7 +36333,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5928</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36353,7 +36356,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36364,16 +36367,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="D114" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="E114" t="s">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="F114" t="s">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36393,7 +36396,7 @@
         <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>5934</v>
+        <v>5935</v>
       </c>
       <c r="F115" t="s">
         <v>66</v>
@@ -36416,7 +36419,7 @@
         <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="F116" t="s">
         <v>66</v>
@@ -36430,19 +36433,19 @@
         <v>706</v>
       </c>
       <c r="B117" t="s">
-        <v>5830</v>
+        <v>67</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>5936</v>
+        <v>5761</v>
       </c>
       <c r="D117" t="s">
-        <v>5832</v>
+        <v>67</v>
       </c>
       <c r="E117" t="s">
         <v>5937</v>
       </c>
       <c r="F117" t="s">
-        <v>5938</v>
+        <v>66</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -36462,13 +36465,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5940</v>
+        <v>5939</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36485,7 +36488,7 @@
         <v>67</v>
       </c>
       <c r="E119" t="s">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F119" t="s">
         <v>66</v>
@@ -36508,7 +36511,7 @@
         <v>67</v>
       </c>
       <c r="E120" t="s">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="F120" t="s">
         <v>66</v>
@@ -36531,13 +36534,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5943</v>
+        <v>5942</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5944</v>
+        <v>5943</v>
       </c>
     </row>
   </sheetData>
@@ -36699,7 +36702,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36745,7 +36748,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36791,10 +36794,10 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
+        <v>5946</v>
+      </c>
+      <c r="F6" t="s">
         <v>5947</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5948</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36814,10 +36817,10 @@
         <v>180</v>
       </c>
       <c r="E7" t="s">
+        <v>5946</v>
+      </c>
+      <c r="F7" t="s">
         <v>5947</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5948</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36837,10 +36840,10 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
+        <v>5946</v>
+      </c>
+      <c r="F8" t="s">
         <v>5947</v>
-      </c>
-      <c r="F8" t="s">
-        <v>5948</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36860,10 +36863,10 @@
         <v>180</v>
       </c>
       <c r="E9" t="s">
+        <v>5946</v>
+      </c>
+      <c r="F9" t="s">
         <v>5947</v>
-      </c>
-      <c r="F9" t="s">
-        <v>5948</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36883,7 +36886,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5949</v>
+        <v>5948</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36952,10 +36955,10 @@
         <v>180</v>
       </c>
       <c r="E13" t="s">
+        <v>5946</v>
+      </c>
+      <c r="F13" t="s">
         <v>5947</v>
-      </c>
-      <c r="F13" t="s">
-        <v>5948</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37090,7 +37093,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5950</v>
+        <v>5949</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37159,7 +37162,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5951</v>
+        <v>5950</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37297,7 +37300,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5952</v>
+        <v>5951</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37320,7 +37323,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5953</v>
+        <v>5952</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37343,7 +37346,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5954</v>
+        <v>5953</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37389,7 +37392,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5955</v>
+        <v>5954</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37435,7 +37438,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5956</v>
+        <v>5955</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37458,7 +37461,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37504,7 +37507,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5956</v>
+        <v>5955</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37573,7 +37576,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37596,7 +37599,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5959</v>
+        <v>5958</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37757,10 +37760,10 @@
         <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="F48" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37780,10 +37783,10 @@
         <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>5961</v>
+        <v>5960</v>
       </c>
       <c r="F49" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37964,10 +37967,10 @@
         <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="F57" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -38056,10 +38059,10 @@
         <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="F61" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -38079,10 +38082,10 @@
         <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="F62" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38102,7 +38105,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5964</v>
+        <v>5963</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38125,10 +38128,10 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="F64" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38240,10 +38243,10 @@
         <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="F69" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38263,7 +38266,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5965</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38631,7 +38634,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5966</v>
+        <v>5965</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38654,10 +38657,10 @@
         <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>5967</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17281" uniqueCount="5967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="5965">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18823,13 +18823,7 @@
     <t>ADM_CUST_099.png</t>
   </si>
   <si>
-    <t>API spec (not e2e)</t>
-  </si>
-  <si>
-    <t>[API] not run as live e2e</t>
-  </si>
-  <si>
-    <t>Verified at API layer (tests/api) — not an e2e/browser test</t>
+    <t>2026-06-21 15:05 IST — skip in n/a</t>
   </si>
   <si>
     <t>TC_CUST_NEG_091.png</t>
@@ -19063,7 +19057,7 @@
     <t>TC_CUST_NEG_093.png</t>
   </si>
   <si>
-    <t>Backend validation gap (parking enabled=true,count=0) — API-layer test, not e2e</t>
+    <t>2026-06-21 15:05 IST — skip in validation gap</t>
   </si>
   <si>
     <t>ADM_CUST_034.png</t>
@@ -21901,9 +21895,15 @@
       <c r="I74" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="J74" s="12"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
+      <c r="J74" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K74" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="L74" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="75" ht="51" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
@@ -23833,9 +23833,15 @@
       <c r="I134" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="J134" s="12"/>
-      <c r="K134" s="13"/>
-      <c r="L134" s="13"/>
+      <c r="J134" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K134" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="L134" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
@@ -35030,19 +35036,19 @@
         <v>357</v>
       </c>
       <c r="B56" t="s">
-        <v>5830</v>
+        <v>180</v>
       </c>
       <c r="C56" s="18" t="s">
+        <v>5761</v>
+      </c>
+      <c r="D56" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" t="s">
         <v>5847</v>
       </c>
-      <c r="D56" t="s">
-        <v>5832</v>
-      </c>
-      <c r="E56" t="s">
-        <v>5848</v>
-      </c>
       <c r="F56" t="s">
-        <v>5849</v>
+        <v>179</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -35068,7 +35074,7 @@
         <v>66</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>5850</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -35085,7 +35091,7 @@
         <v>180</v>
       </c>
       <c r="E58" t="s">
-        <v>5851</v>
+        <v>5849</v>
       </c>
       <c r="F58" t="s">
         <v>179</v>
@@ -35131,13 +35137,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5852</v>
+        <v>5850</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>5853</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -35154,13 +35160,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5854</v>
+        <v>5852</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>5855</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -35183,7 +35189,7 @@
         <v>394</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>5856</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -35200,13 +35206,13 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5857</v>
+        <v>5855</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>5858</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -35269,13 +35275,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>5859</v>
+        <v>5857</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>5860</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -35321,7 +35327,7 @@
         <v>66</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>5861</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -35344,7 +35350,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>5862</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -35361,13 +35367,13 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5863</v>
+        <v>5861</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>5864</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -35390,7 +35396,7 @@
         <v>66</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>5865</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -35407,13 +35413,13 @@
         <v>67</v>
       </c>
       <c r="E72" t="s">
-        <v>5866</v>
+        <v>5864</v>
       </c>
       <c r="F72" t="s">
         <v>451</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>5867</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -35430,13 +35436,13 @@
         <v>67</v>
       </c>
       <c r="E73" t="s">
-        <v>5868</v>
+        <v>5866</v>
       </c>
       <c r="F73" t="s">
         <v>66</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>5869</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -35456,7 +35462,7 @@
         <v>5833</v>
       </c>
       <c r="F74" t="s">
-        <v>5870</v>
+        <v>5868</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35476,13 +35482,13 @@
         <v>67</v>
       </c>
       <c r="E75" t="s">
-        <v>5871</v>
+        <v>5869</v>
       </c>
       <c r="F75" t="s">
         <v>66</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>5872</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -35499,13 +35505,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5873</v>
+        <v>5871</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>5874</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35516,16 +35522,16 @@
         <v>5830</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5875</v>
+        <v>5873</v>
       </c>
       <c r="D77" t="s">
         <v>5832</v>
       </c>
       <c r="E77" t="s">
-        <v>5876</v>
+        <v>5874</v>
       </c>
       <c r="F77" t="s">
-        <v>5877</v>
+        <v>5875</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35539,16 +35545,16 @@
         <v>5830</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5875</v>
+        <v>5873</v>
       </c>
       <c r="D78" t="s">
         <v>5832</v>
       </c>
       <c r="E78" t="s">
+        <v>5874</v>
+      </c>
+      <c r="F78" t="s">
         <v>5876</v>
-      </c>
-      <c r="F78" t="s">
-        <v>5878</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35568,13 +35574,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5879</v>
+        <v>5877</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>5880</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35591,13 +35597,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5881</v>
+        <v>5879</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>5882</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35614,13 +35620,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5883</v>
+        <v>5881</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>5884</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35637,13 +35643,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5883</v>
+        <v>5881</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>5885</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35660,13 +35666,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5873</v>
+        <v>5871</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>5886</v>
+        <v>5884</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35683,13 +35689,13 @@
         <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>5887</v>
+        <v>5885</v>
       </c>
       <c r="F84" t="s">
         <v>179</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>5888</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35706,13 +35712,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5879</v>
+        <v>5877</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>5889</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35729,13 +35735,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5890</v>
+        <v>5888</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>5891</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -35752,13 +35758,13 @@
         <v>67</v>
       </c>
       <c r="E87" t="s">
-        <v>5892</v>
+        <v>5890</v>
       </c>
       <c r="F87" t="s">
         <v>537</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>5893</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -35781,7 +35787,7 @@
         <v>66</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>5894</v>
+        <v>5892</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -35798,13 +35804,13 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>5852</v>
+        <v>5850</v>
       </c>
       <c r="F89" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>5895</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -35827,7 +35833,7 @@
         <v>66</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>5896</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -35850,7 +35856,7 @@
         <v>66</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>5897</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -35873,7 +35879,7 @@
         <v>565</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>5898</v>
+        <v>5896</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -35896,7 +35902,7 @@
         <v>66</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>5899</v>
+        <v>5897</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -35913,13 +35919,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5900</v>
+        <v>5898</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>5901</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -35936,13 +35942,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>5902</v>
+        <v>5900</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>5903</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -35959,7 +35965,7 @@
         <v>67</v>
       </c>
       <c r="E96" t="s">
-        <v>5904</v>
+        <v>5902</v>
       </c>
       <c r="F96" t="s">
         <v>66</v>
@@ -36005,13 +36011,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>5906</v>
+        <v>5904</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -36028,13 +36034,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>5908</v>
+        <v>5906</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -36051,13 +36057,13 @@
         <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5909</v>
+        <v>5907</v>
       </c>
       <c r="F100" t="s">
         <v>66</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>5910</v>
+        <v>5908</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -36074,13 +36080,13 @@
         <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>5911</v>
+        <v>5909</v>
       </c>
       <c r="F101" t="s">
         <v>66</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>5912</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -36097,13 +36103,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5913</v>
+        <v>5911</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>5914</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36120,13 +36126,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5915</v>
+        <v>5913</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>5916</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36143,13 +36149,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5917</v>
+        <v>5915</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>5918</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36166,13 +36172,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5915</v>
+        <v>5913</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>5919</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36189,13 +36195,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5920</v>
+        <v>5918</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>5921</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36212,13 +36218,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5922</v>
+        <v>5920</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>5923</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36235,13 +36241,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5924</v>
+        <v>5922</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>5925</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36264,7 +36270,7 @@
         <v>662</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>5926</v>
+        <v>5924</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36272,19 +36278,19 @@
         <v>663</v>
       </c>
       <c r="B110" t="s">
-        <v>5830</v>
+        <v>180</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>5847</v>
+        <v>5761</v>
       </c>
       <c r="D110" t="s">
-        <v>5832</v>
+        <v>180</v>
       </c>
       <c r="E110" t="s">
-        <v>5848</v>
+        <v>5925</v>
       </c>
       <c r="F110" t="s">
-        <v>5927</v>
+        <v>179</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>
@@ -36310,7 +36316,7 @@
         <v>66</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>5928</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36333,7 +36339,7 @@
         <v>66</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>5929</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36356,7 +36362,7 @@
         <v>66</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>5930</v>
+        <v>5928</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36367,16 +36373,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
+        <v>5929</v>
+      </c>
+      <c r="D114" t="s">
+        <v>5930</v>
+      </c>
+      <c r="E114" t="s">
         <v>5931</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
         <v>5932</v>
-      </c>
-      <c r="E114" t="s">
-        <v>5933</v>
-      </c>
-      <c r="F114" t="s">
-        <v>5934</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36396,7 +36402,7 @@
         <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>5935</v>
+        <v>5933</v>
       </c>
       <c r="F115" t="s">
         <v>66</v>
@@ -36419,7 +36425,7 @@
         <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>5936</v>
+        <v>5934</v>
       </c>
       <c r="F116" t="s">
         <v>66</v>
@@ -36442,7 +36448,7 @@
         <v>67</v>
       </c>
       <c r="E117" t="s">
-        <v>5937</v>
+        <v>5935</v>
       </c>
       <c r="F117" t="s">
         <v>66</v>
@@ -36465,13 +36471,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>5938</v>
+        <v>5936</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>5939</v>
+        <v>5937</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36488,7 +36494,7 @@
         <v>67</v>
       </c>
       <c r="E119" t="s">
-        <v>5940</v>
+        <v>5938</v>
       </c>
       <c r="F119" t="s">
         <v>66</v>
@@ -36511,7 +36517,7 @@
         <v>67</v>
       </c>
       <c r="E120" t="s">
-        <v>5941</v>
+        <v>5939</v>
       </c>
       <c r="F120" t="s">
         <v>66</v>
@@ -36534,13 +36540,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>5942</v>
+        <v>5940</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>5943</v>
+        <v>5941</v>
       </c>
     </row>
   </sheetData>
@@ -36702,7 +36708,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5944</v>
+        <v>5942</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36748,7 +36754,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5945</v>
+        <v>5943</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -36794,10 +36800,10 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>5946</v>
+        <v>5944</v>
       </c>
       <c r="F6" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -36817,10 +36823,10 @@
         <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>5946</v>
+        <v>5944</v>
       </c>
       <c r="F7" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -36840,10 +36846,10 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>5946</v>
+        <v>5944</v>
       </c>
       <c r="F8" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -36863,10 +36869,10 @@
         <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>5946</v>
+        <v>5944</v>
       </c>
       <c r="F9" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -36886,7 +36892,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5948</v>
+        <v>5946</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -36955,10 +36961,10 @@
         <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>5946</v>
+        <v>5944</v>
       </c>
       <c r="F13" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37093,7 +37099,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5949</v>
+        <v>5947</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37162,7 +37168,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5950</v>
+        <v>5948</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37300,7 +37306,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5951</v>
+        <v>5949</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37323,7 +37329,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5952</v>
+        <v>5950</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37346,7 +37352,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5953</v>
+        <v>5951</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37392,7 +37398,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5954</v>
+        <v>5952</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37438,7 +37444,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5955</v>
+        <v>5953</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37461,7 +37467,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5956</v>
+        <v>5954</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37507,7 +37513,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5955</v>
+        <v>5953</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37576,7 +37582,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5957</v>
+        <v>5955</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37599,7 +37605,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5958</v>
+        <v>5956</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37760,10 +37766,10 @@
         <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F48" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -37783,10 +37789,10 @@
         <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>5960</v>
+        <v>5958</v>
       </c>
       <c r="F49" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -37967,10 +37973,10 @@
         <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F57" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -38059,10 +38065,10 @@
         <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>5961</v>
+        <v>5959</v>
       </c>
       <c r="F61" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -38082,10 +38088,10 @@
         <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>5962</v>
+        <v>5960</v>
       </c>
       <c r="F62" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38105,7 +38111,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5963</v>
+        <v>5961</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38128,10 +38134,10 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F64" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38243,10 +38249,10 @@
         <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F69" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38266,7 +38272,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5964</v>
+        <v>5962</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38634,7 +38640,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5965</v>
+        <v>5963</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38657,10 +38663,10 @@
         <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F87" t="s">
-        <v>5947</v>
+        <v>5945</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18823,7 +18823,7 @@
     <t>ADM_CUST_099.png</t>
   </si>
   <si>
-    <t>2026-06-21 15:05 IST — skip in n/a</t>
+    <t>2026-06-21 16:43 IST — skip in n/a</t>
   </si>
   <si>
     <t>TC_CUST_NEG_091.png</t>
@@ -19057,7 +19057,7 @@
     <t>TC_CUST_NEG_093.png</t>
   </si>
   <si>
-    <t>2026-06-21 15:05 IST — skip in validation gap</t>
+    <t>2026-06-21 16:43 IST — skip in validation gap</t>
   </si>
   <si>
     <t>ADM_CUST_034.png</t>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -19057,7 +19057,7 @@
     <t>TC_CUST_NEG_093.png</t>
   </si>
   <si>
-    <t>2026-06-21 16:43 IST — skip in validation gap</t>
+    <t>2026-06-21 16:54 IST — pass in 124ms</t>
   </si>
   <si>
     <t>ADM_CUST_034.png</t>
@@ -23834,10 +23834,10 @@
         <v>668</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L134" s="13" t="s">
         <v>68</v>
@@ -36278,19 +36278,19 @@
         <v>663</v>
       </c>
       <c r="B110" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C110" s="19" t="s">
         <v>5761</v>
       </c>
       <c r="D110" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E110" t="s">
         <v>5925</v>
       </c>
       <c r="F110" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="G110" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -18823,7 +18823,7 @@
     <t>ADM_CUST_099.png</t>
   </si>
   <si>
-    <t>2026-06-21 16:43 IST — skip in n/a</t>
+    <t>2026-06-21 17:30 IST — pass in 164ms</t>
   </si>
   <si>
     <t>TC_CUST_NEG_091.png</t>
@@ -18988,7 +18988,7 @@
     <t>TC_CUST_NEG_067.png</t>
   </si>
   <si>
-    <t>2026-06-21 14:41 IST — pass in 76ms</t>
+    <t>2026-06-21 17:30 IST — pass in 223ms</t>
   </si>
   <si>
     <t>2026-06-20 15:52 IST — pass in 18.2s</t>
@@ -19087,7 +19087,7 @@
     <t>2026-06-21 13:47 IST — pass in 224ms</t>
   </si>
   <si>
-    <t>2026-06-21 14:41 IST — pass in 184ms</t>
+    <t>2026-06-21 17:30 IST — pass in 296ms</t>
   </si>
   <si>
     <t>2026-06-20 15:52 IST — pass in 2.4s</t>
@@ -21896,10 +21896,10 @@
         <v>361</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L74" s="13" t="s">
         <v>68</v>
@@ -35036,19 +35036,19 @@
         <v>357</v>
       </c>
       <c r="B56" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>5761</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E56" t="s">
         <v>5847</v>
       </c>
       <c r="F56" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6053">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18622,127 +18622,172 @@
     <t>ADM_LGN_005.png</t>
   </si>
   <si>
+    <t>2026-06-21 18:59 IST — pass in 2.0s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_040.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 1.9s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_009.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:41 IST — pass in 621ms</t>
+  </si>
+  <si>
+    <t>ADM_LGN_010.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 2.4s</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 1.8s</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 7.6s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_026.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 1.5s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_027.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 1.0m</t>
+  </si>
+  <si>
+    <t>ADM_LGN_028.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 1.1m</t>
+  </si>
+  <si>
+    <t>ADM_LGN_029.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 1.0m</t>
+  </si>
+  <si>
+    <t>ADM_LGN_018.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_019.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 2.0s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_068.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_069.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 1.7s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_020.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 2.3s</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:41 IST — pass in 483ms</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 182ms</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 2.6s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_031.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 1.4s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_011.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_012.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_013.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_017.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 19:03 IST — pass in 4.8s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_074.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_067.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 1.5s</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — pass in 2.3s</t>
+  </si>
+  <si>
+    <t>ADM_LGN_014.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_015.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_016.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_066.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:38 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>ADM_LGN_021.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_022.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_023.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_024.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 19:03 IST — pass in 1.0m</t>
+  </si>
+  <si>
+    <t>ADM_LGN_079.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_025.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_037.png</t>
+  </si>
+  <si>
+    <t>ADM_LGN_038.png</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 109ms</t>
+  </si>
+  <si>
     <t>Not Automated</t>
   </si>
   <si>
-    <t>ADM_LGN_040.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_009.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:41 IST — pass in 621ms</t>
-  </si>
-  <si>
-    <t>ADM_LGN_010.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 7.6s</t>
-  </si>
-  <si>
-    <t>ADM_LGN_026.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 1.5s</t>
-  </si>
-  <si>
-    <t>ADM_LGN_027.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 1.0m</t>
-  </si>
-  <si>
-    <t>ADM_LGN_028.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 1.1m</t>
-  </si>
-  <si>
-    <t>ADM_LGN_029.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_018.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_019.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 2.0s</t>
-  </si>
-  <si>
-    <t>ADM_LGN_068.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_069.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 1.7s</t>
-  </si>
-  <si>
-    <t>ADM_LGN_020.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:41 IST — pass in 483ms</t>
-  </si>
-  <si>
-    <t>ADM_LGN_031.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 1.4s</t>
-  </si>
-  <si>
-    <t>ADM_LGN_011.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_012.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_013.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_017.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_067.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — pass in 2.3s</t>
-  </si>
-  <si>
-    <t>ADM_LGN_014.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_015.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_016.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_066.png</t>
-  </si>
-  <si>
-    <t>2026-06-21 18:38 IST — skip in n/a</t>
-  </si>
-  <si>
-    <t>ADM_LGN_021.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_022.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_023.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_024.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_025.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_037.png</t>
-  </si>
-  <si>
-    <t>ADM_LGN_038.png</t>
+    <t>2026-06-21 18:59 IST — pass in 93ms</t>
   </si>
   <si>
     <t>2026-06-21 18:38 IST — pass in 1.9s</t>
@@ -18757,9 +18802,15 @@
     <t>ADM_LGN_063.png</t>
   </si>
   <si>
+    <t>2026-06-21 18:59 IST — pass in 1.2s</t>
+  </si>
+  <si>
     <t>2026-06-21 18:41 IST — pass in 122ms</t>
   </si>
   <si>
+    <t>2026-06-21 18:59 IST — pass in 872ms</t>
+  </si>
+  <si>
     <t>ADM_LGN_008.png</t>
   </si>
   <si>
@@ -18776,6 +18827,12 @@
   </si>
   <si>
     <t>2026-06-21 18:41 IST — pass in 307ms</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>2026-06-21 18:59 IST — pass in 4.1s</t>
   </si>
   <si>
     <t>2026-06-20 15:52 IST — pass in 17.7s</t>
@@ -32416,19 +32473,19 @@
         <v>780</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C9" s="20" t="s">
+        <v>5768</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
         <v>5780</v>
       </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -32462,19 +32519,19 @@
         <v>792</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>5782</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>
@@ -32500,7 +32557,7 @@
         <v>66</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -32517,7 +32574,7 @@
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
@@ -32546,7 +32603,7 @@
         <v>66</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -32554,19 +32611,19 @@
         <v>820</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>5786</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
         <v>24</v>
@@ -32577,19 +32634,19 @@
         <v>826</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>5787</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
         <v>24</v>
@@ -32609,13 +32666,13 @@
         <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>5785</v>
+        <v>5788</v>
       </c>
       <c r="F17" t="s">
         <v>66</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>5786</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -32632,13 +32689,13 @@
         <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>5787</v>
+        <v>5790</v>
       </c>
       <c r="F18" t="s">
         <v>66</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>5788</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -32655,13 +32712,13 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5789</v>
+        <v>5792</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>5790</v>
+        <v>5793</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -32678,13 +32735,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>5791</v>
+        <v>5794</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>5792</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -32692,19 +32749,19 @@
         <v>856</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>5796</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
         <v>24</v>
@@ -32730,7 +32787,7 @@
         <v>66</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>5793</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -32753,7 +32810,7 @@
         <v>66</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>5794</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -32770,13 +32827,13 @@
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>5795</v>
+        <v>5799</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>5796</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -32799,7 +32856,7 @@
         <v>66</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>5797</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -32816,13 +32873,13 @@
         <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>5798</v>
+        <v>5802</v>
       </c>
       <c r="F26" t="s">
         <v>66</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>5799</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -32830,19 +32887,19 @@
         <v>893</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>5804</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
         <v>24</v>
@@ -32862,7 +32919,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5800</v>
+        <v>5805</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -32885,7 +32942,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5800</v>
+        <v>5805</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -32899,19 +32956,19 @@
         <v>913</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>5806</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
@@ -32922,19 +32979,19 @@
         <v>919</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>5807</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
         <v>24</v>
@@ -32960,7 +33017,7 @@
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>5801</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -32977,13 +33034,13 @@
         <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F33" t="s">
         <v>66</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>5803</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -33000,13 +33057,13 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>5804</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -33023,13 +33080,13 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>5805</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -33046,13 +33103,13 @@
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F36" t="s">
         <v>66</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>5806</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -33060,22 +33117,22 @@
         <v>956</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>5814</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>5815</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -33098,7 +33155,7 @@
         <v>66</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>5807</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -33106,19 +33163,19 @@
         <v>968</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>5817</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G39" t="s">
         <v>24</v>
@@ -33138,13 +33195,13 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5808</v>
+        <v>5818</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>5809</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -33167,7 +33224,7 @@
         <v>66</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>5810</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -33184,13 +33241,13 @@
         <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F42" t="s">
         <v>66</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>5811</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -33213,7 +33270,7 @@
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>5812</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -33230,7 +33287,7 @@
         <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>5813</v>
+        <v>5823</v>
       </c>
       <c r="F44" t="s">
         <v>179</v>
@@ -33259,7 +33316,7 @@
         <v>66</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>5814</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -33276,13 +33333,13 @@
         <v>67</v>
       </c>
       <c r="E46" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F46" t="s">
         <v>66</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>5815</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -33299,13 +33356,13 @@
         <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>5787</v>
+        <v>5790</v>
       </c>
       <c r="F47" t="s">
         <v>66</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>5816</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -33322,13 +33379,13 @@
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>5787</v>
+        <v>5790</v>
       </c>
       <c r="F48" t="s">
         <v>66</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>5817</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -33336,22 +33393,22 @@
         <v>1030</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>24</v>
+        <v>5828</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>5829</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -33374,7 +33431,7 @@
         <v>66</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>5818</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -33391,13 +33448,13 @@
         <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>5787</v>
+        <v>5790</v>
       </c>
       <c r="F51" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>5819</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -33414,13 +33471,13 @@
         <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>5802</v>
+        <v>5809</v>
       </c>
       <c r="F52" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>5820</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -33428,19 +33485,19 @@
         <v>1055</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>5833</v>
       </c>
       <c r="F53" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G53" t="s">
         <v>24</v>
@@ -33500,7 +33557,7 @@
         <v>1070</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -33523,7 +33580,7 @@
         <v>1070</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -33543,19 +33600,19 @@
         <v>1095</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>5835</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -33575,13 +33632,13 @@
         <v>67</v>
       </c>
       <c r="E59" t="s">
-        <v>5821</v>
+        <v>5836</v>
       </c>
       <c r="F59" t="s">
         <v>66</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>5822</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -33598,13 +33655,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5821</v>
+        <v>5836</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>5823</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -33621,13 +33678,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5821</v>
+        <v>5836</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>5824</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -33635,19 +33692,19 @@
         <v>1119</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>5768</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>5840</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -33667,7 +33724,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5825</v>
+        <v>5841</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -33681,19 +33738,19 @@
         <v>1133</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>5842</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -33719,7 +33776,7 @@
         <v>66</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>5826</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -33736,13 +33793,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>5827</v>
+        <v>5844</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>5828</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -33765,7 +33822,7 @@
         <v>66</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>5829</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -33782,7 +33839,7 @@
         <v>180</v>
       </c>
       <c r="E68" t="s">
-        <v>5813</v>
+        <v>5823</v>
       </c>
       <c r="F68" t="s">
         <v>179</v>
@@ -33805,7 +33862,7 @@
         <v>67</v>
       </c>
       <c r="E69" t="s">
-        <v>5830</v>
+        <v>5847</v>
       </c>
       <c r="F69" t="s">
         <v>66</v>
@@ -33828,7 +33885,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5831</v>
+        <v>5848</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -33842,19 +33899,19 @@
         <v>1175</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>5849</v>
       </c>
       <c r="F71" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="G71" t="s">
         <v>24</v>
@@ -33891,7 +33948,7 @@
         <v>1070</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -33914,7 +33971,7 @@
         <v>1070</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
@@ -33934,19 +33991,19 @@
         <v>1207</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>5780</v>
+        <v>5768</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>5850</v>
       </c>
       <c r="F75" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>
@@ -33978,24 +34035,26 @@
     <hyperlink ref="G34" r:id="rId22"/>
     <hyperlink ref="G35" r:id="rId23"/>
     <hyperlink ref="G36" r:id="rId24"/>
-    <hyperlink ref="G38" r:id="rId25"/>
-    <hyperlink ref="G40" r:id="rId26"/>
-    <hyperlink ref="G41" r:id="rId27"/>
-    <hyperlink ref="G42" r:id="rId28"/>
-    <hyperlink ref="G43" r:id="rId29"/>
-    <hyperlink ref="G45" r:id="rId30"/>
-    <hyperlink ref="G46" r:id="rId31"/>
-    <hyperlink ref="G47" r:id="rId32"/>
-    <hyperlink ref="G48" r:id="rId33"/>
-    <hyperlink ref="G50" r:id="rId34"/>
-    <hyperlink ref="G51" r:id="rId35"/>
-    <hyperlink ref="G52" r:id="rId36"/>
-    <hyperlink ref="G59" r:id="rId37"/>
-    <hyperlink ref="G60" r:id="rId38"/>
-    <hyperlink ref="G61" r:id="rId39"/>
-    <hyperlink ref="G65" r:id="rId40"/>
-    <hyperlink ref="G66" r:id="rId41"/>
-    <hyperlink ref="G67" r:id="rId42"/>
+    <hyperlink ref="G37" r:id="rId25"/>
+    <hyperlink ref="G38" r:id="rId26"/>
+    <hyperlink ref="G40" r:id="rId27"/>
+    <hyperlink ref="G41" r:id="rId28"/>
+    <hyperlink ref="G42" r:id="rId29"/>
+    <hyperlink ref="G43" r:id="rId30"/>
+    <hyperlink ref="G45" r:id="rId31"/>
+    <hyperlink ref="G46" r:id="rId32"/>
+    <hyperlink ref="G47" r:id="rId33"/>
+    <hyperlink ref="G48" r:id="rId34"/>
+    <hyperlink ref="G49" r:id="rId35"/>
+    <hyperlink ref="G50" r:id="rId36"/>
+    <hyperlink ref="G51" r:id="rId37"/>
+    <hyperlink ref="G52" r:id="rId38"/>
+    <hyperlink ref="G59" r:id="rId39"/>
+    <hyperlink ref="G60" r:id="rId40"/>
+    <hyperlink ref="G61" r:id="rId41"/>
+    <hyperlink ref="G65" r:id="rId42"/>
+    <hyperlink ref="G66" r:id="rId43"/>
+    <hyperlink ref="G67" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -34053,13 +34112,13 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5832</v>
+        <v>5851</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>5833</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -34076,13 +34135,13 @@
         <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>5832</v>
+        <v>5851</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>5834</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -34099,13 +34158,13 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5832</v>
+        <v>5851</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>5835</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -34122,13 +34181,13 @@
         <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>5836</v>
+        <v>5855</v>
       </c>
       <c r="F5" t="s">
         <v>66</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>5837</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -34145,13 +34204,13 @@
         <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>5838</v>
+        <v>5857</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>5839</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -34168,13 +34227,13 @@
         <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>5838</v>
+        <v>5857</v>
       </c>
       <c r="F7" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>5840</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -34191,13 +34250,13 @@
         <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>5841</v>
+        <v>5860</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>5842</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -34214,13 +34273,13 @@
         <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>5832</v>
+        <v>5851</v>
       </c>
       <c r="F9" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>5843</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -34237,13 +34296,13 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>5844</v>
+        <v>5863</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>5845</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -34260,13 +34319,13 @@
         <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>5846</v>
+        <v>5865</v>
       </c>
       <c r="F11" t="s">
         <v>66</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>5847</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -34283,13 +34342,13 @@
         <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>5844</v>
+        <v>5863</v>
       </c>
       <c r="F12" t="s">
         <v>66</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>5848</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -34306,13 +34365,13 @@
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>5844</v>
+        <v>5863</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>5849</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -34329,13 +34388,13 @@
         <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>5844</v>
+        <v>5863</v>
       </c>
       <c r="F14" t="s">
         <v>66</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>5850</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -34352,13 +34411,13 @@
         <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>5844</v>
+        <v>5863</v>
       </c>
       <c r="F15" t="s">
         <v>66</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>5851</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -34375,13 +34434,13 @@
         <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>5838</v>
+        <v>5857</v>
       </c>
       <c r="F16" t="s">
         <v>66</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>5852</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -34398,13 +34457,13 @@
         <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>5853</v>
+        <v>5872</v>
       </c>
       <c r="F17" t="s">
         <v>66</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>5854</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -34421,13 +34480,13 @@
         <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>5855</v>
+        <v>5874</v>
       </c>
       <c r="F18" t="s">
         <v>66</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>5856</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -34444,13 +34503,13 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>5832</v>
+        <v>5851</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>5857</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -34467,13 +34526,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>5858</v>
+        <v>5877</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>5859</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -34490,13 +34549,13 @@
         <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>5853</v>
+        <v>5872</v>
       </c>
       <c r="F21" t="s">
         <v>66</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>5860</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -34513,13 +34572,13 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>5836</v>
+        <v>5855</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>5861</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -34536,13 +34595,13 @@
         <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>5862</v>
+        <v>5881</v>
       </c>
       <c r="F23" t="s">
         <v>179</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>5863</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -34559,13 +34618,13 @@
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>5864</v>
+        <v>5883</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>5865</v>
+        <v>5884</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -34582,13 +34641,13 @@
         <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>5866</v>
+        <v>5885</v>
       </c>
       <c r="F25" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>5867</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -34605,13 +34664,13 @@
         <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>5858</v>
+        <v>5877</v>
       </c>
       <c r="F26" t="s">
         <v>66</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>5868</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -34628,13 +34687,13 @@
         <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>5855</v>
+        <v>5874</v>
       </c>
       <c r="F27" t="s">
         <v>66</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>5869</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -34651,13 +34710,13 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>5855</v>
+        <v>5874</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>5870</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -34674,13 +34733,13 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>5871</v>
+        <v>5890</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>5872</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -34697,13 +34756,13 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>5873</v>
+        <v>5892</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>5874</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -34720,13 +34779,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>5875</v>
+        <v>5894</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>5876</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -34743,13 +34802,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>5836</v>
+        <v>5855</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>5877</v>
+        <v>5896</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -34766,13 +34825,13 @@
         <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>5836</v>
+        <v>5855</v>
       </c>
       <c r="F33" t="s">
         <v>66</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>5878</v>
+        <v>5897</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -34789,13 +34848,13 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>5879</v>
+        <v>5898</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>5880</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -34812,13 +34871,13 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>5836</v>
+        <v>5855</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>5881</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -34835,13 +34894,13 @@
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>5879</v>
+        <v>5898</v>
       </c>
       <c r="F36" t="s">
         <v>66</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>5882</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -34858,13 +34917,13 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>5864</v>
+        <v>5883</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>5883</v>
+        <v>5902</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -34881,13 +34940,13 @@
         <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>5879</v>
+        <v>5898</v>
       </c>
       <c r="F38" t="s">
         <v>66</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>5884</v>
+        <v>5903</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -34904,13 +34963,13 @@
         <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>5885</v>
+        <v>5904</v>
       </c>
       <c r="F39" t="s">
         <v>66</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>5886</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -34927,13 +34986,13 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>5879</v>
+        <v>5898</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>5887</v>
+        <v>5906</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -34950,13 +35009,13 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>5888</v>
+        <v>5907</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>5889</v>
+        <v>5908</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -34973,13 +35032,13 @@
         <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>5841</v>
+        <v>5860</v>
       </c>
       <c r="F42" t="s">
         <v>66</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>5890</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -34996,13 +35055,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>5891</v>
+        <v>5910</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>5892</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -35019,13 +35078,13 @@
         <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>5893</v>
+        <v>5912</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>5894</v>
+        <v>5913</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -35042,13 +35101,13 @@
         <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>5895</v>
+        <v>5914</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>5896</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -35065,13 +35124,13 @@
         <v>67</v>
       </c>
       <c r="E46" t="s">
-        <v>5897</v>
+        <v>5916</v>
       </c>
       <c r="F46" t="s">
         <v>304</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>5898</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -35079,19 +35138,19 @@
         <v>305</v>
       </c>
       <c r="B47" t="s">
-        <v>5899</v>
+        <v>5918</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5900</v>
+        <v>5919</v>
       </c>
       <c r="D47" t="s">
-        <v>5901</v>
+        <v>5920</v>
       </c>
       <c r="E47" t="s">
-        <v>5902</v>
+        <v>5921</v>
       </c>
       <c r="F47" t="s">
-        <v>5903</v>
+        <v>5922</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
@@ -35111,13 +35170,13 @@
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>5904</v>
+        <v>5923</v>
       </c>
       <c r="F48" t="s">
         <v>66</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>5905</v>
+        <v>5924</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -35134,13 +35193,13 @@
         <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>5891</v>
+        <v>5910</v>
       </c>
       <c r="F49" t="s">
         <v>66</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>5906</v>
+        <v>5925</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -35157,13 +35216,13 @@
         <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>5841</v>
+        <v>5860</v>
       </c>
       <c r="F50" t="s">
         <v>66</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>5907</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -35180,13 +35239,13 @@
         <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>5908</v>
+        <v>5927</v>
       </c>
       <c r="F51" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>5909</v>
+        <v>5928</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -35203,13 +35262,13 @@
         <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>5910</v>
+        <v>5929</v>
       </c>
       <c r="F52" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>5911</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -35226,13 +35285,13 @@
         <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>5912</v>
+        <v>5931</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>5913</v>
+        <v>5932</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -35249,13 +35308,13 @@
         <v>67</v>
       </c>
       <c r="E54" t="s">
-        <v>5914</v>
+        <v>5933</v>
       </c>
       <c r="F54" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>5915</v>
+        <v>5934</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -35272,7 +35331,7 @@
         <v>180</v>
       </c>
       <c r="E55" t="s">
-        <v>5862</v>
+        <v>5881</v>
       </c>
       <c r="F55" t="s">
         <v>179</v>
@@ -35295,7 +35354,7 @@
         <v>67</v>
       </c>
       <c r="E56" t="s">
-        <v>5916</v>
+        <v>5935</v>
       </c>
       <c r="F56" t="s">
         <v>66</v>
@@ -35318,13 +35377,13 @@
         <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>5855</v>
+        <v>5874</v>
       </c>
       <c r="F57" t="s">
         <v>66</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>5917</v>
+        <v>5936</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -35341,7 +35400,7 @@
         <v>180</v>
       </c>
       <c r="E58" t="s">
-        <v>5918</v>
+        <v>5937</v>
       </c>
       <c r="F58" t="s">
         <v>179</v>
@@ -35364,7 +35423,7 @@
         <v>180</v>
       </c>
       <c r="E59" t="s">
-        <v>5862</v>
+        <v>5881</v>
       </c>
       <c r="F59" t="s">
         <v>179</v>
@@ -35387,13 +35446,13 @@
         <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>5919</v>
+        <v>5938</v>
       </c>
       <c r="F60" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>5920</v>
+        <v>5939</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -35410,13 +35469,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>5921</v>
+        <v>5940</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>5922</v>
+        <v>5941</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -35433,13 +35492,13 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>5914</v>
+        <v>5933</v>
       </c>
       <c r="F62" t="s">
         <v>394</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>5923</v>
+        <v>5942</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -35456,13 +35515,13 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>5924</v>
+        <v>5943</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>5925</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -35479,7 +35538,7 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>5862</v>
+        <v>5881</v>
       </c>
       <c r="F64" t="s">
         <v>179</v>
@@ -35502,7 +35561,7 @@
         <v>180</v>
       </c>
       <c r="E65" t="s">
-        <v>5862</v>
+        <v>5881</v>
       </c>
       <c r="F65" t="s">
         <v>179</v>
@@ -35525,13 +35584,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>5926</v>
+        <v>5945</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>5927</v>
+        <v>5946</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -35548,7 +35607,7 @@
         <v>67</v>
       </c>
       <c r="E67" t="s">
-        <v>5914</v>
+        <v>5933</v>
       </c>
       <c r="F67" t="s">
         <v>419</v>
@@ -35571,13 +35630,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>5855</v>
+        <v>5874</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>5928</v>
+        <v>5947</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -35594,13 +35653,13 @@
         <v>67</v>
       </c>
       <c r="E69" t="s">
-        <v>5853</v>
+        <v>5872</v>
       </c>
       <c r="F69" t="s">
         <v>66</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>5929</v>
+        <v>5948</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -35617,13 +35676,13 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>5930</v>
+        <v>5949</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>5931</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -35640,13 +35699,13 @@
         <v>67</v>
       </c>
       <c r="E71" t="s">
-        <v>5873</v>
+        <v>5892</v>
       </c>
       <c r="F71" t="s">
         <v>66</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>5932</v>
+        <v>5951</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -35663,13 +35722,13 @@
         <v>67</v>
       </c>
       <c r="E72" t="s">
-        <v>5933</v>
+        <v>5952</v>
       </c>
       <c r="F72" t="s">
         <v>66</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>5934</v>
+        <v>5953</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -35686,13 +35745,13 @@
         <v>67</v>
       </c>
       <c r="E73" t="s">
-        <v>5935</v>
+        <v>5954</v>
       </c>
       <c r="F73" t="s">
         <v>66</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>5936</v>
+        <v>5955</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -35700,19 +35759,19 @@
         <v>457</v>
       </c>
       <c r="B74" t="s">
-        <v>5899</v>
+        <v>5918</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5900</v>
+        <v>5919</v>
       </c>
       <c r="D74" t="s">
-        <v>5901</v>
+        <v>5920</v>
       </c>
       <c r="E74" t="s">
-        <v>5902</v>
+        <v>5921</v>
       </c>
       <c r="F74" t="s">
-        <v>5937</v>
+        <v>5956</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -35732,13 +35791,13 @@
         <v>67</v>
       </c>
       <c r="E75" t="s">
-        <v>5938</v>
+        <v>5957</v>
       </c>
       <c r="F75" t="s">
         <v>66</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>5939</v>
+        <v>5958</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -35755,13 +35814,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>5940</v>
+        <v>5959</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>5941</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -35769,19 +35828,19 @@
         <v>475</v>
       </c>
       <c r="B77" t="s">
-        <v>5899</v>
+        <v>5918</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>5942</v>
+        <v>5961</v>
       </c>
       <c r="D77" t="s">
-        <v>5901</v>
+        <v>5920</v>
       </c>
       <c r="E77" t="s">
-        <v>5943</v>
+        <v>5962</v>
       </c>
       <c r="F77" t="s">
-        <v>5944</v>
+        <v>5963</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -35792,19 +35851,19 @@
         <v>481</v>
       </c>
       <c r="B78" t="s">
-        <v>5899</v>
+        <v>5918</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>5942</v>
+        <v>5961</v>
       </c>
       <c r="D78" t="s">
-        <v>5901</v>
+        <v>5920</v>
       </c>
       <c r="E78" t="s">
-        <v>5943</v>
+        <v>5962</v>
       </c>
       <c r="F78" t="s">
-        <v>5945</v>
+        <v>5964</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -35824,13 +35883,13 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>5946</v>
+        <v>5965</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>5947</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -35847,13 +35906,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>5948</v>
+        <v>5967</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>5949</v>
+        <v>5968</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -35870,13 +35929,13 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>5950</v>
+        <v>5969</v>
       </c>
       <c r="F81" t="s">
         <v>66</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>5951</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -35893,13 +35952,13 @@
         <v>67</v>
       </c>
       <c r="E82" t="s">
-        <v>5950</v>
+        <v>5969</v>
       </c>
       <c r="F82" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>5952</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -35916,13 +35975,13 @@
         <v>67</v>
       </c>
       <c r="E83" t="s">
-        <v>5940</v>
+        <v>5959</v>
       </c>
       <c r="F83" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>5953</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -35939,13 +35998,13 @@
         <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>5954</v>
+        <v>5973</v>
       </c>
       <c r="F84" t="s">
         <v>179</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>5955</v>
+        <v>5974</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -35962,13 +36021,13 @@
         <v>67</v>
       </c>
       <c r="E85" t="s">
-        <v>5946</v>
+        <v>5965</v>
       </c>
       <c r="F85" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>5956</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -35985,13 +36044,13 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>5957</v>
+        <v>5976</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>5958</v>
+        <v>5977</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -36008,13 +36067,13 @@
         <v>67</v>
       </c>
       <c r="E87" t="s">
-        <v>5959</v>
+        <v>5978</v>
       </c>
       <c r="F87" t="s">
         <v>536</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>5960</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -36031,13 +36090,13 @@
         <v>67</v>
       </c>
       <c r="E88" t="s">
-        <v>5893</v>
+        <v>5912</v>
       </c>
       <c r="F88" t="s">
         <v>66</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>5961</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -36054,13 +36113,13 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>5919</v>
+        <v>5938</v>
       </c>
       <c r="F89" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>5962</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -36077,13 +36136,13 @@
         <v>67</v>
       </c>
       <c r="E90" t="s">
-        <v>5893</v>
+        <v>5912</v>
       </c>
       <c r="F90" t="s">
         <v>66</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>5963</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -36100,13 +36159,13 @@
         <v>67</v>
       </c>
       <c r="E91" t="s">
-        <v>5893</v>
+        <v>5912</v>
       </c>
       <c r="F91" t="s">
         <v>66</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>5964</v>
+        <v>5983</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -36123,13 +36182,13 @@
         <v>67</v>
       </c>
       <c r="E92" t="s">
-        <v>5897</v>
+        <v>5916</v>
       </c>
       <c r="F92" t="s">
         <v>564</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>5965</v>
+        <v>5984</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -36146,13 +36205,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>5893</v>
+        <v>5912</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>5966</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -36169,13 +36228,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>5967</v>
+        <v>5986</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>5968</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -36192,13 +36251,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>5969</v>
+        <v>5988</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>5970</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -36215,7 +36274,7 @@
         <v>67</v>
       </c>
       <c r="E96" t="s">
-        <v>5971</v>
+        <v>5990</v>
       </c>
       <c r="F96" t="s">
         <v>66</v>
@@ -36238,7 +36297,7 @@
         <v>180</v>
       </c>
       <c r="E97" t="s">
-        <v>5862</v>
+        <v>5881</v>
       </c>
       <c r="F97" t="s">
         <v>179</v>
@@ -36261,13 +36320,13 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>5972</v>
+        <v>5991</v>
       </c>
       <c r="F98" t="s">
         <v>66</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>5973</v>
+        <v>5992</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -36284,13 +36343,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>5974</v>
+        <v>5993</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>5975</v>
+        <v>5994</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -36307,13 +36366,13 @@
         <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>5976</v>
+        <v>5995</v>
       </c>
       <c r="F100" t="s">
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>5977</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -36330,13 +36389,13 @@
         <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>5978</v>
+        <v>5997</v>
       </c>
       <c r="F101" t="s">
         <v>66</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>5979</v>
+        <v>5998</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -36353,13 +36412,13 @@
         <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>5980</v>
+        <v>5999</v>
       </c>
       <c r="F102" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>5981</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -36376,13 +36435,13 @@
         <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>5982</v>
+        <v>6001</v>
       </c>
       <c r="F103" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>5983</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -36399,13 +36458,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>5984</v>
+        <v>6003</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>5985</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -36422,13 +36481,13 @@
         <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>5982</v>
+        <v>6001</v>
       </c>
       <c r="F105" t="s">
         <v>66</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>5986</v>
+        <v>6005</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -36445,13 +36504,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>5987</v>
+        <v>6006</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>5988</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -36468,13 +36527,13 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>5989</v>
+        <v>6008</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>5990</v>
+        <v>6009</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -36491,13 +36550,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>5991</v>
+        <v>6010</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>5992</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -36514,13 +36573,13 @@
         <v>67</v>
       </c>
       <c r="E109" t="s">
-        <v>5897</v>
+        <v>5916</v>
       </c>
       <c r="F109" t="s">
         <v>661</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>5993</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -36537,7 +36596,7 @@
         <v>67</v>
       </c>
       <c r="E110" t="s">
-        <v>5994</v>
+        <v>6013</v>
       </c>
       <c r="F110" t="s">
         <v>66</v>
@@ -36560,13 +36619,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>5853</v>
+        <v>5872</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>5995</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -36583,13 +36642,13 @@
         <v>67</v>
       </c>
       <c r="E112" t="s">
-        <v>5875</v>
+        <v>5894</v>
       </c>
       <c r="F112" t="s">
         <v>66</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>5996</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -36606,13 +36665,13 @@
         <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>5873</v>
+        <v>5892</v>
       </c>
       <c r="F113" t="s">
         <v>66</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>5997</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -36623,16 +36682,16 @@
         <v>67</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>5998</v>
+        <v>6017</v>
       </c>
       <c r="D114" t="s">
-        <v>5999</v>
+        <v>6018</v>
       </c>
       <c r="E114" t="s">
-        <v>6000</v>
+        <v>6019</v>
       </c>
       <c r="F114" t="s">
-        <v>6001</v>
+        <v>6020</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -36652,7 +36711,7 @@
         <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>6002</v>
+        <v>6021</v>
       </c>
       <c r="F115" t="s">
         <v>66</v>
@@ -36675,7 +36734,7 @@
         <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>6003</v>
+        <v>6022</v>
       </c>
       <c r="F116" t="s">
         <v>66</v>
@@ -36698,7 +36757,7 @@
         <v>67</v>
       </c>
       <c r="E117" t="s">
-        <v>6004</v>
+        <v>6023</v>
       </c>
       <c r="F117" t="s">
         <v>66</v>
@@ -36721,13 +36780,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6005</v>
+        <v>6024</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6006</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -36744,7 +36803,7 @@
         <v>67</v>
       </c>
       <c r="E119" t="s">
-        <v>6007</v>
+        <v>6026</v>
       </c>
       <c r="F119" t="s">
         <v>66</v>
@@ -36767,7 +36826,7 @@
         <v>67</v>
       </c>
       <c r="E120" t="s">
-        <v>6008</v>
+        <v>6027</v>
       </c>
       <c r="F120" t="s">
         <v>66</v>
@@ -36790,13 +36849,13 @@
         <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>6009</v>
+        <v>6028</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>6010</v>
+        <v>6029</v>
       </c>
     </row>
   </sheetData>
@@ -36958,7 +37017,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>6011</v>
+        <v>6030</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -36975,7 +37034,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -37004,7 +37063,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>6012</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -37021,7 +37080,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -37050,10 +37109,10 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>6013</v>
+        <v>6032</v>
       </c>
       <c r="F6" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -37073,10 +37132,10 @@
         <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>6013</v>
+        <v>6032</v>
       </c>
       <c r="F7" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
@@ -37096,10 +37155,10 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>6013</v>
+        <v>6032</v>
       </c>
       <c r="F8" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -37119,10 +37178,10 @@
         <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>6013</v>
+        <v>6032</v>
       </c>
       <c r="F9" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -37142,7 +37201,7 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>6015</v>
+        <v>6034</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -37159,7 +37218,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -37182,7 +37241,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -37211,10 +37270,10 @@
         <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>6013</v>
+        <v>6032</v>
       </c>
       <c r="F13" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -37228,7 +37287,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -37251,7 +37310,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -37274,7 +37333,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -37297,7 +37356,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -37320,7 +37379,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -37349,7 +37408,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>6016</v>
+        <v>6035</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -37366,7 +37425,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -37389,7 +37448,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -37418,7 +37477,7 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>6017</v>
+        <v>6036</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -37435,7 +37494,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -37458,7 +37517,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -37481,7 +37540,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -37504,7 +37563,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -37527,7 +37586,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -37556,7 +37615,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>6018</v>
+        <v>6037</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -37579,7 +37638,7 @@
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>6019</v>
+        <v>6038</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -37602,7 +37661,7 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>6020</v>
+        <v>6039</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -37619,7 +37678,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -37648,7 +37707,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6021</v>
+        <v>6040</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -37665,7 +37724,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -37694,7 +37753,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>6022</v>
+        <v>6041</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -37717,7 +37776,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>6023</v>
+        <v>6042</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>
@@ -37734,7 +37793,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -37763,7 +37822,7 @@
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>6022</v>
+        <v>6041</v>
       </c>
       <c r="F37" t="s">
         <v>66</v>
@@ -37780,7 +37839,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -37803,7 +37862,7 @@
         <v>24</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
@@ -37832,7 +37891,7 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>6024</v>
+        <v>6043</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -37855,7 +37914,7 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>6025</v>
+        <v>6044</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
@@ -37872,7 +37931,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -37895,7 +37954,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D43" t="s">
         <v>24</v>
@@ -37918,7 +37977,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -37941,7 +38000,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
@@ -37964,7 +38023,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
@@ -37987,7 +38046,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -38016,10 +38075,10 @@
         <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>6026</v>
+        <v>6045</v>
       </c>
       <c r="F48" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -38039,10 +38098,10 @@
         <v>180</v>
       </c>
       <c r="E49" t="s">
-        <v>6027</v>
+        <v>6046</v>
       </c>
       <c r="F49" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -38056,7 +38115,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -38079,7 +38138,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -38102,7 +38161,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -38125,7 +38184,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -38148,7 +38207,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -38223,10 +38282,10 @@
         <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>6026</v>
+        <v>6045</v>
       </c>
       <c r="F57" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -38240,7 +38299,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -38263,7 +38322,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -38286,7 +38345,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -38315,10 +38374,10 @@
         <v>180</v>
       </c>
       <c r="E61" t="s">
-        <v>6028</v>
+        <v>6047</v>
       </c>
       <c r="F61" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -38338,10 +38397,10 @@
         <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>6029</v>
+        <v>6048</v>
       </c>
       <c r="F62" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -38361,7 +38420,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>6030</v>
+        <v>6049</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -38384,10 +38443,10 @@
         <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>6026</v>
+        <v>6045</v>
       </c>
       <c r="F64" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -38401,7 +38460,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -38447,7 +38506,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -38470,7 +38529,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D68" t="s">
         <v>24</v>
@@ -38499,10 +38558,10 @@
         <v>180</v>
       </c>
       <c r="E69" t="s">
-        <v>6026</v>
+        <v>6045</v>
       </c>
       <c r="F69" t="s">
-        <v>6014</v>
+        <v>6033</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -38522,7 +38581,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>6031</v>
+        <v>6050</v>
       </c>
       <c r="F70" t="s">
         <v>66</v>
@@ -38539,7 +38598,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
@@ -38562,7 +38621,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -38585,7 +38644,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -38654,7 +38713,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -38723,7 +38782,7 @@
         <v>24</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
@@ -38746,7 +38805,7 @@
         <v>24</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
@@ -38890,7 +38949,7 @@
         <v>67</v>
       </c>
       <c r="E86" t="s">
-        <v>6032</v>
+        <v>6051</v>
       </c>
       <c r="F86" t="s">
         <v>66</v>
@@ -38913,10 +38972,10 @@
         <v>180</v>
       </c>
       <c r="E87" t="s">
+        <v>6052</v>
+      </c>
+      <c r="F87" t="s">
         <v>6033</v>
-      </c>
-      <c r="F87" t="s">
-        <v>6014</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>
@@ -38930,7 +38989,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D88" t="s">
         <v>24</v>
@@ -38953,7 +39012,7 @@
         <v>24</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D89" t="s">
         <v>24</v>
@@ -38976,7 +39035,7 @@
         <v>24</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D90" t="s">
         <v>24</v>
@@ -38999,7 +39058,7 @@
         <v>24</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D91" t="s">
         <v>24</v>
@@ -39022,7 +39081,7 @@
         <v>24</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D92" t="s">
         <v>24</v>
@@ -39045,7 +39104,7 @@
         <v>24</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D93" t="s">
         <v>24</v>
@@ -39068,7 +39127,7 @@
         <v>24</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D94" t="s">
         <v>24</v>
@@ -39091,7 +39150,7 @@
         <v>24</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
@@ -39114,7 +39173,7 @@
         <v>24</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D96" t="s">
         <v>24</v>
@@ -39137,7 +39196,7 @@
         <v>24</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
@@ -39160,7 +39219,7 @@
         <v>24</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D98" t="s">
         <v>24</v>
@@ -39183,7 +39242,7 @@
         <v>24</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D99" t="s">
         <v>24</v>
@@ -39206,7 +39265,7 @@
         <v>24</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D100" t="s">
         <v>24</v>
@@ -39229,7 +39288,7 @@
         <v>24</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D101" t="s">
         <v>24</v>
@@ -39252,7 +39311,7 @@
         <v>24</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D102" t="s">
         <v>24</v>
@@ -39275,7 +39334,7 @@
         <v>24</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D103" t="s">
         <v>24</v>
@@ -39298,7 +39357,7 @@
         <v>24</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D104" t="s">
         <v>24</v>
@@ -39321,7 +39380,7 @@
         <v>24</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D105" t="s">
         <v>24</v>
@@ -39344,7 +39403,7 @@
         <v>24</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D106" t="s">
         <v>24</v>
@@ -39367,7 +39426,7 @@
         <v>24</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D107" t="s">
         <v>24</v>
@@ -39390,7 +39449,7 @@
         <v>24</v>
       </c>
       <c r="C108" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D108" t="s">
         <v>24</v>
@@ -39413,7 +39472,7 @@
         <v>24</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D109" t="s">
         <v>24</v>
@@ -39436,7 +39495,7 @@
         <v>24</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D110" t="s">
         <v>24</v>
@@ -39459,7 +39518,7 @@
         <v>24</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D111" t="s">
         <v>24</v>
@@ -39482,7 +39541,7 @@
         <v>24</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D112" t="s">
         <v>24</v>
@@ -39594,7 +39653,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -39617,7 +39676,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -39686,7 +39745,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -39709,7 +39768,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -39732,7 +39791,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -39755,7 +39814,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -39778,7 +39837,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -39801,7 +39860,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -39824,7 +39883,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -39870,7 +39929,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -39916,7 +39975,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -39939,7 +39998,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -39962,7 +40021,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -39985,7 +40044,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -40008,7 +40067,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -40077,7 +40136,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -40100,7 +40159,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -40123,7 +40182,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -40146,7 +40205,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -40169,7 +40228,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -40192,7 +40251,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -40261,7 +40320,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -40284,7 +40343,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -40307,7 +40366,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -40330,7 +40389,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
@@ -40376,7 +40435,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -40399,7 +40458,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -40445,7 +40504,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -40468,7 +40527,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D41" t="s">
         <v>24</v>
@@ -40491,7 +40550,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -40514,7 +40573,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D43" t="s">
         <v>24</v>
@@ -40537,7 +40596,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -40560,7 +40619,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
@@ -40583,7 +40642,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
@@ -40606,7 +40665,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -40629,7 +40688,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -40675,7 +40734,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -40698,7 +40757,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -40721,7 +40780,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -40744,7 +40803,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -40767,7 +40826,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -40790,7 +40849,7 @@
         <v>24</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
@@ -40836,7 +40895,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -40882,7 +40941,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -40905,7 +40964,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -40928,7 +40987,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -40951,7 +41010,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -40974,7 +41033,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -40997,7 +41056,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -41020,7 +41079,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -41043,7 +41102,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
@@ -41066,7 +41125,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -41089,7 +41148,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D68" t="s">
         <v>24</v>
@@ -41112,7 +41171,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
@@ -41135,7 +41194,7 @@
         <v>24</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
@@ -41158,7 +41217,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
@@ -41181,7 +41240,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -41204,7 +41263,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -41227,7 +41286,7 @@
         <v>24</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
@@ -41250,7 +41309,7 @@
         <v>24</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D75" t="s">
         <v>24</v>
@@ -41273,7 +41332,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -41296,7 +41355,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
@@ -41385,7 +41444,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -41408,7 +41467,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -41431,7 +41490,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -41454,7 +41513,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -41477,7 +41536,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -41500,7 +41559,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -41523,7 +41582,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -41546,7 +41605,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -41569,7 +41628,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -41592,7 +41651,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -41615,7 +41674,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -41638,7 +41697,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -41661,7 +41720,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -41684,7 +41743,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -41753,7 +41812,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -41776,7 +41835,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -41845,7 +41904,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -41868,7 +41927,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -41891,7 +41950,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -41914,7 +41973,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -41937,7 +41996,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -41983,7 +42042,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -42006,7 +42065,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
@@ -42029,7 +42088,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -42052,7 +42111,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -42098,7 +42157,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -42144,7 +42203,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -42167,7 +42226,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -42213,7 +42272,7 @@
         <v>24</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
@@ -42236,7 +42295,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -42282,7 +42341,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -42305,7 +42364,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D43" t="s">
         <v>24</v>
@@ -42328,7 +42387,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -42397,7 +42456,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -42420,7 +42479,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -42489,7 +42548,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -42512,7 +42571,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -42558,7 +42617,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -42581,7 +42640,7 @@
         <v>24</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
@@ -42604,7 +42663,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -42627,7 +42686,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -42650,7 +42709,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -42673,7 +42732,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -42696,7 +42755,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -42719,7 +42778,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -42742,7 +42801,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -42765,7 +42824,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -42788,7 +42847,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -42811,7 +42870,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -42834,7 +42893,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
@@ -42857,7 +42916,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -42880,7 +42939,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D68" t="s">
         <v>24</v>
@@ -42903,7 +42962,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
@@ -42926,7 +42985,7 @@
         <v>24</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
@@ -42949,7 +43008,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
@@ -42972,7 +43031,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -42995,7 +43054,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -43018,7 +43077,7 @@
         <v>24</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
@@ -43041,7 +43100,7 @@
         <v>24</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D75" t="s">
         <v>24</v>
@@ -43064,7 +43123,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -43110,7 +43169,7 @@
         <v>24</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
@@ -43222,7 +43281,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -43245,7 +43304,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -43268,7 +43327,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -43314,7 +43373,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -43337,7 +43396,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -43360,7 +43419,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -43383,7 +43442,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -43452,7 +43511,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -43475,7 +43534,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -43498,7 +43557,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -43521,7 +43580,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -43544,7 +43603,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -43567,7 +43626,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -43590,7 +43649,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -43613,7 +43672,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -43636,7 +43695,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -43659,7 +43718,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -43682,7 +43741,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -43774,7 +43833,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -43981,7 +44040,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -44004,7 +44063,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -44027,7 +44086,7 @@
         <v>24</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
@@ -44050,7 +44109,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -44073,7 +44132,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D41" t="s">
         <v>24</v>
@@ -44096,7 +44155,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -44165,7 +44224,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
@@ -44211,7 +44270,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -44234,7 +44293,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -44257,7 +44316,7 @@
         <v>24</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
@@ -44280,7 +44339,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -44303,7 +44362,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -44326,7 +44385,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -44349,7 +44408,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -44372,7 +44431,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -44395,7 +44454,7 @@
         <v>24</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
@@ -44418,7 +44477,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -44441,7 +44500,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -44464,7 +44523,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -44487,7 +44546,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -44510,7 +44569,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -44533,7 +44592,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -44556,7 +44615,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -44579,7 +44638,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -44602,7 +44661,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -44625,7 +44684,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -44648,7 +44707,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
@@ -44671,7 +44730,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -44694,7 +44753,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D68" t="s">
         <v>24</v>
@@ -44717,7 +44776,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
@@ -44740,7 +44799,7 @@
         <v>24</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
@@ -44763,7 +44822,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
@@ -44786,7 +44845,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -44809,7 +44868,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -44832,7 +44891,7 @@
         <v>24</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
@@ -44855,7 +44914,7 @@
         <v>24</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D75" t="s">
         <v>24</v>
@@ -44878,7 +44937,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -44901,7 +44960,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
@@ -44924,7 +44983,7 @@
         <v>24</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
@@ -44947,7 +45006,7 @@
         <v>24</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
@@ -44970,7 +45029,7 @@
         <v>24</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
@@ -44993,7 +45052,7 @@
         <v>24</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
@@ -45016,7 +45075,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
@@ -45039,7 +45098,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D83" t="s">
         <v>24</v>
@@ -45062,7 +45121,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D84" t="s">
         <v>24</v>
@@ -45085,7 +45144,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D85" t="s">
         <v>24</v>
@@ -45108,7 +45167,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D86" t="s">
         <v>24</v>
@@ -45131,7 +45190,7 @@
         <v>24</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
@@ -45243,7 +45302,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -45266,7 +45325,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -45289,7 +45348,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -45312,7 +45371,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -45335,7 +45394,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -45358,7 +45417,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -45381,7 +45440,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -45427,7 +45486,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -45473,7 +45532,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -45496,7 +45555,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -45519,7 +45578,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -45542,7 +45601,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -45565,7 +45624,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -45588,7 +45647,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -45611,7 +45670,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -45634,7 +45693,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -45657,7 +45716,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -45680,7 +45739,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -45772,7 +45831,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -45795,7 +45854,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -45818,7 +45877,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -45841,7 +45900,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
@@ -45864,7 +45923,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -45887,7 +45946,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -45910,7 +45969,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -45956,7 +46015,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
@@ -46002,7 +46061,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -46071,7 +46130,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -46117,7 +46176,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -46140,7 +46199,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D43" t="s">
         <v>24</v>
@@ -46163,7 +46222,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -46209,7 +46268,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
@@ -46232,7 +46291,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -46255,7 +46314,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -46278,7 +46337,7 @@
         <v>24</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
@@ -46301,7 +46360,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -46324,7 +46383,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -46347,7 +46406,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -46370,7 +46429,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -46393,7 +46452,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -46439,7 +46498,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -46462,7 +46521,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -46485,7 +46544,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -46508,7 +46567,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -46531,7 +46590,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -46554,7 +46613,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -46577,7 +46636,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -46600,7 +46659,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -46689,7 +46748,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -46758,7 +46817,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -46827,7 +46886,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -46896,7 +46955,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -46919,7 +46978,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -46942,7 +47001,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -46965,7 +47024,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -46988,7 +47047,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -47011,7 +47070,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -47034,7 +47093,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -47103,7 +47162,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -47195,7 +47254,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -47218,7 +47277,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -47241,7 +47300,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -47264,7 +47323,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -47287,7 +47346,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -47310,7 +47369,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
@@ -47333,7 +47392,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -47356,7 +47415,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -47379,7 +47438,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -47402,7 +47461,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -47425,7 +47484,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
@@ -47448,7 +47507,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -47471,7 +47530,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -47494,7 +47553,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -47540,7 +47599,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -47563,7 +47622,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D41" t="s">
         <v>24</v>
@@ -47586,7 +47645,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -47632,7 +47691,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -47678,7 +47737,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
@@ -47701,7 +47760,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -47724,7 +47783,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -47747,7 +47806,7 @@
         <v>24</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
@@ -47770,7 +47829,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -47793,7 +47852,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -47816,7 +47875,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -47839,7 +47898,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -47862,7 +47921,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -47885,7 +47944,7 @@
         <v>24</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
@@ -47908,7 +47967,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -47931,7 +47990,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -47954,7 +48013,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -47977,7 +48036,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -48000,7 +48059,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -48023,7 +48082,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -48046,7 +48105,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -48069,7 +48128,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -48092,7 +48151,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -48115,7 +48174,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -48161,7 +48220,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -48207,7 +48266,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
@@ -48230,7 +48289,7 @@
         <v>24</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
@@ -48253,7 +48312,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
@@ -48276,7 +48335,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -48299,7 +48358,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -48322,7 +48381,7 @@
         <v>24</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
@@ -48368,7 +48427,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -48391,7 +48450,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
@@ -48414,7 +48473,7 @@
         <v>24</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
@@ -48437,7 +48496,7 @@
         <v>24</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
@@ -48460,7 +48519,7 @@
         <v>24</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
@@ -48483,7 +48542,7 @@
         <v>24</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
@@ -48506,7 +48565,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
@@ -48529,7 +48588,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D83" t="s">
         <v>24</v>
@@ -48552,7 +48611,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D84" t="s">
         <v>24</v>
@@ -48575,7 +48634,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D85" t="s">
         <v>24</v>
@@ -48598,7 +48657,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D86" t="s">
         <v>24</v>
@@ -48621,7 +48680,7 @@
         <v>24</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
@@ -48667,7 +48726,7 @@
         <v>24</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D89" t="s">
         <v>24</v>
@@ -48690,7 +48749,7 @@
         <v>24</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D90" t="s">
         <v>24</v>
@@ -48713,7 +48772,7 @@
         <v>24</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D91" t="s">
         <v>24</v>
@@ -48736,7 +48795,7 @@
         <v>24</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D92" t="s">
         <v>24</v>
@@ -48759,7 +48818,7 @@
         <v>24</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D93" t="s">
         <v>24</v>
@@ -48782,7 +48841,7 @@
         <v>24</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D94" t="s">
         <v>24</v>
@@ -48805,7 +48864,7 @@
         <v>24</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
@@ -48851,7 +48910,7 @@
         <v>24</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
@@ -48874,7 +48933,7 @@
         <v>24</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D98" t="s">
         <v>24</v>
@@ -48897,7 +48956,7 @@
         <v>24</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D99" t="s">
         <v>24</v>
@@ -50087,7 +50146,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -50133,7 +50192,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -50156,7 +50215,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -50179,7 +50238,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -50202,7 +50261,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -50225,7 +50284,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -50271,7 +50330,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -50294,7 +50353,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -50317,7 +50376,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -50363,7 +50422,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -50386,7 +50445,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -50432,7 +50491,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -50478,7 +50537,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -50501,7 +50560,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -50524,7 +50583,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -50547,7 +50606,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -50570,7 +50629,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -50593,7 +50652,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -50616,7 +50675,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -50639,7 +50698,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -50662,7 +50721,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
@@ -50708,7 +50767,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -50754,7 +50813,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -50777,7 +50836,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
@@ -50800,7 +50859,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -50846,7 +50905,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -50869,7 +50928,7 @@
         <v>24</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
@@ -50892,7 +50951,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -50961,7 +51020,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D43" t="s">
         <v>24</v>
@@ -50984,7 +51043,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -51007,7 +51066,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
@@ -51076,7 +51135,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -51099,7 +51158,7 @@
         <v>24</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
@@ -51122,7 +51181,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -51145,7 +51204,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -51168,7 +51227,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -51191,7 +51250,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -51237,7 +51296,7 @@
         <v>24</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
@@ -51260,7 +51319,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -51283,7 +51342,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -51306,7 +51365,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -51329,7 +51388,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -51352,7 +51411,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -51375,7 +51434,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -51398,7 +51457,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -51421,7 +51480,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -51444,7 +51503,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -51579,7 +51638,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -51625,7 +51684,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -51648,7 +51707,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -51671,7 +51730,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -51694,7 +51753,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -51740,7 +51799,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -51763,7 +51822,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -51786,7 +51845,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -51832,7 +51891,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -51855,7 +51914,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -51878,7 +51937,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -51901,7 +51960,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -51947,7 +52006,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -51970,7 +52029,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -51993,7 +52052,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -52016,7 +52075,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -52039,7 +52098,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -52062,7 +52121,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -52085,7 +52144,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -52108,7 +52167,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -52131,7 +52190,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -52154,7 +52213,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
@@ -52223,7 +52282,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -52246,7 +52305,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -52269,7 +52328,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
@@ -52292,7 +52351,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -52315,7 +52374,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -52338,7 +52397,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -52361,7 +52420,7 @@
         <v>24</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
@@ -52384,7 +52443,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -52407,7 +52466,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D41" t="s">
         <v>24</v>
@@ -52430,7 +52489,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -52476,7 +52535,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -52522,7 +52581,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
@@ -52545,7 +52604,7 @@
         <v>24</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
@@ -52568,7 +52627,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -52591,7 +52650,7 @@
         <v>24</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
@@ -52614,7 +52673,7 @@
         <v>24</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
@@ -52637,7 +52696,7 @@
         <v>24</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
@@ -52660,7 +52719,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
@@ -52683,7 +52742,7 @@
         <v>24</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -52706,7 +52765,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
@@ -52752,7 +52811,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
@@ -52775,7 +52834,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -52798,7 +52857,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -52844,7 +52903,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -52867,7 +52926,7 @@
         <v>24</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
@@ -52890,7 +52949,7 @@
         <v>24</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -52913,7 +52972,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -52936,7 +52995,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -52959,7 +53018,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -52982,7 +53041,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
@@ -53005,7 +53064,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -53051,7 +53110,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
@@ -53074,7 +53133,7 @@
         <v>24</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
@@ -53097,7 +53156,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
@@ -53120,7 +53179,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -53143,7 +53202,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -53166,7 +53225,7 @@
         <v>24</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
@@ -53189,7 +53248,7 @@
         <v>24</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D75" t="s">
         <v>24</v>
@@ -53212,7 +53271,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -53235,7 +53294,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
@@ -53258,7 +53317,7 @@
         <v>24</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
@@ -53281,7 +53340,7 @@
         <v>24</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
@@ -53327,7 +53386,7 @@
         <v>24</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
@@ -53350,7 +53409,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
@@ -53373,7 +53432,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D83" t="s">
         <v>24</v>
@@ -53396,7 +53455,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D84" t="s">
         <v>24</v>
@@ -53419,7 +53478,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D85" t="s">
         <v>24</v>
@@ -53442,7 +53501,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D86" t="s">
         <v>24</v>
@@ -53465,7 +53524,7 @@
         <v>24</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
@@ -53488,7 +53547,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D88" t="s">
         <v>24</v>
@@ -53511,7 +53570,7 @@
         <v>24</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D89" t="s">
         <v>24</v>
@@ -53557,7 +53616,7 @@
         <v>24</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D91" t="s">
         <v>24</v>
@@ -53580,7 +53639,7 @@
         <v>24</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D92" t="s">
         <v>24</v>
@@ -53626,7 +53685,7 @@
         <v>24</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D94" t="s">
         <v>24</v>
@@ -53649,7 +53708,7 @@
         <v>24</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
@@ -53672,7 +53731,7 @@
         <v>24</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D96" t="s">
         <v>24</v>
@@ -53695,7 +53754,7 @@
         <v>24</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
@@ -53718,7 +53777,7 @@
         <v>24</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D98" t="s">
         <v>24</v>
@@ -53741,7 +53800,7 @@
         <v>24</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D99" t="s">
         <v>24</v>
@@ -53787,7 +53846,7 @@
         <v>24</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D101" t="s">
         <v>24</v>
@@ -53810,7 +53869,7 @@
         <v>24</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D102" t="s">
         <v>24</v>
@@ -53833,7 +53892,7 @@
         <v>24</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D103" t="s">
         <v>24</v>
@@ -53879,7 +53938,7 @@
         <v>24</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D105" t="s">
         <v>24</v>
@@ -53902,7 +53961,7 @@
         <v>24</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D106" t="s">
         <v>24</v>
@@ -53925,7 +53984,7 @@
         <v>24</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D107" t="s">
         <v>24</v>
@@ -53971,7 +54030,7 @@
         <v>24</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D109" t="s">
         <v>24</v>
@@ -54017,7 +54076,7 @@
         <v>24</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D111" t="s">
         <v>24</v>
@@ -54040,7 +54099,7 @@
         <v>24</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D112" t="s">
         <v>24</v>
@@ -54063,7 +54122,7 @@
         <v>24</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D113" t="s">
         <v>24</v>
@@ -54086,7 +54145,7 @@
         <v>24</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D114" t="s">
         <v>24</v>
@@ -54109,7 +54168,7 @@
         <v>24</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D115" t="s">
         <v>24</v>
@@ -54132,7 +54191,7 @@
         <v>24</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D116" t="s">
         <v>24</v>
@@ -54155,7 +54214,7 @@
         <v>24</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D117" t="s">
         <v>24</v>
@@ -54201,7 +54260,7 @@
         <v>24</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D119" t="s">
         <v>24</v>
@@ -54224,7 +54283,7 @@
         <v>24</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>5780</v>
+        <v>5834</v>
       </c>
       <c r="D120" t="s">
         <v>24</v>
@@ -54684,13 +54743,13 @@
         <v>784</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -54760,13 +54819,13 @@
         <v>798</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -54928,13 +54987,13 @@
         <v>825</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -54966,13 +55025,13 @@
         <v>831</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -55156,13 +55215,13 @@
         <v>860</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -55400,13 +55459,13 @@
         <v>898</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -55514,13 +55573,13 @@
         <v>918</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" ht="75" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -55552,13 +55611,13 @@
         <v>924</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -55796,13 +55855,13 @@
         <v>961</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -55872,13 +55931,13 @@
         <v>973</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -56268,13 +56327,13 @@
         <v>1036</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" ht="75" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -56420,13 +56479,13 @@
         <v>1061</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L66" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -56610,13 +56669,13 @@
         <v>1100</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -56778,13 +56837,13 @@
         <v>1125</v>
       </c>
       <c r="J76" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L76" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -56854,13 +56913,13 @@
         <v>1138</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L78" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -57120,13 +57179,13 @@
         <v>1181</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L85" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -57288,13 +57347,13 @@
         <v>1212</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6091">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19463,6 +19463,12 @@
   </si>
   <si>
     <t>ADM_CFG_003.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 16:06 IST — pass in 5.6s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_004.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — skip in n/a</t>
@@ -27901,13 +27907,13 @@
         <v>5015</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51790,22 +51796,22 @@
         <v>5010</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>6061</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>6062</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -51891,13 +51897,13 @@
         <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>6061</v>
+        <v>6063</v>
       </c>
       <c r="F11" t="s">
         <v>179</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>6062</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -51983,13 +51989,13 @@
         <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>6061</v>
+        <v>6063</v>
       </c>
       <c r="F15" t="s">
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6063</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52098,13 +52104,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6064</v>
+        <v>6066</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52351,13 +52357,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6066</v>
+        <v>6068</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52374,13 +52380,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6066</v>
+        <v>6068</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6068</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52627,13 +52633,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6069</v>
+        <v>6071</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6070</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52673,13 +52679,13 @@
         <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>6061</v>
+        <v>6063</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6071</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52903,13 +52909,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6073</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -52995,13 +53001,13 @@
         <v>180</v>
       </c>
       <c r="E59" t="s">
-        <v>6061</v>
+        <v>6063</v>
       </c>
       <c r="F59" t="s">
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53202,13 +53208,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53478,13 +53484,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53708,13 +53714,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53777,13 +53783,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53944,7 +53950,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54030,13 +54036,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54122,13 +54128,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54168,13 +54174,13 @@
         <v>180</v>
       </c>
       <c r="E110" t="s">
-        <v>6061</v>
+        <v>6063</v>
       </c>
       <c r="F110" t="s">
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54352,13 +54358,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6066</v>
+        <v>6068</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54413,24 +54419,25 @@
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G6" r:id="rId4"/>
-    <hyperlink ref="G11" r:id="rId5"/>
-    <hyperlink ref="G15" r:id="rId6"/>
-    <hyperlink ref="G20" r:id="rId7"/>
-    <hyperlink ref="G31" r:id="rId8"/>
-    <hyperlink ref="G32" r:id="rId9"/>
-    <hyperlink ref="G43" r:id="rId10"/>
-    <hyperlink ref="G45" r:id="rId11"/>
-    <hyperlink ref="G55" r:id="rId12"/>
-    <hyperlink ref="G59" r:id="rId13"/>
-    <hyperlink ref="G68" r:id="rId14"/>
-    <hyperlink ref="G80" r:id="rId15"/>
-    <hyperlink ref="G90" r:id="rId16"/>
-    <hyperlink ref="G93" r:id="rId17"/>
-    <hyperlink ref="G100" r:id="rId18"/>
-    <hyperlink ref="G104" r:id="rId19"/>
-    <hyperlink ref="G108" r:id="rId20"/>
-    <hyperlink ref="G110" r:id="rId21"/>
-    <hyperlink ref="G118" r:id="rId22"/>
+    <hyperlink ref="G7" r:id="rId5"/>
+    <hyperlink ref="G11" r:id="rId6"/>
+    <hyperlink ref="G15" r:id="rId7"/>
+    <hyperlink ref="G20" r:id="rId8"/>
+    <hyperlink ref="G31" r:id="rId9"/>
+    <hyperlink ref="G32" r:id="rId10"/>
+    <hyperlink ref="G43" r:id="rId11"/>
+    <hyperlink ref="G45" r:id="rId12"/>
+    <hyperlink ref="G55" r:id="rId13"/>
+    <hyperlink ref="G59" r:id="rId14"/>
+    <hyperlink ref="G68" r:id="rId15"/>
+    <hyperlink ref="G80" r:id="rId16"/>
+    <hyperlink ref="G90" r:id="rId17"/>
+    <hyperlink ref="G93" r:id="rId18"/>
+    <hyperlink ref="G100" r:id="rId19"/>
+    <hyperlink ref="G104" r:id="rId20"/>
+    <hyperlink ref="G108" r:id="rId21"/>
+    <hyperlink ref="G110" r:id="rId22"/>
+    <hyperlink ref="G118" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6093">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19469,6 +19469,12 @@
   </si>
   <si>
     <t>ADM_CFG_004.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 16:10 IST — pass in 3.0s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_007.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — skip in n/a</t>
@@ -27945,13 +27951,13 @@
         <v>5021</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51819,22 +51825,22 @@
         <v>5016</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>6063</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>6064</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -51897,13 +51903,13 @@
         <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>6063</v>
+        <v>6065</v>
       </c>
       <c r="F11" t="s">
         <v>179</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>6064</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -51989,13 +51995,13 @@
         <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>6063</v>
+        <v>6065</v>
       </c>
       <c r="F15" t="s">
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52104,13 +52110,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6066</v>
+        <v>6068</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52357,13 +52363,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6068</v>
+        <v>6070</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6069</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52380,13 +52386,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6068</v>
+        <v>6070</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6070</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52633,13 +52639,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6071</v>
+        <v>6073</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52679,13 +52685,13 @@
         <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>6063</v>
+        <v>6065</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6073</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52909,13 +52915,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53001,13 +53007,13 @@
         <v>180</v>
       </c>
       <c r="E59" t="s">
-        <v>6063</v>
+        <v>6065</v>
       </c>
       <c r="F59" t="s">
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53208,13 +53214,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53484,13 +53490,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53714,13 +53720,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53783,13 +53789,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53950,7 +53956,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54036,13 +54042,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54128,13 +54134,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54174,13 +54180,13 @@
         <v>180</v>
       </c>
       <c r="E110" t="s">
-        <v>6063</v>
+        <v>6065</v>
       </c>
       <c r="F110" t="s">
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54358,13 +54364,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6068</v>
+        <v>6070</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54420,24 +54426,25 @@
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G6" r:id="rId4"/>
     <hyperlink ref="G7" r:id="rId5"/>
-    <hyperlink ref="G11" r:id="rId6"/>
-    <hyperlink ref="G15" r:id="rId7"/>
-    <hyperlink ref="G20" r:id="rId8"/>
-    <hyperlink ref="G31" r:id="rId9"/>
-    <hyperlink ref="G32" r:id="rId10"/>
-    <hyperlink ref="G43" r:id="rId11"/>
-    <hyperlink ref="G45" r:id="rId12"/>
-    <hyperlink ref="G55" r:id="rId13"/>
-    <hyperlink ref="G59" r:id="rId14"/>
-    <hyperlink ref="G68" r:id="rId15"/>
-    <hyperlink ref="G80" r:id="rId16"/>
-    <hyperlink ref="G90" r:id="rId17"/>
-    <hyperlink ref="G93" r:id="rId18"/>
-    <hyperlink ref="G100" r:id="rId19"/>
-    <hyperlink ref="G104" r:id="rId20"/>
-    <hyperlink ref="G108" r:id="rId21"/>
-    <hyperlink ref="G110" r:id="rId22"/>
-    <hyperlink ref="G118" r:id="rId23"/>
+    <hyperlink ref="G8" r:id="rId6"/>
+    <hyperlink ref="G11" r:id="rId7"/>
+    <hyperlink ref="G15" r:id="rId8"/>
+    <hyperlink ref="G20" r:id="rId9"/>
+    <hyperlink ref="G31" r:id="rId10"/>
+    <hyperlink ref="G32" r:id="rId11"/>
+    <hyperlink ref="G43" r:id="rId12"/>
+    <hyperlink ref="G45" r:id="rId13"/>
+    <hyperlink ref="G55" r:id="rId14"/>
+    <hyperlink ref="G59" r:id="rId15"/>
+    <hyperlink ref="G68" r:id="rId16"/>
+    <hyperlink ref="G80" r:id="rId17"/>
+    <hyperlink ref="G90" r:id="rId18"/>
+    <hyperlink ref="G93" r:id="rId19"/>
+    <hyperlink ref="G100" r:id="rId20"/>
+    <hyperlink ref="G104" r:id="rId21"/>
+    <hyperlink ref="G108" r:id="rId22"/>
+    <hyperlink ref="G110" r:id="rId23"/>
+    <hyperlink ref="G118" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6095">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19475,6 +19475,12 @@
   </si>
   <si>
     <t>ADM_CFG_007.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 16:12 IST — pass in 2.9s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_070.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — skip in n/a</t>
@@ -27989,13 +27995,13 @@
         <v>5026</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51848,22 +51854,22 @@
         <v>5022</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>6065</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>6066</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -51903,13 +51909,13 @@
         <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
       <c r="F11" t="s">
         <v>179</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>6066</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -51995,13 +52001,13 @@
         <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
       <c r="F15" t="s">
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52110,13 +52116,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6068</v>
+        <v>6070</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6069</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52363,13 +52369,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6070</v>
+        <v>6072</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6071</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52386,13 +52392,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6070</v>
+        <v>6072</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52639,13 +52645,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6073</v>
+        <v>6075</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52685,13 +52691,13 @@
         <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52915,13 +52921,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53007,13 +53013,13 @@
         <v>180</v>
       </c>
       <c r="E59" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
       <c r="F59" t="s">
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53214,13 +53220,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53490,13 +53496,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53720,13 +53726,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53789,13 +53795,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53956,7 +53962,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54042,13 +54048,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54134,13 +54140,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54180,13 +54186,13 @@
         <v>180</v>
       </c>
       <c r="E110" t="s">
-        <v>6065</v>
+        <v>6067</v>
       </c>
       <c r="F110" t="s">
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54364,13 +54370,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6070</v>
+        <v>6072</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54427,24 +54433,25 @@
     <hyperlink ref="G6" r:id="rId4"/>
     <hyperlink ref="G7" r:id="rId5"/>
     <hyperlink ref="G8" r:id="rId6"/>
-    <hyperlink ref="G11" r:id="rId7"/>
-    <hyperlink ref="G15" r:id="rId8"/>
-    <hyperlink ref="G20" r:id="rId9"/>
-    <hyperlink ref="G31" r:id="rId10"/>
-    <hyperlink ref="G32" r:id="rId11"/>
-    <hyperlink ref="G43" r:id="rId12"/>
-    <hyperlink ref="G45" r:id="rId13"/>
-    <hyperlink ref="G55" r:id="rId14"/>
-    <hyperlink ref="G59" r:id="rId15"/>
-    <hyperlink ref="G68" r:id="rId16"/>
-    <hyperlink ref="G80" r:id="rId17"/>
-    <hyperlink ref="G90" r:id="rId18"/>
-    <hyperlink ref="G93" r:id="rId19"/>
-    <hyperlink ref="G100" r:id="rId20"/>
-    <hyperlink ref="G104" r:id="rId21"/>
-    <hyperlink ref="G108" r:id="rId22"/>
-    <hyperlink ref="G110" r:id="rId23"/>
-    <hyperlink ref="G118" r:id="rId24"/>
+    <hyperlink ref="G9" r:id="rId7"/>
+    <hyperlink ref="G11" r:id="rId8"/>
+    <hyperlink ref="G15" r:id="rId9"/>
+    <hyperlink ref="G20" r:id="rId10"/>
+    <hyperlink ref="G31" r:id="rId11"/>
+    <hyperlink ref="G32" r:id="rId12"/>
+    <hyperlink ref="G43" r:id="rId13"/>
+    <hyperlink ref="G45" r:id="rId14"/>
+    <hyperlink ref="G55" r:id="rId15"/>
+    <hyperlink ref="G59" r:id="rId16"/>
+    <hyperlink ref="G68" r:id="rId17"/>
+    <hyperlink ref="G80" r:id="rId18"/>
+    <hyperlink ref="G90" r:id="rId19"/>
+    <hyperlink ref="G93" r:id="rId20"/>
+    <hyperlink ref="G100" r:id="rId21"/>
+    <hyperlink ref="G104" r:id="rId22"/>
+    <hyperlink ref="G108" r:id="rId23"/>
+    <hyperlink ref="G110" r:id="rId24"/>
+    <hyperlink ref="G118" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6097">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19481,6 +19481,12 @@
   </si>
   <si>
     <t>ADM_CFG_070.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 16:15 IST — pass in 5.6s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_005.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — skip in n/a</t>
@@ -28033,13 +28039,13 @@
         <v>5032</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51877,22 +51883,22 @@
         <v>5027</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>6067</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>6068</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -51909,13 +51915,13 @@
         <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F11" t="s">
         <v>179</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>6068</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -52001,13 +52007,13 @@
         <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F15" t="s">
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6069</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52116,13 +52122,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6070</v>
+        <v>6072</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6071</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52369,13 +52375,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6073</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52392,13 +52398,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52645,13 +52651,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52691,13 +52697,13 @@
         <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52921,13 +52927,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53013,13 +53019,13 @@
         <v>180</v>
       </c>
       <c r="E59" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F59" t="s">
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53220,13 +53226,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53496,13 +53502,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53726,13 +53732,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53795,13 +53801,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53962,7 +53968,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54048,13 +54054,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54140,13 +54146,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54186,13 +54192,13 @@
         <v>180</v>
       </c>
       <c r="E110" t="s">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F110" t="s">
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6093</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54370,13 +54376,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6094</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54434,24 +54440,25 @@
     <hyperlink ref="G7" r:id="rId5"/>
     <hyperlink ref="G8" r:id="rId6"/>
     <hyperlink ref="G9" r:id="rId7"/>
-    <hyperlink ref="G11" r:id="rId8"/>
-    <hyperlink ref="G15" r:id="rId9"/>
-    <hyperlink ref="G20" r:id="rId10"/>
-    <hyperlink ref="G31" r:id="rId11"/>
-    <hyperlink ref="G32" r:id="rId12"/>
-    <hyperlink ref="G43" r:id="rId13"/>
-    <hyperlink ref="G45" r:id="rId14"/>
-    <hyperlink ref="G55" r:id="rId15"/>
-    <hyperlink ref="G59" r:id="rId16"/>
-    <hyperlink ref="G68" r:id="rId17"/>
-    <hyperlink ref="G80" r:id="rId18"/>
-    <hyperlink ref="G90" r:id="rId19"/>
-    <hyperlink ref="G93" r:id="rId20"/>
-    <hyperlink ref="G100" r:id="rId21"/>
-    <hyperlink ref="G104" r:id="rId22"/>
-    <hyperlink ref="G108" r:id="rId23"/>
-    <hyperlink ref="G110" r:id="rId24"/>
-    <hyperlink ref="G118" r:id="rId25"/>
+    <hyperlink ref="G10" r:id="rId8"/>
+    <hyperlink ref="G11" r:id="rId9"/>
+    <hyperlink ref="G15" r:id="rId10"/>
+    <hyperlink ref="G20" r:id="rId11"/>
+    <hyperlink ref="G31" r:id="rId12"/>
+    <hyperlink ref="G32" r:id="rId13"/>
+    <hyperlink ref="G43" r:id="rId14"/>
+    <hyperlink ref="G45" r:id="rId15"/>
+    <hyperlink ref="G55" r:id="rId16"/>
+    <hyperlink ref="G59" r:id="rId17"/>
+    <hyperlink ref="G68" r:id="rId18"/>
+    <hyperlink ref="G80" r:id="rId19"/>
+    <hyperlink ref="G90" r:id="rId20"/>
+    <hyperlink ref="G93" r:id="rId21"/>
+    <hyperlink ref="G100" r:id="rId22"/>
+    <hyperlink ref="G104" r:id="rId23"/>
+    <hyperlink ref="G108" r:id="rId24"/>
+    <hyperlink ref="G110" r:id="rId25"/>
+    <hyperlink ref="G118" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6099">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19493,6 +19493,12 @@
   </si>
   <si>
     <t>ADM_CFG_006.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 16:36 IST — pass in 3.3s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_008.png</t>
   </si>
   <si>
     <t>ADM_CFG_050.png</t>
@@ -28115,13 +28121,13 @@
         <v>5045</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" ht="75" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51929,22 +51935,22 @@
         <v>5040</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>6071</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>6072</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -52013,7 +52019,7 @@
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6071</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52122,13 +52128,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6072</v>
+        <v>6074</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6073</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52375,13 +52381,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52398,13 +52404,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52651,13 +52657,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52703,7 +52709,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52927,13 +52933,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53025,7 +53031,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53226,13 +53232,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53502,13 +53508,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53732,13 +53738,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53801,13 +53807,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53968,7 +53974,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54054,13 +54060,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54146,13 +54152,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6093</v>
+        <v>6095</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6094</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54198,7 +54204,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6095</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54376,13 +54382,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54442,23 +54448,24 @@
     <hyperlink ref="G9" r:id="rId7"/>
     <hyperlink ref="G10" r:id="rId8"/>
     <hyperlink ref="G11" r:id="rId9"/>
-    <hyperlink ref="G15" r:id="rId10"/>
-    <hyperlink ref="G20" r:id="rId11"/>
-    <hyperlink ref="G31" r:id="rId12"/>
-    <hyperlink ref="G32" r:id="rId13"/>
-    <hyperlink ref="G43" r:id="rId14"/>
-    <hyperlink ref="G45" r:id="rId15"/>
-    <hyperlink ref="G55" r:id="rId16"/>
-    <hyperlink ref="G59" r:id="rId17"/>
-    <hyperlink ref="G68" r:id="rId18"/>
-    <hyperlink ref="G80" r:id="rId19"/>
-    <hyperlink ref="G90" r:id="rId20"/>
-    <hyperlink ref="G93" r:id="rId21"/>
-    <hyperlink ref="G100" r:id="rId22"/>
-    <hyperlink ref="G104" r:id="rId23"/>
-    <hyperlink ref="G108" r:id="rId24"/>
-    <hyperlink ref="G110" r:id="rId25"/>
-    <hyperlink ref="G118" r:id="rId26"/>
+    <hyperlink ref="G12" r:id="rId10"/>
+    <hyperlink ref="G15" r:id="rId11"/>
+    <hyperlink ref="G20" r:id="rId12"/>
+    <hyperlink ref="G31" r:id="rId13"/>
+    <hyperlink ref="G32" r:id="rId14"/>
+    <hyperlink ref="G43" r:id="rId15"/>
+    <hyperlink ref="G45" r:id="rId16"/>
+    <hyperlink ref="G55" r:id="rId17"/>
+    <hyperlink ref="G59" r:id="rId18"/>
+    <hyperlink ref="G68" r:id="rId19"/>
+    <hyperlink ref="G80" r:id="rId20"/>
+    <hyperlink ref="G90" r:id="rId21"/>
+    <hyperlink ref="G93" r:id="rId22"/>
+    <hyperlink ref="G100" r:id="rId23"/>
+    <hyperlink ref="G104" r:id="rId24"/>
+    <hyperlink ref="G108" r:id="rId25"/>
+    <hyperlink ref="G110" r:id="rId26"/>
+    <hyperlink ref="G118" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6101">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19499,6 +19499,12 @@
   </si>
   <si>
     <t>ADM_CFG_008.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 21:19 IST — pass in 30.1s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_071.png</t>
   </si>
   <si>
     <t>ADM_CFG_050.png</t>
@@ -28159,13 +28165,13 @@
         <v>5052</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51958,22 +51964,22 @@
         <v>5046</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>6073</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>6074</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -52019,7 +52025,7 @@
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6073</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52128,13 +52134,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6074</v>
+        <v>6076</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52381,13 +52387,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52404,13 +52410,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52657,13 +52663,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52709,7 +52715,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52933,13 +52939,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53031,7 +53037,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53232,13 +53238,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53508,13 +53514,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53738,13 +53744,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53807,13 +53813,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53974,7 +53980,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6093</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54060,13 +54066,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6094</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54152,13 +54158,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6095</v>
+        <v>6097</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54204,7 +54210,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6097</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54382,13 +54388,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54449,23 +54455,24 @@
     <hyperlink ref="G10" r:id="rId8"/>
     <hyperlink ref="G11" r:id="rId9"/>
     <hyperlink ref="G12" r:id="rId10"/>
-    <hyperlink ref="G15" r:id="rId11"/>
-    <hyperlink ref="G20" r:id="rId12"/>
-    <hyperlink ref="G31" r:id="rId13"/>
-    <hyperlink ref="G32" r:id="rId14"/>
-    <hyperlink ref="G43" r:id="rId15"/>
-    <hyperlink ref="G45" r:id="rId16"/>
-    <hyperlink ref="G55" r:id="rId17"/>
-    <hyperlink ref="G59" r:id="rId18"/>
-    <hyperlink ref="G68" r:id="rId19"/>
-    <hyperlink ref="G80" r:id="rId20"/>
-    <hyperlink ref="G90" r:id="rId21"/>
-    <hyperlink ref="G93" r:id="rId22"/>
-    <hyperlink ref="G100" r:id="rId23"/>
-    <hyperlink ref="G104" r:id="rId24"/>
-    <hyperlink ref="G108" r:id="rId25"/>
-    <hyperlink ref="G110" r:id="rId26"/>
-    <hyperlink ref="G118" r:id="rId27"/>
+    <hyperlink ref="G13" r:id="rId11"/>
+    <hyperlink ref="G15" r:id="rId12"/>
+    <hyperlink ref="G20" r:id="rId13"/>
+    <hyperlink ref="G31" r:id="rId14"/>
+    <hyperlink ref="G32" r:id="rId15"/>
+    <hyperlink ref="G43" r:id="rId16"/>
+    <hyperlink ref="G45" r:id="rId17"/>
+    <hyperlink ref="G55" r:id="rId18"/>
+    <hyperlink ref="G59" r:id="rId19"/>
+    <hyperlink ref="G68" r:id="rId20"/>
+    <hyperlink ref="G80" r:id="rId21"/>
+    <hyperlink ref="G90" r:id="rId22"/>
+    <hyperlink ref="G93" r:id="rId23"/>
+    <hyperlink ref="G100" r:id="rId24"/>
+    <hyperlink ref="G104" r:id="rId25"/>
+    <hyperlink ref="G108" r:id="rId26"/>
+    <hyperlink ref="G110" r:id="rId27"/>
+    <hyperlink ref="G118" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6103">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19505,6 +19505,12 @@
   </si>
   <si>
     <t>ADM_CFG_071.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 21:28 IST — pass in 56.9s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_009.png</t>
   </si>
   <si>
     <t>ADM_CFG_050.png</t>
@@ -28203,13 +28209,13 @@
         <v>5059</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -51987,22 +51993,22 @@
         <v>5053</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5834</v>
+        <v>5768</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>6075</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>6076</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -52025,7 +52031,7 @@
         <v>179</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>6075</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -52134,13 +52140,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6076</v>
+        <v>6078</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6077</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52387,13 +52393,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6079</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52410,13 +52416,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6080</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52663,13 +52669,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52715,7 +52721,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52939,13 +52945,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53037,7 +53043,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53238,13 +53244,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53514,13 +53520,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53744,13 +53750,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53813,13 +53819,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6093</v>
+        <v>6095</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6094</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53980,7 +53986,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6095</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54066,13 +54072,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54158,13 +54164,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6097</v>
+        <v>6099</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54210,7 +54216,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6099</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54388,13 +54394,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6078</v>
+        <v>6080</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54456,23 +54462,24 @@
     <hyperlink ref="G11" r:id="rId9"/>
     <hyperlink ref="G12" r:id="rId10"/>
     <hyperlink ref="G13" r:id="rId11"/>
-    <hyperlink ref="G15" r:id="rId12"/>
-    <hyperlink ref="G20" r:id="rId13"/>
-    <hyperlink ref="G31" r:id="rId14"/>
-    <hyperlink ref="G32" r:id="rId15"/>
-    <hyperlink ref="G43" r:id="rId16"/>
-    <hyperlink ref="G45" r:id="rId17"/>
-    <hyperlink ref="G55" r:id="rId18"/>
-    <hyperlink ref="G59" r:id="rId19"/>
-    <hyperlink ref="G68" r:id="rId20"/>
-    <hyperlink ref="G80" r:id="rId21"/>
-    <hyperlink ref="G90" r:id="rId22"/>
-    <hyperlink ref="G93" r:id="rId23"/>
-    <hyperlink ref="G100" r:id="rId24"/>
-    <hyperlink ref="G104" r:id="rId25"/>
-    <hyperlink ref="G108" r:id="rId26"/>
-    <hyperlink ref="G110" r:id="rId27"/>
-    <hyperlink ref="G118" r:id="rId28"/>
+    <hyperlink ref="G14" r:id="rId12"/>
+    <hyperlink ref="G15" r:id="rId13"/>
+    <hyperlink ref="G20" r:id="rId14"/>
+    <hyperlink ref="G31" r:id="rId15"/>
+    <hyperlink ref="G32" r:id="rId16"/>
+    <hyperlink ref="G43" r:id="rId17"/>
+    <hyperlink ref="G45" r:id="rId18"/>
+    <hyperlink ref="G55" r:id="rId19"/>
+    <hyperlink ref="G59" r:id="rId20"/>
+    <hyperlink ref="G68" r:id="rId21"/>
+    <hyperlink ref="G80" r:id="rId22"/>
+    <hyperlink ref="G90" r:id="rId23"/>
+    <hyperlink ref="G93" r:id="rId24"/>
+    <hyperlink ref="G100" r:id="rId25"/>
+    <hyperlink ref="G104" r:id="rId26"/>
+    <hyperlink ref="G108" r:id="rId27"/>
+    <hyperlink ref="G110" r:id="rId28"/>
+    <hyperlink ref="G118" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6108">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16445,7 +16445,7 @@
 2. Inspect the response and the persisted tower state.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable tower id; admin JWT</t>
+    <t>[TEST_DATA_REQUIRED] disposable tower id; admin JWT  →  USED: PUT towers/status-update batch; flip Aura (id) → restore; admin JWT; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>The endpoint applies all toggles in one batch and returns success; tower records reflect the new isActive values.</t>
@@ -19526,6 +19526,9 @@
   </si>
   <si>
     <t>ADM_CFG_072.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 22:00 IST — pass in 20.6s</t>
   </si>
   <si>
     <t>2026-06-27 14:33 IST — pass in 3.0s</t>
@@ -28411,13 +28414,13 @@
         <v>5096</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -52120,19 +52123,19 @@
         <v>5090</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5837</v>
+        <v>5771</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>6082</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
@@ -52152,13 +52155,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6082</v>
+        <v>6083</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6083</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52405,13 +52408,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6085</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52428,13 +52431,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6086</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52681,13 +52684,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6087</v>
+        <v>6088</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6088</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52733,7 +52736,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6089</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52957,13 +52960,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6090</v>
+        <v>6091</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6091</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53055,7 +53058,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6092</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53256,13 +53259,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6093</v>
+        <v>6094</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6094</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53532,13 +53535,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6095</v>
+        <v>6096</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6096</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53762,13 +53765,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6098</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53831,13 +53834,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6099</v>
+        <v>6100</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6100</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -53998,7 +54001,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6101</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54084,13 +54087,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6095</v>
+        <v>6096</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6102</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54176,13 +54179,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6103</v>
+        <v>6104</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6104</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54228,7 +54231,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6105</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54406,13 +54409,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6106</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6110">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16403,7 +16403,7 @@
 2. Check that no buyer or SM notification is dispatched as a side-effect.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable tower; notification-sink visibility</t>
+    <t>[TEST_DATA_REQUIRED] disposable tower; notification-sink visibility  →  USED: Tower: Aura (flip→save→restore); network-monitored for notification calls; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>No SMS / WhatsApp / email is sent on tower-config save (silent by design, FS Feature 1 §8).</t>
@@ -19526,6 +19526,12 @@
   </si>
   <si>
     <t>ADM_CFG_072.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 23:03 IST — pass in 30.7s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_073.png</t>
   </si>
   <si>
     <t>2026-06-27 22:00 IST — pass in 20.6s</t>
@@ -28338,13 +28344,13 @@
         <v>5083</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" ht="75" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52077,22 +52083,22 @@
         <v>5077</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5837</v>
+        <v>5771</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>6082</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>6083</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -52132,7 +52138,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>6082</v>
+        <v>6084</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -52155,13 +52161,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6083</v>
+        <v>6085</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52408,13 +52414,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52431,13 +52437,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52684,13 +52690,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52736,7 +52742,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52960,13 +52966,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53058,7 +53064,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6093</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53259,13 +53265,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6094</v>
+        <v>6096</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6095</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53535,13 +53541,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6097</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53765,13 +53771,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6099</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53834,13 +53840,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6101</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54001,7 +54007,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54087,13 +54093,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6103</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54179,13 +54185,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6105</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54231,7 +54237,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54409,13 +54415,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54480,22 +54486,23 @@
     <hyperlink ref="G14" r:id="rId12"/>
     <hyperlink ref="G15" r:id="rId13"/>
     <hyperlink ref="G16" r:id="rId14"/>
-    <hyperlink ref="G20" r:id="rId15"/>
-    <hyperlink ref="G31" r:id="rId16"/>
-    <hyperlink ref="G32" r:id="rId17"/>
-    <hyperlink ref="G43" r:id="rId18"/>
-    <hyperlink ref="G45" r:id="rId19"/>
-    <hyperlink ref="G55" r:id="rId20"/>
-    <hyperlink ref="G59" r:id="rId21"/>
-    <hyperlink ref="G68" r:id="rId22"/>
-    <hyperlink ref="G80" r:id="rId23"/>
-    <hyperlink ref="G90" r:id="rId24"/>
-    <hyperlink ref="G93" r:id="rId25"/>
-    <hyperlink ref="G100" r:id="rId26"/>
-    <hyperlink ref="G104" r:id="rId27"/>
-    <hyperlink ref="G108" r:id="rId28"/>
-    <hyperlink ref="G110" r:id="rId29"/>
-    <hyperlink ref="G118" r:id="rId30"/>
+    <hyperlink ref="G17" r:id="rId15"/>
+    <hyperlink ref="G20" r:id="rId16"/>
+    <hyperlink ref="G31" r:id="rId17"/>
+    <hyperlink ref="G32" r:id="rId18"/>
+    <hyperlink ref="G43" r:id="rId19"/>
+    <hyperlink ref="G45" r:id="rId20"/>
+    <hyperlink ref="G55" r:id="rId21"/>
+    <hyperlink ref="G59" r:id="rId22"/>
+    <hyperlink ref="G68" r:id="rId23"/>
+    <hyperlink ref="G80" r:id="rId24"/>
+    <hyperlink ref="G90" r:id="rId25"/>
+    <hyperlink ref="G93" r:id="rId26"/>
+    <hyperlink ref="G100" r:id="rId27"/>
+    <hyperlink ref="G104" r:id="rId28"/>
+    <hyperlink ref="G108" r:id="rId29"/>
+    <hyperlink ref="G110" r:id="rId30"/>
+    <hyperlink ref="G118" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6112">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16423,7 +16423,7 @@
 3. Re-check the Customers Active Towers KPI and the buyer-side unit grid.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] one disposable inactive tower; user authorisation</t>
+    <t>[TEST_DATA_REQUIRED] one disposable inactive tower; user authorisation  →  USED: Tower: Aura (flip Active→Inactive→restore); Active Towers KPI/DB before↔after; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>Active Towers KPI in Customers changes by one; the Python real-time unit cache is notified and the buyer-side grid reflects the new tower state (FS Feature 1 §7).</t>
@@ -19532,6 +19532,12 @@
   </si>
   <si>
     <t>ADM_CFG_073.png</t>
+  </si>
+  <si>
+    <t>2026-06-27 23:07 IST — pass in 30.5s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_074.png</t>
   </si>
   <si>
     <t>2026-06-27 22:00 IST — pass in 20.6s</t>
@@ -28382,13 +28388,13 @@
         <v>5089</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52106,22 +52112,22 @@
         <v>5084</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5837</v>
+        <v>5771</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>6084</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>6085</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -52138,7 +52144,7 @@
         <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>6084</v>
+        <v>6086</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -52161,13 +52167,13 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>6086</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -52414,13 +52420,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6088</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52437,13 +52443,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6089</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52690,13 +52696,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6090</v>
+        <v>6092</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6091</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52742,7 +52748,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6092</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52966,13 +52972,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6093</v>
+        <v>6095</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6094</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53064,7 +53070,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6095</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53265,13 +53271,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6096</v>
+        <v>6098</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6097</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53541,13 +53547,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6099</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53771,13 +53777,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6101</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53840,13 +53846,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6103</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54007,7 +54013,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54093,13 +54099,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6105</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54185,13 +54191,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54237,7 +54243,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54415,13 +54421,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54487,22 +54493,23 @@
     <hyperlink ref="G15" r:id="rId13"/>
     <hyperlink ref="G16" r:id="rId14"/>
     <hyperlink ref="G17" r:id="rId15"/>
-    <hyperlink ref="G20" r:id="rId16"/>
-    <hyperlink ref="G31" r:id="rId17"/>
-    <hyperlink ref="G32" r:id="rId18"/>
-    <hyperlink ref="G43" r:id="rId19"/>
-    <hyperlink ref="G45" r:id="rId20"/>
-    <hyperlink ref="G55" r:id="rId21"/>
-    <hyperlink ref="G59" r:id="rId22"/>
-    <hyperlink ref="G68" r:id="rId23"/>
-    <hyperlink ref="G80" r:id="rId24"/>
-    <hyperlink ref="G90" r:id="rId25"/>
-    <hyperlink ref="G93" r:id="rId26"/>
-    <hyperlink ref="G100" r:id="rId27"/>
-    <hyperlink ref="G104" r:id="rId28"/>
-    <hyperlink ref="G108" r:id="rId29"/>
-    <hyperlink ref="G110" r:id="rId30"/>
-    <hyperlink ref="G118" r:id="rId31"/>
+    <hyperlink ref="G18" r:id="rId16"/>
+    <hyperlink ref="G20" r:id="rId17"/>
+    <hyperlink ref="G31" r:id="rId18"/>
+    <hyperlink ref="G32" r:id="rId19"/>
+    <hyperlink ref="G43" r:id="rId20"/>
+    <hyperlink ref="G45" r:id="rId21"/>
+    <hyperlink ref="G55" r:id="rId22"/>
+    <hyperlink ref="G59" r:id="rId23"/>
+    <hyperlink ref="G68" r:id="rId24"/>
+    <hyperlink ref="G80" r:id="rId25"/>
+    <hyperlink ref="G90" r:id="rId26"/>
+    <hyperlink ref="G93" r:id="rId27"/>
+    <hyperlink ref="G100" r:id="rId28"/>
+    <hyperlink ref="G104" r:id="rId29"/>
+    <hyperlink ref="G108" r:id="rId30"/>
+    <hyperlink ref="G110" r:id="rId31"/>
+    <hyperlink ref="G118" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6123">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16551,7 +16551,7 @@
 3. Observe.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable registration numbers; user authorisation</t>
+    <t>[TEST_DATA_REQUIRED] disposable registration numbers; user authorisation  →  USED: Registration: GHNG-1000008364-Q — upload Forbid → availableForAllocation=false (status WAITLIST) → restore Allow; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>Each registration is set status=WAITLIST, availableForAllocation=false and is excluded from the campaign eligible pool (BRD §11.7 dual-write).</t>
@@ -19574,6 +19574,12 @@
   </si>
   <si>
     <t>ADM_CFG_012.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 00:05 IST — pass in 31.5s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_013.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28659,13 +28665,13 @@
         <v>5129</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52277,22 +52283,22 @@
         <v>5123</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>6098</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>6099</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -52447,13 +52453,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6099</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52470,13 +52476,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52723,13 +52729,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6101</v>
+        <v>6103</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52775,7 +52781,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6103</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52999,13 +53005,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6105</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53097,7 +53103,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53298,13 +53304,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53574,13 +53580,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53804,13 +53810,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53873,13 +53879,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54040,7 +54046,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54126,13 +54132,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54218,13 +54224,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54270,7 +54276,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54448,13 +54454,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54525,21 +54531,22 @@
     <hyperlink ref="G21" r:id="rId18"/>
     <hyperlink ref="G22" r:id="rId19"/>
     <hyperlink ref="G23" r:id="rId20"/>
-    <hyperlink ref="G31" r:id="rId21"/>
-    <hyperlink ref="G32" r:id="rId22"/>
-    <hyperlink ref="G43" r:id="rId23"/>
-    <hyperlink ref="G45" r:id="rId24"/>
-    <hyperlink ref="G55" r:id="rId25"/>
-    <hyperlink ref="G59" r:id="rId26"/>
-    <hyperlink ref="G68" r:id="rId27"/>
-    <hyperlink ref="G80" r:id="rId28"/>
-    <hyperlink ref="G90" r:id="rId29"/>
-    <hyperlink ref="G93" r:id="rId30"/>
-    <hyperlink ref="G100" r:id="rId31"/>
-    <hyperlink ref="G104" r:id="rId32"/>
-    <hyperlink ref="G108" r:id="rId33"/>
-    <hyperlink ref="G110" r:id="rId34"/>
-    <hyperlink ref="G118" r:id="rId35"/>
+    <hyperlink ref="G24" r:id="rId21"/>
+    <hyperlink ref="G31" r:id="rId22"/>
+    <hyperlink ref="G32" r:id="rId23"/>
+    <hyperlink ref="G43" r:id="rId24"/>
+    <hyperlink ref="G45" r:id="rId25"/>
+    <hyperlink ref="G55" r:id="rId26"/>
+    <hyperlink ref="G59" r:id="rId27"/>
+    <hyperlink ref="G68" r:id="rId28"/>
+    <hyperlink ref="G80" r:id="rId29"/>
+    <hyperlink ref="G90" r:id="rId30"/>
+    <hyperlink ref="G93" r:id="rId31"/>
+    <hyperlink ref="G100" r:id="rId32"/>
+    <hyperlink ref="G104" r:id="rId33"/>
+    <hyperlink ref="G108" r:id="rId34"/>
+    <hyperlink ref="G110" r:id="rId35"/>
+    <hyperlink ref="G118" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6125">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16574,7 +16574,7 @@
 3. Observe row processing.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable rows with mixed-case Allow values</t>
+    <t>[TEST_DATA_REQUIRED] disposable rows with mixed-case Allow values  →  USED: GHNG-1000008364-Q="allow" (lowercase), -G="ALLOW" (uppercase); Forbid baseline then mixed-case Allow; both → eligible; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>All case variants are accepted and processed identically (BRD §5 case-insensitive note).</t>
@@ -19580,6 +19580,12 @@
   </si>
   <si>
     <t>ADM_CFG_013.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 00:36 IST — pass in 57.8s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_014.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28703,13 +28709,13 @@
         <v>5136</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52306,22 +52312,22 @@
         <v>5130</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>6100</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>6101</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -52453,13 +52459,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6101</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52476,13 +52482,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52729,13 +52735,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6103</v>
+        <v>6105</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52781,7 +52787,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6105</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53005,13 +53011,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53103,7 +53109,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53304,13 +53310,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53580,13 +53586,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53810,13 +53816,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53879,13 +53885,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54046,7 +54052,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54132,13 +54138,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54224,13 +54230,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54276,7 +54282,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54454,13 +54460,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6100</v>
+        <v>6102</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54532,21 +54538,22 @@
     <hyperlink ref="G22" r:id="rId19"/>
     <hyperlink ref="G23" r:id="rId20"/>
     <hyperlink ref="G24" r:id="rId21"/>
-    <hyperlink ref="G31" r:id="rId22"/>
-    <hyperlink ref="G32" r:id="rId23"/>
-    <hyperlink ref="G43" r:id="rId24"/>
-    <hyperlink ref="G45" r:id="rId25"/>
-    <hyperlink ref="G55" r:id="rId26"/>
-    <hyperlink ref="G59" r:id="rId27"/>
-    <hyperlink ref="G68" r:id="rId28"/>
-    <hyperlink ref="G80" r:id="rId29"/>
-    <hyperlink ref="G90" r:id="rId30"/>
-    <hyperlink ref="G93" r:id="rId31"/>
-    <hyperlink ref="G100" r:id="rId32"/>
-    <hyperlink ref="G104" r:id="rId33"/>
-    <hyperlink ref="G108" r:id="rId34"/>
-    <hyperlink ref="G110" r:id="rId35"/>
-    <hyperlink ref="G118" r:id="rId36"/>
+    <hyperlink ref="G25" r:id="rId22"/>
+    <hyperlink ref="G31" r:id="rId23"/>
+    <hyperlink ref="G32" r:id="rId24"/>
+    <hyperlink ref="G43" r:id="rId25"/>
+    <hyperlink ref="G45" r:id="rId26"/>
+    <hyperlink ref="G55" r:id="rId27"/>
+    <hyperlink ref="G59" r:id="rId28"/>
+    <hyperlink ref="G68" r:id="rId29"/>
+    <hyperlink ref="G80" r:id="rId30"/>
+    <hyperlink ref="G90" r:id="rId31"/>
+    <hyperlink ref="G93" r:id="rId32"/>
+    <hyperlink ref="G100" r:id="rId33"/>
+    <hyperlink ref="G104" r:id="rId34"/>
+    <hyperlink ref="G108" r:id="rId35"/>
+    <hyperlink ref="G110" r:id="rId36"/>
+    <hyperlink ref="G118" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6127">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16596,7 +16596,7 @@
 2. Observe the response.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] active campaign + disposable rows</t>
+    <t>[TEST_DATA_REQUIRED] active campaign + disposable rows  →  USED: GHNG-1000008364-Q Forbid upload while campaign ACTIVE → expect rejection ("campaign is active"), no mutation; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>HTTP 400 'Cannot update registration-unit when campaign is active' — the upload is rejected (BRD §11.7).</t>
@@ -19586,6 +19586,12 @@
   </si>
   <si>
     <t>ADM_CFG_014.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 00:49 IST — pass in 33.2s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_076.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28747,13 +28753,13 @@
         <v>5143</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52335,22 +52341,22 @@
         <v>5137</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>6102</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>6103</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -52459,13 +52465,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6103</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52482,13 +52488,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52735,13 +52741,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6105</v>
+        <v>6107</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52787,7 +52793,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53011,13 +53017,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53109,7 +53115,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53310,13 +53316,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53586,13 +53592,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53816,13 +53822,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53885,13 +53891,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54052,7 +54058,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54138,13 +54144,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54230,13 +54236,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54282,7 +54288,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54460,13 +54466,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6124</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54539,21 +54545,22 @@
     <hyperlink ref="G23" r:id="rId20"/>
     <hyperlink ref="G24" r:id="rId21"/>
     <hyperlink ref="G25" r:id="rId22"/>
-    <hyperlink ref="G31" r:id="rId23"/>
-    <hyperlink ref="G32" r:id="rId24"/>
-    <hyperlink ref="G43" r:id="rId25"/>
-    <hyperlink ref="G45" r:id="rId26"/>
-    <hyperlink ref="G55" r:id="rId27"/>
-    <hyperlink ref="G59" r:id="rId28"/>
-    <hyperlink ref="G68" r:id="rId29"/>
-    <hyperlink ref="G80" r:id="rId30"/>
-    <hyperlink ref="G90" r:id="rId31"/>
-    <hyperlink ref="G93" r:id="rId32"/>
-    <hyperlink ref="G100" r:id="rId33"/>
-    <hyperlink ref="G104" r:id="rId34"/>
-    <hyperlink ref="G108" r:id="rId35"/>
-    <hyperlink ref="G110" r:id="rId36"/>
-    <hyperlink ref="G118" r:id="rId37"/>
+    <hyperlink ref="G26" r:id="rId23"/>
+    <hyperlink ref="G31" r:id="rId24"/>
+    <hyperlink ref="G32" r:id="rId25"/>
+    <hyperlink ref="G43" r:id="rId26"/>
+    <hyperlink ref="G45" r:id="rId27"/>
+    <hyperlink ref="G55" r:id="rId28"/>
+    <hyperlink ref="G59" r:id="rId29"/>
+    <hyperlink ref="G68" r:id="rId30"/>
+    <hyperlink ref="G80" r:id="rId31"/>
+    <hyperlink ref="G90" r:id="rId32"/>
+    <hyperlink ref="G93" r:id="rId33"/>
+    <hyperlink ref="G100" r:id="rId34"/>
+    <hyperlink ref="G104" r:id="rId35"/>
+    <hyperlink ref="G108" r:id="rId36"/>
+    <hyperlink ref="G110" r:id="rId37"/>
+    <hyperlink ref="G118" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6129">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16619,7 +16619,7 @@
 3. Inspect which rows were applied.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] a WINNER reg + a HOLD reg + a normal reg</t>
+    <t>[TEST_DATA_REQUIRED] a WINNER reg + a HOLD reg + a normal reg  →  USED: Upload Forbid for -C (WINNER) + -Q (normal): WINNER skipped (unchanged), normal applied; restore -Q; ALLOW_DESTRUCTIVE=1 (campaign OFF)</t>
   </si>
   <si>
     <t>WINNER and HOLD rows are skipped (not updated); only non-WINNER/non-HOLD rows are applied (BRD §11.7, Op.notIn ['WINNER','HOLD']).</t>
@@ -19592,6 +19592,12 @@
   </si>
   <si>
     <t>ADM_CFG_076.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 01:01 IST — pass in 54.5s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_077.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28791,13 +28797,13 @@
         <v>5150</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52364,22 +52370,22 @@
         <v>5144</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>6104</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>6105</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -52465,13 +52471,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6105</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52488,13 +52494,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52741,13 +52747,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52793,7 +52799,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53017,13 +53023,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53115,7 +53121,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53316,13 +53322,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53592,13 +53598,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53822,13 +53828,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53891,13 +53897,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54058,7 +54064,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54144,13 +54150,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54236,13 +54242,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6124</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54288,7 +54294,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6125</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54466,13 +54472,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6126</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54546,21 +54552,22 @@
     <hyperlink ref="G24" r:id="rId21"/>
     <hyperlink ref="G25" r:id="rId22"/>
     <hyperlink ref="G26" r:id="rId23"/>
-    <hyperlink ref="G31" r:id="rId24"/>
-    <hyperlink ref="G32" r:id="rId25"/>
-    <hyperlink ref="G43" r:id="rId26"/>
-    <hyperlink ref="G45" r:id="rId27"/>
-    <hyperlink ref="G55" r:id="rId28"/>
-    <hyperlink ref="G59" r:id="rId29"/>
-    <hyperlink ref="G68" r:id="rId30"/>
-    <hyperlink ref="G80" r:id="rId31"/>
-    <hyperlink ref="G90" r:id="rId32"/>
-    <hyperlink ref="G93" r:id="rId33"/>
-    <hyperlink ref="G100" r:id="rId34"/>
-    <hyperlink ref="G104" r:id="rId35"/>
-    <hyperlink ref="G108" r:id="rId36"/>
-    <hyperlink ref="G110" r:id="rId37"/>
-    <hyperlink ref="G118" r:id="rId38"/>
+    <hyperlink ref="G27" r:id="rId24"/>
+    <hyperlink ref="G31" r:id="rId25"/>
+    <hyperlink ref="G32" r:id="rId26"/>
+    <hyperlink ref="G43" r:id="rId27"/>
+    <hyperlink ref="G45" r:id="rId28"/>
+    <hyperlink ref="G55" r:id="rId29"/>
+    <hyperlink ref="G59" r:id="rId30"/>
+    <hyperlink ref="G68" r:id="rId31"/>
+    <hyperlink ref="G80" r:id="rId32"/>
+    <hyperlink ref="G90" r:id="rId33"/>
+    <hyperlink ref="G93" r:id="rId34"/>
+    <hyperlink ref="G100" r:id="rId35"/>
+    <hyperlink ref="G104" r:id="rId36"/>
+    <hyperlink ref="G108" r:id="rId37"/>
+    <hyperlink ref="G110" r:id="rId38"/>
+    <hyperlink ref="G118" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6131">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16641,7 +16641,7 @@
 2. Inspect each registration's status and availableForAllocation in the DB.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable registrations; admin JWT</t>
+    <t>[TEST_DATA_REQUIRED] disposable registrations; admin JWT  →  USED: GHNG-1000008364-Q: Forbid→{WAITLIST,false} then Allow→{PREALLOCATED,true}; both fields; self-restore; ALLOW_DESTRUCTIVE=1 (campaign OFF)</t>
   </si>
   <si>
     <t>Allow -&gt; {status=PREALLOCATED, availableForAllocation=true}; Forbid -&gt; {status=WAITLIST, availableForAllocation=false}. Both fields are written (BRD §11.7 corrects prior boolean-only FRD).</t>
@@ -19598,6 +19598,12 @@
   </si>
   <si>
     <t>ADM_CFG_077.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 01:11 IST — pass in 42.3s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_FSD_058.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28835,13 +28841,13 @@
         <v>5157</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52393,22 +52399,22 @@
         <v>5151</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>6106</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>6107</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -52471,13 +52477,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6107</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52494,13 +52500,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52747,13 +52753,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52799,7 +52805,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53023,13 +53029,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53121,7 +53127,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53322,13 +53328,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53598,13 +53604,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53828,13 +53834,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53897,13 +53903,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54064,7 +54070,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54150,13 +54156,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6124</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54242,13 +54248,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6125</v>
+        <v>6127</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6126</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54294,7 +54300,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6127</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54472,13 +54478,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6128</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54553,21 +54559,22 @@
     <hyperlink ref="G25" r:id="rId22"/>
     <hyperlink ref="G26" r:id="rId23"/>
     <hyperlink ref="G27" r:id="rId24"/>
-    <hyperlink ref="G31" r:id="rId25"/>
-    <hyperlink ref="G32" r:id="rId26"/>
-    <hyperlink ref="G43" r:id="rId27"/>
-    <hyperlink ref="G45" r:id="rId28"/>
-    <hyperlink ref="G55" r:id="rId29"/>
-    <hyperlink ref="G59" r:id="rId30"/>
-    <hyperlink ref="G68" r:id="rId31"/>
-    <hyperlink ref="G80" r:id="rId32"/>
-    <hyperlink ref="G90" r:id="rId33"/>
-    <hyperlink ref="G93" r:id="rId34"/>
-    <hyperlink ref="G100" r:id="rId35"/>
-    <hyperlink ref="G104" r:id="rId36"/>
-    <hyperlink ref="G108" r:id="rId37"/>
-    <hyperlink ref="G110" r:id="rId38"/>
-    <hyperlink ref="G118" r:id="rId39"/>
+    <hyperlink ref="G28" r:id="rId25"/>
+    <hyperlink ref="G31" r:id="rId26"/>
+    <hyperlink ref="G32" r:id="rId27"/>
+    <hyperlink ref="G43" r:id="rId28"/>
+    <hyperlink ref="G45" r:id="rId29"/>
+    <hyperlink ref="G55" r:id="rId30"/>
+    <hyperlink ref="G59" r:id="rId31"/>
+    <hyperlink ref="G68" r:id="rId32"/>
+    <hyperlink ref="G80" r:id="rId33"/>
+    <hyperlink ref="G90" r:id="rId34"/>
+    <hyperlink ref="G93" r:id="rId35"/>
+    <hyperlink ref="G100" r:id="rId36"/>
+    <hyperlink ref="G104" r:id="rId37"/>
+    <hyperlink ref="G108" r:id="rId38"/>
+    <hyperlink ref="G110" r:id="rId39"/>
+    <hyperlink ref="G118" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6133">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16663,7 +16663,7 @@
 2. Verify no buyer/SM notification is dispatched.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable rows; notification-sink visibility</t>
+    <t>[TEST_DATA_REQUIRED] disposable rows; notification-sink visibility  →  USED: GHNG-1000008364-Q Forbid upload, network-monitored for notifications → none; restore Allow; ALLOW_DESTRUCTIVE=1</t>
   </si>
   <si>
     <t>No SMS / WhatsApp / email is sent (silent by design, FS Feature 2 §8).</t>
@@ -19604,6 +19604,12 @@
   </si>
   <si>
     <t>ADM_CFG_FSD_058.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 01:15 IST — pass in 30.5s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_078.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28879,13 +28885,13 @@
         <v>5164</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52422,22 +52428,22 @@
         <v>5158</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>6108</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>6109</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -52477,13 +52483,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6109</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52500,13 +52506,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52753,13 +52759,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52805,7 +52811,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53029,13 +53035,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53127,7 +53133,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53328,13 +53334,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53604,13 +53610,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53834,13 +53840,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53903,13 +53909,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6124</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54070,7 +54076,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6125</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54156,13 +54162,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6126</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54248,13 +54254,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6127</v>
+        <v>6129</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6128</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54300,7 +54306,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6129</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54478,13 +54484,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6130</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54560,21 +54566,22 @@
     <hyperlink ref="G26" r:id="rId23"/>
     <hyperlink ref="G27" r:id="rId24"/>
     <hyperlink ref="G28" r:id="rId25"/>
-    <hyperlink ref="G31" r:id="rId26"/>
-    <hyperlink ref="G32" r:id="rId27"/>
-    <hyperlink ref="G43" r:id="rId28"/>
-    <hyperlink ref="G45" r:id="rId29"/>
-    <hyperlink ref="G55" r:id="rId30"/>
-    <hyperlink ref="G59" r:id="rId31"/>
-    <hyperlink ref="G68" r:id="rId32"/>
-    <hyperlink ref="G80" r:id="rId33"/>
-    <hyperlink ref="G90" r:id="rId34"/>
-    <hyperlink ref="G93" r:id="rId35"/>
-    <hyperlink ref="G100" r:id="rId36"/>
-    <hyperlink ref="G104" r:id="rId37"/>
-    <hyperlink ref="G108" r:id="rId38"/>
-    <hyperlink ref="G110" r:id="rId39"/>
-    <hyperlink ref="G118" r:id="rId40"/>
+    <hyperlink ref="G29" r:id="rId26"/>
+    <hyperlink ref="G31" r:id="rId27"/>
+    <hyperlink ref="G32" r:id="rId28"/>
+    <hyperlink ref="G43" r:id="rId29"/>
+    <hyperlink ref="G45" r:id="rId30"/>
+    <hyperlink ref="G55" r:id="rId31"/>
+    <hyperlink ref="G59" r:id="rId32"/>
+    <hyperlink ref="G68" r:id="rId33"/>
+    <hyperlink ref="G80" r:id="rId34"/>
+    <hyperlink ref="G90" r:id="rId35"/>
+    <hyperlink ref="G93" r:id="rId36"/>
+    <hyperlink ref="G100" r:id="rId37"/>
+    <hyperlink ref="G104" r:id="rId38"/>
+    <hyperlink ref="G108" r:id="rId39"/>
+    <hyperlink ref="G110" r:id="rId40"/>
+    <hyperlink ref="G118" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6135">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16685,7 +16685,7 @@
 2. Inspect the Redis registration cache and the Python /broadcast-registrations inbound.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable rows; downstream observability</t>
+    <t>[TEST_DATA_REQUIRED] disposable rows; downstream observability  →  USED: N/A — cross-system side-effect; DB trigger verified by Goals 12–19</t>
   </si>
   <si>
     <t>Redis is updated and a Python /broadcast-registrations call fires for the affected registrations (BRD §11.7 side-effects).</t>
@@ -19610,6 +19610,12 @@
   </si>
   <si>
     <t>ADM_CFG_078.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 01:23 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>ADM_CFG_079.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.3s</t>
@@ -28923,13 +28929,13 @@
         <v>5171</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52451,22 +52457,22 @@
         <v>5165</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>6110</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" t="s">
-        <v>24</v>
+        <v>179</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>6111</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -52483,13 +52489,13 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>6111</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -52506,13 +52512,13 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>6112</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -52759,13 +52765,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6113</v>
+        <v>6115</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6114</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52811,7 +52817,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53035,13 +53041,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53133,7 +53139,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53334,13 +53340,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53610,13 +53616,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53840,13 +53846,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6124</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53909,13 +53915,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6125</v>
+        <v>6127</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6126</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54076,7 +54082,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6127</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54162,13 +54168,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6128</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54254,13 +54260,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6129</v>
+        <v>6131</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6130</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54306,7 +54312,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6131</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54484,13 +54490,13 @@
         <v>67</v>
       </c>
       <c r="E118" t="s">
-        <v>6110</v>
+        <v>6112</v>
       </c>
       <c r="F118" t="s">
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6132</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54567,21 +54573,22 @@
     <hyperlink ref="G27" r:id="rId24"/>
     <hyperlink ref="G28" r:id="rId25"/>
     <hyperlink ref="G29" r:id="rId26"/>
-    <hyperlink ref="G31" r:id="rId27"/>
-    <hyperlink ref="G32" r:id="rId28"/>
-    <hyperlink ref="G43" r:id="rId29"/>
-    <hyperlink ref="G45" r:id="rId30"/>
-    <hyperlink ref="G55" r:id="rId31"/>
-    <hyperlink ref="G59" r:id="rId32"/>
-    <hyperlink ref="G68" r:id="rId33"/>
-    <hyperlink ref="G80" r:id="rId34"/>
-    <hyperlink ref="G90" r:id="rId35"/>
-    <hyperlink ref="G93" r:id="rId36"/>
-    <hyperlink ref="G100" r:id="rId37"/>
-    <hyperlink ref="G104" r:id="rId38"/>
-    <hyperlink ref="G108" r:id="rId39"/>
-    <hyperlink ref="G110" r:id="rId40"/>
-    <hyperlink ref="G118" r:id="rId41"/>
+    <hyperlink ref="G30" r:id="rId27"/>
+    <hyperlink ref="G31" r:id="rId28"/>
+    <hyperlink ref="G32" r:id="rId29"/>
+    <hyperlink ref="G43" r:id="rId30"/>
+    <hyperlink ref="G45" r:id="rId31"/>
+    <hyperlink ref="G55" r:id="rId32"/>
+    <hyperlink ref="G59" r:id="rId33"/>
+    <hyperlink ref="G68" r:id="rId34"/>
+    <hyperlink ref="G80" r:id="rId35"/>
+    <hyperlink ref="G90" r:id="rId36"/>
+    <hyperlink ref="G93" r:id="rId37"/>
+    <hyperlink ref="G100" r:id="rId38"/>
+    <hyperlink ref="G104" r:id="rId39"/>
+    <hyperlink ref="G108" r:id="rId40"/>
+    <hyperlink ref="G110" r:id="rId41"/>
+    <hyperlink ref="G118" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6137">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -19625,6 +19625,12 @@
   </si>
   <si>
     <t>ADM_CFG_016.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 01:27 IST — pass in 3.1s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_080.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 2.9s</t>
@@ -29053,19 +29059,19 @@
         <v>5189</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>75</v>
+        <v>5108</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>5190</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52526,22 +52532,22 @@
         <v>5186</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5840</v>
+        <v>5774</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>6115</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>6116</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -52765,13 +52771,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6115</v>
+        <v>6117</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6116</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52817,7 +52823,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6117</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53041,13 +53047,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6118</v>
+        <v>6120</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6119</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53139,7 +53145,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6120</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53340,13 +53346,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6122</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53616,13 +53622,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6124</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53846,13 +53852,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6125</v>
+        <v>6127</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6126</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53915,13 +53921,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6127</v>
+        <v>6129</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6128</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54082,7 +54088,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6129</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54168,13 +54174,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6123</v>
+        <v>6125</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6130</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54260,13 +54266,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6131</v>
+        <v>6133</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6132</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54312,7 +54318,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6133</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54496,7 +54502,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6134</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54576,19 +54582,20 @@
     <hyperlink ref="G30" r:id="rId27"/>
     <hyperlink ref="G31" r:id="rId28"/>
     <hyperlink ref="G32" r:id="rId29"/>
-    <hyperlink ref="G43" r:id="rId30"/>
-    <hyperlink ref="G45" r:id="rId31"/>
-    <hyperlink ref="G55" r:id="rId32"/>
-    <hyperlink ref="G59" r:id="rId33"/>
-    <hyperlink ref="G68" r:id="rId34"/>
-    <hyperlink ref="G80" r:id="rId35"/>
-    <hyperlink ref="G90" r:id="rId36"/>
-    <hyperlink ref="G93" r:id="rId37"/>
-    <hyperlink ref="G100" r:id="rId38"/>
-    <hyperlink ref="G104" r:id="rId39"/>
-    <hyperlink ref="G108" r:id="rId40"/>
-    <hyperlink ref="G110" r:id="rId41"/>
-    <hyperlink ref="G118" r:id="rId42"/>
+    <hyperlink ref="G33" r:id="rId30"/>
+    <hyperlink ref="G43" r:id="rId31"/>
+    <hyperlink ref="G45" r:id="rId32"/>
+    <hyperlink ref="G55" r:id="rId33"/>
+    <hyperlink ref="G59" r:id="rId34"/>
+    <hyperlink ref="G68" r:id="rId35"/>
+    <hyperlink ref="G80" r:id="rId36"/>
+    <hyperlink ref="G90" r:id="rId37"/>
+    <hyperlink ref="G93" r:id="rId38"/>
+    <hyperlink ref="G100" r:id="rId39"/>
+    <hyperlink ref="G104" r:id="rId40"/>
+    <hyperlink ref="G108" r:id="rId41"/>
+    <hyperlink ref="G110" r:id="rId42"/>
+    <hyperlink ref="G118" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6149">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16837,7 +16837,7 @@
 3. Observe the message.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] all-zero Update sample</t>
+    <t>[TEST_DATA_REQUIRED] all-zero Update sample  →  USED: unit_no 302 (testUnit-547664512575) single row Status=RESERVED Update=0 → expect HTTP 400 "No rows marked for update"; no DB write; ALLOW_DESTRUCTIVE=1 (non-mutating)</t>
   </si>
   <si>
     <t>A 'No rows marked for update' message is shown; no unit is changed (BRD §7 validations).</t>
@@ -16860,7 +16860,7 @@
 3. Inspect the result file.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] a row with Status=BLOCKED</t>
+    <t>[TEST_DATA_REQUIRED] a row with Status=BLOCKED  →  USED: unit_no 302 (testUnit-547664512575) Status=BLOCKED Update=1 → expect row-level error in result file (invalid status); no DB write; ALLOW_DESTRUCTIVE=1 (non-mutating)</t>
   </si>
   <si>
     <t>That row returns an error in the result file; the unit is not changed (BRD §7 validations).</t>
@@ -19655,6 +19655,18 @@
   </si>
   <si>
     <t>ADM_CFG_019.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 12:45 IST — pass in 28.4s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_020.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 12:45 IST — pass in 6.0s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_021.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 2.9s</t>
@@ -29241,13 +29253,13 @@
         <v>5218</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -29279,13 +29291,13 @@
         <v>5225</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52648,22 +52660,22 @@
         <v>5212</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>5843</v>
+        <v>5777</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>6125</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>6126</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -52671,22 +52683,22 @@
         <v>5219</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>5843</v>
+        <v>5777</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>6127</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>6128</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -52795,13 +52807,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52847,7 +52859,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53071,13 +53083,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53169,7 +53181,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53370,13 +53382,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53646,13 +53658,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53876,13 +53888,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53945,13 +53957,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54112,7 +54124,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54198,13 +54210,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54290,13 +54302,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54342,7 +54354,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54526,7 +54538,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54609,19 +54621,21 @@
     <hyperlink ref="G33" r:id="rId30"/>
     <hyperlink ref="G35" r:id="rId31"/>
     <hyperlink ref="G36" r:id="rId32"/>
-    <hyperlink ref="G43" r:id="rId33"/>
-    <hyperlink ref="G45" r:id="rId34"/>
-    <hyperlink ref="G55" r:id="rId35"/>
-    <hyperlink ref="G59" r:id="rId36"/>
-    <hyperlink ref="G68" r:id="rId37"/>
-    <hyperlink ref="G80" r:id="rId38"/>
-    <hyperlink ref="G90" r:id="rId39"/>
-    <hyperlink ref="G93" r:id="rId40"/>
-    <hyperlink ref="G100" r:id="rId41"/>
-    <hyperlink ref="G104" r:id="rId42"/>
-    <hyperlink ref="G108" r:id="rId43"/>
-    <hyperlink ref="G110" r:id="rId44"/>
-    <hyperlink ref="G118" r:id="rId45"/>
+    <hyperlink ref="G37" r:id="rId33"/>
+    <hyperlink ref="G38" r:id="rId34"/>
+    <hyperlink ref="G43" r:id="rId35"/>
+    <hyperlink ref="G45" r:id="rId36"/>
+    <hyperlink ref="G55" r:id="rId37"/>
+    <hyperlink ref="G59" r:id="rId38"/>
+    <hyperlink ref="G68" r:id="rId39"/>
+    <hyperlink ref="G80" r:id="rId40"/>
+    <hyperlink ref="G90" r:id="rId41"/>
+    <hyperlink ref="G93" r:id="rId42"/>
+    <hyperlink ref="G100" r:id="rId43"/>
+    <hyperlink ref="G104" r:id="rId44"/>
+    <hyperlink ref="G108" r:id="rId45"/>
+    <hyperlink ref="G110" r:id="rId46"/>
+    <hyperlink ref="G118" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6155">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16883,7 +16883,7 @@
 3. Inspect the result.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] a BOOKED unit</t>
+    <t>[TEST_DATA_REQUIRED] a BOOKED unit  →  USED: unit_no 1001 (testUnit-547664514703, Crest, BOOKED) upload Status=AVAILABLE Update=1 → expect rejection (only AVAILABLE↔RESERVED per §11.8); DB must stay BOOKED (asserted + guarded). ALLOW_DESTRUCTIVE=1; user-authorised touch of a BOOKED unit.</t>
   </si>
   <si>
     <t>The row is rejected/skipped — BOOKED-&gt;AVAILABLE is NOT supported (BRD §11.8). Records DOC_DRIFT-004 against the older FS 'high-risk operation' wording.</t>
@@ -16927,7 +16927,7 @@
 2. Verify no notification dispatched.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable units; notification-sink visibility</t>
+    <t>[TEST_DATA_REQUIRED] disposable units; notification-sink visibility  →  USED: unit_no 302 (testUnit-547664512575) valid AVAILABLE→RESERVED→restore; FS Feature 3 §8 = "Notifications: None" — verify DB side-effect occurs AND zero buyer-notification calls fire (mirrors 078). Admin success toast is expected, not a notification. ALLOW_DESTRUCTIVE=1 (self-restore).</t>
   </si>
   <si>
     <t>No SMS / WhatsApp / email is sent (silent by design).</t>
@@ -16949,7 +16949,7 @@
 2. Inspect the Python unit-cache refresh and the buyer-side grid.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable units; downstream observability</t>
+    <t>[TEST_DATA_REQUIRED] disposable units; downstream observability  →  USED: VERIFY-WITH-DEV — Python real-time unit-cache fan-out (FS Feature 3 §7) is not observable from the UI/DB test layer (no Redis/Python log access). Mirrors ADM_CFG_079. Requires backend log verification with dev.</t>
   </si>
   <si>
     <t>The Python service is notified and the buyer/admin tower grid reflects the new statuses immediately (FS Feature 3 §7).</t>
@@ -19667,6 +19667,24 @@
   </si>
   <si>
     <t>ADM_CFG_021.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 12:56 IST — pass in 27.0s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_081.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 12:56 IST — pass in 15.6s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_082.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 12:56 IST — skip in FS §7</t>
+  </si>
+  <si>
+    <t>ADM_CFG_083.png</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 2.9s</t>
@@ -29329,13 +29347,13 @@
         <v>5232</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L56" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -29405,13 +29423,13 @@
         <v>5246</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L58" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -29443,13 +29461,13 @@
         <v>5253</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -52706,22 +52724,22 @@
         <v>5226</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>5843</v>
+        <v>5777</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>6129</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>6130</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -52752,22 +52770,22 @@
         <v>5240</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>5843</v>
+        <v>5777</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>6131</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>6132</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -52775,22 +52793,22 @@
         <v>5247</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>5843</v>
+        <v>5777</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>6133</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
-      </c>
-      <c r="G42" t="s">
-        <v>24</v>
+        <v>179</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>6134</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -52807,13 +52825,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6129</v>
+        <v>6135</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6130</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52859,7 +52877,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6131</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53083,13 +53101,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6132</v>
+        <v>6138</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6133</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53181,7 +53199,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6134</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53382,13 +53400,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6135</v>
+        <v>6141</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6136</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53658,13 +53676,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6137</v>
+        <v>6143</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6138</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53888,13 +53906,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6139</v>
+        <v>6145</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6140</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53957,13 +53975,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6141</v>
+        <v>6147</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54124,7 +54142,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6143</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54210,13 +54228,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6137</v>
+        <v>6143</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6144</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54302,13 +54320,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6145</v>
+        <v>6151</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6146</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54354,7 +54372,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6147</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54538,7 +54556,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54623,19 +54641,22 @@
     <hyperlink ref="G36" r:id="rId32"/>
     <hyperlink ref="G37" r:id="rId33"/>
     <hyperlink ref="G38" r:id="rId34"/>
-    <hyperlink ref="G43" r:id="rId35"/>
-    <hyperlink ref="G45" r:id="rId36"/>
-    <hyperlink ref="G55" r:id="rId37"/>
-    <hyperlink ref="G59" r:id="rId38"/>
-    <hyperlink ref="G68" r:id="rId39"/>
-    <hyperlink ref="G80" r:id="rId40"/>
-    <hyperlink ref="G90" r:id="rId41"/>
-    <hyperlink ref="G93" r:id="rId42"/>
-    <hyperlink ref="G100" r:id="rId43"/>
-    <hyperlink ref="G104" r:id="rId44"/>
-    <hyperlink ref="G108" r:id="rId45"/>
-    <hyperlink ref="G110" r:id="rId46"/>
-    <hyperlink ref="G118" r:id="rId47"/>
+    <hyperlink ref="G39" r:id="rId35"/>
+    <hyperlink ref="G41" r:id="rId36"/>
+    <hyperlink ref="G42" r:id="rId37"/>
+    <hyperlink ref="G43" r:id="rId38"/>
+    <hyperlink ref="G45" r:id="rId39"/>
+    <hyperlink ref="G55" r:id="rId40"/>
+    <hyperlink ref="G59" r:id="rId41"/>
+    <hyperlink ref="G68" r:id="rId42"/>
+    <hyperlink ref="G80" r:id="rId43"/>
+    <hyperlink ref="G90" r:id="rId44"/>
+    <hyperlink ref="G93" r:id="rId45"/>
+    <hyperlink ref="G100" r:id="rId46"/>
+    <hyperlink ref="G104" r:id="rId47"/>
+    <hyperlink ref="G108" r:id="rId48"/>
+    <hyperlink ref="G110" r:id="rId49"/>
+    <hyperlink ref="G118" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6156">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -16905,7 +16905,7 @@
 2. Inspect per-row outcome.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] units in AVAILABLE, RESERVED, BOOKED; admin JWT</t>
+    <t>[TEST_DATA_REQUIRED] units in AVAILABLE, RESERVED, BOOKED; admin JWT  →  USED: POST /api/v1/admin/update-units-status multipart: Row A 302 (testUnit-547664512575) AVAILABLE→RESERVED = allowed; Row B 1001 (testUnit-547664514703, BOOKED)→AVAILABLE = rejected. Verify result file + DB; restore 302→AVAILABLE. admin JWT; ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>AVAILABLE&lt;-&gt;RESERVED rows succeed; the BOOKED-&gt;AVAILABLE row is rejected (BRD §11.8).</t>
@@ -19673,6 +19673,9 @@
   </si>
   <si>
     <t>ADM_CFG_081.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 13:05 IST — pass in 22.2s</t>
   </si>
   <si>
     <t>2026-06-28 12:56 IST — pass in 15.6s</t>
@@ -29385,13 +29388,13 @@
         <v>5239</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52747,19 +52750,19 @@
         <v>5233</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>5843</v>
+        <v>5777</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>6131</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -52779,13 +52782,13 @@
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>6131</v>
+        <v>6132</v>
       </c>
       <c r="F41" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>6132</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -52802,13 +52805,13 @@
         <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>6133</v>
+        <v>6134</v>
       </c>
       <c r="F42" t="s">
         <v>179</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>6134</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -52825,13 +52828,13 @@
         <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>6135</v>
+        <v>6136</v>
       </c>
       <c r="F43" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>6136</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -52877,7 +52880,7 @@
         <v>179</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6137</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -53101,13 +53104,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6139</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53199,7 +53202,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6140</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53400,13 +53403,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6141</v>
+        <v>6142</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6142</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53676,13 +53679,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6144</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53906,13 +53909,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6145</v>
+        <v>6146</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6146</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -53975,13 +53978,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6147</v>
+        <v>6148</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6148</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54142,7 +54145,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6149</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54228,13 +54231,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6150</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54320,13 +54323,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6151</v>
+        <v>6152</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6152</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54372,7 +54375,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6153</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54556,7 +54559,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6167">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17013,7 +17013,7 @@
 3. Observe the unit detail price.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable units; user authorisation</t>
+    <t>[TEST_DATA_REQUIRED] disposable units; user authorisation  →  USED: unit_no 302 (testUnit-547664512575) Early Bird Benefit captured → set sentinel 5000 (Update=1) → DB reflects 5000 → restore to original (DB-verified). ALLOW_DESTRUCTIVE=1; user-authorised pricing change with capture+restore.</t>
   </si>
   <si>
     <t>Prices update immediately and the new values appear in unit detail/Towers views (FS Feature 4 §7).</t>
@@ -19706,6 +19706,9 @@
   </si>
   <si>
     <t>ADM_CFG_084.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 13:16 IST — pass in 36.2s</t>
   </si>
   <si>
     <t>ADM_CFG_023.png</t>
@@ -29624,10 +29627,10 @@
         <v>5273</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L63" s="15" t="s">
         <v>68</v>
@@ -52895,22 +52898,22 @@
         <v>5267</v>
       </c>
       <c r="B45" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>5779</v>
       </c>
       <c r="D45" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E45" t="s">
-        <v>6080</v>
+        <v>6142</v>
       </c>
       <c r="F45" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>6142</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -52950,13 +52953,13 @@
         <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="F47" t="s">
         <v>66</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>6144</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -52996,13 +52999,13 @@
         <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>6145</v>
+        <v>6146</v>
       </c>
       <c r="F49" t="s">
         <v>66</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>6146</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -53088,13 +53091,13 @@
         <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>6147</v>
+        <v>6148</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>6148</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -53134,13 +53137,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6149</v>
+        <v>6150</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6150</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53232,7 +53235,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6151</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53433,13 +53436,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6152</v>
+        <v>6153</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6153</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53709,13 +53712,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6155</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53939,13 +53942,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6156</v>
+        <v>6157</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6157</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54008,13 +54011,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6158</v>
+        <v>6159</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6159</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54175,7 +54178,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6160</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54261,13 +54264,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6161</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54353,13 +54356,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6162</v>
+        <v>6163</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6163</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54405,7 +54408,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6164</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54589,7 +54592,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6165</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6173">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17036,7 +17036,7 @@
 3. Open that unit's detail.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable unit</t>
+    <t>[TEST_DATA_REQUIRED] disposable unit  →  USED: unit_no 302 (testUnit-547664512575) Early Bird Benefit → sentinel 7777 (Update=1); re-download inventory and confirm the unit row shows 7777; restore original. ALLOW_DESTRUCTIVE=1; capture+restore.</t>
   </si>
   <si>
     <t>The unit detail shows the updated early-bird benefit (FS Feature 4 §7). [VERIFY WITH DEV] exact early-bird column name under §11.8 header set (see ADM_CFG_085).</t>
@@ -17081,7 +17081,7 @@
 2. Observe per-row validation.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] PERCENT row w/o percent; AMOUNT row w/o amount</t>
+    <t>[TEST_DATA_REQUIRED] PERCENT row w/o percent; AMOUNT row w/o amount  →  USED: unit_no 302 (testUnit-547664512575): upload Allocation Calc Type=PERCENT (percent=12) then =AMOUNT (amount=27000), each Update=1; DB reflects calc type + value each time; restore original allocation fields. ALLOW_DESTRUCTIVE=1; capture+restore.</t>
   </si>
   <si>
     <t>Rows missing the required field for their allocationCalcType are rejected. Real columns are allocationAmount/allocationPercent/allocationCalcType — NOT the older Agreement_Value/EarlyBird (DOC_DRIFT-003, BRD §11.8). [VERIFY WITH DEV] exact live header set.</t>
@@ -17171,7 +17171,7 @@
 2. Verify no buyer notification is dispatched.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable unit; notification-sink visibility</t>
+    <t>[TEST_DATA_REQUIRED] disposable unit; notification-sink visibility  →  USED: unit_no 302 (testUnit-547664512575) Early Bird → sentinel 3333 (Update=1) while monitoring for buyer-notification calls → expect zero; DB side-effect confirmed; restore. FS Feature 4 §8 = no notification. ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>No automatic buyer notification about price changes (silent by design, FS Feature 4 §8).</t>
@@ -19714,16 +19714,34 @@
     <t>ADM_CFG_023.png</t>
   </si>
   <si>
+    <t>2026-06-28 13:19 IST — pass in 49.5s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_025.png</t>
+  </si>
+  <si>
     <t>2026-06-28 13:10 IST — pass in 27.5s</t>
   </si>
   <si>
     <t>ADM_CFG_026.png</t>
   </si>
   <si>
+    <t>2026-06-28 13:19 IST — pass in 18.5s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_085.png</t>
+  </si>
+  <si>
     <t>2026-06-28 13:10 IST — pass in 7.2s</t>
   </si>
   <si>
     <t>ADM_CFG_086.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 13:19 IST — pass in 10.4s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_088.png</t>
   </si>
   <si>
     <t>2026-06-28 13:10 IST — pass in 4.5s</t>
@@ -29665,13 +29683,13 @@
         <v>5280</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -29741,13 +29759,13 @@
         <v>5294</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L66" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -29893,13 +29911,13 @@
         <v>5322</v>
       </c>
       <c r="J70" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K70" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L70" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -52921,22 +52939,22 @@
         <v>5274</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>5845</v>
+        <v>5779</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E46" t="s">
-        <v>24</v>
+        <v>6144</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>6145</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -52953,13 +52971,13 @@
         <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>6144</v>
+        <v>6146</v>
       </c>
       <c r="F47" t="s">
         <v>66</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>6145</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -52967,22 +52985,22 @@
         <v>5288</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>5845</v>
+        <v>5779</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>6148</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>6149</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -52999,13 +53017,13 @@
         <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="F49" t="s">
         <v>66</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -53059,22 +53077,22 @@
         <v>5316</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>5845</v>
+        <v>5779</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>6152</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>6153</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -53091,13 +53109,13 @@
         <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>6149</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -53137,13 +53155,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6150</v>
+        <v>6156</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6151</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53235,7 +53253,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6152</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53436,13 +53454,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6153</v>
+        <v>6159</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6154</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53712,13 +53730,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6156</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53942,13 +53960,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6157</v>
+        <v>6163</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6158</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54011,13 +54029,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6159</v>
+        <v>6165</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6160</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54178,7 +54196,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6161</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54264,13 +54282,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6162</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54356,13 +54374,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6163</v>
+        <v>6169</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6164</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54408,7 +54426,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6165</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54592,7 +54610,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6166</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54683,20 +54701,23 @@
     <hyperlink ref="G43" r:id="rId38"/>
     <hyperlink ref="G44" r:id="rId39"/>
     <hyperlink ref="G45" r:id="rId40"/>
-    <hyperlink ref="G47" r:id="rId41"/>
-    <hyperlink ref="G49" r:id="rId42"/>
-    <hyperlink ref="G53" r:id="rId43"/>
-    <hyperlink ref="G55" r:id="rId44"/>
-    <hyperlink ref="G59" r:id="rId45"/>
-    <hyperlink ref="G68" r:id="rId46"/>
-    <hyperlink ref="G80" r:id="rId47"/>
-    <hyperlink ref="G90" r:id="rId48"/>
-    <hyperlink ref="G93" r:id="rId49"/>
-    <hyperlink ref="G100" r:id="rId50"/>
-    <hyperlink ref="G104" r:id="rId51"/>
-    <hyperlink ref="G108" r:id="rId52"/>
-    <hyperlink ref="G110" r:id="rId53"/>
-    <hyperlink ref="G118" r:id="rId54"/>
+    <hyperlink ref="G46" r:id="rId41"/>
+    <hyperlink ref="G47" r:id="rId42"/>
+    <hyperlink ref="G48" r:id="rId43"/>
+    <hyperlink ref="G49" r:id="rId44"/>
+    <hyperlink ref="G52" r:id="rId45"/>
+    <hyperlink ref="G53" r:id="rId46"/>
+    <hyperlink ref="G55" r:id="rId47"/>
+    <hyperlink ref="G59" r:id="rId48"/>
+    <hyperlink ref="G68" r:id="rId49"/>
+    <hyperlink ref="G80" r:id="rId50"/>
+    <hyperlink ref="G90" r:id="rId51"/>
+    <hyperlink ref="G93" r:id="rId52"/>
+    <hyperlink ref="G100" r:id="rId53"/>
+    <hyperlink ref="G104" r:id="rId54"/>
+    <hyperlink ref="G108" r:id="rId55"/>
+    <hyperlink ref="G110" r:id="rId56"/>
+    <hyperlink ref="G118" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6175">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17149,7 +17149,7 @@
 2. Re-fetch the unit detail in an allocation session.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] active campaign + disposable unit</t>
+    <t>[TEST_DATA_REQUIRED] active campaign + disposable unit  →  USED: unit_no 302 (testUnit-547664512575) Early Bird → sentinel 8888 (Update=1): attach file → assert NOT applied yet (no draft/preview), then Submit → assert applied instantly in DB; restore. NOTE: §4 pricing upload has no §2-style campaign guard (high-risk rule); campaign-active path is environmentally gated (verified with campaign OFF). ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>The new price is reflected immediately in new unit-detail requests; no draft/preview step (FS Feature 4 §6, Domain Red Flag HIGH).</t>
@@ -19736,6 +19736,12 @@
   </si>
   <si>
     <t>ADM_CFG_086.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 13:21 IST — pass in 32.4s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_024.png</t>
   </si>
   <si>
     <t>2026-06-28 13:19 IST — pass in 10.4s</t>
@@ -29873,13 +29879,13 @@
         <v>5315</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -53054,22 +53060,22 @@
         <v>5309</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>5845</v>
+        <v>5779</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>24</v>
+        <v>6152</v>
       </c>
       <c r="F51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>6153</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -53086,13 +53092,13 @@
         <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>6152</v>
+        <v>6154</v>
       </c>
       <c r="F52" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>6153</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -53109,13 +53115,13 @@
         <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>6154</v>
+        <v>6156</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>6155</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -53155,13 +53161,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6156</v>
+        <v>6158</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6157</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53253,7 +53259,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6158</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53454,13 +53460,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6159</v>
+        <v>6161</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6160</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53730,13 +53736,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6161</v>
+        <v>6163</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6162</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53960,13 +53966,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6163</v>
+        <v>6165</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6164</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54029,13 +54035,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6165</v>
+        <v>6167</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6166</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54196,7 +54202,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6167</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54282,13 +54288,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6161</v>
+        <v>6163</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6168</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54374,13 +54380,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6169</v>
+        <v>6171</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6170</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54426,7 +54432,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6171</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54610,7 +54616,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6172</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54705,19 +54711,20 @@
     <hyperlink ref="G47" r:id="rId42"/>
     <hyperlink ref="G48" r:id="rId43"/>
     <hyperlink ref="G49" r:id="rId44"/>
-    <hyperlink ref="G52" r:id="rId45"/>
-    <hyperlink ref="G53" r:id="rId46"/>
-    <hyperlink ref="G55" r:id="rId47"/>
-    <hyperlink ref="G59" r:id="rId48"/>
-    <hyperlink ref="G68" r:id="rId49"/>
-    <hyperlink ref="G80" r:id="rId50"/>
-    <hyperlink ref="G90" r:id="rId51"/>
-    <hyperlink ref="G93" r:id="rId52"/>
-    <hyperlink ref="G100" r:id="rId53"/>
-    <hyperlink ref="G104" r:id="rId54"/>
-    <hyperlink ref="G108" r:id="rId55"/>
-    <hyperlink ref="G110" r:id="rId56"/>
-    <hyperlink ref="G118" r:id="rId57"/>
+    <hyperlink ref="G51" r:id="rId45"/>
+    <hyperlink ref="G52" r:id="rId46"/>
+    <hyperlink ref="G53" r:id="rId47"/>
+    <hyperlink ref="G55" r:id="rId48"/>
+    <hyperlink ref="G59" r:id="rId49"/>
+    <hyperlink ref="G68" r:id="rId50"/>
+    <hyperlink ref="G80" r:id="rId51"/>
+    <hyperlink ref="G90" r:id="rId52"/>
+    <hyperlink ref="G93" r:id="rId53"/>
+    <hyperlink ref="G100" r:id="rId54"/>
+    <hyperlink ref="G104" r:id="rId55"/>
+    <hyperlink ref="G108" r:id="rId56"/>
+    <hyperlink ref="G110" r:id="rId57"/>
+    <hyperlink ref="G118" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6177">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17215,7 +17215,7 @@
 2. Inspect the persisted unit.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable unit id; admin JWT</t>
+    <t>[TEST_DATA_REQUIRED] disposable unit id; admin JWT  →  USED: VERIFY-WITH-DEV — PATCH /api/v1/admin/units/:id returns 404 "Not found" on UAT (probed PK 7007 + unit_id + /unit + /units; all 404). Endpoint from FS §11.9 GAP-TL-047 "New Feature" not yet deployed. Re-test when shipped.</t>
   </si>
   <si>
     <t>The unit's pricing and status update in a single call (BRD §11.9). [VERIFY WITH DEV] — endpoint not exposed in the Config UI; API-only.</t>
@@ -19738,6 +19738,9 @@
     <t>ADM_CFG_086.png</t>
   </si>
   <si>
+    <t>2026-06-28 13:25 IST — skip in §11.8</t>
+  </si>
+  <si>
     <t>2026-06-28 13:21 IST — pass in 32.4s</t>
   </si>
   <si>
@@ -19754,6 +19757,9 @@
   </si>
   <si>
     <t>ADM_CFG_089.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 13:25 IST — skip in §11.9</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.1s</t>
@@ -29841,13 +29847,13 @@
         <v>5308</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L68" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -29993,13 +29999,13 @@
         <v>5336</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L72" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -53037,19 +53043,19 @@
         <v>5302</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>5845</v>
+        <v>5779</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>6152</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="G50" t="s">
         <v>24</v>
@@ -53069,13 +53075,13 @@
         <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>6152</v>
+        <v>6153</v>
       </c>
       <c r="F51" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>6153</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -53092,13 +53098,13 @@
         <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
       <c r="F52" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>6155</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -53115,13 +53121,13 @@
         <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>6156</v>
+        <v>6157</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>6157</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -53129,19 +53135,19 @@
         <v>5330</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>5845</v>
+        <v>5779</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>6159</v>
       </c>
       <c r="F54" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="G54" t="s">
         <v>24</v>
@@ -53161,13 +53167,13 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>6158</v>
+        <v>6160</v>
       </c>
       <c r="F55" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>6159</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -53259,7 +53265,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6160</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53460,13 +53466,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6161</v>
+        <v>6163</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6162</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53736,13 +53742,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6163</v>
+        <v>6165</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6164</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53966,13 +53972,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6165</v>
+        <v>6167</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6166</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54035,13 +54041,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6167</v>
+        <v>6169</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6168</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54202,7 +54208,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6169</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54288,13 +54294,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6163</v>
+        <v>6165</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6170</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54380,13 +54386,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6171</v>
+        <v>6173</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6172</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54432,7 +54438,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6173</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54616,7 +54622,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6174</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6188">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17276,7 +17276,7 @@
 3. Observe.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable WINNER bookings; user authorisation</t>
+    <t>[TEST_DATA_REQUIRED] disposable WINNER bookings; user authorisation  →  USED: GHNG-1000008364-O (WINNER, 205-Aspire, Mavis cleared in LSQ by user) → bulk-cancel → reg_unit no longer an active WINNER (soft-deleted/cleared). IRREVERSIBLE; user-authorised. ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>Each listed booking is cancelled and its unit released back to inventory (BRD §11.4 / FS Feature 5 §7).</t>
@@ -19775,6 +19775,12 @@
   </si>
   <si>
     <t>ADM_CFG_090.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 14:12 IST — pass in 31.2s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_028.png</t>
   </si>
   <si>
     <t>ADM_CFG_056.png</t>
@@ -30156,13 +30162,13 @@
         <v>5355</v>
       </c>
       <c r="J76" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L76" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -53231,22 +53237,22 @@
         <v>5349</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>5846</v>
+        <v>5780</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>6165</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>6166</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -53292,7 +53298,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6165</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53332,13 +53338,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>6166</v>
+        <v>6168</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>6167</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -53424,13 +53430,13 @@
         <v>67</v>
       </c>
       <c r="E65" t="s">
-        <v>6168</v>
+        <v>6170</v>
       </c>
       <c r="F65" t="s">
         <v>66</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>6169</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -53447,13 +53453,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>6170</v>
+        <v>6172</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>6171</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -53493,13 +53499,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6172</v>
+        <v>6174</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6173</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53769,13 +53775,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6174</v>
+        <v>6176</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6175</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -53999,13 +54005,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6176</v>
+        <v>6178</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6177</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54068,13 +54074,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6178</v>
+        <v>6180</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6179</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54235,7 +54241,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6180</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54321,13 +54327,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6174</v>
+        <v>6176</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6181</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54413,13 +54419,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6182</v>
+        <v>6184</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6183</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54465,7 +54471,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6184</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54649,7 +54655,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6185</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54749,19 +54755,20 @@
     <hyperlink ref="G53" r:id="rId47"/>
     <hyperlink ref="G55" r:id="rId48"/>
     <hyperlink ref="G56" r:id="rId49"/>
-    <hyperlink ref="G59" r:id="rId50"/>
-    <hyperlink ref="G61" r:id="rId51"/>
-    <hyperlink ref="G65" r:id="rId52"/>
-    <hyperlink ref="G66" r:id="rId53"/>
-    <hyperlink ref="G68" r:id="rId54"/>
-    <hyperlink ref="G80" r:id="rId55"/>
-    <hyperlink ref="G90" r:id="rId56"/>
-    <hyperlink ref="G93" r:id="rId57"/>
-    <hyperlink ref="G100" r:id="rId58"/>
-    <hyperlink ref="G104" r:id="rId59"/>
-    <hyperlink ref="G108" r:id="rId60"/>
-    <hyperlink ref="G110" r:id="rId61"/>
-    <hyperlink ref="G118" r:id="rId62"/>
+    <hyperlink ref="G57" r:id="rId50"/>
+    <hyperlink ref="G59" r:id="rId51"/>
+    <hyperlink ref="G61" r:id="rId52"/>
+    <hyperlink ref="G65" r:id="rId53"/>
+    <hyperlink ref="G66" r:id="rId54"/>
+    <hyperlink ref="G68" r:id="rId55"/>
+    <hyperlink ref="G80" r:id="rId56"/>
+    <hyperlink ref="G90" r:id="rId57"/>
+    <hyperlink ref="G93" r:id="rId58"/>
+    <hyperlink ref="G100" r:id="rId59"/>
+    <hyperlink ref="G104" r:id="rId60"/>
+    <hyperlink ref="G108" r:id="rId61"/>
+    <hyperlink ref="G110" r:id="rId62"/>
+    <hyperlink ref="G118" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6194">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17298,7 +17298,7 @@
 2. Check the unit's status in the Towers grid.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable WINNER booking</t>
+    <t>[TEST_DATA_REQUIRED] disposable WINNER booking  →  USED: GHNG-1000008364-N (WINNER, unit testUnit-547664514130 = 206-Aspire, BOOKED, Mavis cleared) → cancel → unit released from BOOKED. FINDING: actual end-state is RESERVED, not AVAILABLE — cancellation reverts the registration to PREALLOCATED, which still reserves the unit (FS "AVAILABLE inventory" wording is imprecise; the unit is released to the allocatable pool but held as RESERVED). IRREVERSIBLE; user-authorised. ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>The released unit returns to AVAILABLE and becomes selectable in future campaigns (FS Feature 5 §7).</t>
@@ -17386,7 +17386,7 @@
 2. Check the payment/refund state.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] paid disposable booking</t>
+    <t>[TEST_DATA_REQUIRED] paid disposable booking  →  USED: GHNG-1000008364-M (WINNER, 306-Aspire, Mavis cleared) cancelled → payment_refunds unchanged (0→0), refund_at null — no auto-refund (BRD §6 r5). IRREVERSIBLE; user-authorised</t>
   </si>
   <si>
     <t>No automatic refund is initiated; refund is a separate manual step (BRD §6 rule 5).</t>
@@ -17405,7 +17405,7 @@
 2. Verify no buyer notification is dispatched.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] disposable booking; notification-sink visibility</t>
+    <t>[TEST_DATA_REQUIRED] disposable booking; notification-sink visibility  →  USED: GHNG-1000008364-L (WINNER, 307-Aspire, Mavis cleared) cancelled → 0 buyer-notification calls (FS §8). IRREVERSIBLE; user-authorised</t>
   </si>
   <si>
     <t>Zero notifications dispatched (FS Feature 5 §8 — cancelUnitsExcel sends none). Corrects the older 'Buyers receive cancellation notifications' How-to wording.</t>
@@ -17427,7 +17427,7 @@
 2. Submit and inspect the result.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] already-cancelled bookings</t>
+    <t>[TEST_DATA_REQUIRED] already-cancelled bookings  →  USED: GHNG-1000008364-O (already cancelled in 028 → PREALLOCATED) re-uploaded → 400 "No valid units available", skipped (only WINNER cancelable)</t>
   </si>
   <si>
     <t>Already-cancelled rows are reported as Unchanged / skipped (not re-cancelled). [VERIFY WITH DEV] exact label.</t>
@@ -17493,7 +17493,7 @@
 2. Inspect each model after cancellation.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] fully-linked disposable WINNER booking</t>
+    <t>[TEST_DATA_REQUIRED] fully-linked disposable WINNER booking  →  USED: GHNG-1000008364-K (WINNER, reg_unit 9785, 401-Aspire, Mavis cleared) cancelled → cascade cleared: payment_transactions 1→0, schedules 47→0, milestones 2→1. IRREVERSIBLE; user-authorised</t>
   </si>
   <si>
     <t>registration_units clears 20+ columns; payment_transactions, MilestonePaymentTracking, RegistrationUnitPaymentSchedule, RegistrationUnitOffer are soft-deleted; ParkingInventory HOLD/BOOKED rows release to AVAILABLE (BRD §11.6).</t>
@@ -19783,6 +19783,12 @@
     <t>ADM_CFG_028.png</t>
   </si>
   <si>
+    <t>2026-06-28 14:19 IST — pass in 24.0s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_060.png</t>
+  </si>
+  <si>
     <t>ADM_CFG_056.png</t>
   </si>
   <si>
@@ -19792,6 +19798,15 @@
     <t>ADM_CFG_092.png</t>
   </si>
   <si>
+    <t>2026-06-28 14:19 IST — pass in 27.7s</t>
+  </si>
+  <si>
+    <t>2026-06-28 14:19 IST — pass in 6.5s</t>
+  </si>
+  <si>
+    <t>2026-06-28 14:19 IST — pass in 6.3s</t>
+  </si>
+  <si>
     <t>2026-06-28 13:50 IST — pass in 6.2s</t>
   </si>
   <si>
@@ -19802,6 +19817,9 @@
   </si>
   <si>
     <t>ADM_CFG_059.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 14:19 IST — pass in 7.0s</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.9s</t>
@@ -27908,7 +27926,6 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>46</v>
@@ -30200,13 +30217,13 @@
         <v>5362</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -30352,13 +30369,13 @@
         <v>5390</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -30390,13 +30407,13 @@
         <v>5396</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L82" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -30428,13 +30445,13 @@
         <v>5403</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -30542,13 +30559,13 @@
         <v>5424</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L86" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -53260,22 +53277,22 @@
         <v>5356</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>5846</v>
+        <v>5780</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>6167</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>6168</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -53298,7 +53315,7 @@
         <v>179</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6167</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53338,13 +53355,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>6168</v>
+        <v>6170</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>6169</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -53352,19 +53369,19 @@
         <v>5384</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>5846</v>
+        <v>5780</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>6172</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -53375,19 +53392,19 @@
         <v>5391</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>5846</v>
+        <v>5780</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>6173</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -53398,19 +53415,19 @@
         <v>5397</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>5846</v>
+        <v>5780</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>6174</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -53430,13 +53447,13 @@
         <v>67</v>
       </c>
       <c r="E65" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="F65" t="s">
         <v>66</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -53453,13 +53470,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -53467,19 +53484,19 @@
         <v>5418</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>5846</v>
+        <v>5780</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E67" t="s">
-        <v>24</v>
+        <v>6179</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G67" t="s">
         <v>24</v>
@@ -53499,13 +53516,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6174</v>
+        <v>6180</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6175</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53775,13 +53792,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6176</v>
+        <v>6182</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6177</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -54005,13 +54022,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6178</v>
+        <v>6184</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6179</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54074,13 +54091,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6180</v>
+        <v>6186</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6181</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54241,7 +54258,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6182</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54327,13 +54344,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6176</v>
+        <v>6182</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6183</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54419,13 +54436,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6184</v>
+        <v>6190</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6185</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54471,7 +54488,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6186</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54655,7 +54672,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6187</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54756,19 +54773,20 @@
     <hyperlink ref="G55" r:id="rId48"/>
     <hyperlink ref="G56" r:id="rId49"/>
     <hyperlink ref="G57" r:id="rId50"/>
-    <hyperlink ref="G59" r:id="rId51"/>
-    <hyperlink ref="G61" r:id="rId52"/>
-    <hyperlink ref="G65" r:id="rId53"/>
-    <hyperlink ref="G66" r:id="rId54"/>
-    <hyperlink ref="G68" r:id="rId55"/>
-    <hyperlink ref="G80" r:id="rId56"/>
-    <hyperlink ref="G90" r:id="rId57"/>
-    <hyperlink ref="G93" r:id="rId58"/>
-    <hyperlink ref="G100" r:id="rId59"/>
-    <hyperlink ref="G104" r:id="rId60"/>
-    <hyperlink ref="G108" r:id="rId61"/>
-    <hyperlink ref="G110" r:id="rId62"/>
-    <hyperlink ref="G118" r:id="rId63"/>
+    <hyperlink ref="G58" r:id="rId51"/>
+    <hyperlink ref="G59" r:id="rId52"/>
+    <hyperlink ref="G61" r:id="rId53"/>
+    <hyperlink ref="G65" r:id="rId54"/>
+    <hyperlink ref="G66" r:id="rId55"/>
+    <hyperlink ref="G68" r:id="rId56"/>
+    <hyperlink ref="G80" r:id="rId57"/>
+    <hyperlink ref="G90" r:id="rId58"/>
+    <hyperlink ref="G93" r:id="rId59"/>
+    <hyperlink ref="G100" r:id="rId60"/>
+    <hyperlink ref="G104" r:id="rId61"/>
+    <hyperlink ref="G108" r:id="rId62"/>
+    <hyperlink ref="G110" r:id="rId63"/>
+    <hyperlink ref="G118" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6195">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17320,7 +17320,7 @@
 2. Observe.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] active campaign + booking</t>
+    <t>[TEST_DATA_REQUIRED] active campaign + booking  →  USED: GHNG-1000008364-H (WINNER, Mavis intact) bulk-cancel attempted while an allocation campaign is ACTIVE → submit-time re-check (§11.4) must BLOCK; booking stays WINNER (double-guarded: campaign + unresolved Mavis). ALLOW_DESTRUCTIVE=1; campaign-active window.</t>
   </si>
   <si>
     <t>HTTP 400 'Cannot cancel booking when campaign is active' (BRD §11.4).</t>
@@ -19787,6 +19787,9 @@
   </si>
   <si>
     <t>ADM_CFG_060.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 14:52 IST — pass in 26.9s</t>
   </si>
   <si>
     <t>ADM_CFG_056.png</t>
@@ -27926,6 +27929,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>46</v>
@@ -30255,10 +30259,10 @@
         <v>5369</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L78" s="15" t="s">
         <v>68</v>
@@ -53300,22 +53304,22 @@
         <v>5363</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>5780</v>
       </c>
       <c r="D59" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
-        <v>6081</v>
+        <v>6169</v>
       </c>
       <c r="F59" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>6169</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -53355,13 +53359,13 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>6170</v>
+        <v>6171</v>
       </c>
       <c r="F61" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>6171</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -53378,7 +53382,7 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>6172</v>
+        <v>6173</v>
       </c>
       <c r="F62" t="s">
         <v>66</v>
@@ -53401,7 +53405,7 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>6173</v>
+        <v>6174</v>
       </c>
       <c r="F63" t="s">
         <v>66</v>
@@ -53424,7 +53428,7 @@
         <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>6174</v>
+        <v>6175</v>
       </c>
       <c r="F64" t="s">
         <v>66</v>
@@ -53447,13 +53451,13 @@
         <v>67</v>
       </c>
       <c r="E65" t="s">
-        <v>6175</v>
+        <v>6176</v>
       </c>
       <c r="F65" t="s">
         <v>66</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>6176</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -53470,13 +53474,13 @@
         <v>67</v>
       </c>
       <c r="E66" t="s">
-        <v>6177</v>
+        <v>6178</v>
       </c>
       <c r="F66" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>6178</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -53493,7 +53497,7 @@
         <v>67</v>
       </c>
       <c r="E67" t="s">
-        <v>6179</v>
+        <v>6180</v>
       </c>
       <c r="F67" t="s">
         <v>66</v>
@@ -53516,13 +53520,13 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>6180</v>
+        <v>6181</v>
       </c>
       <c r="F68" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>6181</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -53792,13 +53796,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6182</v>
+        <v>6183</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6183</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -54022,13 +54026,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6185</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54091,13 +54095,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6186</v>
+        <v>6187</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6187</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54258,7 +54262,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6188</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54344,13 +54348,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6182</v>
+        <v>6183</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6189</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54436,13 +54440,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6190</v>
+        <v>6191</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6191</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54488,7 +54492,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6192</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54672,7 +54676,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6193</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6212">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17678,7 +17678,7 @@
 2. Upload, Submit, inspect the result file.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] fake registration number</t>
+    <t>[TEST_DATA_REQUIRED] fake registration number  →  USED: fake registration GHNG-9999999999 with Update=1 → row error / not-found; no mutation. Non-destructive. ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>That row is flagged as an error in the result file; no real registration is affected.</t>
@@ -19838,6 +19838,18 @@
   </si>
   <si>
     <t>ADM_CFG_030.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 15:12 IST — pass in 3.0s</t>
+  </si>
+  <si>
+    <t>2026-06-28 15:12 IST — pass in 7.1s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_064.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 15:12 IST — pass in 4.5s</t>
   </si>
   <si>
     <t>2026-06-27 14:24 IST — pass in 3.0s</t>
@@ -30694,13 +30706,13 @@
         <v>5348</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L89" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -30960,13 +30972,13 @@
         <v>5482</v>
       </c>
       <c r="J96" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K96" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L96" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -31074,13 +31086,13 @@
         <v>5501</v>
       </c>
       <c r="J99" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K99" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L99" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -53573,19 +53585,19 @@
         <v>5432</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>5849</v>
+        <v>5783</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>6186</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -53734,22 +53746,22 @@
         <v>5477</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>5849</v>
+        <v>5783</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>6187</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
-      </c>
-      <c r="G76" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G76" s="19" t="s">
+        <v>6188</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -53803,19 +53815,19 @@
         <v>5496</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>5849</v>
+        <v>5783</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>24</v>
+        <v>6189</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G79" t="s">
         <v>24</v>
@@ -53835,13 +53847,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -54065,13 +54077,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54134,13 +54146,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54157,13 +54169,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -54180,13 +54192,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -54272,13 +54284,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -54301,7 +54313,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54387,13 +54399,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54479,13 +54491,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54502,13 +54514,13 @@
         <v>67</v>
       </c>
       <c r="E109" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="F109" t="s">
         <v>66</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -54531,7 +54543,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54548,13 +54560,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -54715,7 +54727,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54822,19 +54834,20 @@
     <hyperlink ref="G65" r:id="rId54"/>
     <hyperlink ref="G66" r:id="rId55"/>
     <hyperlink ref="G68" r:id="rId56"/>
-    <hyperlink ref="G80" r:id="rId57"/>
-    <hyperlink ref="G90" r:id="rId58"/>
-    <hyperlink ref="G93" r:id="rId59"/>
-    <hyperlink ref="G94" r:id="rId60"/>
-    <hyperlink ref="G95" r:id="rId61"/>
-    <hyperlink ref="G99" r:id="rId62"/>
-    <hyperlink ref="G100" r:id="rId63"/>
-    <hyperlink ref="G104" r:id="rId64"/>
-    <hyperlink ref="G108" r:id="rId65"/>
-    <hyperlink ref="G109" r:id="rId66"/>
-    <hyperlink ref="G110" r:id="rId67"/>
-    <hyperlink ref="G111" r:id="rId68"/>
-    <hyperlink ref="G118" r:id="rId69"/>
+    <hyperlink ref="G76" r:id="rId57"/>
+    <hyperlink ref="G80" r:id="rId58"/>
+    <hyperlink ref="G90" r:id="rId59"/>
+    <hyperlink ref="G93" r:id="rId60"/>
+    <hyperlink ref="G94" r:id="rId61"/>
+    <hyperlink ref="G95" r:id="rId62"/>
+    <hyperlink ref="G99" r:id="rId63"/>
+    <hyperlink ref="G100" r:id="rId64"/>
+    <hyperlink ref="G104" r:id="rId65"/>
+    <hyperlink ref="G108" r:id="rId66"/>
+    <hyperlink ref="G109" r:id="rId67"/>
+    <hyperlink ref="G110" r:id="rId68"/>
+    <hyperlink ref="G111" r:id="rId69"/>
+    <hyperlink ref="G118" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6214">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17615,7 +17615,7 @@
 2. Observe.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] active campaign + registration</t>
+    <t>[TEST_DATA_REQUIRED] active campaign + registration  →  USED: GHNG-1000008364-J (WINNER, Mavis cleared) §6 cancel attempted while campaign ACTIVE → submit-time re-check BLOCKS ("campaign is active"); booking stays WINNER. ALLOW_DESTRUCTIVE=1; campaign-active window.</t>
   </si>
   <si>
     <t>The upload is rejected while the campaign is active (HTTP 400, mirroring §11.4/§11.7 campaign guards). [VERIFY WITH DEV] exact message string for Section 6.</t>
@@ -19841,6 +19841,12 @@
   </si>
   <si>
     <t>2026-06-28 15:12 IST — pass in 3.0s</t>
+  </si>
+  <si>
+    <t>2026-06-28 15:24 IST — pass in 27.2s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_061.png</t>
   </si>
   <si>
     <t>2026-06-28 15:12 IST — pass in 7.1s</t>
@@ -30858,13 +30864,13 @@
         <v>5462</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L93" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -53677,22 +53683,22 @@
         <v>5456</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>5849</v>
+        <v>5783</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E73" t="s">
-        <v>24</v>
+        <v>6187</v>
       </c>
       <c r="F73" t="s">
-        <v>24</v>
-      </c>
-      <c r="G73" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>6188</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -53755,13 +53761,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>6187</v>
+        <v>6189</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>6188</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -53824,7 +53830,7 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>6189</v>
+        <v>6191</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
@@ -53847,13 +53853,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6190</v>
+        <v>6192</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6191</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -54077,13 +54083,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6192</v>
+        <v>6194</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6193</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54146,13 +54152,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6194</v>
+        <v>6196</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6195</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54169,13 +54175,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>6196</v>
+        <v>6198</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>6197</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -54192,13 +54198,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>6198</v>
+        <v>6200</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>6199</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -54284,13 +54290,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>6200</v>
+        <v>6202</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>6201</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -54313,7 +54319,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6202</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54399,13 +54405,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6190</v>
+        <v>6192</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6203</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54491,13 +54497,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6204</v>
+        <v>6206</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6205</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54514,13 +54520,13 @@
         <v>67</v>
       </c>
       <c r="E109" t="s">
-        <v>6206</v>
+        <v>6208</v>
       </c>
       <c r="F109" t="s">
         <v>66</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>6207</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -54543,7 +54549,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6208</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54560,13 +54566,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>6209</v>
+        <v>6211</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>6210</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -54727,7 +54733,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6211</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54834,20 +54840,21 @@
     <hyperlink ref="G65" r:id="rId54"/>
     <hyperlink ref="G66" r:id="rId55"/>
     <hyperlink ref="G68" r:id="rId56"/>
-    <hyperlink ref="G76" r:id="rId57"/>
-    <hyperlink ref="G80" r:id="rId58"/>
-    <hyperlink ref="G90" r:id="rId59"/>
-    <hyperlink ref="G93" r:id="rId60"/>
-    <hyperlink ref="G94" r:id="rId61"/>
-    <hyperlink ref="G95" r:id="rId62"/>
-    <hyperlink ref="G99" r:id="rId63"/>
-    <hyperlink ref="G100" r:id="rId64"/>
-    <hyperlink ref="G104" r:id="rId65"/>
-    <hyperlink ref="G108" r:id="rId66"/>
-    <hyperlink ref="G109" r:id="rId67"/>
-    <hyperlink ref="G110" r:id="rId68"/>
-    <hyperlink ref="G111" r:id="rId69"/>
-    <hyperlink ref="G118" r:id="rId70"/>
+    <hyperlink ref="G73" r:id="rId57"/>
+    <hyperlink ref="G76" r:id="rId58"/>
+    <hyperlink ref="G80" r:id="rId59"/>
+    <hyperlink ref="G90" r:id="rId60"/>
+    <hyperlink ref="G93" r:id="rId61"/>
+    <hyperlink ref="G94" r:id="rId62"/>
+    <hyperlink ref="G95" r:id="rId63"/>
+    <hyperlink ref="G99" r:id="rId64"/>
+    <hyperlink ref="G100" r:id="rId65"/>
+    <hyperlink ref="G104" r:id="rId66"/>
+    <hyperlink ref="G108" r:id="rId67"/>
+    <hyperlink ref="G109" r:id="rId68"/>
+    <hyperlink ref="G110" r:id="rId69"/>
+    <hyperlink ref="G111" r:id="rId70"/>
+    <hyperlink ref="G118" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6216">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -17593,7 +17593,7 @@
 3. Inspect which registrations cancelled.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] mixed Update 1/0 rows</t>
+    <t>[TEST_DATA_REQUIRED] mixed Update 1/0 rows  →  USED: GHNG-1000008364-J Update=0 → §6 must NOT cancel (Update=0 skip); -J stays WINNER. Non-destructive (Update=0; WINNER also "already allocated"). ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>Only Update=1 registrations cancel; Update=0 rows are skipped.</t>
@@ -19841,6 +19841,12 @@
   </si>
   <si>
     <t>2026-06-28 15:12 IST — pass in 3.0s</t>
+  </si>
+  <si>
+    <t>2026-06-28 17:52 IST — pass in 27.8s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_062.png</t>
   </si>
   <si>
     <t>2026-06-28 15:24 IST — pass in 27.2s</t>
@@ -30826,13 +30832,13 @@
         <v>5455</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L92" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -53660,22 +53666,22 @@
         <v>5450</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>5849</v>
+        <v>5783</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E72" t="s">
-        <v>24</v>
+        <v>6187</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
-      </c>
-      <c r="G72" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G72" s="19" t="s">
+        <v>6188</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -53692,13 +53698,13 @@
         <v>67</v>
       </c>
       <c r="E73" t="s">
-        <v>6187</v>
+        <v>6189</v>
       </c>
       <c r="F73" t="s">
         <v>66</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>6188</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -53761,13 +53767,13 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>6189</v>
+        <v>6191</v>
       </c>
       <c r="F76" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>6190</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -53830,7 +53836,7 @@
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>6191</v>
+        <v>6193</v>
       </c>
       <c r="F79" t="s">
         <v>66</v>
@@ -53853,13 +53859,13 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>6192</v>
+        <v>6194</v>
       </c>
       <c r="F80" t="s">
         <v>66</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>6193</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -54083,13 +54089,13 @@
         <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>6194</v>
+        <v>6196</v>
       </c>
       <c r="F90" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>6195</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -54152,13 +54158,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>6196</v>
+        <v>6198</v>
       </c>
       <c r="F93" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>6197</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -54175,13 +54181,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>6198</v>
+        <v>6200</v>
       </c>
       <c r="F94" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>6199</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -54198,13 +54204,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>6200</v>
+        <v>6202</v>
       </c>
       <c r="F95" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>6201</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -54290,13 +54296,13 @@
         <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>6202</v>
+        <v>6204</v>
       </c>
       <c r="F99" t="s">
         <v>66</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>6203</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -54319,7 +54325,7 @@
         <v>66</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>6204</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -54405,13 +54411,13 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>6192</v>
+        <v>6194</v>
       </c>
       <c r="F104" t="s">
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6205</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54497,13 +54503,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6206</v>
+        <v>6208</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6207</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54520,13 +54526,13 @@
         <v>67</v>
       </c>
       <c r="E109" t="s">
-        <v>6208</v>
+        <v>6210</v>
       </c>
       <c r="F109" t="s">
         <v>66</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>6209</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -54549,7 +54555,7 @@
         <v>179</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6210</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54566,13 +54572,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>6211</v>
+        <v>6213</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>6212</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -54733,7 +54739,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6213</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54840,21 +54846,22 @@
     <hyperlink ref="G65" r:id="rId54"/>
     <hyperlink ref="G66" r:id="rId55"/>
     <hyperlink ref="G68" r:id="rId56"/>
-    <hyperlink ref="G73" r:id="rId57"/>
-    <hyperlink ref="G76" r:id="rId58"/>
-    <hyperlink ref="G80" r:id="rId59"/>
-    <hyperlink ref="G90" r:id="rId60"/>
-    <hyperlink ref="G93" r:id="rId61"/>
-    <hyperlink ref="G94" r:id="rId62"/>
-    <hyperlink ref="G95" r:id="rId63"/>
-    <hyperlink ref="G99" r:id="rId64"/>
-    <hyperlink ref="G100" r:id="rId65"/>
-    <hyperlink ref="G104" r:id="rId66"/>
-    <hyperlink ref="G108" r:id="rId67"/>
-    <hyperlink ref="G109" r:id="rId68"/>
-    <hyperlink ref="G110" r:id="rId69"/>
-    <hyperlink ref="G111" r:id="rId70"/>
-    <hyperlink ref="G118" r:id="rId71"/>
+    <hyperlink ref="G72" r:id="rId57"/>
+    <hyperlink ref="G73" r:id="rId58"/>
+    <hyperlink ref="G76" r:id="rId59"/>
+    <hyperlink ref="G80" r:id="rId60"/>
+    <hyperlink ref="G90" r:id="rId61"/>
+    <hyperlink ref="G93" r:id="rId62"/>
+    <hyperlink ref="G94" r:id="rId63"/>
+    <hyperlink ref="G95" r:id="rId64"/>
+    <hyperlink ref="G99" r:id="rId65"/>
+    <hyperlink ref="G100" r:id="rId66"/>
+    <hyperlink ref="G104" r:id="rId67"/>
+    <hyperlink ref="G108" r:id="rId68"/>
+    <hyperlink ref="G109" r:id="rId69"/>
+    <hyperlink ref="G110" r:id="rId70"/>
+    <hyperlink ref="G111" r:id="rId71"/>
+    <hyperlink ref="G118" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6231">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18395,7 +18395,7 @@
 3. Reload and re-read.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] user authorisation (restore to 6 after)</t>
+    <t>[TEST_DATA_REQUIRED] user authorisation (restore to 6 after)  →  USED: Max Preferences: capture current value → set a different value → Update → reload &amp; verify persisted → restore original. Project-wide config, capture+restore. ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>The new value (10) persists after reload (FS Feature 9 §7).</t>
@@ -18458,7 +18458,7 @@
 2. Observe.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] user authorisation (no change)</t>
+    <t>[TEST_DATA_REQUIRED] user authorisation (no change)  →  USED: Max Preferences: click Update WITHOUT changing the value → no error, value unchanged (idempotent save). Non-mutating. ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>[VERIFY WITH DEV] — record whether the no-op Update succeeds silently or returns a 'No Change' response (parallel to S8 §11.3).</t>
@@ -19954,6 +19954,9 @@
     <t>ADM_CFG_106.png</t>
   </si>
   <si>
+    <t>2026-06-28 19:38 IST — pass in 10.4s</t>
+  </si>
+  <si>
     <t>ADM_CFG_044.png</t>
   </si>
   <si>
@@ -19961,6 +19964,12 @@
   </si>
   <si>
     <t>ADM_CFG_045.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 19:38 IST — pass in 5.3s</t>
+  </si>
+  <si>
+    <t>ADM_CFG_107.png</t>
   </si>
   <si>
     <t>ADM_CFG_047.png</t>
@@ -32360,10 +32369,10 @@
         <v>5709</v>
       </c>
       <c r="J133" s="15" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="K133" s="15" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="L133" s="15" t="s">
         <v>68</v>
@@ -32474,13 +32483,13 @@
         <v>5729</v>
       </c>
       <c r="J136" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K136" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L136" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="137" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -54576,22 +54585,22 @@
         <v>5704</v>
       </c>
       <c r="B110" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C110" s="18" t="s">
         <v>5784</v>
       </c>
       <c r="D110" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="E110" t="s">
-        <v>6085</v>
+        <v>6224</v>
       </c>
       <c r="F110" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6224</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54608,13 +54617,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>6225</v>
+        <v>6226</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>6226</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -54645,22 +54654,22 @@
         <v>5723</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>5850</v>
+        <v>5784</v>
       </c>
       <c r="D113" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>24</v>
+        <v>6228</v>
       </c>
       <c r="F113" t="s">
-        <v>24</v>
-      </c>
-      <c r="G113" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>6229</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -54775,7 +54784,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54903,7 +54912,8 @@
     <hyperlink ref="G109" r:id="rId75"/>
     <hyperlink ref="G110" r:id="rId76"/>
     <hyperlink ref="G111" r:id="rId77"/>
-    <hyperlink ref="G118" r:id="rId78"/>
+    <hyperlink ref="G113" r:id="rId78"/>
+    <hyperlink ref="G118" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6235">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18522,7 +18522,7 @@
 2. GET to confirm persistence.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] admin JWT; projectId</t>
+    <t>[TEST_DATA_REQUIRED] admin JWT; projectId  →  USED: PUT https://uat-api.xrportal.in/api/v1/admin/max-preferences-per-unit/project-1708669316677 body {maxPreferencesPerUnit:N}: capture current → PUT a different value → GET verify persisted → restore. projectId=project-1708669316677. admin JWT; ALLOW_DESTRUCTIVE=1.</t>
   </si>
   <si>
     <t>The new value persists and is returned by the GET (FRD §10 API).</t>
@@ -19966,10 +19966,22 @@
     <t>ADM_CFG_045.png</t>
   </si>
   <si>
+    <t>2026-06-28 19:46 IST — pass in 382ms</t>
+  </si>
+  <si>
     <t>2026-06-28 19:38 IST — pass in 5.3s</t>
   </si>
   <si>
     <t>ADM_CFG_107.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 19:46 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>2026-06-28 19:46 IST — pass in 7.0s</t>
+  </si>
+  <si>
+    <t>2026-06-28 19:46 IST — pass in 426ms</t>
   </si>
   <si>
     <t>ADM_CFG_047.png</t>
@@ -32445,13 +32457,13 @@
         <v>5722</v>
       </c>
       <c r="J135" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K135" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L135" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32521,13 +32533,13 @@
         <v>5736</v>
       </c>
       <c r="J137" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K137" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L137" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32559,13 +32571,13 @@
         <v>5742</v>
       </c>
       <c r="J138" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K138" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L138" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="139" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32597,13 +32609,13 @@
         <v>5749</v>
       </c>
       <c r="J139" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K139" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L139" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="140" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32635,13 +32647,13 @@
         <v>5756</v>
       </c>
       <c r="J140" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K140" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L140" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -54631,19 +54643,19 @@
         <v>5716</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>5850</v>
+        <v>5784</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E112" t="s">
-        <v>24</v>
+        <v>6228</v>
       </c>
       <c r="F112" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G112" t="s">
         <v>24</v>
@@ -54663,13 +54675,13 @@
         <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>6228</v>
+        <v>6229</v>
       </c>
       <c r="F113" t="s">
         <v>66</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>6229</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -54677,19 +54689,19 @@
         <v>5730</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>5850</v>
+        <v>5784</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E114" t="s">
-        <v>24</v>
+        <v>6231</v>
       </c>
       <c r="F114" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="G114" t="s">
         <v>24</v>
@@ -54700,19 +54712,19 @@
         <v>5737</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>5850</v>
+        <v>5784</v>
       </c>
       <c r="D115" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>24</v>
+        <v>6232</v>
       </c>
       <c r="F115" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -54723,19 +54735,19 @@
         <v>5743</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>5850</v>
+        <v>5784</v>
       </c>
       <c r="D116" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>24</v>
+        <v>6233</v>
       </c>
       <c r="F116" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G116" t="s">
         <v>24</v>
@@ -54746,19 +54758,19 @@
         <v>5750</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>5850</v>
+        <v>5784</v>
       </c>
       <c r="D117" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E117" t="s">
-        <v>24</v>
+        <v>6231</v>
       </c>
       <c r="F117" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="G117" t="s">
         <v>24</v>
@@ -54784,7 +54796,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">

--- a/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-AdminPortal.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17287" uniqueCount="6246">
   <si>
     <t>XR Portal — Admin</t>
   </si>
@@ -18338,7 +18338,7 @@
 2. On the Customer Portal, attempt an additional registration for the affected typology.</t>
   </si>
   <si>
-    <t>[TEST_DATA_REQUIRED] user authorisation; buyer test account</t>
+    <t>[TEST_DATA_REQUIRED] user authorisation; buyer test account  →  USED: VERIFY-WITH-DEV — enforcement of the Customer Actions config during a buyer additional-registration flow is a Buyer-portal/downstream behaviour, out of admin Config scope (cross-portal). Verify in Buyer portal + dev.</t>
   </si>
   <si>
     <t>The Customer Portal immediately reflects the new allow/block + count limits (FS Feature 8 §7, BRD §8 Customers dependency).</t>
@@ -19948,13 +19948,31 @@
     <t>ADM_CFG_FSD_052.png</t>
   </si>
   <si>
+    <t>2026-06-28 20:04 IST — pass in 522ms</t>
+  </si>
+  <si>
+    <t>2026-06-28 20:04 IST — skip in §11.1</t>
+  </si>
+  <si>
+    <t>2026-06-28 20:04 IST — pass in 79ms</t>
+  </si>
+  <si>
     <t>ADM_CFG_FSD_054.png</t>
   </si>
   <si>
+    <t>2026-06-28 20:04 IST — pass in 253ms</t>
+  </si>
+  <si>
     <t>2026-06-28 20:00 IST — pass in 10.5s</t>
   </si>
   <si>
     <t>ADM_CFG_104.png</t>
+  </si>
+  <si>
+    <t>2026-06-28 20:04 IST — skip in n/a</t>
+  </si>
+  <si>
+    <t>ADM_CFG_105.png</t>
   </si>
   <si>
     <t>2026-06-27 14:33 IST — pass in 2.9s</t>
@@ -32038,13 +32056,13 @@
         <v>5651</v>
       </c>
       <c r="J123" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K123" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L123" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="124" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32076,13 +32094,13 @@
         <v>5658</v>
       </c>
       <c r="J124" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K124" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L124" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="125" ht="45" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32114,13 +32132,13 @@
         <v>5664</v>
       </c>
       <c r="J125" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K125" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L125" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="126" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32190,13 +32208,13 @@
         <v>5678</v>
       </c>
       <c r="J127" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K127" s="15" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L127" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="128" ht="60" customHeight="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -32266,13 +32284,13 @@
         <v>5691</v>
       </c>
       <c r="J129" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="K129" s="15" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="L129" s="15" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -54405,19 +54423,19 @@
         <v>5645</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>5851</v>
+        <v>5785</v>
       </c>
       <c r="D101" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>6222</v>
       </c>
       <c r="F101" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G101" t="s">
         <v>24</v>
@@ -54428,19 +54446,19 @@
         <v>5652</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>5851</v>
+        <v>5785</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E102" t="s">
-        <v>24</v>
+        <v>6223</v>
       </c>
       <c r="F102" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="G102" t="s">
         <v>24</v>
@@ -54451,19 +54469,19 @@
         <v>5659</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>5851</v>
+        <v>5785</v>
       </c>
       <c r="D103" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E103" t="s">
-        <v>24</v>
+        <v>6224</v>
       </c>
       <c r="F103" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G103" t="s">
         <v>24</v>
@@ -54489,7 +54507,7 @@
         <v>66</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -54497,19 +54515,19 @@
         <v>5672</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>5851</v>
+        <v>5785</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E105" t="s">
-        <v>24</v>
+        <v>6226</v>
       </c>
       <c r="F105" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G105" t="s">
         <v>24</v>
@@ -54529,13 +54547,13 @@
         <v>67</v>
       </c>
       <c r="E106" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="F106" t="s">
         <v>66</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -54543,22 +54561,22 @@
         <v>5686</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>5851</v>
+        <v>5785</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E107" t="s">
-        <v>24</v>
+        <v>6229</v>
       </c>
       <c r="F107" t="s">
-        <v>24</v>
-      </c>
-      <c r="G107" t="s">
-        <v>24</v>
+        <v>179</v>
+      </c>
+      <c r="G107" s="19" t="s">
+        <v>6230</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -54575,13 +54593,13 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>6225</v>
+        <v>6231</v>
       </c>
       <c r="F108" t="s">
         <v>66</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>6226</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -54598,13 +54616,13 @@
         <v>67</v>
       </c>
       <c r="E109" t="s">
-        <v>6227</v>
+        <v>6233</v>
       </c>
       <c r="F109" t="s">
         <v>66</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>6228</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -54621,13 +54639,13 @@
         <v>67</v>
       </c>
       <c r="E110" t="s">
-        <v>6229</v>
+        <v>6235</v>
       </c>
       <c r="F110" t="s">
         <v>66</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>6230</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -54644,13 +54662,13 @@
         <v>67</v>
       </c>
       <c r="E111" t="s">
-        <v>6231</v>
+        <v>6237</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>6232</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -54667,7 +54685,7 @@
         <v>67</v>
       </c>
       <c r="E112" t="s">
-        <v>6233</v>
+        <v>6239</v>
       </c>
       <c r="F112" t="s">
         <v>66</v>
@@ -54690,13 +54708,13 @@
         <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>6234</v>
+        <v>6240</v>
       </c>
       <c r="F113" t="s">
         <v>66</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>6235</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -54713,7 +54731,7 @@
         <v>180</v>
       </c>
       <c r="E114" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
       <c r="F114" t="s">
         <v>179</v>
@@ -54736,7 +54754,7 @@
         <v>67</v>
       </c>
       <c r="E115" t="s">
-        <v>6237</v>
+        <v>6243</v>
       </c>
       <c r="F115" t="s">
         <v>66</v>
@@ -54759,7 +54777,7 @@
         <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>6238</v>
+        <v>6244</v>
       </c>
       <c r="F116" t="s">
         <v>66</v>
@@ -54782,7 +54800,7 @@
         <v>180</v>
       </c>
       <c r="E117" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
       <c r="F117" t="s">
         <v>179</v>
@@ -54811,7 +54829,7 @@
         <v>66</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -54936,12 +54954,13 @@
     <hyperlink ref="G100" r:id="rId72"/>
     <hyperlink ref="G104" r:id="rId73"/>
     <hyperlink ref="G106" r:id="rId74"/>
-    <hyperlink ref="G108" r:id="rId75"/>
-    <hyperlink ref="G109" r:id="rId76"/>
-    <hyperlink ref="G110" r:id="rId77"/>
-    <hyperlink ref="G111" r:id="rId78"/>
-    <hyperlink ref="G113" r:id="rId79"/>
-    <hyperlink ref="G118" r:id="rId80"/>
+    <hyperlink ref="G107" r:id="rId75"/>
+    <hyperlink ref="G108" r:id="rId76"/>
+    <hyperlink ref="G109" r:id="rId77"/>
+    <hyperlink ref="G110" r:id="rId78"/>
+    <hyperlink ref="G111" r:id="rId79"/>
+    <hyperlink ref="G113" r:id="rId80"/>
+    <hyperlink ref="G118" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
